--- a/data/merged/2026-10-08/MERGED_JP_Wet-Dry-Floor-Washer_2026-10-08.xlsx
+++ b/data/merged/2026-10-08/MERGED_JP_Wet-Dry-Floor-Washer_2026-10-08.xlsx
@@ -4929,7 +4929,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4967,13 +4967,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5055,13 +5055,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5099,13 +5099,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5407,13 +5407,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5539,13 +5539,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6222,358 +6222,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId42" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="43" name="Product 43">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId43" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="44" name="Product 44">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId44" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="45" name="Product 45">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId45" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="46" name="Product 46">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId46" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="47" name="Product 47">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId47" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="48" name="Product 48">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId48" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Product 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6915,7 +6563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -10060,40 +9708,40 @@
       <c r="B14" s="11"/>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>B07221ZY3D</t>
+          <t>B0F2HHFGNK</t>
         </is>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="12"/>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>ミナトワークス</t>
+          <t>MOVA</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%83%9F%E3%83%8A%E3%83%88%E3%83%AF%E3%83%BC%E3%82%AF%E3%82%B9/page/7E77FCE9-0862-4057-994E-E5C8A30E6C6D?lp_asin=B07221ZY3D&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/MOVA/page/1C66BA39-85DA-4EF9-BEE1-43A9D48A27F4?lp_asin=B0F2HHFGNK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>ミナトワークス 干湿两用 商用 吸尘器 真空清洁器 MPV-201 容量20L 电线长度10m</t>
+          <t>MOVA K30 SE 水拭き掃除機 自走式 乾湿両用掃除機 体感重量1.1KG 18,000 Pa の吸引力s180° フラット可能 壁に密着して掃除 自動洗浄 デュアルエッジクリーニング 浄水清掃 絡まり解消 長時間稼働 コードレス軽量水拭き</t>
         </is>
       </c>
       <c r="I14" s="12"/>
       <c r="J14" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B07221ZY3D?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0F2HHFGNK?psc=1</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81CP4O0lOLL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/315qxl2azwL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
-          <t>B07221ZY3D</t>
+          <t>B0F2HHFGNK</t>
         </is>
       </c>
       <c r="M14" s="12" t="inlineStr">
@@ -10107,13 +9755,13 @@
         </is>
       </c>
       <c r="O14" s="13">
-        <v>6134</v>
+        <v>25314</v>
       </c>
       <c r="P14" s="13">
-        <v>1649</v>
+        <v>66371</v>
       </c>
       <c r="Q14" s="14">
-        <v>0.21</v>
+        <v>0.65</v>
       </c>
       <c r="R14" s="15" t="inlineStr">
         <is>
@@ -10122,101 +9770,93 @@
       </c>
       <c r="S14" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="T14" s="13">
-        <v>133</v>
+        <v>41</v>
       </c>
       <c r="U14" s="14">
-        <v>0.15</v>
+        <v>-0.46</v>
       </c>
       <c r="V14" s="13">
-        <v>1569400</v>
-      </c>
-      <c r="W14" s="13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X14" s="13">
-        <v>653826</v>
-      </c>
+        <v>1348080</v>
+      </c>
+      <c r="W14" s="13"/>
+      <c r="X14" s="13"/>
       <c r="Y14" s="17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z14" s="13">
-        <v>11800</v>
+        <v>32880</v>
       </c>
       <c r="AA14"/>
       <c r="AB14"/>
-      <c r="AC14" s="2">
-        <v>3</v>
-      </c>
+      <c r="AC14" s="2"/>
       <c r="AD14" s="17">
-        <v>260</v>
+        <v>552</v>
       </c>
       <c r="AE14" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF14" s="18">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AG14" s="19">
-        <v>0.015</v>
+        <v>0.024399999999999998</v>
       </c>
       <c r="AH14" s="13">
-        <v>1020</v>
+        <v>1100</v>
       </c>
       <c r="AI14" s="14">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="AJ14"/>
       <c r="AK14" s="11" t="inlineStr">
         <is>
-          <t>2017-06-26</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="AL14" s="17">
-        <v>3391</v>
+        <v>508</v>
       </c>
       <c r="AM14" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN14" s="11"/>
       <c r="AO14" s="11"/>
       <c r="AP14"/>
       <c r="AQ14" s="17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR14" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS14" s="12" t="inlineStr">
         <is>
-          <t>【ミナトワークス】</t>
+          <t>MOVA Official</t>
         </is>
       </c>
       <c r="AT14" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU14" s="11" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV14" s="12" t="inlineStr">
         <is>
-          <t>豊前市 福岡県 8280031 JP</t>
+          <t>HONG KONG 000 HK</t>
         </is>
       </c>
       <c r="AW14" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A35R5657DWBR35</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGV9IL82JY4FQ</t>
         </is>
       </c>
       <c r="AX14" s="11"/>
@@ -10233,11 +9873,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD14" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD14" s="11"/>
       <c r="BE14" s="11"/>
       <c r="BF14" s="11"/>
       <c r="BG14" s="11"/>
@@ -10249,42 +9885,38 @@
       </c>
       <c r="BJ14" s="20" t="inlineStr">
         <is>
-          <t>8.5 kg</t>
+          <t>7.23 Kilograms</t>
         </is>
       </c>
       <c r="BK14" s="20" t="inlineStr">
         <is>
-          <t>8.50 kg</t>
+          <t>7.23 kg</t>
         </is>
       </c>
       <c r="BL14" s="20" t="inlineStr">
         <is>
-          <t>38 x 35 x 53 cm</t>
-        </is>
-      </c>
-      <c r="BM14" s="20" t="inlineStr">
-        <is>
-          <t>38.00 x 35.00 x 53.00 cm</t>
-        </is>
-      </c>
+          <t>74.3長さ x 27.5幅 x 32.6高さ cm</t>
+        </is>
+      </c>
+      <c r="BM14" s="20"/>
       <c r="BN14" s="20" t="inlineStr">
         <is>
-          <t>9 kg</t>
+          <t>7.23 kg</t>
         </is>
       </c>
       <c r="BO14" s="20" t="inlineStr">
         <is>
-          <t>9.00 kg</t>
+          <t>7.23 kg</t>
         </is>
       </c>
       <c r="BP14" s="20" t="inlineStr">
         <is>
-          <t>52.6 x 45.5 x 40 cm</t>
+          <t>71.9 x 34.6 x 33.9 cm</t>
         </is>
       </c>
       <c r="BQ14" s="20" t="inlineStr">
         <is>
-          <t>52.60 x 45.50 x 40.00 cm</t>
+          <t>71.90 x 34.60 x 33.90 cm</t>
         </is>
       </c>
       <c r="BR14" s="11" t="inlineStr">
@@ -10300,40 +9932,40 @@
       <c r="B15" s="11"/>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>B0F2HHFGNK</t>
+          <t>B0GXDDCQ3M</t>
         </is>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="12"/>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>MOVA</t>
+          <t>YTE PRO</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/MOVA/page/1C66BA39-85DA-4EF9-BEE1-43A9D48A27F4?lp_asin=B0F2HHFGNK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/YTEPRO/page/A41402B4-AFBB-4C28-82E0-CB901555CE9C?lp_asin=B0GXDDCQ3M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>MOVA K30 SE 水拭き掃除機 自走式 乾湿両用掃除機 体感重量1.1KG 18,000 Pa の吸引力s180° フラット可能 壁に密着して掃除 自動洗浄 デュアルエッジクリーニング 浄水清掃 絡まり解消 長時間稼働 コードレス軽量水拭き</t>
+          <t>YTE PRO [2026新上市 400W 强力吸力] 支持60°C热水 自动清洗 去污 干湿两用 吸尘器 布清洗机 沙发/地毯/布制品/车内/毛绒玩具/羽绒外套/缝隙 移动方便 便于保养 日本国内PSE&amp;METI认证</t>
         </is>
       </c>
       <c r="I15" s="12"/>
       <c r="J15" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0F2HHFGNK?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0GXDDCQ3M?psc=1</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/315qxl2azwL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41LdBO8M33L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>B0F2HHFGNK</t>
+          <t>B0GXDDCQ3M</t>
         </is>
       </c>
       <c r="M15" s="12" t="inlineStr">
@@ -10347,13 +9979,13 @@
         </is>
       </c>
       <c r="O15" s="13">
-        <v>25314</v>
+        <v>15123</v>
       </c>
       <c r="P15" s="13">
-        <v>66371</v>
+        <v>-7411</v>
       </c>
       <c r="Q15" s="14">
-        <v>0.65</v>
+        <v>-3.7</v>
       </c>
       <c r="R15" s="15" t="inlineStr">
         <is>
@@ -10362,78 +9994,76 @@
       </c>
       <c r="S15" s="16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="T15" s="13">
-        <v>41</v>
-      </c>
-      <c r="U15" s="14">
-        <v>-0.46</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="U15" s="14"/>
       <c r="V15" s="13">
-        <v>1348080</v>
+        <v>1313854</v>
       </c>
       <c r="W15" s="13"/>
       <c r="X15" s="13"/>
       <c r="Y15" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z15" s="13">
-        <v>32880</v>
+        <v>8999</v>
       </c>
       <c r="AA15"/>
       <c r="AB15"/>
       <c r="AC15" s="2"/>
       <c r="AD15" s="17">
-        <v>552</v>
+        <v>31</v>
       </c>
       <c r="AE15" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF15" s="18">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AG15" s="19">
-        <v>0.024399999999999998</v>
+        <v>0</v>
       </c>
       <c r="AH15" s="13">
-        <v>1100</v>
+        <v>675</v>
       </c>
       <c r="AI15" s="14">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="AJ15"/>
       <c r="AK15" s="11" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="AL15" s="17">
-        <v>508</v>
+        <v>26</v>
       </c>
       <c r="AM15" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN15" s="11"/>
       <c r="AO15" s="11"/>
       <c r="AP15"/>
       <c r="AQ15" s="17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR15" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS15" s="12" t="inlineStr">
         <is>
-          <t>MOVA Official</t>
+          <t>HighWin LLC</t>
         </is>
       </c>
       <c r="AT15" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU15" s="11" t="inlineStr">
@@ -10443,20 +10073,16 @@
       </c>
       <c r="AV15" s="12" t="inlineStr">
         <is>
-          <t>HONG KONG 000 HK</t>
+          <t>HONG KONG HONG KONG 999077 HK</t>
         </is>
       </c>
       <c r="AW15" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGV9IL82JY4FQ</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AKYM3EEDP1T3V</t>
         </is>
       </c>
       <c r="AX15" s="11"/>
-      <c r="AY15" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY15" s="11"/>
       <c r="AZ15" s="11"/>
       <c r="BA15" s="11"/>
       <c r="BB15" s="11"/>
@@ -10465,50 +10091,46 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD15" s="11"/>
+      <c r="BD15" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE15" s="11"/>
       <c r="BF15" s="11"/>
       <c r="BG15" s="11"/>
       <c r="BH15" s="12"/>
-      <c r="BI15" s="20" t="inlineStr">
-        <is>
-          <t>Amazon おすすめ</t>
-        </is>
-      </c>
+      <c r="BI15" s="20"/>
       <c r="BJ15" s="20" t="inlineStr">
         <is>
-          <t>7.23 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK15" s="20" t="inlineStr">
-        <is>
-          <t>7.23 kg</t>
-        </is>
-      </c>
+          <t>4 キログラム</t>
+        </is>
+      </c>
+      <c r="BK15" s="20"/>
       <c r="BL15" s="20" t="inlineStr">
         <is>
-          <t>74.3長さ x 27.5幅 x 32.6高さ cm</t>
+          <t>19奥行き x 41幅 x 30高さ cm</t>
         </is>
       </c>
       <c r="BM15" s="20"/>
       <c r="BN15" s="20" t="inlineStr">
         <is>
-          <t>7.23 kg</t>
+          <t>5.13 kg</t>
         </is>
       </c>
       <c r="BO15" s="20" t="inlineStr">
         <is>
-          <t>7.23 kg</t>
+          <t>5.13 kg</t>
         </is>
       </c>
       <c r="BP15" s="20" t="inlineStr">
         <is>
-          <t>71.9 x 34.6 x 33.9 cm</t>
+          <t>45.5 x 33.4 x 19.9 cm</t>
         </is>
       </c>
       <c r="BQ15" s="20" t="inlineStr">
         <is>
-          <t>71.90 x 34.60 x 33.90 cm</t>
+          <t>45.50 x 33.40 x 19.90 cm</t>
         </is>
       </c>
       <c r="BR15" s="11" t="inlineStr">
@@ -10524,40 +10146,40 @@
       <c r="B16" s="11"/>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>B0GXDDCQ3M</t>
+          <t>B0HGLFDYL5</t>
         </is>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="12"/>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>YTE PRO</t>
+          <t>Dyson(ダイソン)</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/YTEPRO/page/A41402B4-AFBB-4C28-82E0-CB901555CE9C?lp_asin=B0GXDDCQ3M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jpnull</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>YTE PRO [2026新上市 400W 强力吸力] 支持60°C热水 自动清洗 去污 干湿两用 吸尘器 布清洗机 沙发/地毯/布制品/车内/毛绒玩具/羽绒外套/缝隙 移动方便 便于保养 日本国内PSE&amp;METI认证</t>
+          <t>Dyson(ダイソン) 吸尘器 无线 Dyson V12s Detect Slim Submarine (SV46 SU) 棒 手持式吸尘器 气旋 可用水擦拭 干式吸尘器 带充电支架 【从现在开始用水擦拭】 (New V8 slim)</t>
         </is>
       </c>
       <c r="I16" s="12"/>
       <c r="J16" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0GXDDCQ3M?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0HGLFDYL5?psc=1</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41LdBO8M33L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51O6JFJ9JfL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L16" s="12" t="inlineStr">
         <is>
-          <t>B0GXDDCQ3M</t>
+          <t>B0HGLFDYL5</t>
         </is>
       </c>
       <c r="M16" s="12" t="inlineStr">
@@ -10571,13 +10193,13 @@
         </is>
       </c>
       <c r="O16" s="13">
-        <v>15123</v>
+        <v>50012</v>
       </c>
       <c r="P16" s="13">
-        <v>-7411</v>
+        <v>-10041</v>
       </c>
       <c r="Q16" s="14">
-        <v>-3.7</v>
+        <v>-0.25</v>
       </c>
       <c r="R16" s="15" t="inlineStr">
         <is>
@@ -10586,15 +10208,15 @@
       </c>
       <c r="S16" s="16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="T16" s="13">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="U16" s="14"/>
       <c r="V16" s="13">
-        <v>1313854</v>
+        <v>1044140</v>
       </c>
       <c r="W16" s="13"/>
       <c r="X16" s="13"/>
@@ -10602,75 +10224,75 @@
         <v>1</v>
       </c>
       <c r="Z16" s="13">
-        <v>8999</v>
+        <v>28220</v>
       </c>
       <c r="AA16"/>
       <c r="AB16"/>
       <c r="AC16" s="2"/>
       <c r="AD16" s="17">
-        <v>31</v>
+        <v>230</v>
       </c>
       <c r="AE16" s="13">
         <v>0</v>
       </c>
       <c r="AF16" s="18">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AG16" s="19">
         <v>0</v>
       </c>
       <c r="AH16" s="13">
-        <v>675</v>
+        <v>781</v>
       </c>
       <c r="AI16" s="14">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="AJ16"/>
       <c r="AK16" s="11" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AL16" s="17">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AM16" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN16" s="11"/>
       <c r="AO16" s="11"/>
       <c r="AP16"/>
       <c r="AQ16" s="17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AR16" s="17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AS16" s="12" t="inlineStr">
         <is>
-          <t>HighWin LLC</t>
+          <t>PENTACT JAPAN(土・日・祝休まず出荷 / インボイス登録店)</t>
         </is>
       </c>
       <c r="AT16" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AU16" s="11" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="AV16" s="12" t="inlineStr">
         <is>
-          <t>HONG KONG HONG KONG 999077 HK</t>
+          <t>荒川区 東京都 1160014 JP</t>
         </is>
       </c>
       <c r="AW16" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AKYM3EEDP1T3V</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A24DDJVBL7M2LD</t>
         </is>
       </c>
       <c r="AX16" s="11"/>
@@ -10678,16 +10300,8 @@
       <c r="AZ16" s="11"/>
       <c r="BA16" s="11"/>
       <c r="BB16" s="11"/>
-      <c r="BC16" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD16" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC16" s="11"/>
+      <c r="BD16" s="11"/>
       <c r="BE16" s="11"/>
       <c r="BF16" s="11"/>
       <c r="BG16" s="11"/>
@@ -10695,34 +10309,38 @@
       <c r="BI16" s="20"/>
       <c r="BJ16" s="20" t="inlineStr">
         <is>
-          <t>4 キログラム</t>
-        </is>
-      </c>
-      <c r="BK16" s="20"/>
+          <t>3.2 kg</t>
+        </is>
+      </c>
+      <c r="BK16" s="20" t="inlineStr">
+        <is>
+          <t>3.20 kg</t>
+        </is>
+      </c>
       <c r="BL16" s="20" t="inlineStr">
         <is>
-          <t>19奥行き x 41幅 x 30高さ cm</t>
+          <t>25.7長さ x 25.3幅 x 112.9高さ cm</t>
         </is>
       </c>
       <c r="BM16" s="20"/>
       <c r="BN16" s="20" t="inlineStr">
         <is>
-          <t>5.13 kg</t>
+          <t>3.7 kg</t>
         </is>
       </c>
       <c r="BO16" s="20" t="inlineStr">
         <is>
-          <t>5.13 kg</t>
+          <t>3.70 kg</t>
         </is>
       </c>
       <c r="BP16" s="20" t="inlineStr">
         <is>
-          <t>45.5 x 33.4 x 19.9 cm</t>
+          <t>74 x 27 x 15.5 cm</t>
         </is>
       </c>
       <c r="BQ16" s="20" t="inlineStr">
         <is>
-          <t>45.50 x 33.40 x 19.90 cm</t>
+          <t>74.00 x 27.00 x 15.50 cm</t>
         </is>
       </c>
       <c r="BR16" s="11" t="inlineStr">
@@ -10738,115 +10356,117 @@
       <c r="B17" s="11"/>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>B0HGLFDYL5</t>
+          <t>B0FC18HMRN</t>
         </is>
       </c>
       <c r="D17" s="12"/>
       <c r="E17" s="12"/>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>Dyson(ダイソン)</t>
+          <t>mindoo</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jpnull</t>
+          <t>https://www.amazon.co.jp/stores/mindoo/page/195B1567-B86E-4B16-A2C3-065A70917DA9?lp_asin=B0FC18HMRN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>Dyson(ダイソン) 吸尘器 无线 Dyson V12s Detect Slim Submarine (SV46 SU) 棒 手持式吸尘器 气旋 可用水擦拭 干式吸尘器 带充电支架 【从现在开始用水擦拭】 (New V8 slim)</t>
+          <t>Mindoo AquaX Plus Mindoo AquaX Plus 擦水吸尘器 [吸水、擦拭、除菌、自我清洁、自动干燥 5合1] 自走式 垃圾收集1台5用 强力吸力 超轻 自动清洗 高性能 (黑色)s軽量モデル 3モード 自動洗浄 温風乾燥</t>
         </is>
       </c>
       <c r="I17" s="12"/>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0HGLFDYL5?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FC18HMRN?psc=1</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51O6JFJ9JfL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/21vmJWLJAbL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>B0HGLFDYL5</t>
+          <t>B0FC18HMRN</t>
         </is>
       </c>
       <c r="M17" s="12" t="inlineStr">
         <is>
-          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
+          <t>ホーム＆キッチン:家電:生活家電:掃除機:家庭用湿式/乾式掃除機</t>
         </is>
       </c>
       <c r="N17" s="12" t="inlineStr">
         <is>
-          <t>DIY・工具・ガーデン</t>
+          <t>ホーム＆キッチン</t>
         </is>
       </c>
       <c r="O17" s="13">
-        <v>50012</v>
+        <v>216985</v>
       </c>
       <c r="P17" s="13">
-        <v>-10041</v>
+        <v>-31468</v>
       </c>
       <c r="Q17" s="14">
-        <v>-0.25</v>
+        <v>-0.17</v>
       </c>
       <c r="R17" s="15" t="inlineStr">
         <is>
-          <t>ウェットドライショップ掃除機</t>
+          <t>家庭用湿式/乾式掃除機</t>
         </is>
       </c>
       <c r="S17" s="16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="T17" s="13">
-        <v>37</v>
-      </c>
-      <c r="U17" s="14"/>
+        <v>11</v>
+      </c>
+      <c r="U17" s="14">
+        <v>-0.17</v>
+      </c>
       <c r="V17" s="13">
-        <v>1044140</v>
+        <v>822800</v>
       </c>
       <c r="W17" s="13"/>
       <c r="X17" s="13"/>
       <c r="Y17" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z17" s="13">
-        <v>28220</v>
+        <v>74800</v>
       </c>
       <c r="AA17"/>
       <c r="AB17"/>
       <c r="AC17" s="2"/>
       <c r="AD17" s="17">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="AE17" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF17" s="18">
         <v>4.3</v>
       </c>
       <c r="AG17" s="19">
-        <v>0</v>
+        <v>0.0909</v>
       </c>
       <c r="AH17" s="13">
         <v>781</v>
       </c>
       <c r="AI17" s="14">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="AJ17"/>
       <c r="AK17" s="11" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AL17" s="17">
-        <v>42</v>
+        <v>373</v>
       </c>
       <c r="AM17" s="11" t="inlineStr">
         <is>
@@ -10857,14 +10477,14 @@
       <c r="AO17" s="11"/>
       <c r="AP17"/>
       <c r="AQ17" s="17">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AR17" s="17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AS17" s="12" t="inlineStr">
         <is>
-          <t>PENTACT JAPAN(土・日・祝休まず出荷 / インボイス登録店)</t>
+          <t>〈公式〉Mindoo</t>
         </is>
       </c>
       <c r="AT17" s="11" t="inlineStr">
@@ -10879,60 +10499,72 @@
       </c>
       <c r="AV17" s="12" t="inlineStr">
         <is>
-          <t>荒川区 東京都 1160014 JP</t>
+          <t>港区三田 東京都 1080073 JP</t>
         </is>
       </c>
       <c r="AW17" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A24DDJVBL7M2LD</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3KERCWTE76M89</t>
         </is>
       </c>
       <c r="AX17" s="11"/>
-      <c r="AY17" s="11"/>
+      <c r="AY17" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ17" s="11"/>
       <c r="BA17" s="11"/>
       <c r="BB17" s="11"/>
-      <c r="BC17" s="11"/>
-      <c r="BD17" s="11"/>
+      <c r="BC17" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD17" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE17" s="11"/>
       <c r="BF17" s="11"/>
       <c r="BG17" s="11"/>
       <c r="BH17" s="12"/>
-      <c r="BI17" s="20"/>
+      <c r="BI17" s="20" t="inlineStr">
+        <is>
+          <t>Amazon おすすめ</t>
+        </is>
+      </c>
       <c r="BJ17" s="20" t="inlineStr">
         <is>
-          <t>3.2 kg</t>
-        </is>
-      </c>
-      <c r="BK17" s="20" t="inlineStr">
-        <is>
-          <t>3.20 kg</t>
-        </is>
-      </c>
+          <t>3.6 キログラム</t>
+        </is>
+      </c>
+      <c r="BK17" s="20"/>
       <c r="BL17" s="20" t="inlineStr">
         <is>
-          <t>25.7長さ x 25.3幅 x 112.9高さ cm</t>
+          <t>24.9長さ x 23.2幅 x 110高さ cm</t>
         </is>
       </c>
       <c r="BM17" s="20"/>
       <c r="BN17" s="20" t="inlineStr">
         <is>
-          <t>3.7 kg</t>
+          <t>6.2 kg</t>
         </is>
       </c>
       <c r="BO17" s="20" t="inlineStr">
         <is>
-          <t>3.70 kg</t>
+          <t>6.20 kg</t>
         </is>
       </c>
       <c r="BP17" s="20" t="inlineStr">
         <is>
-          <t>74 x 27 x 15.5 cm</t>
+          <t>64.5 x 30.5 x 23.8 cm</t>
         </is>
       </c>
       <c r="BQ17" s="20" t="inlineStr">
         <is>
-          <t>74.00 x 27.00 x 15.50 cm</t>
+          <t>64.50 x 30.50 x 23.80 cm</t>
         </is>
       </c>
       <c r="BR17" s="11" t="inlineStr">
@@ -10948,168 +10580,158 @@
       <c r="B18" s="11"/>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>B00UUMDMZI</t>
+          <t>B0HGLNPJPC</t>
         </is>
       </c>
       <c r="D18" s="12"/>
       <c r="E18" s="12"/>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>パオック(PAOCK)</t>
+          <t>Dyson(ダイソン)</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%83%91%E3%82%AA%E3%83%83%E3%82%AFPAOCK/page/24D761D2-B57C-4143-A66C-A75C65189148?lp_asin=B00UUMDMZI&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/%E3%83%80%E3%82%A4%E3%82%BD%E3%83%B3/page/0456F1ED-24D4-4719-8E99-5936EC69346F?lp_asin=B0HGLNPJPC&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>PAOCK 不锈钢罐 真空吸尘器 干湿两用 吸入功率210W 20L NVC-20PA</t>
+          <t>Dyson(ダイソン) V12 Detect Slim Absolute 无线吸尘器 戴森官方限定 延长保修1年款s棒手持吸尘器,旋风,带充电座,Amazon.co.jp 独家,高功能 LED 和自动模式不会错过垃圾</t>
         </is>
       </c>
       <c r="I18" s="12"/>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B00UUMDMZI?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0HGLNPJPC?psc=1</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71Y5D7AH22L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/616rJ-dkmUL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L18" s="12" t="inlineStr">
         <is>
-          <t>B00UUMDMZI</t>
+          <t>B0HGLNPJPC</t>
         </is>
       </c>
       <c r="M18" s="12" t="inlineStr">
         <is>
-          <t>産業・研究開発用品:衛生・清掃用品:床・カーペットクリーニング:掃除機・アクセサリ:掃除機:乾湿両用掃除機</t>
+          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
         </is>
       </c>
       <c r="N18" s="12" t="inlineStr">
         <is>
-          <t>産業・研究開発用品</t>
+          <t>DIY・工具・ガーデン</t>
         </is>
       </c>
       <c r="O18" s="13">
-        <v>5988</v>
+        <v>140536</v>
       </c>
       <c r="P18" s="13">
-        <v>531</v>
+        <v>-86532</v>
       </c>
       <c r="Q18" s="14">
-        <v>0.08</v>
+        <v>-1.6</v>
       </c>
       <c r="R18" s="15" t="inlineStr">
         <is>
-          <t>乾湿両用掃除機</t>
+          <t>ウェットドライショップ掃除機</t>
         </is>
       </c>
       <c r="S18" s="16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>40</t>
         </is>
       </c>
       <c r="T18" s="13">
-        <v>89</v>
-      </c>
-      <c r="U18" s="14">
-        <v>-0.36</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="U18" s="14"/>
       <c r="V18" s="13">
-        <v>868284</v>
-      </c>
-      <c r="W18" s="13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X18" s="13">
-        <v>487800</v>
-      </c>
+        <v>639992</v>
+      </c>
+      <c r="W18" s="13"/>
+      <c r="X18" s="13"/>
       <c r="Y18" s="17">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z18" s="13">
-        <v>9756</v>
+        <v>79999</v>
       </c>
       <c r="AA18"/>
       <c r="AB18"/>
-      <c r="AC18" s="2">
-        <v>13</v>
-      </c>
+      <c r="AC18" s="2"/>
       <c r="AD18" s="17">
-        <v>42</v>
+        <v>229</v>
       </c>
       <c r="AE18" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF18" s="18">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="AG18" s="19">
-        <v>0.0225</v>
-      </c>
-      <c r="AH18" s="13">
-        <v>1020</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH18" s="13"/>
       <c r="AI18" s="14">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="AJ18"/>
       <c r="AK18" s="11" t="inlineStr">
         <is>
-          <t>2015-11-16</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AL18" s="17">
-        <v>3978</v>
+        <v>42</v>
       </c>
       <c r="AM18" s="11" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN18" s="11"/>
       <c r="AO18" s="11"/>
       <c r="AP18"/>
-      <c r="AQ18" s="17">
-        <v>9</v>
-      </c>
+      <c r="AQ18" s="17"/>
       <c r="AR18" s="17">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="AS18" s="12" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>ダイソン公式ストア</t>
         </is>
       </c>
       <c r="AT18" s="11" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU18" s="11"/>
-      <c r="AV18" s="12"/>
-      <c r="AW18" s="11"/>
+          <t>FBM</t>
+        </is>
+      </c>
+      <c r="AU18" s="11" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="AV18" s="12" t="inlineStr">
+        <is>
+          <t>千代田区麹町 東京都 1020083 JP</t>
+        </is>
+      </c>
+      <c r="AW18" s="11" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KRDRXNL1G5FA</t>
+        </is>
+      </c>
       <c r="AX18" s="11"/>
       <c r="AY18" s="11"/>
       <c r="AZ18" s="11"/>
       <c r="BA18" s="11"/>
       <c r="BB18" s="11"/>
-      <c r="BC18" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD18" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC18" s="11"/>
+      <c r="BD18" s="11"/>
       <c r="BE18" s="11"/>
       <c r="BF18" s="11"/>
       <c r="BG18" s="11"/>
@@ -11117,49 +10739,25 @@
       <c r="BI18" s="20"/>
       <c r="BJ18" s="20" t="inlineStr">
         <is>
-          <t>5.3 kg</t>
+          <t>3.2 kg</t>
         </is>
       </c>
       <c r="BK18" s="20" t="inlineStr">
         <is>
-          <t>5.30 kg</t>
+          <t>3.20 kg</t>
         </is>
       </c>
       <c r="BL18" s="20" t="inlineStr">
         <is>
-          <t>34 x 34 x 53 cm</t>
-        </is>
-      </c>
-      <c r="BM18" s="20" t="inlineStr">
-        <is>
-          <t>34.00 x 34.00 x 53.00 cm</t>
-        </is>
-      </c>
-      <c r="BN18" s="20" t="inlineStr">
-        <is>
-          <t>8.03 kg</t>
-        </is>
-      </c>
-      <c r="BO18" s="20" t="inlineStr">
-        <is>
-          <t>8.03 kg</t>
-        </is>
-      </c>
-      <c r="BP18" s="20" t="inlineStr">
-        <is>
-          <t>57.8 x 38.5 x 38.5 cm</t>
-        </is>
-      </c>
-      <c r="BQ18" s="20" t="inlineStr">
-        <is>
-          <t>57.80 x 38.50 x 38.50 cm</t>
-        </is>
-      </c>
-      <c r="BR18" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
+          <t>25.7長さ x 25.3幅 x 112.9高さ cm</t>
+        </is>
+      </c>
+      <c r="BM18" s="20"/>
+      <c r="BN18" s="20"/>
+      <c r="BO18" s="20"/>
+      <c r="BP18" s="20"/>
+      <c r="BQ18" s="20"/>
+      <c r="BR18" s="11"/>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
@@ -11168,117 +10766,107 @@
       <c r="B19" s="11"/>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>B0FC18HMRN</t>
+          <t>B0HHN8HTLL</t>
         </is>
       </c>
       <c r="D19" s="12"/>
       <c r="E19" s="12"/>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>mindoo</t>
+          <t>Dyson(ダイソン)</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/mindoo/page/195B1567-B86E-4B16-A2C3-065A70917DA9?lp_asin=B0FC18HMRN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jpnull</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>Mindoo AquaX Plus Mindoo AquaX Plus 擦水吸尘器 [吸水、擦拭、除菌、自我清洁、自动干燥 5合1] 自走式 垃圾收集1台5用 强力吸力 超轻 自动清洗 高性能 (黑色)s軽量モデル 3モード 自動洗浄 温風乾燥</t>
+          <t>Dyson(ダイソン) Dyson V12 Detect Slim Fluffy无线棒式吸尘器 戴森官方限定 延长保修1年款</t>
         </is>
       </c>
       <c r="I19" s="12"/>
       <c r="J19" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FC18HMRN?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0HHN8HTLL?psc=1</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/21vmJWLJAbL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51z7B-TmeXL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>B0FC18HMRN</t>
+          <t>B0HHN8HTLL</t>
         </is>
       </c>
       <c r="M19" s="12" t="inlineStr">
         <is>
-          <t>ホーム＆キッチン:家電:生活家電:掃除機:家庭用湿式/乾式掃除機</t>
+          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
         </is>
       </c>
       <c r="N19" s="12" t="inlineStr">
         <is>
-          <t>ホーム＆キッチン</t>
+          <t>DIY・工具・ガーデン</t>
         </is>
       </c>
       <c r="O19" s="13">
-        <v>216985</v>
+        <v>155961</v>
       </c>
       <c r="P19" s="13">
-        <v>-31468</v>
+        <v>-132420</v>
       </c>
       <c r="Q19" s="14">
-        <v>-0.17</v>
+        <v>-5.63</v>
       </c>
       <c r="R19" s="15" t="inlineStr">
         <is>
-          <t>家庭用湿式/乾式掃除機</t>
+          <t>ウェットドライショップ掃除機</t>
         </is>
       </c>
       <c r="S19" s="16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19</t>
         </is>
       </c>
       <c r="T19" s="13">
-        <v>11</v>
-      </c>
-      <c r="U19" s="14">
-        <v>-0.17</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="U19" s="14"/>
       <c r="V19" s="13">
-        <v>822800</v>
+        <v>605000</v>
       </c>
       <c r="W19" s="13"/>
       <c r="X19" s="13"/>
       <c r="Y19" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z19" s="13">
-        <v>74800</v>
+        <v>60500</v>
       </c>
       <c r="AA19"/>
       <c r="AB19"/>
       <c r="AC19" s="2"/>
-      <c r="AD19" s="17">
-        <v>18</v>
-      </c>
-      <c r="AE19" s="13">
-        <v>1</v>
-      </c>
-      <c r="AF19" s="18">
-        <v>4.3</v>
-      </c>
+      <c r="AD19" s="17"/>
+      <c r="AE19" s="13"/>
+      <c r="AF19" s="18"/>
       <c r="AG19" s="19">
-        <v>0.0909</v>
-      </c>
-      <c r="AH19" s="13">
-        <v>781</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH19" s="13"/>
       <c r="AI19" s="14">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="AJ19"/>
       <c r="AK19" s="11" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AL19" s="17">
-        <v>373</v>
+        <v>34</v>
       </c>
       <c r="AM19" s="11" t="inlineStr">
         <is>
@@ -11288,15 +10876,13 @@
       <c r="AN19" s="11"/>
       <c r="AO19" s="11"/>
       <c r="AP19"/>
-      <c r="AQ19" s="17">
-        <v>9</v>
-      </c>
+      <c r="AQ19" s="17"/>
       <c r="AR19" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS19" s="12" t="inlineStr">
         <is>
-          <t>〈公式〉Mindoo</t>
+          <t>スタッフショップ</t>
         </is>
       </c>
       <c r="AT19" s="11" t="inlineStr">
@@ -11311,79 +10897,47 @@
       </c>
       <c r="AV19" s="12" t="inlineStr">
         <is>
-          <t>港区三田 東京都 1080073 JP</t>
+          <t>三重県 5110284 JP</t>
         </is>
       </c>
       <c r="AW19" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3KERCWTE76M89</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3JH293JNBT5IZ</t>
         </is>
       </c>
       <c r="AX19" s="11"/>
-      <c r="AY19" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY19" s="11"/>
       <c r="AZ19" s="11"/>
       <c r="BA19" s="11"/>
       <c r="BB19" s="11"/>
-      <c r="BC19" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD19" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC19" s="11"/>
+      <c r="BD19" s="11"/>
       <c r="BE19" s="11"/>
       <c r="BF19" s="11"/>
       <c r="BG19" s="11"/>
       <c r="BH19" s="12"/>
-      <c r="BI19" s="20" t="inlineStr">
-        <is>
-          <t>Amazon おすすめ</t>
-        </is>
-      </c>
+      <c r="BI19" s="20"/>
       <c r="BJ19" s="20" t="inlineStr">
         <is>
-          <t>3.6 キログラム</t>
-        </is>
-      </c>
-      <c r="BK19" s="20"/>
+          <t>3.2 kg</t>
+        </is>
+      </c>
+      <c r="BK19" s="20" t="inlineStr">
+        <is>
+          <t>3.20 kg</t>
+        </is>
+      </c>
       <c r="BL19" s="20" t="inlineStr">
         <is>
-          <t>24.9長さ x 23.2幅 x 110高さ cm</t>
+          <t>25.7長さ x 25.3幅 x 112.9高さ cm</t>
         </is>
       </c>
       <c r="BM19" s="20"/>
-      <c r="BN19" s="20" t="inlineStr">
-        <is>
-          <t>6.2 kg</t>
-        </is>
-      </c>
-      <c r="BO19" s="20" t="inlineStr">
-        <is>
-          <t>6.20 kg</t>
-        </is>
-      </c>
-      <c r="BP19" s="20" t="inlineStr">
-        <is>
-          <t>64.5 x 30.5 x 23.8 cm</t>
-        </is>
-      </c>
-      <c r="BQ19" s="20" t="inlineStr">
-        <is>
-          <t>64.50 x 30.50 x 23.80 cm</t>
-        </is>
-      </c>
-      <c r="BR19" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
+      <c r="BN19" s="20"/>
+      <c r="BO19" s="20"/>
+      <c r="BP19" s="20"/>
+      <c r="BQ19" s="20"/>
+      <c r="BR19" s="11"/>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
@@ -11392,40 +10946,40 @@
       <c r="B20" s="11"/>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>B0HGLNPJPC</t>
+          <t>B0FK9HN17M</t>
         </is>
       </c>
       <c r="D20" s="12"/>
       <c r="E20" s="12"/>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>Dyson(ダイソン)</t>
+          <t>JONR</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%83%80%E3%82%A4%E3%82%BD%E3%83%B3/page/0456F1ED-24D4-4719-8E99-5936EC69346F?lp_asin=B0HGLNPJPC&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FK9HN17M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>Dyson(ダイソン) V12 Detect Slim Absolute 无线吸尘器 戴森官方限定 延长保修1年款s棒手持吸尘器,旋风,带充电座,Amazon.co.jp 独家,高功能 LED 和自动模式不会错过垃圾</t>
+          <t>拖水式吸尘器 JONR ED12 Lite【日本最轻量】吸引・水洗・擦拭3合1 无绳式 推杆式吸尘器 20000Pa强力吸引 干湿两用 自动清洗 靠墙1mm清洁 长时间运行 大容量水箱 自立式&amp;自走式 拖把功能 适用于地板擦拭/硬质地板/地毯/缝隙</t>
         </is>
       </c>
       <c r="I20" s="12"/>
       <c r="J20" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0HGLNPJPC?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FK9HN17M?psc=1</t>
         </is>
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/616rJ-dkmUL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61gNWZ3JF6L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L20" s="12" t="inlineStr">
         <is>
-          <t>B0HGLNPJPC</t>
+          <t>B0FK9HN17M</t>
         </is>
       </c>
       <c r="M20" s="12" t="inlineStr">
@@ -11439,13 +10993,13 @@
         </is>
       </c>
       <c r="O20" s="13">
-        <v>140536</v>
+        <v>70661</v>
       </c>
       <c r="P20" s="13">
-        <v>-86532</v>
+        <v>2745</v>
       </c>
       <c r="Q20" s="14">
-        <v>-1.6</v>
+        <v>0.04</v>
       </c>
       <c r="R20" s="15" t="inlineStr">
         <is>
@@ -11454,15 +11008,17 @@
       </c>
       <c r="S20" s="16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>21</t>
         </is>
       </c>
       <c r="T20" s="13">
-        <v>8</v>
-      </c>
-      <c r="U20" s="14"/>
+        <v>30</v>
+      </c>
+      <c r="U20" s="14">
+        <v>0.25</v>
+      </c>
       <c r="V20" s="13">
-        <v>639992</v>
+        <v>551700</v>
       </c>
       <c r="W20" s="13"/>
       <c r="X20" s="13"/>
@@ -11470,71 +11026,75 @@
         <v>1</v>
       </c>
       <c r="Z20" s="13">
-        <v>79999</v>
+        <v>18390</v>
       </c>
       <c r="AA20"/>
       <c r="AB20"/>
       <c r="AC20" s="2"/>
       <c r="AD20" s="17">
-        <v>229</v>
+        <v>84</v>
       </c>
       <c r="AE20" s="13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF20" s="18">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="AG20" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH20" s="13"/>
+        <v>0.0667</v>
+      </c>
+      <c r="AH20" s="13">
+        <v>781</v>
+      </c>
       <c r="AI20" s="14">
-        <v>0.85</v>
+        <v>0.81</v>
       </c>
       <c r="AJ20"/>
       <c r="AK20" s="11" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AL20" s="17">
-        <v>42</v>
+        <v>435</v>
       </c>
       <c r="AM20" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN20" s="11"/>
       <c r="AO20" s="11"/>
       <c r="AP20"/>
-      <c r="AQ20" s="17"/>
+      <c r="AQ20" s="17">
+        <v>8</v>
+      </c>
       <c r="AR20" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS20" s="12" t="inlineStr">
         <is>
-          <t>ダイソン公式ストア</t>
+          <t>JONR公式ストア</t>
         </is>
       </c>
       <c r="AT20" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU20" s="11" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV20" s="12" t="inlineStr">
         <is>
-          <t>千代田区麹町 東京都 1020083 JP</t>
+          <t>香港 999077 HK</t>
         </is>
       </c>
       <c r="AW20" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KRDRXNL1G5FA</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2SR0DVTECF9BI</t>
         </is>
       </c>
       <c r="AX20" s="11"/>
@@ -11543,7 +11103,11 @@
       <c r="BA20" s="11"/>
       <c r="BB20" s="11"/>
       <c r="BC20" s="11"/>
-      <c r="BD20" s="11"/>
+      <c r="BD20" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE20" s="11"/>
       <c r="BF20" s="11"/>
       <c r="BG20" s="11"/>
@@ -11551,25 +11115,45 @@
       <c r="BI20" s="20"/>
       <c r="BJ20" s="20" t="inlineStr">
         <is>
-          <t>3.2 kg</t>
+          <t>3.4 kg</t>
         </is>
       </c>
       <c r="BK20" s="20" t="inlineStr">
         <is>
-          <t>3.20 kg</t>
+          <t>3.40 kg</t>
         </is>
       </c>
       <c r="BL20" s="20" t="inlineStr">
         <is>
-          <t>25.7長さ x 25.3幅 x 112.9高さ cm</t>
+          <t>29.8長さ x 26.9幅 x 113.4高さ cm</t>
         </is>
       </c>
       <c r="BM20" s="20"/>
-      <c r="BN20" s="20"/>
-      <c r="BO20" s="20"/>
-      <c r="BP20" s="20"/>
-      <c r="BQ20" s="20"/>
-      <c r="BR20" s="11"/>
+      <c r="BN20" s="20" t="inlineStr">
+        <is>
+          <t>6.09 kg</t>
+        </is>
+      </c>
+      <c r="BO20" s="20" t="inlineStr">
+        <is>
+          <t>6.09 kg</t>
+        </is>
+      </c>
+      <c r="BP20" s="20" t="inlineStr">
+        <is>
+          <t>55 x 33.3 x 31 cm</t>
+        </is>
+      </c>
+      <c r="BQ20" s="20" t="inlineStr">
+        <is>
+          <t>55.00 x 33.30 x 31.00 cm</t>
+        </is>
+      </c>
+      <c r="BR20" s="11" t="inlineStr">
+        <is>
+          <t>大件</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
@@ -11578,108 +11162,110 @@
       <c r="B21" s="11"/>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>B0HHN8HTLL</t>
+          <t>B0CPPHYW3B</t>
         </is>
       </c>
       <c r="D21" s="12"/>
       <c r="E21" s="12"/>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>Dyson(ダイソン)</t>
+          <t>ミナトワークス</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jpnull</t>
+          <t>https://www.amazon.co.jp/stores/%E3%83%9F%E3%83%8A%E3%83%88%E3%83%AF%E3%83%BC%E3%82%AF%E3%82%B9/page/7E77FCE9-0862-4057-994E-E5C8A30E6C6D?lp_asin=B0CPPHYW3B&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>Dyson(ダイソン) Dyson V12 Detect Slim Fluffy无线棒式吸尘器 戴森官方限定 延长保修1年款</t>
+          <t>Minato Works 干湿两用 吸尘器 真空吸尘器 MPV-101 +附带替换过滤器 水箱容量10升</t>
         </is>
       </c>
       <c r="I21" s="12"/>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0HHN8HTLL?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0CPPHYW3B?psc=1</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51z7B-TmeXL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41ZrF14970L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>B0HHN8HTLL</t>
+          <t>B0CPPHYW3B</t>
         </is>
       </c>
       <c r="M21" s="12" t="inlineStr">
         <is>
-          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
+          <t>産業・研究開発用品:衛生・清掃用品:床・カーペットクリーニング:掃除機・アクセサリ:掃除機:乾湿両用掃除機</t>
         </is>
       </c>
       <c r="N21" s="12" t="inlineStr">
         <is>
-          <t>DIY・工具・ガーデン</t>
+          <t>産業・研究開発用品</t>
         </is>
       </c>
       <c r="O21" s="13">
-        <v>155961</v>
+        <v>13848</v>
       </c>
       <c r="P21" s="13">
-        <v>-132420</v>
+        <v>-4407</v>
       </c>
       <c r="Q21" s="14">
-        <v>-5.63</v>
+        <v>-0.47</v>
       </c>
       <c r="R21" s="15" t="inlineStr">
         <is>
-          <t>ウェットドライショップ掃除機</t>
+          <t>乾湿両用掃除機</t>
         </is>
       </c>
       <c r="S21" s="16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="T21" s="13">
-        <v>10</v>
-      </c>
-      <c r="U21" s="14"/>
+        <v>44</v>
+      </c>
+      <c r="U21" s="14">
+        <v>-0.22</v>
+      </c>
       <c r="V21" s="13">
-        <v>605000</v>
+        <v>461120</v>
       </c>
       <c r="W21" s="13"/>
       <c r="X21" s="13"/>
       <c r="Y21" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z21" s="13">
-        <v>60500</v>
+        <v>10480</v>
       </c>
       <c r="AA21"/>
       <c r="AB21"/>
       <c r="AC21" s="2"/>
-      <c r="AD21" s="17"/>
-      <c r="AE21" s="13"/>
-      <c r="AF21" s="18"/>
+      <c r="AD21" s="17">
+        <v>4</v>
+      </c>
+      <c r="AE21" s="13">
+        <v>1</v>
+      </c>
+      <c r="AF21" s="18">
+        <v>3.6</v>
+      </c>
       <c r="AG21" s="19">
-        <v>0</v>
+        <v>0.0227</v>
       </c>
       <c r="AH21" s="13"/>
       <c r="AI21" s="14">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="AJ21"/>
-      <c r="AK21" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AL21" s="17">
-        <v>34</v>
-      </c>
+      <c r="AK21" s="11"/>
+      <c r="AL21" s="17"/>
       <c r="AM21" s="11" t="inlineStr">
         <is>
           <t>FBM</t>
@@ -11688,13 +11274,15 @@
       <c r="AN21" s="11"/>
       <c r="AO21" s="11"/>
       <c r="AP21"/>
-      <c r="AQ21" s="17"/>
+      <c r="AQ21" s="17">
+        <v>9</v>
+      </c>
       <c r="AR21" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS21" s="12" t="inlineStr">
         <is>
-          <t>スタッフショップ</t>
+          <t>【ミナトワークス】</t>
         </is>
       </c>
       <c r="AT21" s="11" t="inlineStr">
@@ -11709,12 +11297,12 @@
       </c>
       <c r="AV21" s="12" t="inlineStr">
         <is>
-          <t>三重県 5110284 JP</t>
+          <t>豊前市 福岡県 8280031 JP</t>
         </is>
       </c>
       <c r="AW21" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3JH293JNBT5IZ</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A35R5657DWBR35</t>
         </is>
       </c>
       <c r="AX21" s="11"/>
@@ -11722,7 +11310,11 @@
       <c r="AZ21" s="11"/>
       <c r="BA21" s="11"/>
       <c r="BB21" s="11"/>
-      <c r="BC21" s="11"/>
+      <c r="BC21" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD21" s="11"/>
       <c r="BE21" s="11"/>
       <c r="BF21" s="11"/>
@@ -11731,17 +11323,13 @@
       <c r="BI21" s="20"/>
       <c r="BJ21" s="20" t="inlineStr">
         <is>
-          <t>3.2 kg</t>
-        </is>
-      </c>
-      <c r="BK21" s="20" t="inlineStr">
-        <is>
-          <t>3.20 kg</t>
-        </is>
-      </c>
+          <t>4.5 キログラム</t>
+        </is>
+      </c>
+      <c r="BK21" s="20"/>
       <c r="BL21" s="20" t="inlineStr">
         <is>
-          <t>25.7長さ x 25.3幅 x 112.9高さ cm</t>
+          <t>34.5長さ x 31幅 x 36.5高さ cm</t>
         </is>
       </c>
       <c r="BM21" s="20"/>
@@ -11758,40 +11346,40 @@
       <c r="B22" s="11"/>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>B0FK9HN17M</t>
+          <t>B07KR2J116</t>
         </is>
       </c>
       <c r="D22" s="12"/>
       <c r="E22" s="12"/>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>JONR</t>
+          <t>ミナトワークス</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FK9HN17M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/%E3%83%9F%E3%83%8A%E3%83%88%E3%83%AF%E3%83%BC%E3%82%AF%E3%82%B9/page/7E77FCE9-0862-4057-994E-E5C8A30E6C6D?lp_asin=B07KR2J116&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>拖水式吸尘器 JONR ED12 Lite【日本最轻量】吸引・水洗・擦拭3合1 无绳式 推杆式吸尘器 20000Pa强力吸引 干湿两用 自动清洗 靠墙1mm清洁 长时间运行 大容量水箱 自立式&amp;自走式 拖把功能 适用于地板擦拭/硬质地板/地毯/缝隙</t>
+          <t>Minato 干湿两用 业务用 吸尘器 旋风式 真空吸尘器 MPV-151CY (容量15L/吸水0.5L)</t>
         </is>
       </c>
       <c r="I22" s="12"/>
       <c r="J22" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FK9HN17M?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B07KR2J116?psc=1</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61gNWZ3JF6L._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41ovXwP+o+L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L22" s="12" t="inlineStr">
         <is>
-          <t>B0FK9HN17M</t>
+          <t>B07KR2J116</t>
         </is>
       </c>
       <c r="M22" s="12" t="inlineStr">
@@ -11805,13 +11393,13 @@
         </is>
       </c>
       <c r="O22" s="13">
-        <v>70661</v>
+        <v>33132</v>
       </c>
       <c r="P22" s="13">
-        <v>2745</v>
+        <v>23271</v>
       </c>
       <c r="Q22" s="14">
-        <v>0.04</v>
+        <v>0.17</v>
       </c>
       <c r="R22" s="15" t="inlineStr">
         <is>
@@ -11820,93 +11408,91 @@
       </c>
       <c r="S22" s="16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="T22" s="13">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="U22" s="14">
-        <v>0.25</v>
+        <v>2.5</v>
       </c>
       <c r="V22" s="13">
-        <v>551700</v>
+        <v>338200</v>
       </c>
       <c r="W22" s="13"/>
       <c r="X22" s="13"/>
       <c r="Y22" s="17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z22" s="13">
-        <v>18390</v>
+        <v>17800</v>
       </c>
       <c r="AA22"/>
       <c r="AB22"/>
       <c r="AC22" s="2"/>
       <c r="AD22" s="17">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="AE22" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF22" s="18">
         <v>3.3</v>
       </c>
       <c r="AG22" s="19">
-        <v>0.0667</v>
-      </c>
-      <c r="AH22" s="13">
-        <v>781</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH22" s="13"/>
       <c r="AI22" s="14">
-        <v>0.81</v>
+        <v>0.85</v>
       </c>
       <c r="AJ22"/>
       <c r="AK22" s="11" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2018-12-03</t>
         </is>
       </c>
       <c r="AL22" s="17">
-        <v>435</v>
+        <v>2865</v>
       </c>
       <c r="AM22" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN22" s="11"/>
       <c r="AO22" s="11"/>
       <c r="AP22"/>
       <c r="AQ22" s="17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR22" s="17">
         <v>1</v>
       </c>
       <c r="AS22" s="12" t="inlineStr">
         <is>
-          <t>JONR公式ストア</t>
+          <t>【ミナトワークス】</t>
         </is>
       </c>
       <c r="AT22" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AU22" s="11" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="AV22" s="12" t="inlineStr">
         <is>
-          <t>香港 999077 HK</t>
+          <t>豊前市 福岡県 8280031 JP</t>
         </is>
       </c>
       <c r="AW22" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2SR0DVTECF9BI</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A35R5657DWBR35</t>
         </is>
       </c>
       <c r="AX22" s="11"/>
@@ -11914,7 +11500,11 @@
       <c r="AZ22" s="11"/>
       <c r="BA22" s="11"/>
       <c r="BB22" s="11"/>
-      <c r="BC22" s="11"/>
+      <c r="BC22" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD22" s="11" t="inlineStr">
         <is>
           <t>Y</t>
@@ -11927,45 +11517,21 @@
       <c r="BI22" s="20"/>
       <c r="BJ22" s="20" t="inlineStr">
         <is>
-          <t>3.4 kg</t>
-        </is>
-      </c>
-      <c r="BK22" s="20" t="inlineStr">
-        <is>
-          <t>3.40 kg</t>
-        </is>
-      </c>
+          <t>12 キログラム</t>
+        </is>
+      </c>
+      <c r="BK22" s="20"/>
       <c r="BL22" s="20" t="inlineStr">
         <is>
-          <t>29.8長さ x 26.9幅 x 113.4高さ cm</t>
+          <t>33.5長さ x 31幅 x 54高さ cm</t>
         </is>
       </c>
       <c r="BM22" s="20"/>
-      <c r="BN22" s="20" t="inlineStr">
-        <is>
-          <t>6.09 kg</t>
-        </is>
-      </c>
-      <c r="BO22" s="20" t="inlineStr">
-        <is>
-          <t>6.09 kg</t>
-        </is>
-      </c>
-      <c r="BP22" s="20" t="inlineStr">
-        <is>
-          <t>55 x 33.3 x 31 cm</t>
-        </is>
-      </c>
-      <c r="BQ22" s="20" t="inlineStr">
-        <is>
-          <t>55.00 x 33.30 x 31.00 cm</t>
-        </is>
-      </c>
-      <c r="BR22" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
+      <c r="BN22" s="20"/>
+      <c r="BO22" s="20"/>
+      <c r="BP22" s="20"/>
+      <c r="BQ22" s="20"/>
+      <c r="BR22" s="11"/>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
@@ -11974,147 +11540,153 @@
       <c r="B23" s="11"/>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>B0CPPHYW3B</t>
+          <t>B0D2VPQT2V</t>
         </is>
       </c>
       <c r="D23" s="12"/>
       <c r="E23" s="12"/>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>ミナトワークス</t>
+          <t>dreame</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%83%9F%E3%83%8A%E3%83%88%E3%83%AF%E3%83%BC%E3%82%AF%E3%82%B9/page/7E77FCE9-0862-4057-994E-E5C8A30E6C6D?lp_asin=B0CPPHYW3B&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0D2VPQT2V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>Minato Works 干湿两用 吸尘器 真空吸尘器 MPV-101 +附带替换过滤器 水箱容量10升</t>
+          <t>MOVA K10 Pro 水拭き掃除機 自走式 水拭き2in1コードレススティック掃除機 汚れ検知可能 作動時0.9kg超軽量 15000Pa強力吸引 乾湿両用掃除機 自動洗浄 電解水除菌 30分連続稼働 6mm端清掃 大容量水タンク 床拭き LED</t>
         </is>
       </c>
       <c r="I23" s="12"/>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0CPPHYW3B?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0D2VPQT2V?psc=1</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41ZrF14970L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61KqhLRxwYL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>B0CPPHYW3B</t>
+          <t>B0D2VPQT2V</t>
         </is>
       </c>
       <c r="M23" s="12" t="inlineStr">
         <is>
-          <t>産業・研究開発用品:衛生・清掃用品:床・カーペットクリーニング:掃除機・アクセサリ:掃除機:乾湿両用掃除機</t>
+          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
         </is>
       </c>
       <c r="N23" s="12" t="inlineStr">
         <is>
-          <t>産業・研究開発用品</t>
+          <t>DIY・工具・ガーデン</t>
         </is>
       </c>
       <c r="O23" s="13">
-        <v>13848</v>
+        <v>99410</v>
       </c>
       <c r="P23" s="13">
-        <v>-4407</v>
+        <v>2480</v>
       </c>
       <c r="Q23" s="14">
-        <v>-0.47</v>
+        <v>0.02</v>
       </c>
       <c r="R23" s="15" t="inlineStr">
         <is>
-          <t>乾湿両用掃除機</t>
+          <t>ウェットドライショップ掃除機</t>
         </is>
       </c>
       <c r="S23" s="16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>29</t>
         </is>
       </c>
       <c r="T23" s="13">
-        <v>44</v>
-      </c>
-      <c r="U23" s="14">
-        <v>-0.22</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="U23" s="14"/>
       <c r="V23" s="13">
-        <v>461120</v>
+        <v>243200</v>
       </c>
       <c r="W23" s="13"/>
       <c r="X23" s="13"/>
       <c r="Y23" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z23" s="13">
-        <v>10480</v>
+        <v>12800</v>
       </c>
       <c r="AA23"/>
       <c r="AB23"/>
       <c r="AC23" s="2"/>
       <c r="AD23" s="17">
-        <v>4</v>
+        <v>138</v>
       </c>
       <c r="AE23" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF23" s="18">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AG23" s="19">
-        <v>0.0227</v>
-      </c>
-      <c r="AH23" s="13"/>
+        <v>0.10529999999999999</v>
+      </c>
+      <c r="AH23" s="13">
+        <v>1020</v>
+      </c>
       <c r="AI23" s="14">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="AJ23"/>
-      <c r="AK23" s="11"/>
-      <c r="AL23" s="17"/>
+      <c r="AK23" s="11" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AL23" s="17">
+        <v>850</v>
+      </c>
       <c r="AM23" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN23" s="11"/>
       <c r="AO23" s="11"/>
       <c r="AP23"/>
       <c r="AQ23" s="17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR23" s="17">
         <v>1</v>
       </c>
       <c r="AS23" s="12" t="inlineStr">
         <is>
-          <t>【ミナトワークス】</t>
+          <t>Dreametech JP</t>
         </is>
       </c>
       <c r="AT23" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU23" s="11" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV23" s="12" t="inlineStr">
         <is>
-          <t>豊前市 福岡県 8280031 JP</t>
+          <t>Tianjin 300456 CN</t>
         </is>
       </c>
       <c r="AW23" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A35R5657DWBR35</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WSQAA92JSPUW</t>
         </is>
       </c>
       <c r="AX23" s="11"/>
@@ -12127,7 +11699,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD23" s="11"/>
+      <c r="BD23" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE23" s="11"/>
       <c r="BF23" s="11"/>
       <c r="BG23" s="11"/>
@@ -12135,21 +11711,45 @@
       <c r="BI23" s="20"/>
       <c r="BJ23" s="20" t="inlineStr">
         <is>
-          <t>4.5 キログラム</t>
-        </is>
-      </c>
-      <c r="BK23" s="20"/>
+          <t>3.8 kg</t>
+        </is>
+      </c>
+      <c r="BK23" s="20" t="inlineStr">
+        <is>
+          <t>3.80 kg</t>
+        </is>
+      </c>
       <c r="BL23" s="20" t="inlineStr">
         <is>
-          <t>34.5長さ x 31幅 x 36.5高さ cm</t>
+          <t>29長さ x 21.9幅 x 110.5高さ cm</t>
         </is>
       </c>
       <c r="BM23" s="20"/>
-      <c r="BN23" s="20"/>
-      <c r="BO23" s="20"/>
-      <c r="BP23" s="20"/>
-      <c r="BQ23" s="20"/>
-      <c r="BR23" s="11"/>
+      <c r="BN23" s="20" t="inlineStr">
+        <is>
+          <t>6.6 kg</t>
+        </is>
+      </c>
+      <c r="BO23" s="20" t="inlineStr">
+        <is>
+          <t>6.60 kg</t>
+        </is>
+      </c>
+      <c r="BP23" s="20" t="inlineStr">
+        <is>
+          <t>69 x 32 x 29 cm</t>
+        </is>
+      </c>
+      <c r="BQ23" s="20" t="inlineStr">
+        <is>
+          <t>69.00 x 32.00 x 29.00 cm</t>
+        </is>
+      </c>
+      <c r="BR23" s="11" t="inlineStr">
+        <is>
+          <t>大件</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
@@ -12158,40 +11758,40 @@
       <c r="B24" s="11"/>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>B0BW467WC5</t>
+          <t>B0CZKHJXNG</t>
         </is>
       </c>
       <c r="D24" s="12"/>
       <c r="E24" s="12"/>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>longsafe</t>
+          <t>EUREKA</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/Longsafe%E3%83%AD%E3%83%B3%E3%82%B0%E3%82%BB%E3%83%BC%E3%83%95/page/BD939425-D017-4A77-8C40-744607798C52?lp_asin=B0BW467WC5&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/Eureka/page/0DAE79FF-361F-4FFE-9129-4ACEDAF99AD5?lp_asin=B0CZKHJXNG&amp;ref_=ast_bln</t>
         </is>
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>Makita 牧田兼容品 充电式 集尘机 干湿两用 集尘机 业务用 粉尘用 鼓风机 软管 小型 吸 大容量 10L 吸尘器 无线 电动 18V 电池 对应 ※仅本体 电池 充电器 另售 (SYU01-BL)</t>
+          <t>EUREKA NEY100 地毯清洁器 400W强力吸力 汽车座椅和布制品清洗 自洁式 地毯和沙发清洗 干湿两用 淋水清洗器 可用热水清洗 附带洗涤剂 三只刷子</t>
         </is>
       </c>
       <c r="I24" s="12"/>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0BW467WC5?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0CZKHJXNG?psc=1</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71y30b4dMOL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41nAma6e0eL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L24" s="12" t="inlineStr">
         <is>
-          <t>B0BW467WC5</t>
+          <t>B0CZKHJXNG</t>
         </is>
       </c>
       <c r="M24" s="12" t="inlineStr">
@@ -12205,13 +11805,13 @@
         </is>
       </c>
       <c r="O24" s="13">
-        <v>57609</v>
+        <v>74183</v>
       </c>
       <c r="P24" s="13">
-        <v>-20245</v>
+        <v>2118</v>
       </c>
       <c r="Q24" s="14">
-        <v>-0.54</v>
+        <v>0.03</v>
       </c>
       <c r="R24" s="15" t="inlineStr">
         <is>
@@ -12220,17 +11820,15 @@
       </c>
       <c r="S24" s="16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T24" s="13">
-        <v>38</v>
-      </c>
-      <c r="U24" s="14">
-        <v>0.26</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="U24" s="14"/>
       <c r="V24" s="13">
-        <v>448362</v>
+        <v>214800</v>
       </c>
       <c r="W24" s="13"/>
       <c r="X24" s="13"/>
@@ -12238,75 +11836,67 @@
         <v>2</v>
       </c>
       <c r="Z24" s="13">
-        <v>11799</v>
+        <v>7160</v>
       </c>
       <c r="AA24"/>
       <c r="AB24"/>
       <c r="AC24" s="2"/>
       <c r="AD24" s="17">
-        <v>67</v>
+        <v>152</v>
       </c>
       <c r="AE24" s="13">
         <v>0</v>
       </c>
       <c r="AF24" s="18">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AG24" s="19">
         <v>0</v>
       </c>
-      <c r="AH24" s="13">
-        <v>675</v>
-      </c>
+      <c r="AH24" s="13"/>
       <c r="AI24" s="14">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="AJ24"/>
-      <c r="AK24" s="11" t="inlineStr">
-        <is>
-          <t>2023-02-20</t>
-        </is>
-      </c>
-      <c r="AL24" s="17">
-        <v>1325</v>
-      </c>
+      <c r="AK24" s="11"/>
+      <c r="AL24" s="17"/>
       <c r="AM24" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN24" s="11"/>
       <c r="AO24" s="11"/>
       <c r="AP24"/>
       <c r="AQ24" s="17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR24" s="17">
         <v>1</v>
       </c>
       <c r="AS24" s="12" t="inlineStr">
         <is>
-          <t>YSJAPAN</t>
+          <t>Eureka Japan</t>
         </is>
       </c>
       <c r="AT24" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU24" s="11" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV24" s="12" t="inlineStr">
         <is>
-          <t>相模原市中央区 神奈川県 2520231 JP</t>
+          <t>TSIM SHA TSUI 999077 HK</t>
         </is>
       </c>
       <c r="AW24" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A21SFW0V5BVYM</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3JXXBYW06ZFVU</t>
         </is>
       </c>
       <c r="AX24" s="11"/>
@@ -12331,45 +11921,25 @@
       <c r="BI24" s="20"/>
       <c r="BJ24" s="20" t="inlineStr">
         <is>
-          <t>3.4 kg</t>
+          <t>5 Kilograms</t>
         </is>
       </c>
       <c r="BK24" s="20" t="inlineStr">
         <is>
-          <t>3.40 kg</t>
+          <t>5.00 kg</t>
         </is>
       </c>
       <c r="BL24" s="20" t="inlineStr">
         <is>
-          <t>40長さ x 25幅 x 26高さ cm</t>
+          <t>39奥行き x 30幅 x 20高さ cm</t>
         </is>
       </c>
       <c r="BM24" s="20"/>
-      <c r="BN24" s="20" t="inlineStr">
-        <is>
-          <t>3.96 kg</t>
-        </is>
-      </c>
-      <c r="BO24" s="20" t="inlineStr">
-        <is>
-          <t>3.96 kg</t>
-        </is>
-      </c>
-      <c r="BP24" s="20" t="inlineStr">
-        <is>
-          <t>40.9 x 28.4 x 28 cm</t>
-        </is>
-      </c>
-      <c r="BQ24" s="20" t="inlineStr">
-        <is>
-          <t>40.90 x 28.40 x 28.00 cm</t>
-        </is>
-      </c>
-      <c r="BR24" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
+      <c r="BN24" s="20"/>
+      <c r="BO24" s="20"/>
+      <c r="BP24" s="20"/>
+      <c r="BQ24" s="20"/>
+      <c r="BR24" s="11"/>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
@@ -12378,40 +11948,40 @@
       <c r="B25" s="11"/>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>B07KR2J116</t>
+          <t>B0HHN61KPZ</t>
         </is>
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="12"/>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>ミナトワークス</t>
+          <t>Dyson(ダイソン)</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%83%9F%E3%83%8A%E3%83%88%E3%83%AF%E3%83%BC%E3%82%AF%E3%82%B9/page/7E77FCE9-0862-4057-994E-E5C8A30E6C6D?lp_asin=B07KR2J116&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jpnull</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>Minato 干湿两用 业务用 吸尘器 旋风式 真空吸尘器 MPV-151CY (容量15L/吸水0.5L)</t>
+          <t>Dyson(ダイソン) Dyson V12s Detect Slim Submarine 无线棒式吸尘器 戴森官方限定 延长保修1年款</t>
         </is>
       </c>
       <c r="I25" s="12"/>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B07KR2J116?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0HHN61KPZ?psc=1</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41ovXwP+o+L._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31eRC+N6IRL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>B07KR2J116</t>
+          <t>B0HHN61KPZ</t>
         </is>
       </c>
       <c r="M25" s="12" t="inlineStr">
@@ -12425,13 +11995,11 @@
         </is>
       </c>
       <c r="O25" s="13">
-        <v>33132</v>
-      </c>
-      <c r="P25" s="13">
-        <v>23271</v>
-      </c>
+        <v>13685</v>
+      </c>
+      <c r="P25" s="13"/>
       <c r="Q25" s="14">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="R25" s="15" t="inlineStr">
         <is>
@@ -12440,38 +12008,30 @@
       </c>
       <c r="S25" s="16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="T25" s="13">
-        <v>19</v>
-      </c>
-      <c r="U25" s="14">
-        <v>2.5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="U25" s="14"/>
       <c r="V25" s="13">
-        <v>338200</v>
+        <v>179997</v>
       </c>
       <c r="W25" s="13"/>
       <c r="X25" s="13"/>
       <c r="Y25" s="17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z25" s="13">
-        <v>17800</v>
+        <v>59999</v>
       </c>
       <c r="AA25"/>
       <c r="AB25"/>
       <c r="AC25" s="2"/>
-      <c r="AD25" s="17">
-        <v>29</v>
-      </c>
-      <c r="AE25" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF25" s="18">
-        <v>3.3</v>
-      </c>
+      <c r="AD25" s="17"/>
+      <c r="AE25" s="13"/>
+      <c r="AF25" s="18"/>
       <c r="AG25" s="19">
         <v>0</v>
       </c>
@@ -12482,11 +12042,11 @@
       <c r="AJ25"/>
       <c r="AK25" s="11" t="inlineStr">
         <is>
-          <t>2018-12-03</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AL25" s="17">
-        <v>2865</v>
+        <v>34</v>
       </c>
       <c r="AM25" s="11" t="inlineStr">
         <is>
@@ -12496,15 +12056,13 @@
       <c r="AN25" s="11"/>
       <c r="AO25" s="11"/>
       <c r="AP25"/>
-      <c r="AQ25" s="17">
-        <v>9</v>
-      </c>
+      <c r="AQ25" s="17"/>
       <c r="AR25" s="17">
         <v>1</v>
       </c>
       <c r="AS25" s="12" t="inlineStr">
         <is>
-          <t>【ミナトワークス】</t>
+          <t>ダイソン公式ストア</t>
         </is>
       </c>
       <c r="AT25" s="11" t="inlineStr">
@@ -12519,12 +12077,12 @@
       </c>
       <c r="AV25" s="12" t="inlineStr">
         <is>
-          <t>豊前市 福岡県 8280031 JP</t>
+          <t>千代田区麹町 東京都 1020083 JP</t>
         </is>
       </c>
       <c r="AW25" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A35R5657DWBR35</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KRDRXNL1G5FA</t>
         </is>
       </c>
       <c r="AX25" s="11"/>
@@ -12532,16 +12090,8 @@
       <c r="AZ25" s="11"/>
       <c r="BA25" s="11"/>
       <c r="BB25" s="11"/>
-      <c r="BC25" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD25" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC25" s="11"/>
+      <c r="BD25" s="11"/>
       <c r="BE25" s="11"/>
       <c r="BF25" s="11"/>
       <c r="BG25" s="11"/>
@@ -12549,13 +12099,13 @@
       <c r="BI25" s="20"/>
       <c r="BJ25" s="20" t="inlineStr">
         <is>
-          <t>12 キログラム</t>
+          <t>3.2 キログラム</t>
         </is>
       </c>
       <c r="BK25" s="20"/>
       <c r="BL25" s="20" t="inlineStr">
         <is>
-          <t>33.5長さ x 31幅 x 54高さ cm</t>
+          <t>25.7長さ x 25.3幅 x 112.9高さ cm</t>
         </is>
       </c>
       <c r="BM25" s="20"/>
@@ -12572,7 +12122,7 @@
       <c r="B26" s="11"/>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>B0D2VPQT2V</t>
+          <t>B0CNJT8933</t>
         </is>
       </c>
       <c r="D26" s="12"/>
@@ -12584,28 +12134,28 @@
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0D2VPQT2V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0CNJT8933&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>MOVA K10 Pro 水拭き掃除機 自走式 水拭き2in1コードレススティック掃除機 汚れ検知可能 作動時0.9kg超軽量 15000Pa強力吸引 乾湿両用掃除機 自動洗浄 電解水除菌 30分連続稼働 6mm端清掃 大容量水タンク 床拭き LED</t>
+          <t>dreame (ドリーミー) H12 Dual 水拭き掃除機【4wayコードレス水拭き掃除機】 自动清洗和温风干燥 双向旋转式清洗 可达墙角的刷子设计 16000Pa强力吸力 电解水除菌 35分钟连续运行 智能污垢检测和自动吸力调节 语音引导 大容量</t>
         </is>
       </c>
       <c r="I26" s="12"/>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0D2VPQT2V?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0CNJT8933?psc=1</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61KqhLRxwYL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61b-HbgIkBL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L26" s="12" t="inlineStr">
         <is>
-          <t>B0D2VPQT2V</t>
+          <t>B0CNJT8933</t>
         </is>
       </c>
       <c r="M26" s="12" t="inlineStr">
@@ -12619,10 +12169,10 @@
         </is>
       </c>
       <c r="O26" s="13">
-        <v>99410</v>
+        <v>133273</v>
       </c>
       <c r="P26" s="13">
-        <v>2480</v>
+        <v>2289</v>
       </c>
       <c r="Q26" s="14">
         <v>0.02</v>
@@ -12634,15 +12184,17 @@
       </c>
       <c r="S26" s="16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>38</t>
         </is>
       </c>
       <c r="T26" s="13">
-        <v>19</v>
-      </c>
-      <c r="U26" s="14"/>
+        <v>4</v>
+      </c>
+      <c r="U26" s="14">
+        <v>0.06</v>
+      </c>
       <c r="V26" s="13">
-        <v>243200</v>
+        <v>171600</v>
       </c>
       <c r="W26" s="13"/>
       <c r="X26" s="13"/>
@@ -12650,37 +12202,37 @@
         <v>1</v>
       </c>
       <c r="Z26" s="13">
-        <v>12800</v>
+        <v>42900</v>
       </c>
       <c r="AA26"/>
       <c r="AB26"/>
       <c r="AC26" s="2"/>
       <c r="AD26" s="17">
-        <v>138</v>
+        <v>45</v>
       </c>
       <c r="AE26" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF26" s="18">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AG26" s="19">
-        <v>0.10529999999999999</v>
+        <v>0</v>
       </c>
       <c r="AH26" s="13">
-        <v>1020</v>
+        <v>1100</v>
       </c>
       <c r="AI26" s="14">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="AJ26"/>
       <c r="AK26" s="11" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2023-11-20</t>
         </is>
       </c>
       <c r="AL26" s="17">
-        <v>850</v>
+        <v>1053</v>
       </c>
       <c r="AM26" s="11" t="inlineStr">
         <is>
@@ -12691,14 +12243,14 @@
       <c r="AO26" s="11"/>
       <c r="AP26"/>
       <c r="AQ26" s="17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR26" s="17">
         <v>1</v>
       </c>
       <c r="AS26" s="12" t="inlineStr">
         <is>
-          <t>Dreametech JP</t>
+          <t>Dreame公式ストア</t>
         </is>
       </c>
       <c r="AT26" s="11" t="inlineStr">
@@ -12708,17 +12260,17 @@
       </c>
       <c r="AU26" s="11" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV26" s="12" t="inlineStr">
         <is>
-          <t>Tianjin 300456 CN</t>
+          <t>ROOM H28G BLK EH 10TH FLOOR GOLDEN BEAR IND CTR 66-82</t>
         </is>
       </c>
       <c r="AW26" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WSQAA92JSPUW</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WV0MTJICL1UJ</t>
         </is>
       </c>
       <c r="AX26" s="11"/>
@@ -12743,38 +12295,38 @@
       <c r="BI26" s="20"/>
       <c r="BJ26" s="20" t="inlineStr">
         <is>
-          <t>3.8 kg</t>
+          <t>5.13 kg</t>
         </is>
       </c>
       <c r="BK26" s="20" t="inlineStr">
         <is>
-          <t>3.80 kg</t>
+          <t>5.13 kg</t>
         </is>
       </c>
       <c r="BL26" s="20" t="inlineStr">
         <is>
-          <t>29長さ x 21.9幅 x 110.5高さ cm</t>
+          <t>27.5長さ x 27.8幅 x 110.5高さ cm</t>
         </is>
       </c>
       <c r="BM26" s="20"/>
       <c r="BN26" s="20" t="inlineStr">
         <is>
-          <t>6.6 kg</t>
+          <t>13 kg</t>
         </is>
       </c>
       <c r="BO26" s="20" t="inlineStr">
         <is>
-          <t>6.60 kg</t>
+          <t>13.00 kg</t>
         </is>
       </c>
       <c r="BP26" s="20" t="inlineStr">
         <is>
-          <t>69 x 32 x 29 cm</t>
+          <t>75 x 38 x 35 cm</t>
         </is>
       </c>
       <c r="BQ26" s="20" t="inlineStr">
         <is>
-          <t>69.00 x 32.00 x 29.00 cm</t>
+          <t>75.00 x 38.00 x 35.00 cm</t>
         </is>
       </c>
       <c r="BR26" s="11" t="inlineStr">
@@ -12790,40 +12342,40 @@
       <c r="B27" s="11"/>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>B0CZKHJXNG</t>
+          <t>B08XLW562G</t>
         </is>
       </c>
       <c r="D27" s="12"/>
       <c r="E27" s="12"/>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>EUREKA</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/Eureka/page/0DAE79FF-361F-4FFE-9129-4ACEDAF99AD5?lp_asin=B0CZKHJXNG&amp;ref_=ast_bln</t>
+          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=%E4%B8%8D%E6%98%8E</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>EUREKA NEY100 地毯清洁器 400W强力吸力 汽车座椅和布制品清洗 自洁式 地毯和沙发清洗 干湿两用 淋水清洗器 可用热水清洗 附带洗涤剂 三只刷子</t>
+          <t>黑色+Decker 干湿两用锂电池吸尘器 4536178960298</t>
         </is>
       </c>
       <c r="I27" s="12"/>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0CZKHJXNG?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B08XLW562G?psc=1</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41nAma6e0eL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/31NELDCajpL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>B0CZKHJXNG</t>
+          <t>B08XLW562G</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
@@ -12837,13 +12389,13 @@
         </is>
       </c>
       <c r="O27" s="13">
-        <v>74183</v>
+        <v>73669</v>
       </c>
       <c r="P27" s="13">
-        <v>2118</v>
+        <v>-54113</v>
       </c>
       <c r="Q27" s="14">
-        <v>0.03</v>
+        <v>-2.77</v>
       </c>
       <c r="R27" s="15" t="inlineStr">
         <is>
@@ -12852,7 +12404,7 @@
       </c>
       <c r="S27" s="16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>22</t>
         </is>
       </c>
       <c r="T27" s="13">
@@ -12860,38 +12412,46 @@
       </c>
       <c r="U27" s="14"/>
       <c r="V27" s="13">
-        <v>214800</v>
+        <v>135000</v>
       </c>
       <c r="W27" s="13"/>
       <c r="X27" s="13"/>
       <c r="Y27" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z27" s="13">
-        <v>7160</v>
+        <v>4500</v>
       </c>
       <c r="AA27"/>
       <c r="AB27"/>
       <c r="AC27" s="2"/>
       <c r="AD27" s="17">
-        <v>152</v>
+        <v>3</v>
       </c>
       <c r="AE27" s="13">
         <v>0</v>
       </c>
       <c r="AF27" s="18">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="AG27" s="19">
         <v>0</v>
       </c>
-      <c r="AH27" s="13"/>
+      <c r="AH27" s="13">
+        <v>472</v>
+      </c>
       <c r="AI27" s="14">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AJ27"/>
-      <c r="AK27" s="11"/>
-      <c r="AL27" s="17"/>
+      <c r="AK27" s="11" t="inlineStr">
+        <is>
+          <t>2021-06-13</t>
+        </is>
+      </c>
+      <c r="AL27" s="17">
+        <v>1943</v>
+      </c>
       <c r="AM27" s="11" t="inlineStr">
         <is>
           <t>NA</t>
@@ -12901,14 +12461,14 @@
       <c r="AO27" s="11"/>
       <c r="AP27"/>
       <c r="AQ27" s="17">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AR27" s="17">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AS27" s="12" t="inlineStr">
         <is>
-          <t>Eureka Japan</t>
+          <t>Abeショップ関西</t>
         </is>
       </c>
       <c r="AT27" s="11" t="inlineStr">
@@ -12918,17 +12478,17 @@
       </c>
       <c r="AU27" s="11" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="AV27" s="12" t="inlineStr">
         <is>
-          <t>TSIM SHA TSUI 999077 HK</t>
+          <t>初瀬６９３</t>
         </is>
       </c>
       <c r="AW27" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3JXXBYW06ZFVU</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2RYDH17QLIL3V</t>
         </is>
       </c>
       <c r="AX27" s="11"/>
@@ -12936,16 +12496,8 @@
       <c r="AZ27" s="11"/>
       <c r="BA27" s="11"/>
       <c r="BB27" s="11"/>
-      <c r="BC27" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD27" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC27" s="11"/>
+      <c r="BD27" s="11"/>
       <c r="BE27" s="11"/>
       <c r="BF27" s="11"/>
       <c r="BG27" s="11"/>
@@ -12953,25 +12505,49 @@
       <c r="BI27" s="20"/>
       <c r="BJ27" s="20" t="inlineStr">
         <is>
-          <t>5 Kilograms</t>
+          <t>1 Kilograms</t>
         </is>
       </c>
       <c r="BK27" s="20" t="inlineStr">
         <is>
-          <t>5.00 kg</t>
+          <t>1,000.00 g</t>
         </is>
       </c>
       <c r="BL27" s="20" t="inlineStr">
         <is>
-          <t>39奥行き x 30幅 x 20高さ cm</t>
-        </is>
-      </c>
-      <c r="BM27" s="20"/>
-      <c r="BN27" s="20"/>
-      <c r="BO27" s="20"/>
-      <c r="BP27" s="20"/>
-      <c r="BQ27" s="20"/>
-      <c r="BR27" s="11"/>
+          <t>30 x 10 x 10 cm</t>
+        </is>
+      </c>
+      <c r="BM27" s="20" t="inlineStr">
+        <is>
+          <t>30.00 x 10.00 x 10.00 cm</t>
+        </is>
+      </c>
+      <c r="BN27" s="20" t="inlineStr">
+        <is>
+          <t>1 kg</t>
+        </is>
+      </c>
+      <c r="BO27" s="20" t="inlineStr">
+        <is>
+          <t>1,000.00 g</t>
+        </is>
+      </c>
+      <c r="BP27" s="20" t="inlineStr">
+        <is>
+          <t>43.8 x 13.9 x 11.7 cm</t>
+        </is>
+      </c>
+      <c r="BQ27" s="20" t="inlineStr">
+        <is>
+          <t>43.80 x 13.90 x 11.70 cm</t>
+        </is>
+      </c>
+      <c r="BR27" s="11" t="inlineStr">
+        <is>
+          <t>标准</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
@@ -12980,40 +12556,40 @@
       <c r="B28" s="11"/>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>B0HHN61KPZ</t>
+          <t>B0GS4QDH7R</t>
         </is>
       </c>
       <c r="D28" s="12"/>
       <c r="E28" s="12"/>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>Dyson(ダイソン)</t>
+          <t>uwant</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jpnull</t>
+          <t>https://www.amazon.co.jp/stores/%E3%83%A6%E3%83%AF%E3%83%B3%E3%83%88%EF%BC%88UWANT/page/CFD932E4-87F0-4563-8A00-7E6F0611A613?lp_asin=B0GS4QDH7R&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>Dyson(ダイソン) Dyson V12s Detect Slim Submarine 无线棒式吸尘器 戴森官方限定 延长保修1年款</t>
+          <t>uwant 擦水吸尘器 自动清洗 干湿两用吸尘器 热风干燥 电解水除菌 连续工作35分钟 大容量清污分离水箱 水花吸尘器 D100</t>
         </is>
       </c>
       <c r="I28" s="12"/>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0HHN61KPZ?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0GS4QDH7R?psc=1</t>
         </is>
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31eRC+N6IRL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61j3dNdQj4L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L28" s="12" t="inlineStr">
         <is>
-          <t>B0HHN61KPZ</t>
+          <t>B0GS4QDH7R</t>
         </is>
       </c>
       <c r="M28" s="12" t="inlineStr">
@@ -13027,11 +12603,13 @@
         </is>
       </c>
       <c r="O28" s="13">
-        <v>13685</v>
-      </c>
-      <c r="P28" s="13"/>
+        <v>152194</v>
+      </c>
+      <c r="P28" s="13">
+        <v>-13127</v>
+      </c>
       <c r="Q28" s="14">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="R28" s="15" t="inlineStr">
         <is>
@@ -13040,15 +12618,17 @@
       </c>
       <c r="S28" s="16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>42</t>
         </is>
       </c>
       <c r="T28" s="13">
-        <v>3</v>
-      </c>
-      <c r="U28" s="14"/>
+        <v>4</v>
+      </c>
+      <c r="U28" s="14">
+        <v>-0.94</v>
+      </c>
       <c r="V28" s="13">
-        <v>179997</v>
+        <v>46644</v>
       </c>
       <c r="W28" s="13"/>
       <c r="X28" s="13"/>
@@ -13056,96 +12636,142 @@
         <v>1</v>
       </c>
       <c r="Z28" s="13">
-        <v>59999</v>
+        <v>11661</v>
       </c>
       <c r="AA28"/>
       <c r="AB28"/>
       <c r="AC28" s="2"/>
-      <c r="AD28" s="17"/>
-      <c r="AE28" s="13"/>
-      <c r="AF28" s="18"/>
+      <c r="AD28" s="17">
+        <v>15</v>
+      </c>
+      <c r="AE28" s="13">
+        <v>3</v>
+      </c>
+      <c r="AF28" s="18">
+        <v>3.9</v>
+      </c>
       <c r="AG28" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH28" s="13"/>
+        <v>0.75</v>
+      </c>
+      <c r="AH28" s="13">
+        <v>1020</v>
+      </c>
       <c r="AI28" s="14">
-        <v>0.85</v>
+        <v>0.76</v>
       </c>
       <c r="AJ28"/>
       <c r="AK28" s="11" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AL28" s="17">
-        <v>34</v>
+        <v>175</v>
       </c>
       <c r="AM28" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN28" s="11"/>
       <c r="AO28" s="11"/>
       <c r="AP28"/>
-      <c r="AQ28" s="17"/>
+      <c r="AQ28" s="17">
+        <v>5</v>
+      </c>
       <c r="AR28" s="17">
         <v>1</v>
       </c>
       <c r="AS28" s="12" t="inlineStr">
         <is>
-          <t>ダイソン公式ストア</t>
+          <t>Uwant公式ストア</t>
         </is>
       </c>
       <c r="AT28" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU28" s="11" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV28" s="12" t="inlineStr">
         <is>
-          <t>千代田区麹町 東京都 1020083 JP</t>
+          <t>深圳市 广东省 518000 CN</t>
         </is>
       </c>
       <c r="AW28" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KRDRXNL1G5FA</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1O5QS9O13RS09</t>
         </is>
       </c>
       <c r="AX28" s="11"/>
-      <c r="AY28" s="11"/>
+      <c r="AY28" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ28" s="11"/>
       <c r="BA28" s="11"/>
       <c r="BB28" s="11"/>
       <c r="BC28" s="11"/>
-      <c r="BD28" s="11"/>
+      <c r="BD28" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE28" s="11"/>
       <c r="BF28" s="11"/>
       <c r="BG28" s="11"/>
       <c r="BH28" s="12"/>
-      <c r="BI28" s="20"/>
+      <c r="BI28" s="20" t="inlineStr">
+        <is>
+          <t>Amazon おすすめ</t>
+        </is>
+      </c>
       <c r="BJ28" s="20" t="inlineStr">
         <is>
-          <t>3.2 キログラム</t>
-        </is>
-      </c>
-      <c r="BK28" s="20"/>
+          <t>4.29 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK28" s="20" t="inlineStr">
+        <is>
+          <t>4.29 kg</t>
+        </is>
+      </c>
       <c r="BL28" s="20" t="inlineStr">
         <is>
-          <t>25.7長さ x 25.3幅 x 112.9高さ cm</t>
+          <t>26.5長さ x 23.5幅 x 111.5高さ cm</t>
         </is>
       </c>
       <c r="BM28" s="20"/>
-      <c r="BN28" s="20"/>
-      <c r="BO28" s="20"/>
-      <c r="BP28" s="20"/>
-      <c r="BQ28" s="20"/>
-      <c r="BR28" s="11"/>
+      <c r="BN28" s="20" t="inlineStr">
+        <is>
+          <t>4.29 kg</t>
+        </is>
+      </c>
+      <c r="BO28" s="20" t="inlineStr">
+        <is>
+          <t>4.29 kg</t>
+        </is>
+      </c>
+      <c r="BP28" s="20" t="inlineStr">
+        <is>
+          <t>72.5 x 31.2 x 29.1 cm</t>
+        </is>
+      </c>
+      <c r="BQ28" s="20" t="inlineStr">
+        <is>
+          <t>72.50 x 31.20 x 29.10 cm</t>
+        </is>
+      </c>
+      <c r="BR28" s="11" t="inlineStr">
+        <is>
+          <t>大件</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
@@ -13154,7 +12780,7 @@
       <c r="B29" s="11"/>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>B0CNJT8933</t>
+          <t>B0H6DZMNPV</t>
         </is>
       </c>
       <c r="D29" s="12"/>
@@ -13166,28 +12792,28 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0CNJT8933&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0H6DZMNPV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>dreame (ドリーミー) H12 Dual 水拭き掃除機【4wayコードレス水拭き掃除機】 自动清洗和温风干燥 双向旋转式清洗 可达墙角的刷子设计 16000Pa强力吸力 电解水除菌 35分钟连续运行 智能污垢检测和自动吸力调节 语音引导 大容量</t>
+          <t>dreame T16 擦水吸尘器&amp;旋转刷套装</t>
         </is>
       </c>
       <c r="I29" s="12"/>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0CNJT8933?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0H6DZMNPV?psc=1</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61b-HbgIkBL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31ddgJIAJbL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>B0CNJT8933</t>
+          <t>B0H6DZMNPV</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr">
@@ -13201,13 +12827,13 @@
         </is>
       </c>
       <c r="O29" s="13">
-        <v>133273</v>
+        <v>32651</v>
       </c>
       <c r="P29" s="13">
-        <v>2289</v>
+        <v>540152</v>
       </c>
       <c r="Q29" s="14">
-        <v>0.02</v>
+        <v>0.89</v>
       </c>
       <c r="R29" s="15" t="inlineStr">
         <is>
@@ -13216,17 +12842,15 @@
       </c>
       <c r="S29" s="16" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>13</t>
         </is>
       </c>
       <c r="T29" s="13">
-        <v>4</v>
-      </c>
-      <c r="U29" s="14">
-        <v>0.06</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U29" s="14"/>
       <c r="V29" s="13">
-        <v>171600</v>
+        <v>41862</v>
       </c>
       <c r="W29" s="13"/>
       <c r="X29" s="13"/>
@@ -13234,48 +12858,40 @@
         <v>1</v>
       </c>
       <c r="Z29" s="13">
-        <v>42900</v>
+        <v>41862</v>
       </c>
       <c r="AA29"/>
       <c r="AB29"/>
       <c r="AC29" s="2"/>
-      <c r="AD29" s="17">
-        <v>45</v>
-      </c>
-      <c r="AE29" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="18">
-        <v>3.8</v>
-      </c>
+      <c r="AD29" s="17"/>
+      <c r="AE29" s="13"/>
+      <c r="AF29" s="18"/>
       <c r="AG29" s="19">
         <v>0</v>
       </c>
-      <c r="AH29" s="13">
-        <v>1100</v>
-      </c>
+      <c r="AH29" s="13"/>
       <c r="AI29" s="14">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="AJ29"/>
       <c r="AK29" s="11" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AL29" s="17">
-        <v>1053</v>
+        <v>106</v>
       </c>
       <c r="AM29" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN29" s="11"/>
       <c r="AO29" s="11"/>
       <c r="AP29"/>
       <c r="AQ29" s="17">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AR29" s="17">
         <v>1</v>
@@ -13287,7 +12903,7 @@
       </c>
       <c r="AT29" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU29" s="11" t="inlineStr">
@@ -13310,62 +12926,22 @@
       <c r="AZ29" s="11"/>
       <c r="BA29" s="11"/>
       <c r="BB29" s="11"/>
-      <c r="BC29" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD29" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC29" s="11"/>
+      <c r="BD29" s="11"/>
       <c r="BE29" s="11"/>
       <c r="BF29" s="11"/>
       <c r="BG29" s="11"/>
       <c r="BH29" s="12"/>
       <c r="BI29" s="20"/>
-      <c r="BJ29" s="20" t="inlineStr">
-        <is>
-          <t>5.13 kg</t>
-        </is>
-      </c>
-      <c r="BK29" s="20" t="inlineStr">
-        <is>
-          <t>5.13 kg</t>
-        </is>
-      </c>
-      <c r="BL29" s="20" t="inlineStr">
-        <is>
-          <t>27.5長さ x 27.8幅 x 110.5高さ cm</t>
-        </is>
-      </c>
+      <c r="BJ29" s="20"/>
+      <c r="BK29" s="20"/>
+      <c r="BL29" s="20"/>
       <c r="BM29" s="20"/>
-      <c r="BN29" s="20" t="inlineStr">
-        <is>
-          <t>13 kg</t>
-        </is>
-      </c>
-      <c r="BO29" s="20" t="inlineStr">
-        <is>
-          <t>13.00 kg</t>
-        </is>
-      </c>
-      <c r="BP29" s="20" t="inlineStr">
-        <is>
-          <t>75 x 38 x 35 cm</t>
-        </is>
-      </c>
-      <c r="BQ29" s="20" t="inlineStr">
-        <is>
-          <t>75.00 x 38.00 x 35.00 cm</t>
-        </is>
-      </c>
-      <c r="BR29" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
+      <c r="BN29" s="20"/>
+      <c r="BO29" s="20"/>
+      <c r="BP29" s="20"/>
+      <c r="BQ29" s="20"/>
+      <c r="BR29" s="11"/>
     </row>
     <row r="30" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
@@ -13374,155 +12950,83 @@
       <c r="B30" s="11"/>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>B08XLW562G</t>
+          <t>B09P2RKRWX</t>
         </is>
       </c>
       <c r="D30" s="12"/>
       <c r="E30" s="12"/>
-      <c r="F30" s="12" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
+      <c r="F30" s="12"/>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=%E4%B8%8D%E6%98%8E</t>
+          <t>https://www.amazon.co.jpundefined</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>黑色+Decker 干湿两用锂电池吸尘器 4536178960298</t>
+          <t>Tineco Floor One S5 Plus 无线擦水吸尘器 干湿两用siLoop 智能传感器检测污垢,吸力强,自动清洁干燥,长时间运行,大容量水箱,2 年保修</t>
         </is>
       </c>
       <c r="I30" s="12"/>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B08XLW562G?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B09P2RKRWX?psc=1</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/31NELDCajpL._AC_US600_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/615lYQCrd2L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L30" s="12" t="inlineStr">
         <is>
-          <t>B08XLW562G</t>
-        </is>
-      </c>
-      <c r="M30" s="12" t="inlineStr">
-        <is>
-          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
-        </is>
-      </c>
-      <c r="N30" s="12" t="inlineStr">
-        <is>
-          <t>DIY・工具・ガーデン</t>
-        </is>
-      </c>
-      <c r="O30" s="13">
-        <v>73669</v>
-      </c>
-      <c r="P30" s="13">
-        <v>-54113</v>
-      </c>
-      <c r="Q30" s="14">
-        <v>-2.77</v>
-      </c>
-      <c r="R30" s="15" t="inlineStr">
-        <is>
-          <t>ウェットドライショップ掃除機</t>
-        </is>
-      </c>
-      <c r="S30" s="16" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="T30" s="13">
-        <v>30</v>
-      </c>
+          <t>B09P2RKRWX</t>
+        </is>
+      </c>
+      <c r="M30" s="12"/>
+      <c r="N30" s="12"/>
+      <c r="O30" s="13"/>
+      <c r="P30" s="13"/>
+      <c r="Q30" s="14"/>
+      <c r="R30" s="15"/>
+      <c r="S30" s="16"/>
+      <c r="T30" s="13"/>
       <c r="U30" s="14"/>
-      <c r="V30" s="13">
-        <v>135000</v>
-      </c>
+      <c r="V30" s="13"/>
       <c r="W30" s="13"/>
       <c r="X30" s="13"/>
-      <c r="Y30" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z30" s="13">
-        <v>4500</v>
-      </c>
+      <c r="Y30" s="17"/>
+      <c r="Z30" s="13"/>
       <c r="AA30"/>
       <c r="AB30"/>
       <c r="AC30" s="2"/>
       <c r="AD30" s="17">
-        <v>3</v>
-      </c>
-      <c r="AE30" s="13">
-        <v>0</v>
-      </c>
+        <v>3903</v>
+      </c>
+      <c r="AE30" s="13"/>
       <c r="AF30" s="18">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="AG30" s="19">
         <v>0</v>
       </c>
-      <c r="AH30" s="13">
-        <v>472</v>
-      </c>
+      <c r="AH30" s="13"/>
       <c r="AI30" s="14">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AJ30"/>
-      <c r="AK30" s="11" t="inlineStr">
-        <is>
-          <t>2021-06-13</t>
-        </is>
-      </c>
-      <c r="AL30" s="17">
-        <v>1943</v>
-      </c>
-      <c r="AM30" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="AK30" s="11"/>
+      <c r="AL30" s="17"/>
+      <c r="AM30" s="11"/>
       <c r="AN30" s="11"/>
       <c r="AO30" s="11"/>
       <c r="AP30"/>
-      <c r="AQ30" s="17">
-        <v>3</v>
-      </c>
-      <c r="AR30" s="17">
-        <v>8</v>
-      </c>
-      <c r="AS30" s="12" t="inlineStr">
-        <is>
-          <t>Abeショップ関西</t>
-        </is>
-      </c>
-      <c r="AT30" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU30" s="11" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="AV30" s="12" t="inlineStr">
-        <is>
-          <t>初瀬６９３</t>
-        </is>
-      </c>
-      <c r="AW30" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2RYDH17QLIL3V</t>
-        </is>
-      </c>
+      <c r="AQ30" s="17"/>
+      <c r="AR30" s="17"/>
+      <c r="AS30" s="12"/>
+      <c r="AT30" s="11"/>
+      <c r="AU30" s="11"/>
+      <c r="AV30" s="12"/>
+      <c r="AW30" s="11"/>
       <c r="AX30" s="11"/>
       <c r="AY30" s="11"/>
       <c r="AZ30" s="11"/>
@@ -13535,51 +13039,15 @@
       <c r="BG30" s="11"/>
       <c r="BH30" s="12"/>
       <c r="BI30" s="20"/>
-      <c r="BJ30" s="20" t="inlineStr">
-        <is>
-          <t>1 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK30" s="20" t="inlineStr">
-        <is>
-          <t>1,000.00 g</t>
-        </is>
-      </c>
-      <c r="BL30" s="20" t="inlineStr">
-        <is>
-          <t>30 x 10 x 10 cm</t>
-        </is>
-      </c>
-      <c r="BM30" s="20" t="inlineStr">
-        <is>
-          <t>30.00 x 10.00 x 10.00 cm</t>
-        </is>
-      </c>
-      <c r="BN30" s="20" t="inlineStr">
-        <is>
-          <t>1 kg</t>
-        </is>
-      </c>
-      <c r="BO30" s="20" t="inlineStr">
-        <is>
-          <t>1,000.00 g</t>
-        </is>
-      </c>
-      <c r="BP30" s="20" t="inlineStr">
-        <is>
-          <t>43.8 x 13.9 x 11.7 cm</t>
-        </is>
-      </c>
-      <c r="BQ30" s="20" t="inlineStr">
-        <is>
-          <t>43.80 x 13.90 x 11.70 cm</t>
-        </is>
-      </c>
-      <c r="BR30" s="11" t="inlineStr">
-        <is>
-          <t>标准</t>
-        </is>
-      </c>
+      <c r="BJ30" s="20"/>
+      <c r="BK30" s="20"/>
+      <c r="BL30" s="20"/>
+      <c r="BM30" s="20"/>
+      <c r="BN30" s="20"/>
+      <c r="BO30" s="20"/>
+      <c r="BP30" s="20"/>
+      <c r="BQ30" s="20"/>
+      <c r="BR30" s="11"/>
     </row>
     <row r="31" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
@@ -13588,40 +13056,40 @@
       <c r="B31" s="11"/>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>B0GS4QDH7R</t>
+          <t>B0C4HGZ1L6</t>
         </is>
       </c>
       <c r="D31" s="12"/>
       <c r="E31" s="12"/>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>uwant</t>
+          <t>NEODIT</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%83%A6%E3%83%AF%E3%83%B3%E3%83%88%EF%BC%88UWANT/page/CFD932E4-87F0-4563-8A00-7E6F0611A613?lp_asin=B0GS4QDH7R&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/NEODIT%E3%83%8D%E3%82%AA%E3%83%87%E3%82%A3%E3%83%83%E3%83%88/page/CD7250ED-8E04-4E58-A881-68B2A928AE8C?lp_asin=B0C4HGZ1L6&amp;ref_=ast_bln</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>uwant 擦水吸尘器 自动清洗 干湿两用吸尘器 热风干燥 电解水除菌 连续工作35分钟 大容量清污分离水箱 水花吸尘器 D100</t>
+          <t>NEODIT 地毯清洁剂 14000Pa强力吸力 淋水机清洗机 可温水40度清洗 地毯清洗机 去污 干湿两用吸尘器 沙发清洁剂 地毯清洁剂 水洗 车用吸尘器 浴室清洁器 地毯/布制品/宠物坐垫/车内/地毯/沙发/地毯/毛绒玩具/清扫用品</t>
         </is>
       </c>
       <c r="I31" s="12"/>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0GS4QDH7R?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0C4HGZ1L6?psc=1</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61j3dNdQj4L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81DHFglSw9L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>B0GS4QDH7R</t>
+          <t>B0C4HGZ1L6</t>
         </is>
       </c>
       <c r="M31" s="12" t="inlineStr">
@@ -13635,13 +13103,13 @@
         </is>
       </c>
       <c r="O31" s="13">
-        <v>152194</v>
+        <v>169234</v>
       </c>
       <c r="P31" s="13">
-        <v>-13127</v>
+        <v>-1650</v>
       </c>
       <c r="Q31" s="14">
-        <v>-0.09</v>
+        <v>-0.01</v>
       </c>
       <c r="R31" s="15" t="inlineStr">
         <is>
@@ -13650,55 +13118,49 @@
       </c>
       <c r="S31" s="16" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="T31" s="13">
-        <v>4</v>
-      </c>
-      <c r="U31" s="14">
-        <v>-0.94</v>
-      </c>
-      <c r="V31" s="13">
-        <v>46644</v>
-      </c>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="T31" s="13"/>
+      <c r="U31" s="14"/>
+      <c r="V31" s="13"/>
       <c r="W31" s="13"/>
       <c r="X31" s="13"/>
       <c r="Y31" s="17">
         <v>1</v>
       </c>
       <c r="Z31" s="13">
-        <v>11661</v>
+        <v>13998</v>
       </c>
       <c r="AA31"/>
       <c r="AB31"/>
       <c r="AC31" s="2"/>
       <c r="AD31" s="17">
-        <v>15</v>
+        <v>322</v>
       </c>
       <c r="AE31" s="13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF31" s="18">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AG31" s="19">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AH31" s="13">
-        <v>1020</v>
+        <v>781</v>
       </c>
       <c r="AI31" s="14">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="AJ31"/>
       <c r="AK31" s="11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="AL31" s="17">
-        <v>175</v>
+        <v>1197</v>
       </c>
       <c r="AM31" s="11" t="inlineStr">
         <is>
@@ -13709,14 +13171,14 @@
       <c r="AO31" s="11"/>
       <c r="AP31"/>
       <c r="AQ31" s="17">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AR31" s="17">
         <v>1</v>
       </c>
       <c r="AS31" s="12" t="inlineStr">
         <is>
-          <t>Uwant公式ストア</t>
+          <t>Neodit-tools</t>
         </is>
       </c>
       <c r="AT31" s="11" t="inlineStr">
@@ -13731,24 +13193,24 @@
       </c>
       <c r="AV31" s="12" t="inlineStr">
         <is>
-          <t>深圳市 广东省 518000 CN</t>
+          <t>nanjingshi jiangsusheng 210043 CN</t>
         </is>
       </c>
       <c r="AW31" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1O5QS9O13RS09</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2YB9P0HYGN84U</t>
         </is>
       </c>
       <c r="AX31" s="11"/>
-      <c r="AY31" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY31" s="11"/>
       <c r="AZ31" s="11"/>
       <c r="BA31" s="11"/>
       <c r="BB31" s="11"/>
-      <c r="BC31" s="11"/>
+      <c r="BC31" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD31" s="11" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13758,45 +13220,45 @@
       <c r="BF31" s="11"/>
       <c r="BG31" s="11"/>
       <c r="BH31" s="12"/>
-      <c r="BI31" s="20" t="inlineStr">
-        <is>
-          <t>Amazon おすすめ</t>
-        </is>
-      </c>
+      <c r="BI31" s="20"/>
       <c r="BJ31" s="20" t="inlineStr">
         <is>
-          <t>4.29 Kilograms</t>
+          <t>5.24 Kilograms</t>
         </is>
       </c>
       <c r="BK31" s="20" t="inlineStr">
         <is>
-          <t>4.29 kg</t>
+          <t>5.24 kg</t>
         </is>
       </c>
       <c r="BL31" s="20" t="inlineStr">
         <is>
-          <t>26.5長さ x 23.5幅 x 111.5高さ cm</t>
-        </is>
-      </c>
-      <c r="BM31" s="20"/>
+          <t>18 x 35 x 29 cm</t>
+        </is>
+      </c>
+      <c r="BM31" s="20" t="inlineStr">
+        <is>
+          <t>18.00 x 35.00 x 29.00 cm</t>
+        </is>
+      </c>
       <c r="BN31" s="20" t="inlineStr">
         <is>
-          <t>4.29 kg</t>
+          <t>5.24 kg</t>
         </is>
       </c>
       <c r="BO31" s="20" t="inlineStr">
         <is>
-          <t>4.29 kg</t>
+          <t>5.24 kg</t>
         </is>
       </c>
       <c r="BP31" s="20" t="inlineStr">
         <is>
-          <t>72.5 x 31.2 x 29.1 cm</t>
+          <t>37.9 x 36.9 x 26.2 cm</t>
         </is>
       </c>
       <c r="BQ31" s="20" t="inlineStr">
         <is>
-          <t>72.50 x 31.20 x 29.10 cm</t>
+          <t>37.90 x 36.90 x 26.20 cm</t>
         </is>
       </c>
       <c r="BR31" s="11" t="inlineStr">
@@ -13812,147 +13274,83 @@
       <c r="B32" s="11"/>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>B0H6DZMNPV</t>
+          <t>B0CF9P7W51</t>
         </is>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="12"/>
-      <c r="F32" s="12" t="inlineStr">
-        <is>
-          <t>dreame</t>
-        </is>
-      </c>
+      <c r="F32" s="12"/>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0H6DZMNPV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jpundefined</t>
         </is>
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>dreame T16 擦水吸尘器&amp;旋转刷套装</t>
+          <t>Tineco Floor One S7 Lite 擦水吸尘器 无线/干湿两用/强力吸力/轻量化/长时间驾驶/静音 自洁式 自走式 iLoop 智能传感器 应用操作 语音指南 制造商2年保修</t>
         </is>
       </c>
       <c r="I32" s="12"/>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0H6DZMNPV?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0CF9P7W51?psc=1</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31ddgJIAJbL._AC_US600_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61bJ0J+PfIL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L32" s="12" t="inlineStr">
         <is>
-          <t>B0H6DZMNPV</t>
-        </is>
-      </c>
-      <c r="M32" s="12" t="inlineStr">
-        <is>
-          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
-        </is>
-      </c>
-      <c r="N32" s="12" t="inlineStr">
-        <is>
-          <t>DIY・工具・ガーデン</t>
-        </is>
-      </c>
-      <c r="O32" s="13">
-        <v>32651</v>
-      </c>
-      <c r="P32" s="13">
-        <v>540152</v>
-      </c>
-      <c r="Q32" s="14">
-        <v>0.89</v>
-      </c>
-      <c r="R32" s="15" t="inlineStr">
-        <is>
-          <t>ウェットドライショップ掃除機</t>
-        </is>
-      </c>
-      <c r="S32" s="16" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="T32" s="13">
-        <v>1</v>
-      </c>
+          <t>B0CF9P7W51</t>
+        </is>
+      </c>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="13"/>
+      <c r="P32" s="13"/>
+      <c r="Q32" s="14"/>
+      <c r="R32" s="15"/>
+      <c r="S32" s="16"/>
+      <c r="T32" s="13"/>
       <c r="U32" s="14"/>
-      <c r="V32" s="13">
-        <v>41862</v>
-      </c>
+      <c r="V32" s="13"/>
       <c r="W32" s="13"/>
       <c r="X32" s="13"/>
-      <c r="Y32" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z32" s="13">
-        <v>41862</v>
-      </c>
+      <c r="Y32" s="17"/>
+      <c r="Z32" s="13"/>
       <c r="AA32"/>
       <c r="AB32"/>
       <c r="AC32" s="2"/>
-      <c r="AD32" s="17"/>
+      <c r="AD32" s="17">
+        <v>23</v>
+      </c>
       <c r="AE32" s="13"/>
-      <c r="AF32" s="18"/>
+      <c r="AF32" s="18">
+        <v>4.1</v>
+      </c>
       <c r="AG32" s="19">
         <v>0</v>
       </c>
       <c r="AH32" s="13"/>
       <c r="AI32" s="14">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="AJ32"/>
-      <c r="AK32" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="AL32" s="17">
-        <v>106</v>
-      </c>
-      <c r="AM32" s="11" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
+      <c r="AK32" s="11"/>
+      <c r="AL32" s="17"/>
+      <c r="AM32" s="11"/>
       <c r="AN32" s="11"/>
       <c r="AO32" s="11"/>
       <c r="AP32"/>
-      <c r="AQ32" s="17">
-        <v>5</v>
-      </c>
-      <c r="AR32" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS32" s="12" t="inlineStr">
-        <is>
-          <t>Dreame公式ストア</t>
-        </is>
-      </c>
-      <c r="AT32" s="11" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU32" s="11" t="inlineStr">
-        <is>
-          <t>CN(HK)</t>
-        </is>
-      </c>
-      <c r="AV32" s="12" t="inlineStr">
-        <is>
-          <t>ROOM H28G BLK EH 10TH FLOOR GOLDEN BEAR IND CTR 66-82</t>
-        </is>
-      </c>
-      <c r="AW32" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WV0MTJICL1UJ</t>
-        </is>
-      </c>
+      <c r="AQ32" s="17"/>
+      <c r="AR32" s="17"/>
+      <c r="AS32" s="12"/>
+      <c r="AT32" s="11"/>
+      <c r="AU32" s="11"/>
+      <c r="AV32" s="12"/>
+      <c r="AW32" s="11"/>
       <c r="AX32" s="11"/>
       <c r="AY32" s="11"/>
       <c r="AZ32" s="11"/>
@@ -13982,7 +13380,7 @@
       <c r="B33" s="11"/>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>B01IEEM1KU</t>
+          <t>B0D5HBSJFX</t>
         </is>
       </c>
       <c r="D33" s="12"/>
@@ -13995,23 +13393,23 @@
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>日動 業務用バキュームクリーナー２０Ｌ 09446 NVC-20L-S</t>
+          <t>dreame (ドリーミー) H12S 湿拖吸尘器 吸尘&amp;湿拖2in1 刷头自动清洗和温风干燥 除菌 贴墙边刷头设计 16000Pa强力吸力 35分钟连续运行 智能污垢检测和自动吸力调整 大容量水箱 语音导航 高速电机 静音设计 3种运行模式 专用清</t>
         </is>
       </c>
       <c r="I33" s="12"/>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B01IEEM1KU?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0D5HBSJFX?psc=1</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/413OXJC5WwL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/51ioK4Vk3NL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>B01IEEM1KU</t>
+          <t>B0D5HBSJFX</t>
         </is>
       </c>
       <c r="M33" s="12"/>
@@ -14032,7 +13430,7 @@
       <c r="AB33"/>
       <c r="AC33" s="2"/>
       <c r="AD33" s="17">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="AE33" s="13"/>
       <c r="AF33" s="18">
@@ -14088,7 +13486,7 @@
       <c r="B34" s="11"/>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>B09P2RKRWX</t>
+          <t>B0DHV7QRSK</t>
         </is>
       </c>
       <c r="D34" s="12"/>
@@ -14101,23 +13499,23 @@
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>Tineco Floor One S5 Plus 无线擦水吸尘器 干湿两用siLoop 智能传感器检测污垢,吸力强,自动清洁干燥,长时间运行,大容量水箱,2 年保修</t>
+          <t>Vittorio(ヴィットリオ) 乾湿両用掃除機 WET&amp;DRYクリーナー ZV-04-WDs【吸込仕事率65W 集塵約3.0L/吸水約1.5L】 小型コンパクトモデル(33×31×23cm) 本体重量2.5Kg 玄関 ベランダ掃除 作業現場の簡</t>
         </is>
       </c>
       <c r="I34" s="12"/>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B09P2RKRWX?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0DHV7QRSK?psc=1</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/615lYQCrd2L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61Coq6GGchL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L34" s="12" t="inlineStr">
         <is>
-          <t>B09P2RKRWX</t>
+          <t>B0DHV7QRSK</t>
         </is>
       </c>
       <c r="M34" s="12"/>
@@ -14133,16 +13531,18 @@
       <c r="W34" s="13"/>
       <c r="X34" s="13"/>
       <c r="Y34" s="17"/>
-      <c r="Z34" s="13"/>
+      <c r="Z34" s="13">
+        <v>46</v>
+      </c>
       <c r="AA34"/>
       <c r="AB34"/>
       <c r="AC34" s="2"/>
       <c r="AD34" s="17">
-        <v>3903</v>
+        <v>30</v>
       </c>
       <c r="AE34" s="13"/>
       <c r="AF34" s="18">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AG34" s="19">
         <v>0</v>
@@ -14194,216 +13594,104 @@
       <c r="B35" s="11"/>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>B0C4HGZ1L6</t>
+          <t>B0DXY4BJ5K</t>
         </is>
       </c>
       <c r="D35" s="12"/>
       <c r="E35" s="12"/>
-      <c r="F35" s="12" t="inlineStr">
-        <is>
-          <t>NEODIT</t>
-        </is>
-      </c>
+      <c r="F35" s="12"/>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/NEODIT%E3%83%8D%E3%82%AA%E3%83%87%E3%82%A3%E3%83%83%E3%83%88/page/CD7250ED-8E04-4E58-A881-68B2A928AE8C?lp_asin=B0C4HGZ1L6&amp;ref_=ast_bln</t>
+          <t>https://www.amazon.co.jpundefined</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>NEODIT 地毯清洁剂 14000Pa强力吸力 淋水机清洗机 可温水40度清洗 地毯清洗机 去污 干湿两用吸尘器 沙发清洁剂 地毯清洁剂 水洗 车用吸尘器 浴室清洁器 地毯/布制品/宠物坐垫/车内/地毯/沙发/地毯/毛绒玩具/清扫用品</t>
+          <t>Narwal (ナーワル) S20 Pro コードレス水拭き掃除機 20,000Pa強力吸引 自動洗浄s家電批評ベストバイ, 自走式,モップ自動洗浄機能付き,乾湿両用 家具の下も清掃可能 フローリング、タイル、石床専用 絡まりゼロブラシ搭載 子ど</t>
         </is>
       </c>
       <c r="I35" s="12"/>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0C4HGZ1L6?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0DXY4BJ5K?psc=1</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81DHFglSw9L._AC_US600_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/516bWwYYlQL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
-          <t>B0C4HGZ1L6</t>
-        </is>
-      </c>
-      <c r="M35" s="12" t="inlineStr">
-        <is>
-          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
-        </is>
-      </c>
-      <c r="N35" s="12" t="inlineStr">
-        <is>
-          <t>DIY・工具・ガーデン</t>
-        </is>
-      </c>
-      <c r="O35" s="13">
-        <v>169234</v>
-      </c>
-      <c r="P35" s="13">
-        <v>-1650</v>
-      </c>
-      <c r="Q35" s="14">
-        <v>-0.01</v>
-      </c>
-      <c r="R35" s="15" t="inlineStr">
-        <is>
-          <t>ウェットドライショップ掃除機</t>
-        </is>
-      </c>
-      <c r="S35" s="16" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
+          <t>B0DXY4BJ5K</t>
+        </is>
+      </c>
+      <c r="M35" s="12"/>
+      <c r="N35" s="12"/>
+      <c r="O35" s="13"/>
+      <c r="P35" s="13"/>
+      <c r="Q35" s="14"/>
+      <c r="R35" s="15"/>
+      <c r="S35" s="16"/>
       <c r="T35" s="13"/>
       <c r="U35" s="14"/>
       <c r="V35" s="13"/>
       <c r="W35" s="13"/>
       <c r="X35" s="13"/>
-      <c r="Y35" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z35" s="13">
-        <v>13998</v>
-      </c>
+      <c r="Y35" s="17"/>
+      <c r="Z35" s="13"/>
       <c r="AA35"/>
       <c r="AB35"/>
       <c r="AC35" s="2"/>
       <c r="AD35" s="17">
-        <v>322</v>
-      </c>
-      <c r="AE35" s="13">
-        <v>0</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="AE35" s="13"/>
       <c r="AF35" s="18">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AG35" s="19">
         <v>0</v>
       </c>
-      <c r="AH35" s="13">
-        <v>781</v>
-      </c>
+      <c r="AH35" s="13"/>
       <c r="AI35" s="14">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="AJ35"/>
-      <c r="AK35" s="11" t="inlineStr">
-        <is>
-          <t>2023-06-29</t>
-        </is>
-      </c>
-      <c r="AL35" s="17">
-        <v>1197</v>
-      </c>
-      <c r="AM35" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="AK35" s="11"/>
+      <c r="AL35" s="17"/>
+      <c r="AM35" s="11"/>
       <c r="AN35" s="11"/>
       <c r="AO35" s="11"/>
       <c r="AP35"/>
-      <c r="AQ35" s="17">
-        <v>10</v>
-      </c>
-      <c r="AR35" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS35" s="12" t="inlineStr">
-        <is>
-          <t>Neodit-tools</t>
-        </is>
-      </c>
-      <c r="AT35" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU35" s="11" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV35" s="12" t="inlineStr">
-        <is>
-          <t>nanjingshi jiangsusheng 210043 CN</t>
-        </is>
-      </c>
-      <c r="AW35" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2YB9P0HYGN84U</t>
-        </is>
-      </c>
+      <c r="AQ35" s="17"/>
+      <c r="AR35" s="17"/>
+      <c r="AS35" s="12"/>
+      <c r="AT35" s="11"/>
+      <c r="AU35" s="11"/>
+      <c r="AV35" s="12"/>
+      <c r="AW35" s="11"/>
       <c r="AX35" s="11"/>
       <c r="AY35" s="11"/>
       <c r="AZ35" s="11"/>
       <c r="BA35" s="11"/>
       <c r="BB35" s="11"/>
-      <c r="BC35" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD35" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC35" s="11"/>
+      <c r="BD35" s="11"/>
       <c r="BE35" s="11"/>
       <c r="BF35" s="11"/>
       <c r="BG35" s="11"/>
       <c r="BH35" s="12"/>
       <c r="BI35" s="20"/>
-      <c r="BJ35" s="20" t="inlineStr">
-        <is>
-          <t>5.24 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK35" s="20" t="inlineStr">
-        <is>
-          <t>5.24 kg</t>
-        </is>
-      </c>
-      <c r="BL35" s="20" t="inlineStr">
-        <is>
-          <t>18 x 35 x 29 cm</t>
-        </is>
-      </c>
-      <c r="BM35" s="20" t="inlineStr">
-        <is>
-          <t>18.00 x 35.00 x 29.00 cm</t>
-        </is>
-      </c>
-      <c r="BN35" s="20" t="inlineStr">
-        <is>
-          <t>5.24 kg</t>
-        </is>
-      </c>
-      <c r="BO35" s="20" t="inlineStr">
-        <is>
-          <t>5.24 kg</t>
-        </is>
-      </c>
-      <c r="BP35" s="20" t="inlineStr">
-        <is>
-          <t>37.9 x 36.9 x 26.2 cm</t>
-        </is>
-      </c>
-      <c r="BQ35" s="20" t="inlineStr">
-        <is>
-          <t>37.90 x 36.90 x 26.20 cm</t>
-        </is>
-      </c>
-      <c r="BR35" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
+      <c r="BJ35" s="20"/>
+      <c r="BK35" s="20"/>
+      <c r="BL35" s="20"/>
+      <c r="BM35" s="20"/>
+      <c r="BN35" s="20"/>
+      <c r="BO35" s="20"/>
+      <c r="BP35" s="20"/>
+      <c r="BQ35" s="20"/>
+      <c r="BR35" s="11"/>
     </row>
     <row r="36" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
@@ -14412,7 +13700,7 @@
       <c r="B36" s="11"/>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>B0CF9P7W51</t>
+          <t>B0FBR52FBV</t>
         </is>
       </c>
       <c r="D36" s="12"/>
@@ -14425,23 +13713,23 @@
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>Tineco Floor One S7 Lite 擦水吸尘器 无线/干湿两用/强力吸力/轻量化/长时间驾驶/静音 自洁式 自走式 iLoop 智能传感器 应用操作 语音指南 制造商2年保修</t>
+          <t>dreame (Dream) G10 干湿两用 擦水吸尘器 7000Pa吸力 暖风干燥 自动清洗 30分钟长时间运行 LED显示屏s地板擦拭 带拖把功能 擦拭 两用 无线棒 吸尘器 轻量级吸尘器</t>
         </is>
       </c>
       <c r="I36" s="12"/>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0CF9P7W51?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FBR52FBV?psc=1</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61bJ0J+PfIL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/51Gx-JJE9mL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L36" s="12" t="inlineStr">
         <is>
-          <t>B0CF9P7W51</t>
+          <t>B0FBR52FBV</t>
         </is>
       </c>
       <c r="M36" s="12"/>
@@ -14462,11 +13750,11 @@
       <c r="AB36"/>
       <c r="AC36" s="2"/>
       <c r="AD36" s="17">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="AE36" s="13"/>
       <c r="AF36" s="18">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="AG36" s="19">
         <v>0</v>
@@ -14518,104 +13806,208 @@
       <c r="B37" s="11"/>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>B0D5HBSJFX</t>
+          <t>B0FGC7422M</t>
         </is>
       </c>
       <c r="D37" s="12"/>
       <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>JONR</t>
+        </is>
+      </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jpundefined</t>
+          <t>https://www.amazon.co.jp/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FGC7422M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>dreame (ドリーミー) H12S 湿拖吸尘器 吸尘&amp;湿拖2in1 刷头自动清洗和温风干燥 除菌 贴墙边刷头设计 16000Pa强力吸力 35分钟连续运行 智能污垢检测和自动吸力调整 大容量水箱 语音导航 高速电机 静音设计 3种运行模式 专用清</t>
+          <t>擦水吸尘器 吸水&amp;擦拭2合1无绳棒吸尘器 干湿两用 滚轮刷自动清洗&amp;干燥 150°睡眠结构 墙时1mm清扫 20000Pa强力吸力 长时间运行大容量清水&amp;污水桶 独自生活 家庭用 日语使用说明书 PSE认证</t>
         </is>
       </c>
       <c r="I37" s="12"/>
       <c r="J37" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0D5HBSJFX?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FGC7422M?psc=1</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/51ioK4Vk3NL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51PDVCpecuL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
-          <t>B0D5HBSJFX</t>
-        </is>
-      </c>
-      <c r="M37" s="12"/>
-      <c r="N37" s="12"/>
-      <c r="O37" s="13"/>
-      <c r="P37" s="13"/>
-      <c r="Q37" s="14"/>
-      <c r="R37" s="15"/>
-      <c r="S37" s="16"/>
+          <t>B0FGC7422M</t>
+        </is>
+      </c>
+      <c r="M37" s="12" t="inlineStr">
+        <is>
+          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
+        </is>
+      </c>
+      <c r="N37" s="12" t="inlineStr">
+        <is>
+          <t>DIY・工具・ガーデン</t>
+        </is>
+      </c>
+      <c r="O37" s="13">
+        <v>156632</v>
+      </c>
+      <c r="P37" s="13">
+        <v>4124</v>
+      </c>
+      <c r="Q37" s="14">
+        <v>0.03</v>
+      </c>
+      <c r="R37" s="15" t="inlineStr">
+        <is>
+          <t>ウェットドライショップ掃除機</t>
+        </is>
+      </c>
+      <c r="S37" s="16" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="T37" s="13"/>
       <c r="U37" s="14"/>
       <c r="V37" s="13"/>
       <c r="W37" s="13"/>
       <c r="X37" s="13"/>
-      <c r="Y37" s="17"/>
-      <c r="Z37" s="13"/>
+      <c r="Y37" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z37" s="13">
+        <v>118000</v>
+      </c>
       <c r="AA37"/>
       <c r="AB37"/>
       <c r="AC37" s="2"/>
       <c r="AD37" s="17">
-        <v>81</v>
-      </c>
-      <c r="AE37" s="13"/>
+        <v>29</v>
+      </c>
+      <c r="AE37" s="13">
+        <v>2</v>
+      </c>
       <c r="AF37" s="18">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AG37" s="19">
         <v>0</v>
       </c>
-      <c r="AH37" s="13"/>
+      <c r="AH37" s="13">
+        <v>1020</v>
+      </c>
       <c r="AI37" s="14">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AJ37"/>
-      <c r="AK37" s="11"/>
-      <c r="AL37" s="17"/>
-      <c r="AM37" s="11"/>
+      <c r="AK37" s="11" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="AL37" s="17">
+        <v>443</v>
+      </c>
+      <c r="AM37" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="AN37" s="11"/>
       <c r="AO37" s="11"/>
       <c r="AP37"/>
-      <c r="AQ37" s="17"/>
-      <c r="AR37" s="17"/>
-      <c r="AS37" s="12"/>
-      <c r="AT37" s="11"/>
-      <c r="AU37" s="11"/>
-      <c r="AV37" s="12"/>
-      <c r="AW37" s="11"/>
+      <c r="AQ37" s="17">
+        <v>8</v>
+      </c>
+      <c r="AR37" s="17">
+        <v>1</v>
+      </c>
+      <c r="AS37" s="12" t="inlineStr">
+        <is>
+          <t>-公式ストア</t>
+        </is>
+      </c>
+      <c r="AT37" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU37" s="11" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV37" s="12" t="inlineStr">
+        <is>
+          <t>莆田市 福建 351119 CN</t>
+        </is>
+      </c>
+      <c r="AW37" s="11" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1UV3PJGHZIHW6</t>
+        </is>
+      </c>
       <c r="AX37" s="11"/>
       <c r="AY37" s="11"/>
       <c r="AZ37" s="11"/>
       <c r="BA37" s="11"/>
       <c r="BB37" s="11"/>
       <c r="BC37" s="11"/>
-      <c r="BD37" s="11"/>
+      <c r="BD37" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE37" s="11"/>
       <c r="BF37" s="11"/>
       <c r="BG37" s="11"/>
       <c r="BH37" s="12"/>
       <c r="BI37" s="20"/>
-      <c r="BJ37" s="20"/>
-      <c r="BK37" s="20"/>
-      <c r="BL37" s="20"/>
+      <c r="BJ37" s="20" t="inlineStr">
+        <is>
+          <t>3 kg</t>
+        </is>
+      </c>
+      <c r="BK37" s="20" t="inlineStr">
+        <is>
+          <t>3.00 kg</t>
+        </is>
+      </c>
+      <c r="BL37" s="20" t="inlineStr">
+        <is>
+          <t>29.6長さ x 26.9幅 x 113.4高さ cm</t>
+        </is>
+      </c>
       <c r="BM37" s="20"/>
-      <c r="BN37" s="20"/>
-      <c r="BO37" s="20"/>
-      <c r="BP37" s="20"/>
-      <c r="BQ37" s="20"/>
-      <c r="BR37" s="11"/>
+      <c r="BN37" s="20" t="inlineStr">
+        <is>
+          <t>5.96 kg</t>
+        </is>
+      </c>
+      <c r="BO37" s="20" t="inlineStr">
+        <is>
+          <t>5.96 kg</t>
+        </is>
+      </c>
+      <c r="BP37" s="20" t="inlineStr">
+        <is>
+          <t>55.4 x 33.7 x 31.2 cm</t>
+        </is>
+      </c>
+      <c r="BQ37" s="20" t="inlineStr">
+        <is>
+          <t>55.40 x 33.70 x 31.20 cm</t>
+        </is>
+      </c>
+      <c r="BR37" s="11" t="inlineStr">
+        <is>
+          <t>大件</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="11">
@@ -14624,7 +14016,7 @@
       <c r="B38" s="11"/>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>B0DHV7QRSK</t>
+          <t>B0FL2KXDMX</t>
         </is>
       </c>
       <c r="D38" s="12"/>
@@ -14637,23 +14029,23 @@
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>Vittorio(ヴィットリオ) 乾湿両用掃除機 WET&amp;DRYクリーナー ZV-04-WDs【吸込仕事率65W 集塵約3.0L/吸水約1.5L】 小型コンパクトモデル(33×31×23cm) 本体重量2.5Kg 玄関 ベランダ掃除 作業現場の簡</t>
+          <t>水擦拭吸尘器 JONR ED12 Lite 干湿两用吸尘器 吸水&amp;擦拭2合1无绳棒吸尘器 自动清洗&amp;干燥 150°睡眠结构 墙时1mm清扫 17000Pa强力吸力 长时间运行LED面板 大容量清水&amp;污水罐 经PSE认证</t>
         </is>
       </c>
       <c r="I38" s="12"/>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0DHV7QRSK?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FL2KXDMX?psc=1</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61Coq6GGchL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61j+d1U1UHL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L38" s="12" t="inlineStr">
         <is>
-          <t>B0DHV7QRSK</t>
+          <t>B0FL2KXDMX</t>
         </is>
       </c>
       <c r="M38" s="12"/>
@@ -14669,18 +14061,16 @@
       <c r="W38" s="13"/>
       <c r="X38" s="13"/>
       <c r="Y38" s="17"/>
-      <c r="Z38" s="13">
-        <v>46</v>
-      </c>
+      <c r="Z38" s="13"/>
       <c r="AA38"/>
       <c r="AB38"/>
       <c r="AC38" s="2"/>
       <c r="AD38" s="17">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AE38" s="13"/>
       <c r="AF38" s="18">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AG38" s="19">
         <v>0</v>
@@ -14732,80 +14122,138 @@
       <c r="B39" s="11"/>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>B0DXY4BJ5K</t>
+          <t>B0FPXLZSWP</t>
         </is>
       </c>
       <c r="D39" s="12"/>
       <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>NARWAL(ナーワル)</t>
+        </is>
+      </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jpundefined</t>
+          <t>https://www.amazon.co.jp/stores/NARWAL/page/48E89FF8-D8FF-42EA-91FA-300E4D5D5CBA?lp_asin=B0FPXLZSWP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>Narwal (ナーワル) S20 Pro コードレス水拭き掃除機 20,000Pa強力吸引 自動洗浄s家電批評ベストバイ, 自走式,モップ自動洗浄機能付き,乾湿両用 家具の下も清掃可能 フローリング、タイル、石床専用 絡まりゼロブラシ搭載 子ど</t>
+          <t>Narwal (ナーワル) S30 コードレス水拭き掃除機 20,000Pa吸引 使い捨てゴミネットs自走式 80℃温水モップ自動洗浄 ヒートアイロン乾燥 乾湿両用掃除機 家具の下も清掃可能 絡まり防止機能 子どもやペットのいるご家庭に最適 メン</t>
         </is>
       </c>
       <c r="I39" s="12"/>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0DXY4BJ5K?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FPXLZSWP?psc=1</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/516bWwYYlQL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51o9M+0xsCL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L39" s="12" t="inlineStr">
         <is>
-          <t>B0DXY4BJ5K</t>
-        </is>
-      </c>
-      <c r="M39" s="12"/>
-      <c r="N39" s="12"/>
-      <c r="O39" s="13"/>
-      <c r="P39" s="13"/>
-      <c r="Q39" s="14"/>
-      <c r="R39" s="15"/>
-      <c r="S39" s="16"/>
+          <t>B0FPXLZSWP</t>
+        </is>
+      </c>
+      <c r="M39" s="12" t="inlineStr">
+        <is>
+          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
+        </is>
+      </c>
+      <c r="N39" s="12" t="inlineStr">
+        <is>
+          <t>DIY・工具・ガーデン</t>
+        </is>
+      </c>
+      <c r="O39" s="13">
+        <v>155663</v>
+      </c>
+      <c r="P39" s="13">
+        <v>2593</v>
+      </c>
+      <c r="Q39" s="14">
+        <v>0.02</v>
+      </c>
+      <c r="R39" s="15" t="inlineStr">
+        <is>
+          <t>ウェットドライショップ掃除機</t>
+        </is>
+      </c>
+      <c r="S39" s="16" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="T39" s="13"/>
-      <c r="U39" s="14"/>
+      <c r="U39" s="14">
+        <v>-0.78</v>
+      </c>
       <c r="V39" s="13"/>
       <c r="W39" s="13"/>
       <c r="X39" s="13"/>
-      <c r="Y39" s="17"/>
-      <c r="Z39" s="13"/>
+      <c r="Y39" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z39" s="13">
+        <v>54951</v>
+      </c>
       <c r="AA39"/>
       <c r="AB39"/>
       <c r="AC39" s="2"/>
       <c r="AD39" s="17">
-        <v>62</v>
-      </c>
-      <c r="AE39" s="13"/>
+        <v>41</v>
+      </c>
+      <c r="AE39" s="13">
+        <v>0</v>
+      </c>
       <c r="AF39" s="18">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="AG39" s="19">
         <v>0</v>
       </c>
-      <c r="AH39" s="13"/>
+      <c r="AH39" s="13">
+        <v>1020</v>
+      </c>
       <c r="AI39" s="14">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AJ39"/>
-      <c r="AK39" s="11"/>
-      <c r="AL39" s="17"/>
-      <c r="AM39" s="11"/>
+      <c r="AK39" s="11" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AL39" s="17">
+        <v>377</v>
+      </c>
+      <c r="AM39" s="11" t="inlineStr">
+        <is>
+          <t>AMZ</t>
+        </is>
+      </c>
       <c r="AN39" s="11"/>
       <c r="AO39" s="11"/>
       <c r="AP39"/>
-      <c r="AQ39" s="17"/>
-      <c r="AR39" s="17"/>
-      <c r="AS39" s="12"/>
-      <c r="AT39" s="11"/>
+      <c r="AQ39" s="17">
+        <v>9</v>
+      </c>
+      <c r="AR39" s="17">
+        <v>1</v>
+      </c>
+      <c r="AS39" s="12" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="AT39" s="11" t="inlineStr">
+        <is>
+          <t>AMZ</t>
+        </is>
+      </c>
       <c r="AU39" s="11"/>
       <c r="AV39" s="12"/>
       <c r="AW39" s="11"/>
@@ -14814,22 +14262,62 @@
       <c r="AZ39" s="11"/>
       <c r="BA39" s="11"/>
       <c r="BB39" s="11"/>
-      <c r="BC39" s="11"/>
-      <c r="BD39" s="11"/>
+      <c r="BC39" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD39" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE39" s="11"/>
       <c r="BF39" s="11"/>
       <c r="BG39" s="11"/>
       <c r="BH39" s="12"/>
       <c r="BI39" s="20"/>
-      <c r="BJ39" s="20"/>
-      <c r="BK39" s="20"/>
-      <c r="BL39" s="20"/>
+      <c r="BJ39" s="20" t="inlineStr">
+        <is>
+          <t>8 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK39" s="20" t="inlineStr">
+        <is>
+          <t>8.00 kg</t>
+        </is>
+      </c>
+      <c r="BL39" s="20" t="inlineStr">
+        <is>
+          <t>30長さ x 27.1幅 x 22.5高さ cm</t>
+        </is>
+      </c>
       <c r="BM39" s="20"/>
-      <c r="BN39" s="20"/>
-      <c r="BO39" s="20"/>
-      <c r="BP39" s="20"/>
-      <c r="BQ39" s="20"/>
-      <c r="BR39" s="11"/>
+      <c r="BN39" s="20" t="inlineStr">
+        <is>
+          <t>8 kg</t>
+        </is>
+      </c>
+      <c r="BO39" s="20" t="inlineStr">
+        <is>
+          <t>8.00 kg</t>
+        </is>
+      </c>
+      <c r="BP39" s="20" t="inlineStr">
+        <is>
+          <t>74 x 35 x 29 cm</t>
+        </is>
+      </c>
+      <c r="BQ39" s="20" t="inlineStr">
+        <is>
+          <t>74.00 x 35.00 x 29.00 cm</t>
+        </is>
+      </c>
+      <c r="BR39" s="11" t="inlineStr">
+        <is>
+          <t>大件</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
@@ -14838,7 +14326,7 @@
       <c r="B40" s="11"/>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>B0FBR52FBV</t>
+          <t>B0G4RMHHWV</t>
         </is>
       </c>
       <c r="D40" s="12"/>
@@ -14851,23 +14339,23 @@
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>dreame (Dream) G10 干湿两用 擦水吸尘器 7000Pa吸力 暖风干燥 自动清洗 30分钟长时间运行 LED显示屏s地板擦拭 带拖把功能 擦拭 两用 无线棒 吸尘器 轻量级吸尘器</t>
+          <t>【4个清洗头×17000Pa超强吸力地毯清洁器】 家用地毯清洁剂 漂浮污垢 布清洗机 浮起污垢强力吸力 去污 布清洗机 附带轻松进水口 沙发/地毯清洁剂 带去污功能 沙发/地毯/床垫/车内/玩偶/宠物垫 干湿两用 小巧(白)</t>
         </is>
       </c>
       <c r="I40" s="12"/>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FBR52FBV?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0G4RMHHWV?psc=1</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/51Gx-JJE9mL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61OeNyo9j3L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L40" s="12" t="inlineStr">
         <is>
-          <t>B0FBR52FBV</t>
+          <t>B0G4RMHHWV</t>
         </is>
       </c>
       <c r="M40" s="12"/>
@@ -14888,11 +14376,11 @@
       <c r="AB40"/>
       <c r="AC40" s="2"/>
       <c r="AD40" s="17">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="AE40" s="13"/>
       <c r="AF40" s="18">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AG40" s="19">
         <v>0</v>
@@ -14944,208 +14432,100 @@
       <c r="B41" s="11"/>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>B0FGC7422M</t>
+          <t>B0GJZNZZBG</t>
         </is>
       </c>
       <c r="D41" s="12"/>
       <c r="E41" s="12"/>
-      <c r="F41" s="12" t="inlineStr">
-        <is>
-          <t>JONR</t>
-        </is>
-      </c>
+      <c r="F41" s="12"/>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FGC7422M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jpundefined</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>擦水吸尘器 吸水&amp;擦拭2合1无绳棒吸尘器 干湿两用 滚轮刷自动清洗&amp;干燥 150°睡眠结构 墙时1mm清扫 20000Pa强力吸力 长时间运行大容量清水&amp;污水桶 独自生活 家庭用 日语使用说明书 PSE认证</t>
+          <t>BOSCH 多功能吸尘器 VAC115 轻巧 小巧 干湿两用多功能吸尘器 鼓风机功能 大型脚轮 小巧收纳 博世</t>
         </is>
       </c>
       <c r="I41" s="12"/>
       <c r="J41" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FGC7422M?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0GJZNZZBG?psc=1</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51PDVCpecuL._AC_US600_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/41bBBiQaOQL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
-          <t>B0FGC7422M</t>
-        </is>
-      </c>
-      <c r="M41" s="12" t="inlineStr">
-        <is>
-          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
-        </is>
-      </c>
-      <c r="N41" s="12" t="inlineStr">
-        <is>
-          <t>DIY・工具・ガーデン</t>
-        </is>
-      </c>
-      <c r="O41" s="13">
-        <v>156632</v>
-      </c>
-      <c r="P41" s="13">
-        <v>4124</v>
-      </c>
-      <c r="Q41" s="14">
-        <v>0.03</v>
-      </c>
-      <c r="R41" s="15" t="inlineStr">
-        <is>
-          <t>ウェットドライショップ掃除機</t>
-        </is>
-      </c>
-      <c r="S41" s="16" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>B0GJZNZZBG</t>
+        </is>
+      </c>
+      <c r="M41" s="12"/>
+      <c r="N41" s="12"/>
+      <c r="O41" s="13"/>
+      <c r="P41" s="13"/>
+      <c r="Q41" s="14"/>
+      <c r="R41" s="15"/>
+      <c r="S41" s="16"/>
       <c r="T41" s="13"/>
       <c r="U41" s="14"/>
       <c r="V41" s="13"/>
       <c r="W41" s="13"/>
       <c r="X41" s="13"/>
-      <c r="Y41" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z41" s="13">
-        <v>118000</v>
-      </c>
+      <c r="Y41" s="17"/>
+      <c r="Z41" s="13"/>
       <c r="AA41"/>
       <c r="AB41"/>
       <c r="AC41" s="2"/>
-      <c r="AD41" s="17">
-        <v>29</v>
-      </c>
-      <c r="AE41" s="13">
-        <v>2</v>
-      </c>
-      <c r="AF41" s="18">
-        <v>3.8</v>
-      </c>
+      <c r="AD41" s="17"/>
+      <c r="AE41" s="13"/>
+      <c r="AF41" s="18"/>
       <c r="AG41" s="19">
         <v>0</v>
       </c>
-      <c r="AH41" s="13">
-        <v>1020</v>
-      </c>
+      <c r="AH41" s="13"/>
       <c r="AI41" s="14">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="AJ41"/>
-      <c r="AK41" s="11" t="inlineStr">
-        <is>
-          <t>2025-07-21</t>
-        </is>
-      </c>
-      <c r="AL41" s="17">
-        <v>443</v>
-      </c>
-      <c r="AM41" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="AK41" s="11"/>
+      <c r="AL41" s="17"/>
+      <c r="AM41" s="11"/>
       <c r="AN41" s="11"/>
       <c r="AO41" s="11"/>
       <c r="AP41"/>
-      <c r="AQ41" s="17">
-        <v>8</v>
-      </c>
-      <c r="AR41" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS41" s="12" t="inlineStr">
-        <is>
-          <t>-公式ストア</t>
-        </is>
-      </c>
-      <c r="AT41" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU41" s="11" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV41" s="12" t="inlineStr">
-        <is>
-          <t>莆田市 福建 351119 CN</t>
-        </is>
-      </c>
-      <c r="AW41" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1UV3PJGHZIHW6</t>
-        </is>
-      </c>
+      <c r="AQ41" s="17"/>
+      <c r="AR41" s="17"/>
+      <c r="AS41" s="12"/>
+      <c r="AT41" s="11"/>
+      <c r="AU41" s="11"/>
+      <c r="AV41" s="12"/>
+      <c r="AW41" s="11"/>
       <c r="AX41" s="11"/>
       <c r="AY41" s="11"/>
       <c r="AZ41" s="11"/>
       <c r="BA41" s="11"/>
       <c r="BB41" s="11"/>
       <c r="BC41" s="11"/>
-      <c r="BD41" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD41" s="11"/>
       <c r="BE41" s="11"/>
       <c r="BF41" s="11"/>
       <c r="BG41" s="11"/>
       <c r="BH41" s="12"/>
       <c r="BI41" s="20"/>
-      <c r="BJ41" s="20" t="inlineStr">
-        <is>
-          <t>3 kg</t>
-        </is>
-      </c>
-      <c r="BK41" s="20" t="inlineStr">
-        <is>
-          <t>3.00 kg</t>
-        </is>
-      </c>
-      <c r="BL41" s="20" t="inlineStr">
-        <is>
-          <t>29.6長さ x 26.9幅 x 113.4高さ cm</t>
-        </is>
-      </c>
+      <c r="BJ41" s="20"/>
+      <c r="BK41" s="20"/>
+      <c r="BL41" s="20"/>
       <c r="BM41" s="20"/>
-      <c r="BN41" s="20" t="inlineStr">
-        <is>
-          <t>5.96 kg</t>
-        </is>
-      </c>
-      <c r="BO41" s="20" t="inlineStr">
-        <is>
-          <t>5.96 kg</t>
-        </is>
-      </c>
-      <c r="BP41" s="20" t="inlineStr">
-        <is>
-          <t>55.4 x 33.7 x 31.2 cm</t>
-        </is>
-      </c>
-      <c r="BQ41" s="20" t="inlineStr">
-        <is>
-          <t>55.40 x 33.70 x 31.20 cm</t>
-        </is>
-      </c>
-      <c r="BR41" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
+      <c r="BN41" s="20"/>
+      <c r="BO41" s="20"/>
+      <c r="BP41" s="20"/>
+      <c r="BQ41" s="20"/>
+      <c r="BR41" s="11"/>
     </row>
     <row r="42" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="11">
@@ -15154,7 +14534,7 @@
       <c r="B42" s="11"/>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>B0FL2KXDMX</t>
+          <t>B0GP76R477</t>
         </is>
       </c>
       <c r="D42" s="12"/>
@@ -15167,23 +14547,23 @@
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>水擦拭吸尘器 JONR ED12 Lite 干湿两用吸尘器 吸水&amp;擦拭2合1无绳棒吸尘器 自动清洗&amp;干燥 150°睡眠结构 墙时1mm清扫 17000Pa强力吸力 长时间运行LED面板 大容量清水&amp;污水罐 经PSE认证</t>
+          <t>【官方/替换用卷刷&amp;过滤网×1】Mindoo AquaX Plus Mindoo AquaX Plus 可擦拭水的吸尘器 [吸水、擦拭、除菌、自我清洁、自动干燥] 自走式 垃圾收集1台3用 强力吸力 超轻 自动清洗 高性能 (黑色)</t>
         </is>
       </c>
       <c r="I42" s="12"/>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FL2KXDMX?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0GP76R477?psc=1</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61j+d1U1UHL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/21UZYI0dymL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L42" s="12" t="inlineStr">
         <is>
-          <t>B0FL2KXDMX</t>
+          <t>B0GP76R477</t>
         </is>
       </c>
       <c r="M42" s="12"/>
@@ -15203,13 +14583,9 @@
       <c r="AA42"/>
       <c r="AB42"/>
       <c r="AC42" s="2"/>
-      <c r="AD42" s="17">
-        <v>27</v>
-      </c>
+      <c r="AD42" s="17"/>
       <c r="AE42" s="13"/>
-      <c r="AF42" s="18">
-        <v>3.5</v>
-      </c>
+      <c r="AF42" s="18"/>
       <c r="AG42" s="19">
         <v>0</v>
       </c>
@@ -15260,138 +14636,76 @@
       <c r="B43" s="11"/>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>B0FPXLZSWP</t>
+          <t>B0H5WDMCLX</t>
         </is>
       </c>
       <c r="D43" s="12"/>
       <c r="E43" s="12"/>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>NARWAL(ナーワル)</t>
-        </is>
-      </c>
+      <c r="F43" s="12"/>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/NARWAL/page/48E89FF8-D8FF-42EA-91FA-300E4D5D5CBA?lp_asin=B0FPXLZSWP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jpundefined</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>Narwal (ナーワル) S30 コードレス水拭き掃除機 20,000Pa吸引 使い捨てゴミネットs自走式 80℃温水モップ自動洗浄 ヒートアイロン乾燥 乾湿両用掃除機 家具の下も清掃可能 絡まり防止機能 子どもやペットのいるご家庭に最適 メン</t>
+          <t>dreame H12 Pro FlexReach 擦水吸尘器与替换用过滤器 套装</t>
         </is>
       </c>
       <c r="I43" s="12"/>
       <c r="J43" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FPXLZSWP?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0H5WDMCLX?psc=1</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51o9M+0xsCL._AC_US600_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/31ZGQqLBLNL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
-          <t>B0FPXLZSWP</t>
-        </is>
-      </c>
-      <c r="M43" s="12" t="inlineStr">
-        <is>
-          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
-        </is>
-      </c>
-      <c r="N43" s="12" t="inlineStr">
-        <is>
-          <t>DIY・工具・ガーデン</t>
-        </is>
-      </c>
-      <c r="O43" s="13">
-        <v>155663</v>
-      </c>
-      <c r="P43" s="13">
-        <v>2593</v>
-      </c>
-      <c r="Q43" s="14">
-        <v>0.02</v>
-      </c>
-      <c r="R43" s="15" t="inlineStr">
-        <is>
-          <t>ウェットドライショップ掃除機</t>
-        </is>
-      </c>
-      <c r="S43" s="16" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
+          <t>B0H5WDMCLX</t>
+        </is>
+      </c>
+      <c r="M43" s="12"/>
+      <c r="N43" s="12"/>
+      <c r="O43" s="13"/>
+      <c r="P43" s="13"/>
+      <c r="Q43" s="14"/>
+      <c r="R43" s="15"/>
+      <c r="S43" s="16"/>
       <c r="T43" s="13"/>
-      <c r="U43" s="14">
-        <v>-0.78</v>
-      </c>
+      <c r="U43" s="14"/>
       <c r="V43" s="13"/>
       <c r="W43" s="13"/>
       <c r="X43" s="13"/>
-      <c r="Y43" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z43" s="13">
-        <v>54951</v>
-      </c>
+      <c r="Y43" s="17"/>
+      <c r="Z43" s="13"/>
       <c r="AA43"/>
       <c r="AB43"/>
       <c r="AC43" s="2"/>
-      <c r="AD43" s="17">
-        <v>41</v>
-      </c>
-      <c r="AE43" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF43" s="18">
-        <v>3.6</v>
-      </c>
+      <c r="AD43" s="17"/>
+      <c r="AE43" s="13"/>
+      <c r="AF43" s="18"/>
       <c r="AG43" s="19">
         <v>0</v>
       </c>
-      <c r="AH43" s="13">
-        <v>1020</v>
-      </c>
+      <c r="AH43" s="13"/>
       <c r="AI43" s="14">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="AJ43"/>
-      <c r="AK43" s="11" t="inlineStr">
-        <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="AL43" s="17">
-        <v>377</v>
-      </c>
-      <c r="AM43" s="11" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
+      <c r="AK43" s="11"/>
+      <c r="AL43" s="17"/>
+      <c r="AM43" s="11"/>
       <c r="AN43" s="11"/>
       <c r="AO43" s="11"/>
       <c r="AP43"/>
-      <c r="AQ43" s="17">
-        <v>9</v>
-      </c>
-      <c r="AR43" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS43" s="12" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT43" s="11" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
+      <c r="AQ43" s="17"/>
+      <c r="AR43" s="17"/>
+      <c r="AS43" s="12"/>
+      <c r="AT43" s="11"/>
       <c r="AU43" s="11"/>
       <c r="AV43" s="12"/>
       <c r="AW43" s="11"/>
@@ -15400,882 +14714,22 @@
       <c r="AZ43" s="11"/>
       <c r="BA43" s="11"/>
       <c r="BB43" s="11"/>
-      <c r="BC43" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD43" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC43" s="11"/>
+      <c r="BD43" s="11"/>
       <c r="BE43" s="11"/>
       <c r="BF43" s="11"/>
       <c r="BG43" s="11"/>
       <c r="BH43" s="12"/>
       <c r="BI43" s="20"/>
-      <c r="BJ43" s="20" t="inlineStr">
-        <is>
-          <t>8 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK43" s="20" t="inlineStr">
-        <is>
-          <t>8.00 kg</t>
-        </is>
-      </c>
-      <c r="BL43" s="20" t="inlineStr">
-        <is>
-          <t>30長さ x 27.1幅 x 22.5高さ cm</t>
-        </is>
-      </c>
+      <c r="BJ43" s="20"/>
+      <c r="BK43" s="20"/>
+      <c r="BL43" s="20"/>
       <c r="BM43" s="20"/>
-      <c r="BN43" s="20" t="inlineStr">
-        <is>
-          <t>8 kg</t>
-        </is>
-      </c>
-      <c r="BO43" s="20" t="inlineStr">
-        <is>
-          <t>8.00 kg</t>
-        </is>
-      </c>
-      <c r="BP43" s="20" t="inlineStr">
-        <is>
-          <t>74 x 35 x 29 cm</t>
-        </is>
-      </c>
-      <c r="BQ43" s="20" t="inlineStr">
-        <is>
-          <t>74.00 x 35.00 x 29.00 cm</t>
-        </is>
-      </c>
-      <c r="BR43" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="11">
-        <v>43</v>
-      </c>
-      <c r="B44" s="11"/>
-      <c r="C44" s="12" t="inlineStr">
-        <is>
-          <t>B0G4RMHHWV</t>
-        </is>
-      </c>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>【4个清洗头×17000Pa超强吸力地毯清洁器】 家用地毯清洁剂 漂浮污垢 布清洗机 浮起污垢强力吸力 去污 布清洗机 附带轻松进水口 沙发/地毯清洁剂 带去污功能 沙发/地毯/床垫/车内/玩偶/宠物垫 干湿两用 小巧(白)</t>
-        </is>
-      </c>
-      <c r="I44" s="12"/>
-      <c r="J44" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0G4RMHHWV?psc=1</t>
-        </is>
-      </c>
-      <c r="K44" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61OeNyo9j3L._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L44" s="12" t="inlineStr">
-        <is>
-          <t>B0G4RMHHWV</t>
-        </is>
-      </c>
-      <c r="M44" s="12"/>
-      <c r="N44" s="12"/>
-      <c r="O44" s="13"/>
-      <c r="P44" s="13"/>
-      <c r="Q44" s="14"/>
-      <c r="R44" s="15"/>
-      <c r="S44" s="16"/>
-      <c r="T44" s="13"/>
-      <c r="U44" s="14"/>
-      <c r="V44" s="13"/>
-      <c r="W44" s="13"/>
-      <c r="X44" s="13"/>
-      <c r="Y44" s="17"/>
-      <c r="Z44" s="13"/>
-      <c r="AA44"/>
-      <c r="AB44"/>
-      <c r="AC44" s="2"/>
-      <c r="AD44" s="17">
-        <v>43</v>
-      </c>
-      <c r="AE44" s="13"/>
-      <c r="AF44" s="18">
-        <v>4.1</v>
-      </c>
-      <c r="AG44" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH44" s="13"/>
-      <c r="AI44" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ44"/>
-      <c r="AK44" s="11"/>
-      <c r="AL44" s="17"/>
-      <c r="AM44" s="11"/>
-      <c r="AN44" s="11"/>
-      <c r="AO44" s="11"/>
-      <c r="AP44"/>
-      <c r="AQ44" s="17"/>
-      <c r="AR44" s="17"/>
-      <c r="AS44" s="12"/>
-      <c r="AT44" s="11"/>
-      <c r="AU44" s="11"/>
-      <c r="AV44" s="12"/>
-      <c r="AW44" s="11"/>
-      <c r="AX44" s="11"/>
-      <c r="AY44" s="11"/>
-      <c r="AZ44" s="11"/>
-      <c r="BA44" s="11"/>
-      <c r="BB44" s="11"/>
-      <c r="BC44" s="11"/>
-      <c r="BD44" s="11"/>
-      <c r="BE44" s="11"/>
-      <c r="BF44" s="11"/>
-      <c r="BG44" s="11"/>
-      <c r="BH44" s="12"/>
-      <c r="BI44" s="20"/>
-      <c r="BJ44" s="20"/>
-      <c r="BK44" s="20"/>
-      <c r="BL44" s="20"/>
-      <c r="BM44" s="20"/>
-      <c r="BN44" s="20"/>
-      <c r="BO44" s="20"/>
-      <c r="BP44" s="20"/>
-      <c r="BQ44" s="20"/>
-      <c r="BR44" s="11"/>
-    </row>
-    <row r="45" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="11">
-        <v>44</v>
-      </c>
-      <c r="B45" s="11"/>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>B0GJZNZZBG</t>
-        </is>
-      </c>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H45" s="12" t="inlineStr">
-        <is>
-          <t>BOSCH 多功能吸尘器 VAC115 轻巧 小巧 干湿两用多功能吸尘器 鼓风机功能 大型脚轮 小巧收纳 博世</t>
-        </is>
-      </c>
-      <c r="I45" s="12"/>
-      <c r="J45" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0GJZNZZBG?psc=1</t>
-        </is>
-      </c>
-      <c r="K45" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/41bBBiQaOQL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L45" s="12" t="inlineStr">
-        <is>
-          <t>B0GJZNZZBG</t>
-        </is>
-      </c>
-      <c r="M45" s="12"/>
-      <c r="N45" s="12"/>
-      <c r="O45" s="13"/>
-      <c r="P45" s="13"/>
-      <c r="Q45" s="14"/>
-      <c r="R45" s="15"/>
-      <c r="S45" s="16"/>
-      <c r="T45" s="13"/>
-      <c r="U45" s="14"/>
-      <c r="V45" s="13"/>
-      <c r="W45" s="13"/>
-      <c r="X45" s="13"/>
-      <c r="Y45" s="17"/>
-      <c r="Z45" s="13"/>
-      <c r="AA45"/>
-      <c r="AB45"/>
-      <c r="AC45" s="2"/>
-      <c r="AD45" s="17"/>
-      <c r="AE45" s="13"/>
-      <c r="AF45" s="18"/>
-      <c r="AG45" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH45" s="13"/>
-      <c r="AI45" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ45"/>
-      <c r="AK45" s="11"/>
-      <c r="AL45" s="17"/>
-      <c r="AM45" s="11"/>
-      <c r="AN45" s="11"/>
-      <c r="AO45" s="11"/>
-      <c r="AP45"/>
-      <c r="AQ45" s="17"/>
-      <c r="AR45" s="17"/>
-      <c r="AS45" s="12"/>
-      <c r="AT45" s="11"/>
-      <c r="AU45" s="11"/>
-      <c r="AV45" s="12"/>
-      <c r="AW45" s="11"/>
-      <c r="AX45" s="11"/>
-      <c r="AY45" s="11"/>
-      <c r="AZ45" s="11"/>
-      <c r="BA45" s="11"/>
-      <c r="BB45" s="11"/>
-      <c r="BC45" s="11"/>
-      <c r="BD45" s="11"/>
-      <c r="BE45" s="11"/>
-      <c r="BF45" s="11"/>
-      <c r="BG45" s="11"/>
-      <c r="BH45" s="12"/>
-      <c r="BI45" s="20"/>
-      <c r="BJ45" s="20"/>
-      <c r="BK45" s="20"/>
-      <c r="BL45" s="20"/>
-      <c r="BM45" s="20"/>
-      <c r="BN45" s="20"/>
-      <c r="BO45" s="20"/>
-      <c r="BP45" s="20"/>
-      <c r="BQ45" s="20"/>
-      <c r="BR45" s="11"/>
-    </row>
-    <row r="46" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="11">
-        <v>45</v>
-      </c>
-      <c r="B46" s="11"/>
-      <c r="C46" s="12" t="inlineStr">
-        <is>
-          <t>B0GP76R477</t>
-        </is>
-      </c>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H46" s="12" t="inlineStr">
-        <is>
-          <t>【官方/替换用卷刷&amp;过滤网×1】Mindoo AquaX Plus Mindoo AquaX Plus 可擦拭水的吸尘器 [吸水、擦拭、除菌、自我清洁、自动干燥] 自走式 垃圾收集1台3用 强力吸力 超轻 自动清洗 高性能 (黑色)</t>
-        </is>
-      </c>
-      <c r="I46" s="12"/>
-      <c r="J46" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0GP76R477?psc=1</t>
-        </is>
-      </c>
-      <c r="K46" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/21UZYI0dymL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L46" s="12" t="inlineStr">
-        <is>
-          <t>B0GP76R477</t>
-        </is>
-      </c>
-      <c r="M46" s="12"/>
-      <c r="N46" s="12"/>
-      <c r="O46" s="13"/>
-      <c r="P46" s="13"/>
-      <c r="Q46" s="14"/>
-      <c r="R46" s="15"/>
-      <c r="S46" s="16"/>
-      <c r="T46" s="13"/>
-      <c r="U46" s="14"/>
-      <c r="V46" s="13"/>
-      <c r="W46" s="13"/>
-      <c r="X46" s="13"/>
-      <c r="Y46" s="17"/>
-      <c r="Z46" s="13"/>
-      <c r="AA46"/>
-      <c r="AB46"/>
-      <c r="AC46" s="2"/>
-      <c r="AD46" s="17"/>
-      <c r="AE46" s="13"/>
-      <c r="AF46" s="18"/>
-      <c r="AG46" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH46" s="13"/>
-      <c r="AI46" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ46"/>
-      <c r="AK46" s="11"/>
-      <c r="AL46" s="17"/>
-      <c r="AM46" s="11"/>
-      <c r="AN46" s="11"/>
-      <c r="AO46" s="11"/>
-      <c r="AP46"/>
-      <c r="AQ46" s="17"/>
-      <c r="AR46" s="17"/>
-      <c r="AS46" s="12"/>
-      <c r="AT46" s="11"/>
-      <c r="AU46" s="11"/>
-      <c r="AV46" s="12"/>
-      <c r="AW46" s="11"/>
-      <c r="AX46" s="11"/>
-      <c r="AY46" s="11"/>
-      <c r="AZ46" s="11"/>
-      <c r="BA46" s="11"/>
-      <c r="BB46" s="11"/>
-      <c r="BC46" s="11"/>
-      <c r="BD46" s="11"/>
-      <c r="BE46" s="11"/>
-      <c r="BF46" s="11"/>
-      <c r="BG46" s="11"/>
-      <c r="BH46" s="12"/>
-      <c r="BI46" s="20"/>
-      <c r="BJ46" s="20"/>
-      <c r="BK46" s="20"/>
-      <c r="BL46" s="20"/>
-      <c r="BM46" s="20"/>
-      <c r="BN46" s="20"/>
-      <c r="BO46" s="20"/>
-      <c r="BP46" s="20"/>
-      <c r="BQ46" s="20"/>
-      <c r="BR46" s="11"/>
-    </row>
-    <row r="47" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="11">
-        <v>46</v>
-      </c>
-      <c r="B47" s="11"/>
-      <c r="C47" s="12" t="inlineStr">
-        <is>
-          <t>B0H5WDMCLX</t>
-        </is>
-      </c>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H47" s="12" t="inlineStr">
-        <is>
-          <t>dreame H12 Pro FlexReach 擦水吸尘器与替换用过滤器 套装</t>
-        </is>
-      </c>
-      <c r="I47" s="12"/>
-      <c r="J47" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0H5WDMCLX?psc=1</t>
-        </is>
-      </c>
-      <c r="K47" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/31ZGQqLBLNL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L47" s="12" t="inlineStr">
-        <is>
-          <t>B0H5WDMCLX</t>
-        </is>
-      </c>
-      <c r="M47" s="12"/>
-      <c r="N47" s="12"/>
-      <c r="O47" s="13"/>
-      <c r="P47" s="13"/>
-      <c r="Q47" s="14"/>
-      <c r="R47" s="15"/>
-      <c r="S47" s="16"/>
-      <c r="T47" s="13"/>
-      <c r="U47" s="14"/>
-      <c r="V47" s="13"/>
-      <c r="W47" s="13"/>
-      <c r="X47" s="13"/>
-      <c r="Y47" s="17"/>
-      <c r="Z47" s="13"/>
-      <c r="AA47"/>
-      <c r="AB47"/>
-      <c r="AC47" s="2"/>
-      <c r="AD47" s="17"/>
-      <c r="AE47" s="13"/>
-      <c r="AF47" s="18"/>
-      <c r="AG47" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH47" s="13"/>
-      <c r="AI47" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ47"/>
-      <c r="AK47" s="11"/>
-      <c r="AL47" s="17"/>
-      <c r="AM47" s="11"/>
-      <c r="AN47" s="11"/>
-      <c r="AO47" s="11"/>
-      <c r="AP47"/>
-      <c r="AQ47" s="17"/>
-      <c r="AR47" s="17"/>
-      <c r="AS47" s="12"/>
-      <c r="AT47" s="11"/>
-      <c r="AU47" s="11"/>
-      <c r="AV47" s="12"/>
-      <c r="AW47" s="11"/>
-      <c r="AX47" s="11"/>
-      <c r="AY47" s="11"/>
-      <c r="AZ47" s="11"/>
-      <c r="BA47" s="11"/>
-      <c r="BB47" s="11"/>
-      <c r="BC47" s="11"/>
-      <c r="BD47" s="11"/>
-      <c r="BE47" s="11"/>
-      <c r="BF47" s="11"/>
-      <c r="BG47" s="11"/>
-      <c r="BH47" s="12"/>
-      <c r="BI47" s="20"/>
-      <c r="BJ47" s="20"/>
-      <c r="BK47" s="20"/>
-      <c r="BL47" s="20"/>
-      <c r="BM47" s="20"/>
-      <c r="BN47" s="20"/>
-      <c r="BO47" s="20"/>
-      <c r="BP47" s="20"/>
-      <c r="BQ47" s="20"/>
-      <c r="BR47" s="11"/>
-    </row>
-    <row r="48" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="11">
-        <v>47</v>
-      </c>
-      <c r="B48" s="11"/>
-      <c r="C48" s="12" t="inlineStr">
-        <is>
-          <t>B0H99BC6SP</t>
-        </is>
-      </c>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H48" s="12" t="inlineStr">
-        <is>
-          <t>Gwrv 干湿两用 真空 带鼓风机功能 15L 家用 商用 吸尘器 800W (15L,塑料制 标准型号(附9件套))</t>
-        </is>
-      </c>
-      <c r="I48" s="12"/>
-      <c r="J48" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0H99BC6SP?psc=1</t>
-        </is>
-      </c>
-      <c r="K48" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61w-2YImFbL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L48" s="12" t="inlineStr">
-        <is>
-          <t>B0H99BC6SP</t>
-        </is>
-      </c>
-      <c r="M48" s="12"/>
-      <c r="N48" s="12"/>
-      <c r="O48" s="13"/>
-      <c r="P48" s="13"/>
-      <c r="Q48" s="14"/>
-      <c r="R48" s="15"/>
-      <c r="S48" s="16"/>
-      <c r="T48" s="13"/>
-      <c r="U48" s="14"/>
-      <c r="V48" s="13"/>
-      <c r="W48" s="13"/>
-      <c r="X48" s="13"/>
-      <c r="Y48" s="17"/>
-      <c r="Z48" s="13"/>
-      <c r="AA48"/>
-      <c r="AB48"/>
-      <c r="AC48" s="2"/>
-      <c r="AD48" s="17"/>
-      <c r="AE48" s="13"/>
-      <c r="AF48" s="18"/>
-      <c r="AG48" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH48" s="13"/>
-      <c r="AI48" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ48"/>
-      <c r="AK48" s="11"/>
-      <c r="AL48" s="17"/>
-      <c r="AM48" s="11"/>
-      <c r="AN48" s="11"/>
-      <c r="AO48" s="11"/>
-      <c r="AP48"/>
-      <c r="AQ48" s="17"/>
-      <c r="AR48" s="17"/>
-      <c r="AS48" s="12"/>
-      <c r="AT48" s="11"/>
-      <c r="AU48" s="11"/>
-      <c r="AV48" s="12"/>
-      <c r="AW48" s="11"/>
-      <c r="AX48" s="11"/>
-      <c r="AY48" s="11"/>
-      <c r="AZ48" s="11"/>
-      <c r="BA48" s="11"/>
-      <c r="BB48" s="11"/>
-      <c r="BC48" s="11"/>
-      <c r="BD48" s="11"/>
-      <c r="BE48" s="11"/>
-      <c r="BF48" s="11"/>
-      <c r="BG48" s="11"/>
-      <c r="BH48" s="12"/>
-      <c r="BI48" s="20"/>
-      <c r="BJ48" s="20"/>
-      <c r="BK48" s="20"/>
-      <c r="BL48" s="20"/>
-      <c r="BM48" s="20"/>
-      <c r="BN48" s="20"/>
-      <c r="BO48" s="20"/>
-      <c r="BP48" s="20"/>
-      <c r="BQ48" s="20"/>
-      <c r="BR48" s="11"/>
-    </row>
-    <row r="49" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="11">
-        <v>48</v>
-      </c>
-      <c r="B49" s="11"/>
-      <c r="C49" s="12" t="inlineStr">
-        <is>
-          <t>B0HFW5C8BX</t>
-        </is>
-      </c>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H49" s="12" t="inlineStr">
-        <is>
-          <t>乾湿両用掃除機 15L・18L 大容量 強力吸引 送風機能付き 4段階フィルター キャスター付き 業務用・家庭用 ウェット＆ドライバキューム 洗車・リフォーム・ガレージ清掃用 (ステンレス鋼標準構成,15L) [並行輸入品]</t>
-        </is>
-      </c>
-      <c r="I49" s="12"/>
-      <c r="J49" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0HFW5C8BX?psc=1</t>
-        </is>
-      </c>
-      <c r="K49" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/41tXijm5C2L._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L49" s="12" t="inlineStr">
-        <is>
-          <t>B0HFW5C8BX</t>
-        </is>
-      </c>
-      <c r="M49" s="12"/>
-      <c r="N49" s="12"/>
-      <c r="O49" s="13"/>
-      <c r="P49" s="13"/>
-      <c r="Q49" s="14"/>
-      <c r="R49" s="15"/>
-      <c r="S49" s="16"/>
-      <c r="T49" s="13"/>
-      <c r="U49" s="14"/>
-      <c r="V49" s="13"/>
-      <c r="W49" s="13"/>
-      <c r="X49" s="13"/>
-      <c r="Y49" s="17"/>
-      <c r="Z49" s="13"/>
-      <c r="AA49"/>
-      <c r="AB49"/>
-      <c r="AC49" s="2"/>
-      <c r="AD49" s="17"/>
-      <c r="AE49" s="13"/>
-      <c r="AF49" s="18"/>
-      <c r="AG49" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH49" s="13"/>
-      <c r="AI49" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ49"/>
-      <c r="AK49" s="11"/>
-      <c r="AL49" s="17"/>
-      <c r="AM49" s="11"/>
-      <c r="AN49" s="11"/>
-      <c r="AO49" s="11"/>
-      <c r="AP49"/>
-      <c r="AQ49" s="17"/>
-      <c r="AR49" s="17"/>
-      <c r="AS49" s="12"/>
-      <c r="AT49" s="11"/>
-      <c r="AU49" s="11"/>
-      <c r="AV49" s="12"/>
-      <c r="AW49" s="11"/>
-      <c r="AX49" s="11"/>
-      <c r="AY49" s="11"/>
-      <c r="AZ49" s="11"/>
-      <c r="BA49" s="11"/>
-      <c r="BB49" s="11"/>
-      <c r="BC49" s="11"/>
-      <c r="BD49" s="11"/>
-      <c r="BE49" s="11"/>
-      <c r="BF49" s="11"/>
-      <c r="BG49" s="11"/>
-      <c r="BH49" s="12"/>
-      <c r="BI49" s="20"/>
-      <c r="BJ49" s="20"/>
-      <c r="BK49" s="20"/>
-      <c r="BL49" s="20"/>
-      <c r="BM49" s="20"/>
-      <c r="BN49" s="20"/>
-      <c r="BO49" s="20"/>
-      <c r="BP49" s="20"/>
-      <c r="BQ49" s="20"/>
-      <c r="BR49" s="11"/>
-    </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="11">
-        <v>49</v>
-      </c>
-      <c r="B50" s="11"/>
-      <c r="C50" s="12" t="inlineStr">
-        <is>
-          <t>B0HJ22HH2H</t>
-        </is>
-      </c>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="12"/>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
-          <t>掃除機：業務用・家庭用を問わず、乾湿両用でお使いいただけます。110V電源で強力な吸引力、大容量、キャスター付きで移動も簡単です (18Lステンレス製バケツ) [並行輸入品]</t>
-        </is>
-      </c>
-      <c r="I50" s="12"/>
-      <c r="J50" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0HJ22HH2H?psc=1</t>
-        </is>
-      </c>
-      <c r="K50" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/519xXj4dKQL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L50" s="12" t="inlineStr">
-        <is>
-          <t>B0HJ22HH2H</t>
-        </is>
-      </c>
-      <c r="M50" s="12"/>
-      <c r="N50" s="12"/>
-      <c r="O50" s="13"/>
-      <c r="P50" s="13"/>
-      <c r="Q50" s="14"/>
-      <c r="R50" s="15"/>
-      <c r="S50" s="16"/>
-      <c r="T50" s="13"/>
-      <c r="U50" s="14"/>
-      <c r="V50" s="13"/>
-      <c r="W50" s="13"/>
-      <c r="X50" s="13"/>
-      <c r="Y50" s="17"/>
-      <c r="Z50" s="13"/>
-      <c r="AA50"/>
-      <c r="AB50"/>
-      <c r="AC50" s="2"/>
-      <c r="AD50" s="17"/>
-      <c r="AE50" s="13"/>
-      <c r="AF50" s="18"/>
-      <c r="AG50" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH50" s="13"/>
-      <c r="AI50" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="11"/>
-      <c r="AL50" s="17"/>
-      <c r="AM50" s="11"/>
-      <c r="AN50" s="11"/>
-      <c r="AO50" s="11"/>
-      <c r="AP50"/>
-      <c r="AQ50" s="17"/>
-      <c r="AR50" s="17"/>
-      <c r="AS50" s="12"/>
-      <c r="AT50" s="11"/>
-      <c r="AU50" s="11"/>
-      <c r="AV50" s="12"/>
-      <c r="AW50" s="11"/>
-      <c r="AX50" s="11"/>
-      <c r="AY50" s="11"/>
-      <c r="AZ50" s="11"/>
-      <c r="BA50" s="11"/>
-      <c r="BB50" s="11"/>
-      <c r="BC50" s="11"/>
-      <c r="BD50" s="11"/>
-      <c r="BE50" s="11"/>
-      <c r="BF50" s="11"/>
-      <c r="BG50" s="11"/>
-      <c r="BH50" s="12"/>
-      <c r="BI50" s="20"/>
-      <c r="BJ50" s="20"/>
-      <c r="BK50" s="20"/>
-      <c r="BL50" s="20"/>
-      <c r="BM50" s="20"/>
-      <c r="BN50" s="20"/>
-      <c r="BO50" s="20"/>
-      <c r="BP50" s="20"/>
-      <c r="BQ50" s="20"/>
-      <c r="BR50" s="11"/>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="11">
-        <v>50</v>
-      </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="12" t="inlineStr">
-        <is>
-          <t>B0HJZ443Z7</t>
-        </is>
-      </c>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>LumoLight掃除機 業務用掃除機 バキュームクリーナー 乾湿両用大容量バキューム集塵機 四重フィルター 全方位キャスター 家庭/オフィス/リフォーム用 (18Lステンレススチール標準構成) [並行輸入品]</t>
-        </is>
-      </c>
-      <c r="I51" s="12"/>
-      <c r="J51" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0HJZ443Z7?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/51QZUn8fZ2L._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="12" t="inlineStr">
-        <is>
-          <t>B0HJZ443Z7</t>
-        </is>
-      </c>
-      <c r="M51" s="12"/>
-      <c r="N51" s="12"/>
-      <c r="O51" s="13"/>
-      <c r="P51" s="13"/>
-      <c r="Q51" s="14"/>
-      <c r="R51" s="15"/>
-      <c r="S51" s="16"/>
-      <c r="T51" s="13"/>
-      <c r="U51" s="14"/>
-      <c r="V51" s="13"/>
-      <c r="W51" s="13"/>
-      <c r="X51" s="13"/>
-      <c r="Y51" s="17"/>
-      <c r="Z51" s="13"/>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51" s="2"/>
-      <c r="AD51" s="17"/>
-      <c r="AE51" s="13"/>
-      <c r="AF51" s="18"/>
-      <c r="AG51" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="13"/>
-      <c r="AI51" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="11"/>
-      <c r="AL51" s="17"/>
-      <c r="AM51" s="11"/>
-      <c r="AN51" s="11"/>
-      <c r="AO51" s="11"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="17"/>
-      <c r="AR51" s="17"/>
-      <c r="AS51" s="12"/>
-      <c r="AT51" s="11"/>
-      <c r="AU51" s="11"/>
-      <c r="AV51" s="12"/>
-      <c r="AW51" s="11"/>
-      <c r="AX51" s="11"/>
-      <c r="AY51" s="11"/>
-      <c r="AZ51" s="11"/>
-      <c r="BA51" s="11"/>
-      <c r="BB51" s="11"/>
-      <c r="BC51" s="11"/>
-      <c r="BD51" s="11"/>
-      <c r="BE51" s="11"/>
-      <c r="BF51" s="11"/>
-      <c r="BG51" s="11"/>
-      <c r="BH51" s="12"/>
-      <c r="BI51" s="20"/>
-      <c r="BJ51" s="20"/>
-      <c r="BK51" s="20"/>
-      <c r="BL51" s="20"/>
-      <c r="BM51" s="20"/>
-      <c r="BN51" s="20"/>
-      <c r="BO51" s="20"/>
-      <c r="BP51" s="20"/>
-      <c r="BQ51" s="20"/>
-      <c r="BR51" s="11"/>
+      <c r="BN43" s="20"/>
+      <c r="BO43" s="20"/>
+      <c r="BP43" s="20"/>
+      <c r="BQ43" s="20"/>
+      <c r="BR43" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16375,268 +14829,220 @@
     <hyperlink ref="M13" r:id="rId92" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N13" r:id="rId93"/>
     <hyperlink ref="AW13" r:id="rId94" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A24DDJVBL7M2LD"/>
-    <hyperlink ref="C14" r:id="rId95" tooltip="https://www.amazon.co.jp/dp/B07221ZY3D"/>
-    <hyperlink ref="G14" r:id="rId96" tooltip="https://www.amazon.co.jp/stores/%E3%83%9F%E3%83%8A%E3%83%88%E3%83%AF%E3%83%BC%E3%82%AF%E3%82%B9/page/7E77FCE9-0862-4057-994E-E5C8A30E6C6D?lp_asin=B07221ZY3D&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J14" r:id="rId97" tooltip="https://www.amazon.co.jp/dp/B07221ZY3D?psc=1"/>
-    <hyperlink ref="K14" r:id="rId98" tooltip="https://images-na.ssl-images-amazon.com/images/I/81CP4O0lOLL._AC_US600_.jpg"/>
-    <hyperlink ref="L14" r:id="rId99" tooltip="https://www.amazon.co.jp/dp/B07221ZY3D"/>
+    <hyperlink ref="C14" r:id="rId95" tooltip="https://www.amazon.co.jp/dp/B0F2HHFGNK"/>
+    <hyperlink ref="G14" r:id="rId96" tooltip="https://www.amazon.co.jp/stores/MOVA/page/1C66BA39-85DA-4EF9-BEE1-43A9D48A27F4?lp_asin=B0F2HHFGNK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J14" r:id="rId97" tooltip="https://www.amazon.co.jp/dp/B0F2HHFGNK?psc=1"/>
+    <hyperlink ref="K14" r:id="rId98" tooltip="https://m.media-amazon.com/images/I/315qxl2azwL._AC_US600_.jpg"/>
+    <hyperlink ref="L14" r:id="rId99" tooltip="https://www.amazon.co.jp/dp/B0F2HHFGNK"/>
     <hyperlink ref="M14" r:id="rId100" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N14" r:id="rId101"/>
-    <hyperlink ref="AW14" r:id="rId102" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A35R5657DWBR35"/>
-    <hyperlink ref="C15" r:id="rId103" tooltip="https://www.amazon.co.jp/dp/B0F2HHFGNK"/>
-    <hyperlink ref="G15" r:id="rId104" tooltip="https://www.amazon.co.jp/stores/MOVA/page/1C66BA39-85DA-4EF9-BEE1-43A9D48A27F4?lp_asin=B0F2HHFGNK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J15" r:id="rId105" tooltip="https://www.amazon.co.jp/dp/B0F2HHFGNK?psc=1"/>
-    <hyperlink ref="K15" r:id="rId106" tooltip="https://m.media-amazon.com/images/I/315qxl2azwL._AC_US600_.jpg"/>
-    <hyperlink ref="L15" r:id="rId107" tooltip="https://www.amazon.co.jp/dp/B0F2HHFGNK"/>
+    <hyperlink ref="AW14" r:id="rId102" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGV9IL82JY4FQ"/>
+    <hyperlink ref="C15" r:id="rId103" tooltip="https://www.amazon.co.jp/dp/B0GXDDCQ3M"/>
+    <hyperlink ref="G15" r:id="rId104" tooltip="https://www.amazon.co.jp/stores/YTEPRO/page/A41402B4-AFBB-4C28-82E0-CB901555CE9C?lp_asin=B0GXDDCQ3M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J15" r:id="rId105" tooltip="https://www.amazon.co.jp/dp/B0GXDDCQ3M?psc=1"/>
+    <hyperlink ref="K15" r:id="rId106" tooltip="https://m.media-amazon.com/images/I/41LdBO8M33L._AC_US600_.jpg"/>
+    <hyperlink ref="L15" r:id="rId107" tooltip="https://www.amazon.co.jp/dp/B0GXDDCQ3M"/>
     <hyperlink ref="M15" r:id="rId108" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N15" r:id="rId109"/>
-    <hyperlink ref="AW15" r:id="rId110" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGV9IL82JY4FQ"/>
-    <hyperlink ref="C16" r:id="rId111" tooltip="https://www.amazon.co.jp/dp/B0GXDDCQ3M"/>
-    <hyperlink ref="G16" r:id="rId112" tooltip="https://www.amazon.co.jp/stores/YTEPRO/page/A41402B4-AFBB-4C28-82E0-CB901555CE9C?lp_asin=B0GXDDCQ3M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J16" r:id="rId113" tooltip="https://www.amazon.co.jp/dp/B0GXDDCQ3M?psc=1"/>
-    <hyperlink ref="K16" r:id="rId114" tooltip="https://m.media-amazon.com/images/I/41LdBO8M33L._AC_US600_.jpg"/>
-    <hyperlink ref="L16" r:id="rId115" tooltip="https://www.amazon.co.jp/dp/B0GXDDCQ3M"/>
+    <hyperlink ref="AW15" r:id="rId110" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AKYM3EEDP1T3V"/>
+    <hyperlink ref="C16" r:id="rId111" tooltip="https://www.amazon.co.jp/dp/B0HGLFDYL5"/>
+    <hyperlink ref="G16" r:id="rId112" tooltip="https://www.amazon.co.jpnull"/>
+    <hyperlink ref="J16" r:id="rId113" tooltip="https://www.amazon.co.jp/dp/B0HGLFDYL5?psc=1"/>
+    <hyperlink ref="K16" r:id="rId114" tooltip="https://images-na.ssl-images-amazon.com/images/I/51O6JFJ9JfL._AC_US600_.jpg"/>
+    <hyperlink ref="L16" r:id="rId115" tooltip="https://www.amazon.co.jp/dp/B0HGLFDYL5"/>
     <hyperlink ref="M16" r:id="rId116" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N16" r:id="rId117"/>
-    <hyperlink ref="AW16" r:id="rId118" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AKYM3EEDP1T3V"/>
-    <hyperlink ref="C17" r:id="rId119" tooltip="https://www.amazon.co.jp/dp/B0HGLFDYL5"/>
-    <hyperlink ref="G17" r:id="rId120" tooltip="https://www.amazon.co.jpnull"/>
-    <hyperlink ref="J17" r:id="rId121" tooltip="https://www.amazon.co.jp/dp/B0HGLFDYL5?psc=1"/>
-    <hyperlink ref="K17" r:id="rId122" tooltip="https://images-na.ssl-images-amazon.com/images/I/51O6JFJ9JfL._AC_US600_.jpg"/>
-    <hyperlink ref="L17" r:id="rId123" tooltip="https://www.amazon.co.jp/dp/B0HGLFDYL5"/>
-    <hyperlink ref="M17" r:id="rId124" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="AW16" r:id="rId118" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A24DDJVBL7M2LD"/>
+    <hyperlink ref="C17" r:id="rId119" tooltip="https://www.amazon.co.jp/dp/B0FC18HMRN"/>
+    <hyperlink ref="G17" r:id="rId120" tooltip="https://www.amazon.co.jp/stores/mindoo/page/195B1567-B86E-4B16-A2C3-065A70917DA9?lp_asin=B0FC18HMRN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J17" r:id="rId121" tooltip="https://www.amazon.co.jp/dp/B0FC18HMRN?psc=1"/>
+    <hyperlink ref="K17" r:id="rId122" tooltip="https://m.media-amazon.com/images/I/21vmJWLJAbL._AC_US600_.jpg"/>
+    <hyperlink ref="L17" r:id="rId123" tooltip="https://www.amazon.co.jp/dp/B0FC18HMRN"/>
+    <hyperlink ref="M17" r:id="rId124" tooltip="https://www.amazon.co.jp/b?node=218875650051"/>
     <hyperlink ref="N17" r:id="rId125"/>
-    <hyperlink ref="AW17" r:id="rId126" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A24DDJVBL7M2LD"/>
-    <hyperlink ref="C18" r:id="rId127" tooltip="https://www.amazon.co.jp/dp/B00UUMDMZI"/>
-    <hyperlink ref="G18" r:id="rId128" tooltip="https://www.amazon.co.jp/stores/%E3%83%91%E3%82%AA%E3%83%83%E3%82%AFPAOCK/page/24D761D2-B57C-4143-A66C-A75C65189148?lp_asin=B00UUMDMZI&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J18" r:id="rId129" tooltip="https://www.amazon.co.jp/dp/B00UUMDMZI?psc=1"/>
-    <hyperlink ref="K18" r:id="rId130" tooltip="https://images-na.ssl-images-amazon.com/images/I/71Y5D7AH22L._AC_US600_.jpg"/>
-    <hyperlink ref="L18" r:id="rId131" tooltip="https://www.amazon.co.jp/dp/B00UUMDMZI"/>
-    <hyperlink ref="M18" r:id="rId132" tooltip="https://www.amazon.co.jp/b?node=3450851051"/>
+    <hyperlink ref="AW17" r:id="rId126" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3KERCWTE76M89"/>
+    <hyperlink ref="C18" r:id="rId127" tooltip="https://www.amazon.co.jp/dp/B0HGLNPJPC"/>
+    <hyperlink ref="G18" r:id="rId128" tooltip="https://www.amazon.co.jp/stores/%E3%83%80%E3%82%A4%E3%82%BD%E3%83%B3/page/0456F1ED-24D4-4719-8E99-5936EC69346F?lp_asin=B0HGLNPJPC&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J18" r:id="rId129" tooltip="https://www.amazon.co.jp/dp/B0HGLNPJPC?psc=1"/>
+    <hyperlink ref="K18" r:id="rId130" tooltip="https://images-na.ssl-images-amazon.com/images/I/616rJ-dkmUL._AC_US600_.jpg"/>
+    <hyperlink ref="L18" r:id="rId131" tooltip="https://www.amazon.co.jp/dp/B0HGLNPJPC"/>
+    <hyperlink ref="M18" r:id="rId132" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N18" r:id="rId133"/>
-    <hyperlink ref="C19" r:id="rId134" tooltip="https://www.amazon.co.jp/dp/B0FC18HMRN"/>
-    <hyperlink ref="G19" r:id="rId135" tooltip="https://www.amazon.co.jp/stores/mindoo/page/195B1567-B86E-4B16-A2C3-065A70917DA9?lp_asin=B0FC18HMRN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J19" r:id="rId136" tooltip="https://www.amazon.co.jp/dp/B0FC18HMRN?psc=1"/>
-    <hyperlink ref="K19" r:id="rId137" tooltip="https://m.media-amazon.com/images/I/21vmJWLJAbL._AC_US600_.jpg"/>
-    <hyperlink ref="L19" r:id="rId138" tooltip="https://www.amazon.co.jp/dp/B0FC18HMRN"/>
-    <hyperlink ref="M19" r:id="rId139" tooltip="https://www.amazon.co.jp/b?node=218875650051"/>
-    <hyperlink ref="N19" r:id="rId140"/>
-    <hyperlink ref="AW19" r:id="rId141" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3KERCWTE76M89"/>
-    <hyperlink ref="C20" r:id="rId142" tooltip="https://www.amazon.co.jp/dp/B0HGLNPJPC"/>
-    <hyperlink ref="G20" r:id="rId143" tooltip="https://www.amazon.co.jp/stores/%E3%83%80%E3%82%A4%E3%82%BD%E3%83%B3/page/0456F1ED-24D4-4719-8E99-5936EC69346F?lp_asin=B0HGLNPJPC&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J20" r:id="rId144" tooltip="https://www.amazon.co.jp/dp/B0HGLNPJPC?psc=1"/>
-    <hyperlink ref="K20" r:id="rId145" tooltip="https://images-na.ssl-images-amazon.com/images/I/616rJ-dkmUL._AC_US600_.jpg"/>
-    <hyperlink ref="L20" r:id="rId146" tooltip="https://www.amazon.co.jp/dp/B0HGLNPJPC"/>
-    <hyperlink ref="M20" r:id="rId147" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N20" r:id="rId148"/>
-    <hyperlink ref="AW20" r:id="rId149" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KRDRXNL1G5FA"/>
-    <hyperlink ref="C21" r:id="rId150" tooltip="https://www.amazon.co.jp/dp/B0HHN8HTLL"/>
-    <hyperlink ref="G21" r:id="rId151" tooltip="https://www.amazon.co.jpnull"/>
-    <hyperlink ref="J21" r:id="rId152" tooltip="https://www.amazon.co.jp/dp/B0HHN8HTLL?psc=1"/>
-    <hyperlink ref="K21" r:id="rId153" tooltip="https://images-na.ssl-images-amazon.com/images/I/51z7B-TmeXL._AC_US600_.jpg"/>
-    <hyperlink ref="L21" r:id="rId154" tooltip="https://www.amazon.co.jp/dp/B0HHN8HTLL"/>
-    <hyperlink ref="M21" r:id="rId155" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N21" r:id="rId156"/>
-    <hyperlink ref="AW21" r:id="rId157" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3JH293JNBT5IZ"/>
-    <hyperlink ref="C22" r:id="rId158" tooltip="https://www.amazon.co.jp/dp/B0FK9HN17M"/>
-    <hyperlink ref="G22" r:id="rId159" tooltip="https://www.amazon.co.jp/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FK9HN17M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J22" r:id="rId160" tooltip="https://www.amazon.co.jp/dp/B0FK9HN17M?psc=1"/>
-    <hyperlink ref="K22" r:id="rId161" tooltip="https://images-na.ssl-images-amazon.com/images/I/61gNWZ3JF6L._AC_US600_.jpg"/>
-    <hyperlink ref="L22" r:id="rId162" tooltip="https://www.amazon.co.jp/dp/B0FK9HN17M"/>
-    <hyperlink ref="M22" r:id="rId163" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N22" r:id="rId164"/>
-    <hyperlink ref="AW22" r:id="rId165" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2SR0DVTECF9BI"/>
-    <hyperlink ref="C23" r:id="rId166" tooltip="https://www.amazon.co.jp/dp/B0CPPHYW3B"/>
-    <hyperlink ref="G23" r:id="rId167" tooltip="https://www.amazon.co.jp/stores/%E3%83%9F%E3%83%8A%E3%83%88%E3%83%AF%E3%83%BC%E3%82%AF%E3%82%B9/page/7E77FCE9-0862-4057-994E-E5C8A30E6C6D?lp_asin=B0CPPHYW3B&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J23" r:id="rId168" tooltip="https://www.amazon.co.jp/dp/B0CPPHYW3B?psc=1"/>
-    <hyperlink ref="K23" r:id="rId169" tooltip="https://m.media-amazon.com/images/I/41ZrF14970L._AC_US600_.jpg"/>
-    <hyperlink ref="L23" r:id="rId170" tooltip="https://www.amazon.co.jp/dp/B0CPPHYW3B"/>
-    <hyperlink ref="M23" r:id="rId171" tooltip="https://www.amazon.co.jp/b?node=3450851051"/>
-    <hyperlink ref="N23" r:id="rId172"/>
-    <hyperlink ref="AW23" r:id="rId173" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A35R5657DWBR35"/>
-    <hyperlink ref="C24" r:id="rId174" tooltip="https://www.amazon.co.jp/dp/B0BW467WC5"/>
-    <hyperlink ref="G24" r:id="rId175" tooltip="https://www.amazon.co.jp/stores/Longsafe%E3%83%AD%E3%83%B3%E3%82%B0%E3%82%BB%E3%83%BC%E3%83%95/page/BD939425-D017-4A77-8C40-744607798C52?lp_asin=B0BW467WC5&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J24" r:id="rId176" tooltip="https://www.amazon.co.jp/dp/B0BW467WC5?psc=1"/>
-    <hyperlink ref="K24" r:id="rId177" tooltip="https://images-na.ssl-images-amazon.com/images/I/71y30b4dMOL._AC_US600_.jpg"/>
-    <hyperlink ref="L24" r:id="rId178" tooltip="https://www.amazon.co.jp/dp/B0BW467WC5"/>
-    <hyperlink ref="M24" r:id="rId179" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N24" r:id="rId180"/>
-    <hyperlink ref="AW24" r:id="rId181" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A21SFW0V5BVYM"/>
-    <hyperlink ref="C25" r:id="rId182" tooltip="https://www.amazon.co.jp/dp/B07KR2J116"/>
-    <hyperlink ref="G25" r:id="rId183" tooltip="https://www.amazon.co.jp/stores/%E3%83%9F%E3%83%8A%E3%83%88%E3%83%AF%E3%83%BC%E3%82%AF%E3%82%B9/page/7E77FCE9-0862-4057-994E-E5C8A30E6C6D?lp_asin=B07KR2J116&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J25" r:id="rId184" tooltip="https://www.amazon.co.jp/dp/B07KR2J116?psc=1"/>
-    <hyperlink ref="K25" r:id="rId185" tooltip="https://m.media-amazon.com/images/I/41ovXwP+o+L._AC_US600_.jpg"/>
-    <hyperlink ref="L25" r:id="rId186" tooltip="https://www.amazon.co.jp/dp/B07KR2J116"/>
-    <hyperlink ref="M25" r:id="rId187" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N25" r:id="rId188"/>
-    <hyperlink ref="AW25" r:id="rId189" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A35R5657DWBR35"/>
-    <hyperlink ref="C26" r:id="rId190" tooltip="https://www.amazon.co.jp/dp/B0D2VPQT2V"/>
-    <hyperlink ref="G26" r:id="rId191" tooltip="https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0D2VPQT2V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J26" r:id="rId192" tooltip="https://www.amazon.co.jp/dp/B0D2VPQT2V?psc=1"/>
-    <hyperlink ref="K26" r:id="rId193" tooltip="https://images-na.ssl-images-amazon.com/images/I/61KqhLRxwYL._AC_US600_.jpg"/>
-    <hyperlink ref="L26" r:id="rId194" tooltip="https://www.amazon.co.jp/dp/B0D2VPQT2V"/>
-    <hyperlink ref="M26" r:id="rId195" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N26" r:id="rId196"/>
-    <hyperlink ref="AW26" r:id="rId197" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WSQAA92JSPUW"/>
-    <hyperlink ref="C27" r:id="rId198" tooltip="https://www.amazon.co.jp/dp/B0CZKHJXNG"/>
-    <hyperlink ref="G27" r:id="rId199" tooltip="https://www.amazon.co.jp/stores/Eureka/page/0DAE79FF-361F-4FFE-9129-4ACEDAF99AD5?lp_asin=B0CZKHJXNG&amp;ref_=ast_bln"/>
-    <hyperlink ref="J27" r:id="rId200" tooltip="https://www.amazon.co.jp/dp/B0CZKHJXNG?psc=1"/>
-    <hyperlink ref="K27" r:id="rId201" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41nAma6e0eL._AC_US600_.jpg"/>
-    <hyperlink ref="L27" r:id="rId202" tooltip="https://www.amazon.co.jp/dp/B0CZKHJXNG"/>
-    <hyperlink ref="M27" r:id="rId203" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N27" r:id="rId204"/>
-    <hyperlink ref="AW27" r:id="rId205" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3JXXBYW06ZFVU"/>
-    <hyperlink ref="C28" r:id="rId206" tooltip="https://www.amazon.co.jp/dp/B0HHN61KPZ"/>
-    <hyperlink ref="G28" r:id="rId207" tooltip="https://www.amazon.co.jpnull"/>
-    <hyperlink ref="J28" r:id="rId208" tooltip="https://www.amazon.co.jp/dp/B0HHN61KPZ?psc=1"/>
-    <hyperlink ref="K28" r:id="rId209" tooltip="https://m.media-amazon.com/images/I/31eRC+N6IRL._AC_US600_.jpg"/>
-    <hyperlink ref="L28" r:id="rId210" tooltip="https://www.amazon.co.jp/dp/B0HHN61KPZ"/>
-    <hyperlink ref="M28" r:id="rId211" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N28" r:id="rId212"/>
-    <hyperlink ref="AW28" r:id="rId213" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KRDRXNL1G5FA"/>
-    <hyperlink ref="C29" r:id="rId214" tooltip="https://www.amazon.co.jp/dp/B0CNJT8933"/>
-    <hyperlink ref="G29" r:id="rId215" tooltip="https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0CNJT8933&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J29" r:id="rId216" tooltip="https://www.amazon.co.jp/dp/B0CNJT8933?psc=1"/>
-    <hyperlink ref="K29" r:id="rId217" tooltip="https://images-na.ssl-images-amazon.com/images/I/61b-HbgIkBL._AC_US600_.jpg"/>
-    <hyperlink ref="L29" r:id="rId218" tooltip="https://www.amazon.co.jp/dp/B0CNJT8933"/>
-    <hyperlink ref="M29" r:id="rId219" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N29" r:id="rId220"/>
-    <hyperlink ref="AW29" r:id="rId221" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WV0MTJICL1UJ"/>
-    <hyperlink ref="C30" r:id="rId222" tooltip="https://www.amazon.co.jp/dp/B08XLW562G"/>
-    <hyperlink ref="G30" r:id="rId223" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=%E4%B8%8D%E6%98%8E"/>
-    <hyperlink ref="J30" r:id="rId224" tooltip="https://www.amazon.co.jp/dp/B08XLW562G?psc=1"/>
-    <hyperlink ref="K30" r:id="rId225" tooltip="https://images-na.ssl-images-amazon.com/images/I/31NELDCajpL._AC_US600_.jpg"/>
-    <hyperlink ref="L30" r:id="rId226" tooltip="https://www.amazon.co.jp/dp/B08XLW562G"/>
-    <hyperlink ref="M30" r:id="rId227" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N30" r:id="rId228"/>
-    <hyperlink ref="AW30" r:id="rId229" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2RYDH17QLIL3V"/>
-    <hyperlink ref="C31" r:id="rId230" tooltip="https://www.amazon.co.jp/dp/B0GS4QDH7R"/>
-    <hyperlink ref="G31" r:id="rId231" tooltip="https://www.amazon.co.jp/stores/%E3%83%A6%E3%83%AF%E3%83%B3%E3%83%88%EF%BC%88UWANT/page/CFD932E4-87F0-4563-8A00-7E6F0611A613?lp_asin=B0GS4QDH7R&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J31" r:id="rId232" tooltip="https://www.amazon.co.jp/dp/B0GS4QDH7R?psc=1"/>
-    <hyperlink ref="K31" r:id="rId233" tooltip="https://images-na.ssl-images-amazon.com/images/I/61j3dNdQj4L._AC_US600_.jpg"/>
-    <hyperlink ref="L31" r:id="rId234" tooltip="https://www.amazon.co.jp/dp/B0GS4QDH7R"/>
-    <hyperlink ref="M31" r:id="rId235" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N31" r:id="rId236"/>
-    <hyperlink ref="AW31" r:id="rId237" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1O5QS9O13RS09"/>
-    <hyperlink ref="C32" r:id="rId238" tooltip="https://www.amazon.co.jp/dp/B0H6DZMNPV"/>
-    <hyperlink ref="G32" r:id="rId239" tooltip="https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0H6DZMNPV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J32" r:id="rId240" tooltip="https://www.amazon.co.jp/dp/B0H6DZMNPV?psc=1"/>
-    <hyperlink ref="K32" r:id="rId241" tooltip="https://m.media-amazon.com/images/I/31ddgJIAJbL._AC_US600_.jpg"/>
-    <hyperlink ref="L32" r:id="rId242" tooltip="https://www.amazon.co.jp/dp/B0H6DZMNPV"/>
-    <hyperlink ref="M32" r:id="rId243" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N32" r:id="rId244"/>
-    <hyperlink ref="AW32" r:id="rId245" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WV0MTJICL1UJ"/>
-    <hyperlink ref="C33" r:id="rId246" tooltip="https://www.amazon.co.jp/dp/B01IEEM1KU"/>
-    <hyperlink ref="G33" r:id="rId247" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J33" r:id="rId248" tooltip="https://www.amazon.co.jp/dp/B01IEEM1KU?psc=1"/>
-    <hyperlink ref="K33" r:id="rId249" tooltip="https://images-fe.ssl-images-amazon.com/images/I/413OXJC5WwL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L33" r:id="rId250" tooltip="https://www.amazon.co.jp/dp/B01IEEM1KU"/>
-    <hyperlink ref="C34" r:id="rId251" tooltip="https://www.amazon.co.jp/dp/B09P2RKRWX"/>
-    <hyperlink ref="G34" r:id="rId252" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J34" r:id="rId253" tooltip="https://www.amazon.co.jp/dp/B09P2RKRWX?psc=1"/>
-    <hyperlink ref="K34" r:id="rId254" tooltip="https://images-fe.ssl-images-amazon.com/images/I/615lYQCrd2L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L34" r:id="rId255" tooltip="https://www.amazon.co.jp/dp/B09P2RKRWX"/>
-    <hyperlink ref="C35" r:id="rId256" tooltip="https://www.amazon.co.jp/dp/B0C4HGZ1L6"/>
-    <hyperlink ref="G35" r:id="rId257" tooltip="https://www.amazon.co.jp/stores/NEODIT%E3%83%8D%E3%82%AA%E3%83%87%E3%82%A3%E3%83%83%E3%83%88/page/CD7250ED-8E04-4E58-A881-68B2A928AE8C?lp_asin=B0C4HGZ1L6&amp;ref_=ast_bln"/>
-    <hyperlink ref="J35" r:id="rId258" tooltip="https://www.amazon.co.jp/dp/B0C4HGZ1L6?psc=1"/>
-    <hyperlink ref="K35" r:id="rId259" tooltip="https://images-na.ssl-images-amazon.com/images/I/81DHFglSw9L._AC_US600_.jpg"/>
-    <hyperlink ref="L35" r:id="rId260" tooltip="https://www.amazon.co.jp/dp/B0C4HGZ1L6"/>
-    <hyperlink ref="M35" r:id="rId261" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N35" r:id="rId262"/>
-    <hyperlink ref="AW35" r:id="rId263" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2YB9P0HYGN84U"/>
-    <hyperlink ref="C36" r:id="rId264" tooltip="https://www.amazon.co.jp/dp/B0CF9P7W51"/>
-    <hyperlink ref="G36" r:id="rId265" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J36" r:id="rId266" tooltip="https://www.amazon.co.jp/dp/B0CF9P7W51?psc=1"/>
-    <hyperlink ref="K36" r:id="rId267" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61bJ0J+PfIL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L36" r:id="rId268" tooltip="https://www.amazon.co.jp/dp/B0CF9P7W51"/>
-    <hyperlink ref="C37" r:id="rId269" tooltip="https://www.amazon.co.jp/dp/B0D5HBSJFX"/>
-    <hyperlink ref="G37" r:id="rId270" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J37" r:id="rId271" tooltip="https://www.amazon.co.jp/dp/B0D5HBSJFX?psc=1"/>
-    <hyperlink ref="K37" r:id="rId272" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51ioK4Vk3NL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L37" r:id="rId273" tooltip="https://www.amazon.co.jp/dp/B0D5HBSJFX"/>
-    <hyperlink ref="C38" r:id="rId274" tooltip="https://www.amazon.co.jp/dp/B0DHV7QRSK"/>
-    <hyperlink ref="G38" r:id="rId275" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J38" r:id="rId276" tooltip="https://www.amazon.co.jp/dp/B0DHV7QRSK?psc=1"/>
-    <hyperlink ref="K38" r:id="rId277" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61Coq6GGchL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L38" r:id="rId278" tooltip="https://www.amazon.co.jp/dp/B0DHV7QRSK"/>
-    <hyperlink ref="C39" r:id="rId279" tooltip="https://www.amazon.co.jp/dp/B0DXY4BJ5K"/>
-    <hyperlink ref="G39" r:id="rId280" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J39" r:id="rId281" tooltip="https://www.amazon.co.jp/dp/B0DXY4BJ5K?psc=1"/>
-    <hyperlink ref="K39" r:id="rId282" tooltip="https://images-fe.ssl-images-amazon.com/images/I/516bWwYYlQL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L39" r:id="rId283" tooltip="https://www.amazon.co.jp/dp/B0DXY4BJ5K"/>
-    <hyperlink ref="C40" r:id="rId284" tooltip="https://www.amazon.co.jp/dp/B0FBR52FBV"/>
-    <hyperlink ref="G40" r:id="rId285" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J40" r:id="rId286" tooltip="https://www.amazon.co.jp/dp/B0FBR52FBV?psc=1"/>
-    <hyperlink ref="K40" r:id="rId287" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51Gx-JJE9mL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L40" r:id="rId288" tooltip="https://www.amazon.co.jp/dp/B0FBR52FBV"/>
-    <hyperlink ref="C41" r:id="rId289" tooltip="https://www.amazon.co.jp/dp/B0FGC7422M"/>
-    <hyperlink ref="G41" r:id="rId290" tooltip="https://www.amazon.co.jp/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FGC7422M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J41" r:id="rId291" tooltip="https://www.amazon.co.jp/dp/B0FGC7422M?psc=1"/>
-    <hyperlink ref="K41" r:id="rId292" tooltip="https://images-na.ssl-images-amazon.com/images/I/51PDVCpecuL._AC_US600_.jpg"/>
-    <hyperlink ref="L41" r:id="rId293" tooltip="https://www.amazon.co.jp/dp/B0FGC7422M"/>
-    <hyperlink ref="M41" r:id="rId294" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N41" r:id="rId295"/>
-    <hyperlink ref="AW41" r:id="rId296" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1UV3PJGHZIHW6"/>
-    <hyperlink ref="C42" r:id="rId297" tooltip="https://www.amazon.co.jp/dp/B0FL2KXDMX"/>
-    <hyperlink ref="G42" r:id="rId298" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J42" r:id="rId299" tooltip="https://www.amazon.co.jp/dp/B0FL2KXDMX?psc=1"/>
-    <hyperlink ref="K42" r:id="rId300" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61j+d1U1UHL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L42" r:id="rId301" tooltip="https://www.amazon.co.jp/dp/B0FL2KXDMX"/>
-    <hyperlink ref="C43" r:id="rId302" tooltip="https://www.amazon.co.jp/dp/B0FPXLZSWP"/>
-    <hyperlink ref="G43" r:id="rId303" tooltip="https://www.amazon.co.jp/stores/NARWAL/page/48E89FF8-D8FF-42EA-91FA-300E4D5D5CBA?lp_asin=B0FPXLZSWP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J43" r:id="rId304" tooltip="https://www.amazon.co.jp/dp/B0FPXLZSWP?psc=1"/>
-    <hyperlink ref="K43" r:id="rId305" tooltip="https://images-na.ssl-images-amazon.com/images/I/51o9M+0xsCL._AC_US600_.jpg"/>
-    <hyperlink ref="L43" r:id="rId306" tooltip="https://www.amazon.co.jp/dp/B0FPXLZSWP"/>
-    <hyperlink ref="M43" r:id="rId307" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N43" r:id="rId308"/>
-    <hyperlink ref="C44" r:id="rId309" tooltip="https://www.amazon.co.jp/dp/B0G4RMHHWV"/>
-    <hyperlink ref="G44" r:id="rId310" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J44" r:id="rId311" tooltip="https://www.amazon.co.jp/dp/B0G4RMHHWV?psc=1"/>
-    <hyperlink ref="K44" r:id="rId312" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61OeNyo9j3L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L44" r:id="rId313" tooltip="https://www.amazon.co.jp/dp/B0G4RMHHWV"/>
-    <hyperlink ref="C45" r:id="rId314" tooltip="https://www.amazon.co.jp/dp/B0GJZNZZBG"/>
-    <hyperlink ref="G45" r:id="rId315" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J45" r:id="rId316" tooltip="https://www.amazon.co.jp/dp/B0GJZNZZBG?psc=1"/>
-    <hyperlink ref="K45" r:id="rId317" tooltip="https://images-fe.ssl-images-amazon.com/images/I/41bBBiQaOQL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L45" r:id="rId318" tooltip="https://www.amazon.co.jp/dp/B0GJZNZZBG"/>
-    <hyperlink ref="C46" r:id="rId319" tooltip="https://www.amazon.co.jp/dp/B0GP76R477"/>
-    <hyperlink ref="G46" r:id="rId320" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J46" r:id="rId321" tooltip="https://www.amazon.co.jp/dp/B0GP76R477?psc=1"/>
-    <hyperlink ref="K46" r:id="rId322" tooltip="https://images-fe.ssl-images-amazon.com/images/I/21UZYI0dymL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L46" r:id="rId323" tooltip="https://www.amazon.co.jp/dp/B0GP76R477"/>
-    <hyperlink ref="C47" r:id="rId324" tooltip="https://www.amazon.co.jp/dp/B0H5WDMCLX"/>
-    <hyperlink ref="G47" r:id="rId325" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J47" r:id="rId326" tooltip="https://www.amazon.co.jp/dp/B0H5WDMCLX?psc=1"/>
-    <hyperlink ref="K47" r:id="rId327" tooltip="https://images-fe.ssl-images-amazon.com/images/I/31ZGQqLBLNL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L47" r:id="rId328" tooltip="https://www.amazon.co.jp/dp/B0H5WDMCLX"/>
-    <hyperlink ref="C48" r:id="rId329" tooltip="https://www.amazon.co.jp/dp/B0H99BC6SP"/>
-    <hyperlink ref="G48" r:id="rId330" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J48" r:id="rId331" tooltip="https://www.amazon.co.jp/dp/B0H99BC6SP?psc=1"/>
-    <hyperlink ref="K48" r:id="rId332" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61w-2YImFbL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L48" r:id="rId333" tooltip="https://www.amazon.co.jp/dp/B0H99BC6SP"/>
-    <hyperlink ref="C49" r:id="rId334" tooltip="https://www.amazon.co.jp/dp/B0HFW5C8BX"/>
-    <hyperlink ref="G49" r:id="rId335" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J49" r:id="rId336" tooltip="https://www.amazon.co.jp/dp/B0HFW5C8BX?psc=1"/>
-    <hyperlink ref="K49" r:id="rId337" tooltip="https://images-fe.ssl-images-amazon.com/images/I/41tXijm5C2L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L49" r:id="rId338" tooltip="https://www.amazon.co.jp/dp/B0HFW5C8BX"/>
-    <hyperlink ref="C50" r:id="rId339" tooltip="https://www.amazon.co.jp/dp/B0HJ22HH2H"/>
-    <hyperlink ref="G50" r:id="rId340" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J50" r:id="rId341" tooltip="https://www.amazon.co.jp/dp/B0HJ22HH2H?psc=1"/>
-    <hyperlink ref="K50" r:id="rId342" tooltip="https://images-fe.ssl-images-amazon.com/images/I/519xXj4dKQL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L50" r:id="rId343" tooltip="https://www.amazon.co.jp/dp/B0HJ22HH2H"/>
-    <hyperlink ref="C51" r:id="rId344" tooltip="https://www.amazon.co.jp/dp/B0HJZ443Z7"/>
-    <hyperlink ref="G51" r:id="rId345" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J51" r:id="rId346" tooltip="https://www.amazon.co.jp/dp/B0HJZ443Z7?psc=1"/>
-    <hyperlink ref="K51" r:id="rId347" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51QZUn8fZ2L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId348" tooltip="https://www.amazon.co.jp/dp/B0HJZ443Z7"/>
+    <hyperlink ref="AW18" r:id="rId134" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KRDRXNL1G5FA"/>
+    <hyperlink ref="C19" r:id="rId135" tooltip="https://www.amazon.co.jp/dp/B0HHN8HTLL"/>
+    <hyperlink ref="G19" r:id="rId136" tooltip="https://www.amazon.co.jpnull"/>
+    <hyperlink ref="J19" r:id="rId137" tooltip="https://www.amazon.co.jp/dp/B0HHN8HTLL?psc=1"/>
+    <hyperlink ref="K19" r:id="rId138" tooltip="https://images-na.ssl-images-amazon.com/images/I/51z7B-TmeXL._AC_US600_.jpg"/>
+    <hyperlink ref="L19" r:id="rId139" tooltip="https://www.amazon.co.jp/dp/B0HHN8HTLL"/>
+    <hyperlink ref="M19" r:id="rId140" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="N19" r:id="rId141"/>
+    <hyperlink ref="AW19" r:id="rId142" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3JH293JNBT5IZ"/>
+    <hyperlink ref="C20" r:id="rId143" tooltip="https://www.amazon.co.jp/dp/B0FK9HN17M"/>
+    <hyperlink ref="G20" r:id="rId144" tooltip="https://www.amazon.co.jp/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FK9HN17M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J20" r:id="rId145" tooltip="https://www.amazon.co.jp/dp/B0FK9HN17M?psc=1"/>
+    <hyperlink ref="K20" r:id="rId146" tooltip="https://images-na.ssl-images-amazon.com/images/I/61gNWZ3JF6L._AC_US600_.jpg"/>
+    <hyperlink ref="L20" r:id="rId147" tooltip="https://www.amazon.co.jp/dp/B0FK9HN17M"/>
+    <hyperlink ref="M20" r:id="rId148" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="N20" r:id="rId149"/>
+    <hyperlink ref="AW20" r:id="rId150" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2SR0DVTECF9BI"/>
+    <hyperlink ref="C21" r:id="rId151" tooltip="https://www.amazon.co.jp/dp/B0CPPHYW3B"/>
+    <hyperlink ref="G21" r:id="rId152" tooltip="https://www.amazon.co.jp/stores/%E3%83%9F%E3%83%8A%E3%83%88%E3%83%AF%E3%83%BC%E3%82%AF%E3%82%B9/page/7E77FCE9-0862-4057-994E-E5C8A30E6C6D?lp_asin=B0CPPHYW3B&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J21" r:id="rId153" tooltip="https://www.amazon.co.jp/dp/B0CPPHYW3B?psc=1"/>
+    <hyperlink ref="K21" r:id="rId154" tooltip="https://m.media-amazon.com/images/I/41ZrF14970L._AC_US600_.jpg"/>
+    <hyperlink ref="L21" r:id="rId155" tooltip="https://www.amazon.co.jp/dp/B0CPPHYW3B"/>
+    <hyperlink ref="M21" r:id="rId156" tooltip="https://www.amazon.co.jp/b?node=3450851051"/>
+    <hyperlink ref="N21" r:id="rId157"/>
+    <hyperlink ref="AW21" r:id="rId158" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A35R5657DWBR35"/>
+    <hyperlink ref="C22" r:id="rId159" tooltip="https://www.amazon.co.jp/dp/B07KR2J116"/>
+    <hyperlink ref="G22" r:id="rId160" tooltip="https://www.amazon.co.jp/stores/%E3%83%9F%E3%83%8A%E3%83%88%E3%83%AF%E3%83%BC%E3%82%AF%E3%82%B9/page/7E77FCE9-0862-4057-994E-E5C8A30E6C6D?lp_asin=B07KR2J116&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J22" r:id="rId161" tooltip="https://www.amazon.co.jp/dp/B07KR2J116?psc=1"/>
+    <hyperlink ref="K22" r:id="rId162" tooltip="https://m.media-amazon.com/images/I/41ovXwP+o+L._AC_US600_.jpg"/>
+    <hyperlink ref="L22" r:id="rId163" tooltip="https://www.amazon.co.jp/dp/B07KR2J116"/>
+    <hyperlink ref="M22" r:id="rId164" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="N22" r:id="rId165"/>
+    <hyperlink ref="AW22" r:id="rId166" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A35R5657DWBR35"/>
+    <hyperlink ref="C23" r:id="rId167" tooltip="https://www.amazon.co.jp/dp/B0D2VPQT2V"/>
+    <hyperlink ref="G23" r:id="rId168" tooltip="https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0D2VPQT2V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J23" r:id="rId169" tooltip="https://www.amazon.co.jp/dp/B0D2VPQT2V?psc=1"/>
+    <hyperlink ref="K23" r:id="rId170" tooltip="https://images-na.ssl-images-amazon.com/images/I/61KqhLRxwYL._AC_US600_.jpg"/>
+    <hyperlink ref="L23" r:id="rId171" tooltip="https://www.amazon.co.jp/dp/B0D2VPQT2V"/>
+    <hyperlink ref="M23" r:id="rId172" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="N23" r:id="rId173"/>
+    <hyperlink ref="AW23" r:id="rId174" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WSQAA92JSPUW"/>
+    <hyperlink ref="C24" r:id="rId175" tooltip="https://www.amazon.co.jp/dp/B0CZKHJXNG"/>
+    <hyperlink ref="G24" r:id="rId176" tooltip="https://www.amazon.co.jp/stores/Eureka/page/0DAE79FF-361F-4FFE-9129-4ACEDAF99AD5?lp_asin=B0CZKHJXNG&amp;ref_=ast_bln"/>
+    <hyperlink ref="J24" r:id="rId177" tooltip="https://www.amazon.co.jp/dp/B0CZKHJXNG?psc=1"/>
+    <hyperlink ref="K24" r:id="rId178" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41nAma6e0eL._AC_US600_.jpg"/>
+    <hyperlink ref="L24" r:id="rId179" tooltip="https://www.amazon.co.jp/dp/B0CZKHJXNG"/>
+    <hyperlink ref="M24" r:id="rId180" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="N24" r:id="rId181"/>
+    <hyperlink ref="AW24" r:id="rId182" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3JXXBYW06ZFVU"/>
+    <hyperlink ref="C25" r:id="rId183" tooltip="https://www.amazon.co.jp/dp/B0HHN61KPZ"/>
+    <hyperlink ref="G25" r:id="rId184" tooltip="https://www.amazon.co.jpnull"/>
+    <hyperlink ref="J25" r:id="rId185" tooltip="https://www.amazon.co.jp/dp/B0HHN61KPZ?psc=1"/>
+    <hyperlink ref="K25" r:id="rId186" tooltip="https://m.media-amazon.com/images/I/31eRC+N6IRL._AC_US600_.jpg"/>
+    <hyperlink ref="L25" r:id="rId187" tooltip="https://www.amazon.co.jp/dp/B0HHN61KPZ"/>
+    <hyperlink ref="M25" r:id="rId188" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="N25" r:id="rId189"/>
+    <hyperlink ref="AW25" r:id="rId190" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KRDRXNL1G5FA"/>
+    <hyperlink ref="C26" r:id="rId191" tooltip="https://www.amazon.co.jp/dp/B0CNJT8933"/>
+    <hyperlink ref="G26" r:id="rId192" tooltip="https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0CNJT8933&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J26" r:id="rId193" tooltip="https://www.amazon.co.jp/dp/B0CNJT8933?psc=1"/>
+    <hyperlink ref="K26" r:id="rId194" tooltip="https://images-na.ssl-images-amazon.com/images/I/61b-HbgIkBL._AC_US600_.jpg"/>
+    <hyperlink ref="L26" r:id="rId195" tooltip="https://www.amazon.co.jp/dp/B0CNJT8933"/>
+    <hyperlink ref="M26" r:id="rId196" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="N26" r:id="rId197"/>
+    <hyperlink ref="AW26" r:id="rId198" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WV0MTJICL1UJ"/>
+    <hyperlink ref="C27" r:id="rId199" tooltip="https://www.amazon.co.jp/dp/B08XLW562G"/>
+    <hyperlink ref="G27" r:id="rId200" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=%E4%B8%8D%E6%98%8E"/>
+    <hyperlink ref="J27" r:id="rId201" tooltip="https://www.amazon.co.jp/dp/B08XLW562G?psc=1"/>
+    <hyperlink ref="K27" r:id="rId202" tooltip="https://images-na.ssl-images-amazon.com/images/I/31NELDCajpL._AC_US600_.jpg"/>
+    <hyperlink ref="L27" r:id="rId203" tooltip="https://www.amazon.co.jp/dp/B08XLW562G"/>
+    <hyperlink ref="M27" r:id="rId204" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="N27" r:id="rId205"/>
+    <hyperlink ref="AW27" r:id="rId206" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2RYDH17QLIL3V"/>
+    <hyperlink ref="C28" r:id="rId207" tooltip="https://www.amazon.co.jp/dp/B0GS4QDH7R"/>
+    <hyperlink ref="G28" r:id="rId208" tooltip="https://www.amazon.co.jp/stores/%E3%83%A6%E3%83%AF%E3%83%B3%E3%83%88%EF%BC%88UWANT/page/CFD932E4-87F0-4563-8A00-7E6F0611A613?lp_asin=B0GS4QDH7R&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J28" r:id="rId209" tooltip="https://www.amazon.co.jp/dp/B0GS4QDH7R?psc=1"/>
+    <hyperlink ref="K28" r:id="rId210" tooltip="https://images-na.ssl-images-amazon.com/images/I/61j3dNdQj4L._AC_US600_.jpg"/>
+    <hyperlink ref="L28" r:id="rId211" tooltip="https://www.amazon.co.jp/dp/B0GS4QDH7R"/>
+    <hyperlink ref="M28" r:id="rId212" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="N28" r:id="rId213"/>
+    <hyperlink ref="AW28" r:id="rId214" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1O5QS9O13RS09"/>
+    <hyperlink ref="C29" r:id="rId215" tooltip="https://www.amazon.co.jp/dp/B0H6DZMNPV"/>
+    <hyperlink ref="G29" r:id="rId216" tooltip="https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0H6DZMNPV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J29" r:id="rId217" tooltip="https://www.amazon.co.jp/dp/B0H6DZMNPV?psc=1"/>
+    <hyperlink ref="K29" r:id="rId218" tooltip="https://m.media-amazon.com/images/I/31ddgJIAJbL._AC_US600_.jpg"/>
+    <hyperlink ref="L29" r:id="rId219" tooltip="https://www.amazon.co.jp/dp/B0H6DZMNPV"/>
+    <hyperlink ref="M29" r:id="rId220" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="N29" r:id="rId221"/>
+    <hyperlink ref="AW29" r:id="rId222" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WV0MTJICL1UJ"/>
+    <hyperlink ref="C30" r:id="rId223" tooltip="https://www.amazon.co.jp/dp/B09P2RKRWX"/>
+    <hyperlink ref="G30" r:id="rId224" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J30" r:id="rId225" tooltip="https://www.amazon.co.jp/dp/B09P2RKRWX?psc=1"/>
+    <hyperlink ref="K30" r:id="rId226" tooltip="https://images-fe.ssl-images-amazon.com/images/I/615lYQCrd2L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L30" r:id="rId227" tooltip="https://www.amazon.co.jp/dp/B09P2RKRWX"/>
+    <hyperlink ref="C31" r:id="rId228" tooltip="https://www.amazon.co.jp/dp/B0C4HGZ1L6"/>
+    <hyperlink ref="G31" r:id="rId229" tooltip="https://www.amazon.co.jp/stores/NEODIT%E3%83%8D%E3%82%AA%E3%83%87%E3%82%A3%E3%83%83%E3%83%88/page/CD7250ED-8E04-4E58-A881-68B2A928AE8C?lp_asin=B0C4HGZ1L6&amp;ref_=ast_bln"/>
+    <hyperlink ref="J31" r:id="rId230" tooltip="https://www.amazon.co.jp/dp/B0C4HGZ1L6?psc=1"/>
+    <hyperlink ref="K31" r:id="rId231" tooltip="https://images-na.ssl-images-amazon.com/images/I/81DHFglSw9L._AC_US600_.jpg"/>
+    <hyperlink ref="L31" r:id="rId232" tooltip="https://www.amazon.co.jp/dp/B0C4HGZ1L6"/>
+    <hyperlink ref="M31" r:id="rId233" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="N31" r:id="rId234"/>
+    <hyperlink ref="AW31" r:id="rId235" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2YB9P0HYGN84U"/>
+    <hyperlink ref="C32" r:id="rId236" tooltip="https://www.amazon.co.jp/dp/B0CF9P7W51"/>
+    <hyperlink ref="G32" r:id="rId237" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J32" r:id="rId238" tooltip="https://www.amazon.co.jp/dp/B0CF9P7W51?psc=1"/>
+    <hyperlink ref="K32" r:id="rId239" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61bJ0J+PfIL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L32" r:id="rId240" tooltip="https://www.amazon.co.jp/dp/B0CF9P7W51"/>
+    <hyperlink ref="C33" r:id="rId241" tooltip="https://www.amazon.co.jp/dp/B0D5HBSJFX"/>
+    <hyperlink ref="G33" r:id="rId242" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J33" r:id="rId243" tooltip="https://www.amazon.co.jp/dp/B0D5HBSJFX?psc=1"/>
+    <hyperlink ref="K33" r:id="rId244" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51ioK4Vk3NL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L33" r:id="rId245" tooltip="https://www.amazon.co.jp/dp/B0D5HBSJFX"/>
+    <hyperlink ref="C34" r:id="rId246" tooltip="https://www.amazon.co.jp/dp/B0DHV7QRSK"/>
+    <hyperlink ref="G34" r:id="rId247" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J34" r:id="rId248" tooltip="https://www.amazon.co.jp/dp/B0DHV7QRSK?psc=1"/>
+    <hyperlink ref="K34" r:id="rId249" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61Coq6GGchL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L34" r:id="rId250" tooltip="https://www.amazon.co.jp/dp/B0DHV7QRSK"/>
+    <hyperlink ref="C35" r:id="rId251" tooltip="https://www.amazon.co.jp/dp/B0DXY4BJ5K"/>
+    <hyperlink ref="G35" r:id="rId252" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J35" r:id="rId253" tooltip="https://www.amazon.co.jp/dp/B0DXY4BJ5K?psc=1"/>
+    <hyperlink ref="K35" r:id="rId254" tooltip="https://images-fe.ssl-images-amazon.com/images/I/516bWwYYlQL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L35" r:id="rId255" tooltip="https://www.amazon.co.jp/dp/B0DXY4BJ5K"/>
+    <hyperlink ref="C36" r:id="rId256" tooltip="https://www.amazon.co.jp/dp/B0FBR52FBV"/>
+    <hyperlink ref="G36" r:id="rId257" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J36" r:id="rId258" tooltip="https://www.amazon.co.jp/dp/B0FBR52FBV?psc=1"/>
+    <hyperlink ref="K36" r:id="rId259" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51Gx-JJE9mL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L36" r:id="rId260" tooltip="https://www.amazon.co.jp/dp/B0FBR52FBV"/>
+    <hyperlink ref="C37" r:id="rId261" tooltip="https://www.amazon.co.jp/dp/B0FGC7422M"/>
+    <hyperlink ref="G37" r:id="rId262" tooltip="https://www.amazon.co.jp/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FGC7422M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J37" r:id="rId263" tooltip="https://www.amazon.co.jp/dp/B0FGC7422M?psc=1"/>
+    <hyperlink ref="K37" r:id="rId264" tooltip="https://images-na.ssl-images-amazon.com/images/I/51PDVCpecuL._AC_US600_.jpg"/>
+    <hyperlink ref="L37" r:id="rId265" tooltip="https://www.amazon.co.jp/dp/B0FGC7422M"/>
+    <hyperlink ref="M37" r:id="rId266" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="N37" r:id="rId267"/>
+    <hyperlink ref="AW37" r:id="rId268" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1UV3PJGHZIHW6"/>
+    <hyperlink ref="C38" r:id="rId269" tooltip="https://www.amazon.co.jp/dp/B0FL2KXDMX"/>
+    <hyperlink ref="G38" r:id="rId270" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J38" r:id="rId271" tooltip="https://www.amazon.co.jp/dp/B0FL2KXDMX?psc=1"/>
+    <hyperlink ref="K38" r:id="rId272" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61j+d1U1UHL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L38" r:id="rId273" tooltip="https://www.amazon.co.jp/dp/B0FL2KXDMX"/>
+    <hyperlink ref="C39" r:id="rId274" tooltip="https://www.amazon.co.jp/dp/B0FPXLZSWP"/>
+    <hyperlink ref="G39" r:id="rId275" tooltip="https://www.amazon.co.jp/stores/NARWAL/page/48E89FF8-D8FF-42EA-91FA-300E4D5D5CBA?lp_asin=B0FPXLZSWP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J39" r:id="rId276" tooltip="https://www.amazon.co.jp/dp/B0FPXLZSWP?psc=1"/>
+    <hyperlink ref="K39" r:id="rId277" tooltip="https://images-na.ssl-images-amazon.com/images/I/51o9M+0xsCL._AC_US600_.jpg"/>
+    <hyperlink ref="L39" r:id="rId278" tooltip="https://www.amazon.co.jp/dp/B0FPXLZSWP"/>
+    <hyperlink ref="M39" r:id="rId279" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="N39" r:id="rId280"/>
+    <hyperlink ref="C40" r:id="rId281" tooltip="https://www.amazon.co.jp/dp/B0G4RMHHWV"/>
+    <hyperlink ref="G40" r:id="rId282" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J40" r:id="rId283" tooltip="https://www.amazon.co.jp/dp/B0G4RMHHWV?psc=1"/>
+    <hyperlink ref="K40" r:id="rId284" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61OeNyo9j3L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L40" r:id="rId285" tooltip="https://www.amazon.co.jp/dp/B0G4RMHHWV"/>
+    <hyperlink ref="C41" r:id="rId286" tooltip="https://www.amazon.co.jp/dp/B0GJZNZZBG"/>
+    <hyperlink ref="G41" r:id="rId287" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J41" r:id="rId288" tooltip="https://www.amazon.co.jp/dp/B0GJZNZZBG?psc=1"/>
+    <hyperlink ref="K41" r:id="rId289" tooltip="https://images-fe.ssl-images-amazon.com/images/I/41bBBiQaOQL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L41" r:id="rId290" tooltip="https://www.amazon.co.jp/dp/B0GJZNZZBG"/>
+    <hyperlink ref="C42" r:id="rId291" tooltip="https://www.amazon.co.jp/dp/B0GP76R477"/>
+    <hyperlink ref="G42" r:id="rId292" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J42" r:id="rId293" tooltip="https://www.amazon.co.jp/dp/B0GP76R477?psc=1"/>
+    <hyperlink ref="K42" r:id="rId294" tooltip="https://images-fe.ssl-images-amazon.com/images/I/21UZYI0dymL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L42" r:id="rId295" tooltip="https://www.amazon.co.jp/dp/B0GP76R477"/>
+    <hyperlink ref="C43" r:id="rId296" tooltip="https://www.amazon.co.jp/dp/B0H5WDMCLX"/>
+    <hyperlink ref="G43" r:id="rId297" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J43" r:id="rId298" tooltip="https://www.amazon.co.jp/dp/B0H5WDMCLX?psc=1"/>
+    <hyperlink ref="K43" r:id="rId299" tooltip="https://images-fe.ssl-images-amazon.com/images/I/31ZGQqLBLNL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L43" r:id="rId300" tooltip="https://www.amazon.co.jp/dp/B0H5WDMCLX"/>
   </hyperlinks>
-  <drawing r:id="rId349"/>
+  <drawing r:id="rId301"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -16700,7 +15106,7 @@
         <v>73103.28519195612</v>
       </c>
       <c r="G2" s="19">
-        <v>0.12237136465324384</v>
+        <v>0.12992874109263658</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16721,7 +15127,7 @@
         <v>26550.59405940594</v>
       </c>
       <c r="G3" s="19">
-        <v>0.11297539149888143</v>
+        <v>0.11995249406175772</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16742,7 +15148,7 @@
         <v>48783.15238095238</v>
       </c>
       <c r="G4" s="19">
-        <v>0.04697986577181208</v>
+        <v>0.0498812351543943</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16763,7 +15169,7 @@
         <v>4980.0</v>
       </c>
       <c r="G5" s="19">
-        <v>0.363758389261745</v>
+        <v>0.3862232779097387</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16784,7 +15190,7 @@
         <v>39377.755102040814</v>
       </c>
       <c r="G6" s="19">
-        <v>0.04384787472035794</v>
+        <v>0.04655581947743468</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16805,7 +15211,7 @@
         <v>15955.0</v>
       </c>
       <c r="G7" s="19">
-        <v>0.09888143176733781</v>
+        <v>0.10498812351543943</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16826,7 +15232,7 @@
         <v>64446.76119402985</v>
       </c>
       <c r="G8" s="19">
-        <v>0.014988814317673379</v>
+        <v>0.015914489311163897</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16847,181 +15253,177 @@
         <v>8999.0</v>
       </c>
       <c r="G9" s="19">
-        <v>0.09798657718120805</v>
+        <v>0.10403800475059383</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>ミナトワークス</t>
+          <t>MOVA</t>
         </is>
       </c>
       <c r="B10" s="13">
-        <v>196</v>
+        <v>41</v>
       </c>
       <c r="C10" s="13">
-        <v>2368720</v>
+        <v>1348080</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
       <c r="F10" s="13">
-        <v>12085.30612244898</v>
+        <v>32880.0</v>
       </c>
       <c r="G10" s="19">
-        <v>0.04384787472035794</v>
+        <v>0.009738717339667458</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>MOVA</t>
+          <t>mindoo</t>
         </is>
       </c>
       <c r="B11" s="13">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="C11" s="13">
-        <v>1348080</v>
+        <v>822800</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
       <c r="F11" s="13">
-        <v>32880.0</v>
+        <v>74800.0</v>
       </c>
       <c r="G11" s="19">
-        <v>0.009172259507829978</v>
+        <v>0.0026128266033254156</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>パオック(PAOCK)</t>
+          <t>ミナトワークス</t>
         </is>
       </c>
       <c r="B12" s="13">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="C12" s="13">
-        <v>868284</v>
+        <v>799320</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
       <c r="F12" s="13">
-        <v>9756.0</v>
+        <v>12687.619047619048</v>
       </c>
       <c r="G12" s="19">
-        <v>0.019910514541387026</v>
+        <v>0.01496437054631829</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>mindoo</t>
+          <t>EUREKA</t>
         </is>
       </c>
       <c r="B13" s="13">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C13" s="13">
-        <v>822800</v>
+        <v>214800</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
       <c r="F13" s="13">
-        <v>74800.0</v>
+        <v>7160.0</v>
       </c>
       <c r="G13" s="19">
-        <v>0.0024608501118568234</v>
+        <v>0.007125890736342043</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>longsafe</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="B14" s="13">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C14" s="13">
-        <v>448362</v>
+        <v>135000</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
       <c r="F14" s="13">
-        <v>11799.0</v>
+        <v>4500.0</v>
       </c>
       <c r="G14" s="19">
-        <v>0.008501118568232663</v>
+        <v>0.007125890736342043</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>EUREKA</t>
+          <t>uwant</t>
         </is>
       </c>
       <c r="B15" s="13">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C15" s="13">
-        <v>214800</v>
+        <v>46644</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
       <c r="F15" s="13">
-        <v>7160.0</v>
+        <v>11661.0</v>
       </c>
       <c r="G15" s="19">
-        <v>0.006711409395973154</v>
+        <v>0.0009501187648456057</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>NARWAL(ナーワル)</t>
         </is>
       </c>
       <c r="B16" s="13">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C16" s="13">
-        <v>135000</v>
+        <v>0</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
-      <c r="F16" s="13">
-        <v>4500.0</v>
-      </c>
+      <c r="F16" s="13"/>
       <c r="G16" s="19">
-        <v>0.006711409395973154</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>uwant</t>
+          <t>NEODIT</t>
         </is>
       </c>
       <c r="B17" s="13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C17" s="13">
-        <v>46644</v>
+        <v>0</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
-      <c r="F17" s="13">
-        <v>11661.0</v>
-      </c>
+      <c r="F17" s="13"/>
       <c r="G17" s="19">
-        <v>0.0008948545861297539</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>NARWAL(ナーワル)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B18" s="13">
@@ -17034,44 +15436,6 @@
       <c r="E18" s="13"/>
       <c r="F18" s="13"/>
       <c r="G18" s="19">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>NEODIT</t>
-        </is>
-      </c>
-      <c r="B19" s="13">
-        <v>0</v>
-      </c>
-      <c r="C19" s="13">
-        <v>0</v>
-      </c>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="19">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B20" s="13">
-        <v>0</v>
-      </c>
-      <c r="C20" s="13">
-        <v>0</v>
-      </c>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="19">
         <v>0.0</v>
       </c>
     </row>
@@ -17083,7 +15447,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -17136,18 +15500,18 @@
         </is>
       </c>
       <c r="B2" s="13">
-        <v>952</v>
+        <v>863</v>
       </c>
       <c r="C2" s="13">
-        <v>43671714</v>
+        <v>42803430</v>
       </c>
       <c r="D2" s="13"/>
       <c r="E2" s="13"/>
       <c r="F2" s="13">
-        <v>45873.649159663866</v>
+        <v>49598.41251448436</v>
       </c>
       <c r="G2" s="19">
-        <v>0.21297539149888142</v>
+        <v>0.20498812351543944</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17168,7 +15532,7 @@
         <v>26550.59405940594</v>
       </c>
       <c r="G3" s="19">
-        <v>0.11297539149888143</v>
+        <v>0.11995249406175772</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17189,7 +15553,7 @@
         <v>52362.628272251306</v>
       </c>
       <c r="G4" s="19">
-        <v>0.042729306487695747</v>
+        <v>0.04536817102137767</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17210,7 +15574,7 @@
         <v>4980.0</v>
       </c>
       <c r="G5" s="19">
-        <v>0.363758389261745</v>
+        <v>0.3862232779097387</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17231,7 +15595,7 @@
         <v>39377.755102040814</v>
       </c>
       <c r="G6" s="19">
-        <v>0.04384787472035794</v>
+        <v>0.04655581947743468</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17252,7 +15616,7 @@
         <v>64446.76119402985</v>
       </c>
       <c r="G7" s="19">
-        <v>0.014988814317673379</v>
+        <v>0.015914489311163897</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17273,7 +15637,7 @@
         <v>8999.0</v>
       </c>
       <c r="G8" s="19">
-        <v>0.09798657718120805</v>
+        <v>0.10403800475059383</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17294,91 +15658,91 @@
         <v>26773.219047619048</v>
       </c>
       <c r="G9" s="19">
-        <v>0.02348993288590604</v>
+        <v>0.02494061757719715</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>【ミナトワークス】</t>
+          <t>MOVA Official</t>
         </is>
       </c>
       <c r="B10" s="13">
-        <v>196</v>
+        <v>41</v>
       </c>
       <c r="C10" s="13">
-        <v>2368720</v>
+        <v>1348080</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
       <c r="F10" s="13">
-        <v>12085.30612244898</v>
+        <v>32880.0</v>
       </c>
       <c r="G10" s="19">
-        <v>0.04384787472035794</v>
+        <v>0.009738717339667458</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>MOVA Official</t>
+          <t>〈公式〉Mindoo</t>
         </is>
       </c>
       <c r="B11" s="13">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="C11" s="13">
-        <v>1348080</v>
+        <v>822800</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
       <c r="F11" s="13">
-        <v>32880.0</v>
+        <v>74800.0</v>
       </c>
       <c r="G11" s="19">
-        <v>0.009172259507829978</v>
+        <v>0.0026128266033254156</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>〈公式〉Mindoo</t>
+          <t>ダイソン公式ストア</t>
         </is>
       </c>
       <c r="B12" s="13">
         <v>11</v>
       </c>
       <c r="C12" s="13">
-        <v>822800</v>
+        <v>819989</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
       <c r="F12" s="13">
-        <v>74800.0</v>
+        <v>74544.45454545454</v>
       </c>
       <c r="G12" s="19">
-        <v>0.0024608501118568234</v>
+        <v>0.0026128266033254156</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>ダイソン公式ストア</t>
+          <t>【ミナトワークス】</t>
         </is>
       </c>
       <c r="B13" s="13">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="C13" s="13">
-        <v>819989</v>
+        <v>799320</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
       <c r="F13" s="13">
-        <v>74544.45454545454</v>
+        <v>12687.619047619048</v>
       </c>
       <c r="G13" s="19">
-        <v>0.0024608501118568234</v>
+        <v>0.01496437054631829</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17399,118 +15763,116 @@
         <v>60500.0</v>
       </c>
       <c r="G14" s="19">
-        <v>0.0022371364653243847</v>
+        <v>0.0023752969121140144</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>YSJAPAN</t>
+          <t>Dreametech JP</t>
         </is>
       </c>
       <c r="B15" s="13">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="C15" s="13">
-        <v>448362</v>
+        <v>243200</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
       <c r="F15" s="13">
-        <v>11799.0</v>
+        <v>12800.0</v>
       </c>
       <c r="G15" s="19">
-        <v>0.008501118568232663</v>
+        <v>0.004513064133016627</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>Dreametech JP</t>
+          <t>Eureka Japan</t>
         </is>
       </c>
       <c r="B16" s="13">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C16" s="13">
-        <v>243200</v>
+        <v>214800</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
       <c r="F16" s="13">
-        <v>12800.0</v>
+        <v>7160.0</v>
       </c>
       <c r="G16" s="19">
-        <v>0.004250559284116331</v>
+        <v>0.007125890736342043</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Eureka Japan</t>
+          <t>Abeショップ関西</t>
         </is>
       </c>
       <c r="B17" s="13">
         <v>30</v>
       </c>
       <c r="C17" s="13">
-        <v>214800</v>
+        <v>135000</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
       <c r="F17" s="13">
-        <v>7160.0</v>
+        <v>4500.0</v>
       </c>
       <c r="G17" s="19">
-        <v>0.006711409395973154</v>
+        <v>0.007125890736342043</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>Abeショップ関西</t>
+          <t>Uwant公式ストア</t>
         </is>
       </c>
       <c r="B18" s="13">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C18" s="13">
-        <v>135000</v>
+        <v>46644</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
       <c r="F18" s="13">
-        <v>4500.0</v>
+        <v>11661.0</v>
       </c>
       <c r="G18" s="19">
-        <v>0.006711409395973154</v>
+        <v>0.0009501187648456057</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>Uwant公式ストア</t>
+          <t>-公式ストア</t>
         </is>
       </c>
       <c r="B19" s="13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C19" s="13">
-        <v>46644</v>
+        <v>0</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
-      <c r="F19" s="13">
-        <v>11661.0</v>
-      </c>
+      <c r="F19" s="13"/>
       <c r="G19" s="19">
-        <v>0.0008948545861297539</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>-公式ストア</t>
+          <t>Neodit-tools</t>
         </is>
       </c>
       <c r="B20" s="13">
@@ -17529,7 +15891,7 @@
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Neodit-tools</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B21" s="13">
@@ -17542,25 +15904,6 @@
       <c r="E21" s="13"/>
       <c r="F21" s="13"/>
       <c r="G21" s="19">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B22" s="13">
-        <v>0</v>
-      </c>
-      <c r="C22" s="13">
-        <v>0</v>
-      </c>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="19">
         <v>0.0</v>
       </c>
     </row>

--- a/data/merged/2026-10-08/MERGED_JP_Wet-Dry-Floor-Washer_2026-10-08.xlsx
+++ b/data/merged/2026-10-08/MERGED_JP_Wet-Dry-Floor-Washer_2026-10-08.xlsx
@@ -5011,13 +5011,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5407,13 +5407,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6134,94 +6134,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId40" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="41" name="Product 41">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId41" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="42" name="Product 42">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId42" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6563,7 +6475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR43"/>
+  <dimension ref="A1:BR41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -10146,115 +10058,117 @@
       <c r="B16" s="11"/>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>B0HGLFDYL5</t>
+          <t>B0FC18HMRN</t>
         </is>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="12"/>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>Dyson(ダイソン)</t>
+          <t>mindoo</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jpnull</t>
+          <t>https://www.amazon.co.jp/stores/mindoo/page/195B1567-B86E-4B16-A2C3-065A70917DA9?lp_asin=B0FC18HMRN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>Dyson(ダイソン) 吸尘器 无线 Dyson V12s Detect Slim Submarine (SV46 SU) 棒 手持式吸尘器 气旋 可用水擦拭 干式吸尘器 带充电支架 【从现在开始用水擦拭】 (New V8 slim)</t>
+          <t>Mindoo AquaX Plus Mindoo AquaX Plus 擦水吸尘器 [吸水、擦拭、除菌、自我清洁、自动干燥 5合1] 自走式 垃圾收集1台5用 强力吸力 超轻 自动清洗 高性能 (黑色)s軽量モデル 3モード 自動洗浄 温風乾燥</t>
         </is>
       </c>
       <c r="I16" s="12"/>
       <c r="J16" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0HGLFDYL5?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FC18HMRN?psc=1</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51O6JFJ9JfL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/21vmJWLJAbL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L16" s="12" t="inlineStr">
         <is>
-          <t>B0HGLFDYL5</t>
+          <t>B0FC18HMRN</t>
         </is>
       </c>
       <c r="M16" s="12" t="inlineStr">
         <is>
-          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
+          <t>ホーム＆キッチン:家電:生活家電:掃除機:家庭用湿式/乾式掃除機</t>
         </is>
       </c>
       <c r="N16" s="12" t="inlineStr">
         <is>
-          <t>DIY・工具・ガーデン</t>
+          <t>ホーム＆キッチン</t>
         </is>
       </c>
       <c r="O16" s="13">
-        <v>50012</v>
+        <v>216985</v>
       </c>
       <c r="P16" s="13">
-        <v>-10041</v>
+        <v>-31468</v>
       </c>
       <c r="Q16" s="14">
-        <v>-0.25</v>
+        <v>-0.17</v>
       </c>
       <c r="R16" s="15" t="inlineStr">
         <is>
-          <t>ウェットドライショップ掃除機</t>
+          <t>家庭用湿式/乾式掃除機</t>
         </is>
       </c>
       <c r="S16" s="16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="T16" s="13">
-        <v>37</v>
-      </c>
-      <c r="U16" s="14"/>
+        <v>11</v>
+      </c>
+      <c r="U16" s="14">
+        <v>-0.17</v>
+      </c>
       <c r="V16" s="13">
-        <v>1044140</v>
+        <v>822800</v>
       </c>
       <c r="W16" s="13"/>
       <c r="X16" s="13"/>
       <c r="Y16" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z16" s="13">
-        <v>28220</v>
+        <v>74800</v>
       </c>
       <c r="AA16"/>
       <c r="AB16"/>
       <c r="AC16" s="2"/>
       <c r="AD16" s="17">
-        <v>230</v>
+        <v>18</v>
       </c>
       <c r="AE16" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" s="18">
         <v>4.3</v>
       </c>
       <c r="AG16" s="19">
-        <v>0</v>
+        <v>0.0909</v>
       </c>
       <c r="AH16" s="13">
         <v>781</v>
       </c>
       <c r="AI16" s="14">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="AJ16"/>
       <c r="AK16" s="11" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="AL16" s="17">
-        <v>42</v>
+        <v>373</v>
       </c>
       <c r="AM16" s="11" t="inlineStr">
         <is>
@@ -10265,14 +10179,14 @@
       <c r="AO16" s="11"/>
       <c r="AP16"/>
       <c r="AQ16" s="17">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AR16" s="17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AS16" s="12" t="inlineStr">
         <is>
-          <t>PENTACT JAPAN(土・日・祝休まず出荷 / インボイス登録店)</t>
+          <t>〈公式〉Mindoo</t>
         </is>
       </c>
       <c r="AT16" s="11" t="inlineStr">
@@ -10287,60 +10201,72 @@
       </c>
       <c r="AV16" s="12" t="inlineStr">
         <is>
-          <t>荒川区 東京都 1160014 JP</t>
+          <t>港区三田 東京都 1080073 JP</t>
         </is>
       </c>
       <c r="AW16" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A24DDJVBL7M2LD</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3KERCWTE76M89</t>
         </is>
       </c>
       <c r="AX16" s="11"/>
-      <c r="AY16" s="11"/>
+      <c r="AY16" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ16" s="11"/>
       <c r="BA16" s="11"/>
       <c r="BB16" s="11"/>
-      <c r="BC16" s="11"/>
-      <c r="BD16" s="11"/>
+      <c r="BC16" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD16" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE16" s="11"/>
       <c r="BF16" s="11"/>
       <c r="BG16" s="11"/>
       <c r="BH16" s="12"/>
-      <c r="BI16" s="20"/>
+      <c r="BI16" s="20" t="inlineStr">
+        <is>
+          <t>Amazon おすすめ</t>
+        </is>
+      </c>
       <c r="BJ16" s="20" t="inlineStr">
         <is>
-          <t>3.2 kg</t>
-        </is>
-      </c>
-      <c r="BK16" s="20" t="inlineStr">
-        <is>
-          <t>3.20 kg</t>
-        </is>
-      </c>
+          <t>3.6 キログラム</t>
+        </is>
+      </c>
+      <c r="BK16" s="20"/>
       <c r="BL16" s="20" t="inlineStr">
         <is>
-          <t>25.7長さ x 25.3幅 x 112.9高さ cm</t>
+          <t>24.9長さ x 23.2幅 x 110高さ cm</t>
         </is>
       </c>
       <c r="BM16" s="20"/>
       <c r="BN16" s="20" t="inlineStr">
         <is>
-          <t>3.7 kg</t>
+          <t>6.2 kg</t>
         </is>
       </c>
       <c r="BO16" s="20" t="inlineStr">
         <is>
-          <t>3.70 kg</t>
+          <t>6.20 kg</t>
         </is>
       </c>
       <c r="BP16" s="20" t="inlineStr">
         <is>
-          <t>74 x 27 x 15.5 cm</t>
+          <t>64.5 x 30.5 x 23.8 cm</t>
         </is>
       </c>
       <c r="BQ16" s="20" t="inlineStr">
         <is>
-          <t>74.00 x 27.00 x 15.50 cm</t>
+          <t>64.50 x 30.50 x 23.80 cm</t>
         </is>
       </c>
       <c r="BR16" s="11" t="inlineStr">
@@ -10356,117 +10282,113 @@
       <c r="B17" s="11"/>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>B0FC18HMRN</t>
+          <t>B0HGLNPJPC</t>
         </is>
       </c>
       <c r="D17" s="12"/>
       <c r="E17" s="12"/>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>mindoo</t>
+          <t>Dyson(ダイソン)</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/mindoo/page/195B1567-B86E-4B16-A2C3-065A70917DA9?lp_asin=B0FC18HMRN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/%E3%83%80%E3%82%A4%E3%82%BD%E3%83%B3/page/0456F1ED-24D4-4719-8E99-5936EC69346F?lp_asin=B0HGLNPJPC&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>Mindoo AquaX Plus Mindoo AquaX Plus 擦水吸尘器 [吸水、擦拭、除菌、自我清洁、自动干燥 5合1] 自走式 垃圾收集1台5用 强力吸力 超轻 自动清洗 高性能 (黑色)s軽量モデル 3モード 自動洗浄 温風乾燥</t>
+          <t>Dyson(ダイソン) V12 Detect Slim Absolute 无线吸尘器 戴森官方限定 延长保修1年款s棒手持吸尘器,旋风,带充电座,Amazon.co.jp 独家,高功能 LED 和自动模式不会错过垃圾</t>
         </is>
       </c>
       <c r="I17" s="12"/>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FC18HMRN?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0HGLNPJPC?psc=1</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/21vmJWLJAbL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/616rJ-dkmUL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>B0FC18HMRN</t>
+          <t>B0HGLNPJPC</t>
         </is>
       </c>
       <c r="M17" s="12" t="inlineStr">
         <is>
-          <t>ホーム＆キッチン:家電:生活家電:掃除機:家庭用湿式/乾式掃除機</t>
+          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
         </is>
       </c>
       <c r="N17" s="12" t="inlineStr">
         <is>
-          <t>ホーム＆キッチン</t>
+          <t>DIY・工具・ガーデン</t>
         </is>
       </c>
       <c r="O17" s="13">
-        <v>216985</v>
+        <v>140536</v>
       </c>
       <c r="P17" s="13">
-        <v>-31468</v>
+        <v>-86532</v>
       </c>
       <c r="Q17" s="14">
-        <v>-0.17</v>
+        <v>-1.6</v>
       </c>
       <c r="R17" s="15" t="inlineStr">
         <is>
-          <t>家庭用湿式/乾式掃除機</t>
+          <t>ウェットドライショップ掃除機</t>
         </is>
       </c>
       <c r="S17" s="16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>40</t>
         </is>
       </c>
       <c r="T17" s="13">
-        <v>11</v>
-      </c>
-      <c r="U17" s="14">
-        <v>-0.17</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="U17" s="14"/>
       <c r="V17" s="13">
-        <v>822800</v>
+        <v>639992</v>
       </c>
       <c r="W17" s="13"/>
       <c r="X17" s="13"/>
       <c r="Y17" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z17" s="13">
-        <v>74800</v>
+        <v>79999</v>
       </c>
       <c r="AA17"/>
       <c r="AB17"/>
       <c r="AC17" s="2"/>
       <c r="AD17" s="17">
-        <v>18</v>
+        <v>229</v>
       </c>
       <c r="AE17" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF17" s="18">
         <v>4.3</v>
       </c>
       <c r="AG17" s="19">
-        <v>0.0909</v>
-      </c>
-      <c r="AH17" s="13">
-        <v>781</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH17" s="13"/>
       <c r="AI17" s="14">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="AJ17"/>
       <c r="AK17" s="11" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AL17" s="17">
-        <v>373</v>
+        <v>42</v>
       </c>
       <c r="AM17" s="11" t="inlineStr">
         <is>
@@ -10476,15 +10398,13 @@
       <c r="AN17" s="11"/>
       <c r="AO17" s="11"/>
       <c r="AP17"/>
-      <c r="AQ17" s="17">
-        <v>9</v>
-      </c>
+      <c r="AQ17" s="17"/>
       <c r="AR17" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS17" s="12" t="inlineStr">
         <is>
-          <t>〈公式〉Mindoo</t>
+          <t>ダイソン公式ストア</t>
         </is>
       </c>
       <c r="AT17" s="11" t="inlineStr">
@@ -10499,79 +10419,47 @@
       </c>
       <c r="AV17" s="12" t="inlineStr">
         <is>
-          <t>港区三田 東京都 1080073 JP</t>
+          <t>千代田区麹町 東京都 1020083 JP</t>
         </is>
       </c>
       <c r="AW17" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3KERCWTE76M89</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KRDRXNL1G5FA</t>
         </is>
       </c>
       <c r="AX17" s="11"/>
-      <c r="AY17" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY17" s="11"/>
       <c r="AZ17" s="11"/>
       <c r="BA17" s="11"/>
       <c r="BB17" s="11"/>
-      <c r="BC17" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD17" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC17" s="11"/>
+      <c r="BD17" s="11"/>
       <c r="BE17" s="11"/>
       <c r="BF17" s="11"/>
       <c r="BG17" s="11"/>
       <c r="BH17" s="12"/>
-      <c r="BI17" s="20" t="inlineStr">
-        <is>
-          <t>Amazon おすすめ</t>
-        </is>
-      </c>
+      <c r="BI17" s="20"/>
       <c r="BJ17" s="20" t="inlineStr">
         <is>
-          <t>3.6 キログラム</t>
-        </is>
-      </c>
-      <c r="BK17" s="20"/>
+          <t>3.2 kg</t>
+        </is>
+      </c>
+      <c r="BK17" s="20" t="inlineStr">
+        <is>
+          <t>3.20 kg</t>
+        </is>
+      </c>
       <c r="BL17" s="20" t="inlineStr">
         <is>
-          <t>24.9長さ x 23.2幅 x 110高さ cm</t>
+          <t>25.7長さ x 25.3幅 x 112.9高さ cm</t>
         </is>
       </c>
       <c r="BM17" s="20"/>
-      <c r="BN17" s="20" t="inlineStr">
-        <is>
-          <t>6.2 kg</t>
-        </is>
-      </c>
-      <c r="BO17" s="20" t="inlineStr">
-        <is>
-          <t>6.20 kg</t>
-        </is>
-      </c>
-      <c r="BP17" s="20" t="inlineStr">
-        <is>
-          <t>64.5 x 30.5 x 23.8 cm</t>
-        </is>
-      </c>
-      <c r="BQ17" s="20" t="inlineStr">
-        <is>
-          <t>64.50 x 30.50 x 23.80 cm</t>
-        </is>
-      </c>
-      <c r="BR17" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
+      <c r="BN17" s="20"/>
+      <c r="BO17" s="20"/>
+      <c r="BP17" s="20"/>
+      <c r="BQ17" s="20"/>
+      <c r="BR17" s="11"/>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
@@ -10580,7 +10468,7 @@
       <c r="B18" s="11"/>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>B0HGLNPJPC</t>
+          <t>B0HHN8HTLL</t>
         </is>
       </c>
       <c r="D18" s="12"/>
@@ -10592,28 +10480,28 @@
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%83%80%E3%82%A4%E3%82%BD%E3%83%B3/page/0456F1ED-24D4-4719-8E99-5936EC69346F?lp_asin=B0HGLNPJPC&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jpnull</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>Dyson(ダイソン) V12 Detect Slim Absolute 无线吸尘器 戴森官方限定 延长保修1年款s棒手持吸尘器,旋风,带充电座,Amazon.co.jp 独家,高功能 LED 和自动模式不会错过垃圾</t>
+          <t>Dyson(ダイソン) Dyson V12 Detect Slim Fluffy无线棒式吸尘器 戴森官方限定 延长保修1年款</t>
         </is>
       </c>
       <c r="I18" s="12"/>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0HGLNPJPC?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0HHN8HTLL?psc=1</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/616rJ-dkmUL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51z7B-TmeXL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L18" s="12" t="inlineStr">
         <is>
-          <t>B0HGLNPJPC</t>
+          <t>B0HHN8HTLL</t>
         </is>
       </c>
       <c r="M18" s="12" t="inlineStr">
@@ -10627,13 +10515,13 @@
         </is>
       </c>
       <c r="O18" s="13">
-        <v>140536</v>
+        <v>155961</v>
       </c>
       <c r="P18" s="13">
-        <v>-86532</v>
+        <v>-132420</v>
       </c>
       <c r="Q18" s="14">
-        <v>-1.6</v>
+        <v>-5.63</v>
       </c>
       <c r="R18" s="15" t="inlineStr">
         <is>
@@ -10642,15 +10530,15 @@
       </c>
       <c r="S18" s="16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>19</t>
         </is>
       </c>
       <c r="T18" s="13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U18" s="14"/>
       <c r="V18" s="13">
-        <v>639992</v>
+        <v>605000</v>
       </c>
       <c r="W18" s="13"/>
       <c r="X18" s="13"/>
@@ -10658,20 +10546,14 @@
         <v>1</v>
       </c>
       <c r="Z18" s="13">
-        <v>79999</v>
+        <v>60500</v>
       </c>
       <c r="AA18"/>
       <c r="AB18"/>
       <c r="AC18" s="2"/>
-      <c r="AD18" s="17">
-        <v>229</v>
-      </c>
-      <c r="AE18" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF18" s="18">
-        <v>4.3</v>
-      </c>
+      <c r="AD18" s="17"/>
+      <c r="AE18" s="13"/>
+      <c r="AF18" s="18"/>
       <c r="AG18" s="19">
         <v>0</v>
       </c>
@@ -10682,11 +10564,11 @@
       <c r="AJ18"/>
       <c r="AK18" s="11" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AL18" s="17">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AM18" s="11" t="inlineStr">
         <is>
@@ -10702,7 +10584,7 @@
       </c>
       <c r="AS18" s="12" t="inlineStr">
         <is>
-          <t>ダイソン公式ストア</t>
+          <t>スタッフショップ</t>
         </is>
       </c>
       <c r="AT18" s="11" t="inlineStr">
@@ -10717,12 +10599,12 @@
       </c>
       <c r="AV18" s="12" t="inlineStr">
         <is>
-          <t>千代田区麹町 東京都 1020083 JP</t>
+          <t>三重県 5110284 JP</t>
         </is>
       </c>
       <c r="AW18" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KRDRXNL1G5FA</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3JH293JNBT5IZ</t>
         </is>
       </c>
       <c r="AX18" s="11"/>
@@ -10766,40 +10648,40 @@
       <c r="B19" s="11"/>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>B0HHN8HTLL</t>
+          <t>B0FK9HN17M</t>
         </is>
       </c>
       <c r="D19" s="12"/>
       <c r="E19" s="12"/>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>Dyson(ダイソン)</t>
+          <t>JONR</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jpnull</t>
+          <t>https://www.amazon.co.jp/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FK9HN17M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>Dyson(ダイソン) Dyson V12 Detect Slim Fluffy无线棒式吸尘器 戴森官方限定 延长保修1年款</t>
+          <t>拖水式吸尘器 JONR ED12 Lite【日本最轻量】吸引・水洗・擦拭3合1 无绳式 推杆式吸尘器 20000Pa强力吸引 干湿两用 自动清洗 靠墙1mm清洁 长时间运行 大容量水箱 自立式&amp;自走式 拖把功能 适用于地板擦拭/硬质地板/地毯/缝隙</t>
         </is>
       </c>
       <c r="I19" s="12"/>
       <c r="J19" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0HHN8HTLL?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FK9HN17M?psc=1</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51z7B-TmeXL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61gNWZ3JF6L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>B0HHN8HTLL</t>
+          <t>B0FK9HN17M</t>
         </is>
       </c>
       <c r="M19" s="12" t="inlineStr">
@@ -10813,13 +10695,13 @@
         </is>
       </c>
       <c r="O19" s="13">
-        <v>155961</v>
+        <v>70661</v>
       </c>
       <c r="P19" s="13">
-        <v>-132420</v>
+        <v>2745</v>
       </c>
       <c r="Q19" s="14">
-        <v>-5.63</v>
+        <v>0.04</v>
       </c>
       <c r="R19" s="15" t="inlineStr">
         <is>
@@ -10828,15 +10710,17 @@
       </c>
       <c r="S19" s="16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="T19" s="13">
-        <v>10</v>
-      </c>
-      <c r="U19" s="14"/>
+        <v>30</v>
+      </c>
+      <c r="U19" s="14">
+        <v>0.25</v>
+      </c>
       <c r="V19" s="13">
-        <v>605000</v>
+        <v>551700</v>
       </c>
       <c r="W19" s="13"/>
       <c r="X19" s="13"/>
@@ -10844,65 +10728,75 @@
         <v>1</v>
       </c>
       <c r="Z19" s="13">
-        <v>60500</v>
+        <v>18390</v>
       </c>
       <c r="AA19"/>
       <c r="AB19"/>
       <c r="AC19" s="2"/>
-      <c r="AD19" s="17"/>
-      <c r="AE19" s="13"/>
-      <c r="AF19" s="18"/>
+      <c r="AD19" s="17">
+        <v>84</v>
+      </c>
+      <c r="AE19" s="13">
+        <v>2</v>
+      </c>
+      <c r="AF19" s="18">
+        <v>3.3</v>
+      </c>
       <c r="AG19" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH19" s="13"/>
+        <v>0.0667</v>
+      </c>
+      <c r="AH19" s="13">
+        <v>781</v>
+      </c>
       <c r="AI19" s="14">
-        <v>0.85</v>
+        <v>0.81</v>
       </c>
       <c r="AJ19"/>
       <c r="AK19" s="11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AL19" s="17">
-        <v>34</v>
+        <v>435</v>
       </c>
       <c r="AM19" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN19" s="11"/>
       <c r="AO19" s="11"/>
       <c r="AP19"/>
-      <c r="AQ19" s="17"/>
+      <c r="AQ19" s="17">
+        <v>8</v>
+      </c>
       <c r="AR19" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS19" s="12" t="inlineStr">
         <is>
-          <t>スタッフショップ</t>
+          <t>JONR公式ストア</t>
         </is>
       </c>
       <c r="AT19" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU19" s="11" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV19" s="12" t="inlineStr">
         <is>
-          <t>三重県 5110284 JP</t>
+          <t>香港 999077 HK</t>
         </is>
       </c>
       <c r="AW19" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3JH293JNBT5IZ</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2SR0DVTECF9BI</t>
         </is>
       </c>
       <c r="AX19" s="11"/>
@@ -10911,7 +10805,11 @@
       <c r="BA19" s="11"/>
       <c r="BB19" s="11"/>
       <c r="BC19" s="11"/>
-      <c r="BD19" s="11"/>
+      <c r="BD19" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE19" s="11"/>
       <c r="BF19" s="11"/>
       <c r="BG19" s="11"/>
@@ -10919,25 +10817,45 @@
       <c r="BI19" s="20"/>
       <c r="BJ19" s="20" t="inlineStr">
         <is>
-          <t>3.2 kg</t>
+          <t>3.4 kg</t>
         </is>
       </c>
       <c r="BK19" s="20" t="inlineStr">
         <is>
-          <t>3.20 kg</t>
+          <t>3.40 kg</t>
         </is>
       </c>
       <c r="BL19" s="20" t="inlineStr">
         <is>
-          <t>25.7長さ x 25.3幅 x 112.9高さ cm</t>
+          <t>29.8長さ x 26.9幅 x 113.4高さ cm</t>
         </is>
       </c>
       <c r="BM19" s="20"/>
-      <c r="BN19" s="20"/>
-      <c r="BO19" s="20"/>
-      <c r="BP19" s="20"/>
-      <c r="BQ19" s="20"/>
-      <c r="BR19" s="11"/>
+      <c r="BN19" s="20" t="inlineStr">
+        <is>
+          <t>6.09 kg</t>
+        </is>
+      </c>
+      <c r="BO19" s="20" t="inlineStr">
+        <is>
+          <t>6.09 kg</t>
+        </is>
+      </c>
+      <c r="BP19" s="20" t="inlineStr">
+        <is>
+          <t>55 x 33.3 x 31 cm</t>
+        </is>
+      </c>
+      <c r="BQ19" s="20" t="inlineStr">
+        <is>
+          <t>55.00 x 33.30 x 31.00 cm</t>
+        </is>
+      </c>
+      <c r="BR19" s="11" t="inlineStr">
+        <is>
+          <t>大件</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
@@ -10946,155 +10864,147 @@
       <c r="B20" s="11"/>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>B0FK9HN17M</t>
+          <t>B0CPPHYW3B</t>
         </is>
       </c>
       <c r="D20" s="12"/>
       <c r="E20" s="12"/>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>JONR</t>
+          <t>ミナトワークス</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FK9HN17M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/%E3%83%9F%E3%83%8A%E3%83%88%E3%83%AF%E3%83%BC%E3%82%AF%E3%82%B9/page/7E77FCE9-0862-4057-994E-E5C8A30E6C6D?lp_asin=B0CPPHYW3B&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>拖水式吸尘器 JONR ED12 Lite【日本最轻量】吸引・水洗・擦拭3合1 无绳式 推杆式吸尘器 20000Pa强力吸引 干湿两用 自动清洗 靠墙1mm清洁 长时间运行 大容量水箱 自立式&amp;自走式 拖把功能 适用于地板擦拭/硬质地板/地毯/缝隙</t>
+          <t>Minato Works 干湿两用 吸尘器 真空吸尘器 MPV-101 +附带替换过滤器 水箱容量10升</t>
         </is>
       </c>
       <c r="I20" s="12"/>
       <c r="J20" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FK9HN17M?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0CPPHYW3B?psc=1</t>
         </is>
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61gNWZ3JF6L._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41ZrF14970L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L20" s="12" t="inlineStr">
         <is>
-          <t>B0FK9HN17M</t>
+          <t>B0CPPHYW3B</t>
         </is>
       </c>
       <c r="M20" s="12" t="inlineStr">
         <is>
-          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
+          <t>産業・研究開発用品:衛生・清掃用品:床・カーペットクリーニング:掃除機・アクセサリ:掃除機:乾湿両用掃除機</t>
         </is>
       </c>
       <c r="N20" s="12" t="inlineStr">
         <is>
-          <t>DIY・工具・ガーデン</t>
+          <t>産業・研究開発用品</t>
         </is>
       </c>
       <c r="O20" s="13">
-        <v>70661</v>
+        <v>13848</v>
       </c>
       <c r="P20" s="13">
-        <v>2745</v>
+        <v>-4407</v>
       </c>
       <c r="Q20" s="14">
-        <v>0.04</v>
+        <v>-0.47</v>
       </c>
       <c r="R20" s="15" t="inlineStr">
         <is>
-          <t>ウェットドライショップ掃除機</t>
+          <t>乾湿両用掃除機</t>
         </is>
       </c>
       <c r="S20" s="16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="T20" s="13">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="U20" s="14">
-        <v>0.25</v>
+        <v>-0.22</v>
       </c>
       <c r="V20" s="13">
-        <v>551700</v>
+        <v>461120</v>
       </c>
       <c r="W20" s="13"/>
       <c r="X20" s="13"/>
       <c r="Y20" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z20" s="13">
-        <v>18390</v>
+        <v>10480</v>
       </c>
       <c r="AA20"/>
       <c r="AB20"/>
       <c r="AC20" s="2"/>
       <c r="AD20" s="17">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="AE20" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF20" s="18">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AG20" s="19">
-        <v>0.0667</v>
-      </c>
-      <c r="AH20" s="13">
-        <v>781</v>
-      </c>
+        <v>0.0227</v>
+      </c>
+      <c r="AH20" s="13"/>
       <c r="AI20" s="14">
-        <v>0.81</v>
+        <v>0</v>
       </c>
       <c r="AJ20"/>
-      <c r="AK20" s="11" t="inlineStr">
-        <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AL20" s="17">
-        <v>435</v>
-      </c>
+      <c r="AK20" s="11"/>
+      <c r="AL20" s="17"/>
       <c r="AM20" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN20" s="11"/>
       <c r="AO20" s="11"/>
       <c r="AP20"/>
       <c r="AQ20" s="17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR20" s="17">
         <v>1</v>
       </c>
       <c r="AS20" s="12" t="inlineStr">
         <is>
-          <t>JONR公式ストア</t>
+          <t>【ミナトワークス】</t>
         </is>
       </c>
       <c r="AT20" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AU20" s="11" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="AV20" s="12" t="inlineStr">
         <is>
-          <t>香港 999077 HK</t>
+          <t>豊前市 福岡県 8280031 JP</t>
         </is>
       </c>
       <c r="AW20" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2SR0DVTECF9BI</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A35R5657DWBR35</t>
         </is>
       </c>
       <c r="AX20" s="11"/>
@@ -11102,12 +11012,12 @@
       <c r="AZ20" s="11"/>
       <c r="BA20" s="11"/>
       <c r="BB20" s="11"/>
-      <c r="BC20" s="11"/>
-      <c r="BD20" s="11" t="inlineStr">
+      <c r="BC20" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="BD20" s="11"/>
       <c r="BE20" s="11"/>
       <c r="BF20" s="11"/>
       <c r="BG20" s="11"/>
@@ -11115,45 +11025,21 @@
       <c r="BI20" s="20"/>
       <c r="BJ20" s="20" t="inlineStr">
         <is>
-          <t>3.4 kg</t>
-        </is>
-      </c>
-      <c r="BK20" s="20" t="inlineStr">
-        <is>
-          <t>3.40 kg</t>
-        </is>
-      </c>
+          <t>4.5 キログラム</t>
+        </is>
+      </c>
+      <c r="BK20" s="20"/>
       <c r="BL20" s="20" t="inlineStr">
         <is>
-          <t>29.8長さ x 26.9幅 x 113.4高さ cm</t>
+          <t>34.5長さ x 31幅 x 36.5高さ cm</t>
         </is>
       </c>
       <c r="BM20" s="20"/>
-      <c r="BN20" s="20" t="inlineStr">
-        <is>
-          <t>6.09 kg</t>
-        </is>
-      </c>
-      <c r="BO20" s="20" t="inlineStr">
-        <is>
-          <t>6.09 kg</t>
-        </is>
-      </c>
-      <c r="BP20" s="20" t="inlineStr">
-        <is>
-          <t>55 x 33.3 x 31 cm</t>
-        </is>
-      </c>
-      <c r="BQ20" s="20" t="inlineStr">
-        <is>
-          <t>55.00 x 33.30 x 31.00 cm</t>
-        </is>
-      </c>
-      <c r="BR20" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
+      <c r="BN20" s="20"/>
+      <c r="BO20" s="20"/>
+      <c r="BP20" s="20"/>
+      <c r="BQ20" s="20"/>
+      <c r="BR20" s="11"/>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
@@ -11162,7 +11048,7 @@
       <c r="B21" s="11"/>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>B0CPPHYW3B</t>
+          <t>B07KR2J116</t>
         </is>
       </c>
       <c r="D21" s="12"/>
@@ -11174,98 +11060,104 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%83%9F%E3%83%8A%E3%83%88%E3%83%AF%E3%83%BC%E3%82%AF%E3%82%B9/page/7E77FCE9-0862-4057-994E-E5C8A30E6C6D?lp_asin=B0CPPHYW3B&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/%E3%83%9F%E3%83%8A%E3%83%88%E3%83%AF%E3%83%BC%E3%82%AF%E3%82%B9/page/7E77FCE9-0862-4057-994E-E5C8A30E6C6D?lp_asin=B07KR2J116&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>Minato Works 干湿两用 吸尘器 真空吸尘器 MPV-101 +附带替换过滤器 水箱容量10升</t>
+          <t>Minato 干湿两用 业务用 吸尘器 旋风式 真空吸尘器 MPV-151CY (容量15L/吸水0.5L)</t>
         </is>
       </c>
       <c r="I21" s="12"/>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0CPPHYW3B?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B07KR2J116?psc=1</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41ZrF14970L._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41ovXwP+o+L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>B0CPPHYW3B</t>
+          <t>B07KR2J116</t>
         </is>
       </c>
       <c r="M21" s="12" t="inlineStr">
         <is>
-          <t>産業・研究開発用品:衛生・清掃用品:床・カーペットクリーニング:掃除機・アクセサリ:掃除機:乾湿両用掃除機</t>
+          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
         </is>
       </c>
       <c r="N21" s="12" t="inlineStr">
         <is>
-          <t>産業・研究開発用品</t>
+          <t>DIY・工具・ガーデン</t>
         </is>
       </c>
       <c r="O21" s="13">
-        <v>13848</v>
+        <v>33132</v>
       </c>
       <c r="P21" s="13">
-        <v>-4407</v>
+        <v>23271</v>
       </c>
       <c r="Q21" s="14">
-        <v>-0.47</v>
+        <v>0.17</v>
       </c>
       <c r="R21" s="15" t="inlineStr">
         <is>
-          <t>乾湿両用掃除機</t>
+          <t>ウェットドライショップ掃除機</t>
         </is>
       </c>
       <c r="S21" s="16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="T21" s="13">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="U21" s="14">
-        <v>-0.22</v>
+        <v>2.5</v>
       </c>
       <c r="V21" s="13">
-        <v>461120</v>
+        <v>338200</v>
       </c>
       <c r="W21" s="13"/>
       <c r="X21" s="13"/>
       <c r="Y21" s="17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z21" s="13">
-        <v>10480</v>
+        <v>17800</v>
       </c>
       <c r="AA21"/>
       <c r="AB21"/>
       <c r="AC21" s="2"/>
       <c r="AD21" s="17">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="AE21" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF21" s="18">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AG21" s="19">
-        <v>0.0227</v>
+        <v>0</v>
       </c>
       <c r="AH21" s="13"/>
       <c r="AI21" s="14">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AJ21"/>
-      <c r="AK21" s="11"/>
-      <c r="AL21" s="17"/>
+      <c r="AK21" s="11" t="inlineStr">
+        <is>
+          <t>2018-12-03</t>
+        </is>
+      </c>
+      <c r="AL21" s="17">
+        <v>2865</v>
+      </c>
       <c r="AM21" s="11" t="inlineStr">
         <is>
           <t>FBM</t>
@@ -11315,7 +11207,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD21" s="11"/>
+      <c r="BD21" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE21" s="11"/>
       <c r="BF21" s="11"/>
       <c r="BG21" s="11"/>
@@ -11323,13 +11219,13 @@
       <c r="BI21" s="20"/>
       <c r="BJ21" s="20" t="inlineStr">
         <is>
-          <t>4.5 キログラム</t>
+          <t>12 キログラム</t>
         </is>
       </c>
       <c r="BK21" s="20"/>
       <c r="BL21" s="20" t="inlineStr">
         <is>
-          <t>34.5長さ x 31幅 x 36.5高さ cm</t>
+          <t>33.5長さ x 31幅 x 54高さ cm</t>
         </is>
       </c>
       <c r="BM21" s="20"/>
@@ -11346,40 +11242,40 @@
       <c r="B22" s="11"/>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>B07KR2J116</t>
+          <t>B0D2VPQT2V</t>
         </is>
       </c>
       <c r="D22" s="12"/>
       <c r="E22" s="12"/>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>ミナトワークス</t>
+          <t>dreame</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%83%9F%E3%83%8A%E3%83%88%E3%83%AF%E3%83%BC%E3%82%AF%E3%82%B9/page/7E77FCE9-0862-4057-994E-E5C8A30E6C6D?lp_asin=B07KR2J116&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0D2VPQT2V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>Minato 干湿两用 业务用 吸尘器 旋风式 真空吸尘器 MPV-151CY (容量15L/吸水0.5L)</t>
+          <t>MOVA K10 Pro 水拭き掃除機 自走式 水拭き2in1コードレススティック掃除機 汚れ検知可能 作動時0.9kg超軽量 15000Pa強力吸引 乾湿両用掃除機 自動洗浄 電解水除菌 30分連続稼働 6mm端清掃 大容量水タンク 床拭き LED</t>
         </is>
       </c>
       <c r="I22" s="12"/>
       <c r="J22" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B07KR2J116?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0D2VPQT2V?psc=1</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41ovXwP+o+L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61KqhLRxwYL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L22" s="12" t="inlineStr">
         <is>
-          <t>B07KR2J116</t>
+          <t>B0D2VPQT2V</t>
         </is>
       </c>
       <c r="M22" s="12" t="inlineStr">
@@ -11393,13 +11289,13 @@
         </is>
       </c>
       <c r="O22" s="13">
-        <v>33132</v>
+        <v>99410</v>
       </c>
       <c r="P22" s="13">
-        <v>23271</v>
+        <v>2480</v>
       </c>
       <c r="Q22" s="14">
-        <v>0.17</v>
+        <v>0.02</v>
       </c>
       <c r="R22" s="15" t="inlineStr">
         <is>
@@ -11408,91 +11304,91 @@
       </c>
       <c r="S22" s="16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>29</t>
         </is>
       </c>
       <c r="T22" s="13">
         <v>19</v>
       </c>
-      <c r="U22" s="14">
-        <v>2.5</v>
-      </c>
+      <c r="U22" s="14"/>
       <c r="V22" s="13">
-        <v>338200</v>
+        <v>243200</v>
       </c>
       <c r="W22" s="13"/>
       <c r="X22" s="13"/>
       <c r="Y22" s="17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z22" s="13">
-        <v>17800</v>
+        <v>12800</v>
       </c>
       <c r="AA22"/>
       <c r="AB22"/>
       <c r="AC22" s="2"/>
       <c r="AD22" s="17">
-        <v>29</v>
+        <v>138</v>
       </c>
       <c r="AE22" s="13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF22" s="18">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AG22" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH22" s="13"/>
+        <v>0.10529999999999999</v>
+      </c>
+      <c r="AH22" s="13">
+        <v>1020</v>
+      </c>
       <c r="AI22" s="14">
-        <v>0.85</v>
+        <v>0.77</v>
       </c>
       <c r="AJ22"/>
       <c r="AK22" s="11" t="inlineStr">
         <is>
-          <t>2018-12-03</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AL22" s="17">
-        <v>2865</v>
+        <v>850</v>
       </c>
       <c r="AM22" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN22" s="11"/>
       <c r="AO22" s="11"/>
       <c r="AP22"/>
       <c r="AQ22" s="17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR22" s="17">
         <v>1</v>
       </c>
       <c r="AS22" s="12" t="inlineStr">
         <is>
-          <t>【ミナトワークス】</t>
+          <t>Dreametech JP</t>
         </is>
       </c>
       <c r="AT22" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU22" s="11" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV22" s="12" t="inlineStr">
         <is>
-          <t>豊前市 福岡県 8280031 JP</t>
+          <t>Tianjin 300456 CN</t>
         </is>
       </c>
       <c r="AW22" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A35R5657DWBR35</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WSQAA92JSPUW</t>
         </is>
       </c>
       <c r="AX22" s="11"/>
@@ -11517,21 +11413,45 @@
       <c r="BI22" s="20"/>
       <c r="BJ22" s="20" t="inlineStr">
         <is>
-          <t>12 キログラム</t>
-        </is>
-      </c>
-      <c r="BK22" s="20"/>
+          <t>3.8 kg</t>
+        </is>
+      </c>
+      <c r="BK22" s="20" t="inlineStr">
+        <is>
+          <t>3.80 kg</t>
+        </is>
+      </c>
       <c r="BL22" s="20" t="inlineStr">
         <is>
-          <t>33.5長さ x 31幅 x 54高さ cm</t>
+          <t>29長さ x 21.9幅 x 110.5高さ cm</t>
         </is>
       </c>
       <c r="BM22" s="20"/>
-      <c r="BN22" s="20"/>
-      <c r="BO22" s="20"/>
-      <c r="BP22" s="20"/>
-      <c r="BQ22" s="20"/>
-      <c r="BR22" s="11"/>
+      <c r="BN22" s="20" t="inlineStr">
+        <is>
+          <t>6.6 kg</t>
+        </is>
+      </c>
+      <c r="BO22" s="20" t="inlineStr">
+        <is>
+          <t>6.60 kg</t>
+        </is>
+      </c>
+      <c r="BP22" s="20" t="inlineStr">
+        <is>
+          <t>69 x 32 x 29 cm</t>
+        </is>
+      </c>
+      <c r="BQ22" s="20" t="inlineStr">
+        <is>
+          <t>69.00 x 32.00 x 29.00 cm</t>
+        </is>
+      </c>
+      <c r="BR22" s="11" t="inlineStr">
+        <is>
+          <t>大件</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
@@ -11540,40 +11460,40 @@
       <c r="B23" s="11"/>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>B0D2VPQT2V</t>
+          <t>B0CZKHJXNG</t>
         </is>
       </c>
       <c r="D23" s="12"/>
       <c r="E23" s="12"/>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>dreame</t>
+          <t>EUREKA</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0D2VPQT2V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/Eureka/page/0DAE79FF-361F-4FFE-9129-4ACEDAF99AD5?lp_asin=B0CZKHJXNG&amp;ref_=ast_bln</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>MOVA K10 Pro 水拭き掃除機 自走式 水拭き2in1コードレススティック掃除機 汚れ検知可能 作動時0.9kg超軽量 15000Pa強力吸引 乾湿両用掃除機 自動洗浄 電解水除菌 30分連続稼働 6mm端清掃 大容量水タンク 床拭き LED</t>
+          <t>EUREKA NEY100 地毯清洁器 400W强力吸力 汽车座椅和布制品清洗 自洁式 地毯和沙发清洗 干湿两用 淋水清洗器 可用热水清洗 附带洗涤剂 三只刷子</t>
         </is>
       </c>
       <c r="I23" s="12"/>
       <c r="J23" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0D2VPQT2V?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0CZKHJXNG?psc=1</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61KqhLRxwYL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41nAma6e0eL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>B0D2VPQT2V</t>
+          <t>B0CZKHJXNG</t>
         </is>
       </c>
       <c r="M23" s="12" t="inlineStr">
@@ -11587,13 +11507,13 @@
         </is>
       </c>
       <c r="O23" s="13">
-        <v>99410</v>
+        <v>74183</v>
       </c>
       <c r="P23" s="13">
-        <v>2480</v>
+        <v>2118</v>
       </c>
       <c r="Q23" s="14">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="R23" s="15" t="inlineStr">
         <is>
@@ -11602,54 +11522,46 @@
       </c>
       <c r="S23" s="16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T23" s="13">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="U23" s="14"/>
       <c r="V23" s="13">
-        <v>243200</v>
+        <v>214800</v>
       </c>
       <c r="W23" s="13"/>
       <c r="X23" s="13"/>
       <c r="Y23" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z23" s="13">
-        <v>12800</v>
+        <v>7160</v>
       </c>
       <c r="AA23"/>
       <c r="AB23"/>
       <c r="AC23" s="2"/>
       <c r="AD23" s="17">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="AE23" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF23" s="18">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AG23" s="19">
-        <v>0.10529999999999999</v>
-      </c>
-      <c r="AH23" s="13">
-        <v>1020</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH23" s="13"/>
       <c r="AI23" s="14">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="AJ23"/>
-      <c r="AK23" s="11" t="inlineStr">
-        <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AL23" s="17">
-        <v>850</v>
-      </c>
+      <c r="AK23" s="11"/>
+      <c r="AL23" s="17"/>
       <c r="AM23" s="11" t="inlineStr">
         <is>
           <t>NA</t>
@@ -11666,7 +11578,7 @@
       </c>
       <c r="AS23" s="12" t="inlineStr">
         <is>
-          <t>Dreametech JP</t>
+          <t>Eureka Japan</t>
         </is>
       </c>
       <c r="AT23" s="11" t="inlineStr">
@@ -11676,17 +11588,17 @@
       </c>
       <c r="AU23" s="11" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV23" s="12" t="inlineStr">
         <is>
-          <t>Tianjin 300456 CN</t>
+          <t>TSIM SHA TSUI 999077 HK</t>
         </is>
       </c>
       <c r="AW23" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WSQAA92JSPUW</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3JXXBYW06ZFVU</t>
         </is>
       </c>
       <c r="AX23" s="11"/>
@@ -11711,45 +11623,25 @@
       <c r="BI23" s="20"/>
       <c r="BJ23" s="20" t="inlineStr">
         <is>
-          <t>3.8 kg</t>
+          <t>5 Kilograms</t>
         </is>
       </c>
       <c r="BK23" s="20" t="inlineStr">
         <is>
-          <t>3.80 kg</t>
+          <t>5.00 kg</t>
         </is>
       </c>
       <c r="BL23" s="20" t="inlineStr">
         <is>
-          <t>29長さ x 21.9幅 x 110.5高さ cm</t>
+          <t>39奥行き x 30幅 x 20高さ cm</t>
         </is>
       </c>
       <c r="BM23" s="20"/>
-      <c r="BN23" s="20" t="inlineStr">
-        <is>
-          <t>6.6 kg</t>
-        </is>
-      </c>
-      <c r="BO23" s="20" t="inlineStr">
-        <is>
-          <t>6.60 kg</t>
-        </is>
-      </c>
-      <c r="BP23" s="20" t="inlineStr">
-        <is>
-          <t>69 x 32 x 29 cm</t>
-        </is>
-      </c>
-      <c r="BQ23" s="20" t="inlineStr">
-        <is>
-          <t>69.00 x 32.00 x 29.00 cm</t>
-        </is>
-      </c>
-      <c r="BR23" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
+      <c r="BN23" s="20"/>
+      <c r="BO23" s="20"/>
+      <c r="BP23" s="20"/>
+      <c r="BQ23" s="20"/>
+      <c r="BR23" s="11"/>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
@@ -11758,40 +11650,40 @@
       <c r="B24" s="11"/>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>B0CZKHJXNG</t>
+          <t>B0CNJT8933</t>
         </is>
       </c>
       <c r="D24" s="12"/>
       <c r="E24" s="12"/>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>EUREKA</t>
+          <t>dreame</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/Eureka/page/0DAE79FF-361F-4FFE-9129-4ACEDAF99AD5?lp_asin=B0CZKHJXNG&amp;ref_=ast_bln</t>
+          <t>https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0CNJT8933&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>EUREKA NEY100 地毯清洁器 400W强力吸力 汽车座椅和布制品清洗 自洁式 地毯和沙发清洗 干湿两用 淋水清洗器 可用热水清洗 附带洗涤剂 三只刷子</t>
+          <t>dreame (ドリーミー) H12 Dual 水拭き掃除機【4wayコードレス水拭き掃除機】 自动清洗和温风干燥 双向旋转式清洗 可达墙角的刷子设计 16000Pa强力吸力 电解水除菌 35分钟连续运行 智能污垢检测和自动吸力调节 语音引导 大容量</t>
         </is>
       </c>
       <c r="I24" s="12"/>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0CZKHJXNG?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0CNJT8933?psc=1</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41nAma6e0eL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61b-HbgIkBL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L24" s="12" t="inlineStr">
         <is>
-          <t>B0CZKHJXNG</t>
+          <t>B0CNJT8933</t>
         </is>
       </c>
       <c r="M24" s="12" t="inlineStr">
@@ -11805,13 +11697,13 @@
         </is>
       </c>
       <c r="O24" s="13">
-        <v>74183</v>
+        <v>133273</v>
       </c>
       <c r="P24" s="13">
-        <v>2118</v>
+        <v>2289</v>
       </c>
       <c r="Q24" s="14">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="R24" s="15" t="inlineStr">
         <is>
@@ -11820,46 +11712,56 @@
       </c>
       <c r="S24" s="16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>38</t>
         </is>
       </c>
       <c r="T24" s="13">
-        <v>30</v>
-      </c>
-      <c r="U24" s="14"/>
+        <v>4</v>
+      </c>
+      <c r="U24" s="14">
+        <v>0.06</v>
+      </c>
       <c r="V24" s="13">
-        <v>214800</v>
+        <v>171600</v>
       </c>
       <c r="W24" s="13"/>
       <c r="X24" s="13"/>
       <c r="Y24" s="17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z24" s="13">
-        <v>7160</v>
+        <v>42900</v>
       </c>
       <c r="AA24"/>
       <c r="AB24"/>
       <c r="AC24" s="2"/>
       <c r="AD24" s="17">
-        <v>152</v>
+        <v>45</v>
       </c>
       <c r="AE24" s="13">
         <v>0</v>
       </c>
       <c r="AF24" s="18">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AG24" s="19">
         <v>0</v>
       </c>
-      <c r="AH24" s="13"/>
+      <c r="AH24" s="13">
+        <v>1100</v>
+      </c>
       <c r="AI24" s="14">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AJ24"/>
-      <c r="AK24" s="11"/>
-      <c r="AL24" s="17"/>
+      <c r="AK24" s="11" t="inlineStr">
+        <is>
+          <t>2023-11-20</t>
+        </is>
+      </c>
+      <c r="AL24" s="17">
+        <v>1053</v>
+      </c>
       <c r="AM24" s="11" t="inlineStr">
         <is>
           <t>NA</t>
@@ -11869,14 +11771,14 @@
       <c r="AO24" s="11"/>
       <c r="AP24"/>
       <c r="AQ24" s="17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR24" s="17">
         <v>1</v>
       </c>
       <c r="AS24" s="12" t="inlineStr">
         <is>
-          <t>Eureka Japan</t>
+          <t>Dreame公式ストア</t>
         </is>
       </c>
       <c r="AT24" s="11" t="inlineStr">
@@ -11891,12 +11793,12 @@
       </c>
       <c r="AV24" s="12" t="inlineStr">
         <is>
-          <t>TSIM SHA TSUI 999077 HK</t>
+          <t>ROOM H28G BLK EH 10TH FLOOR GOLDEN BEAR IND CTR 66-82</t>
         </is>
       </c>
       <c r="AW24" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3JXXBYW06ZFVU</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WV0MTJICL1UJ</t>
         </is>
       </c>
       <c r="AX24" s="11"/>
@@ -11921,25 +11823,45 @@
       <c r="BI24" s="20"/>
       <c r="BJ24" s="20" t="inlineStr">
         <is>
-          <t>5 Kilograms</t>
+          <t>5.13 kg</t>
         </is>
       </c>
       <c r="BK24" s="20" t="inlineStr">
         <is>
-          <t>5.00 kg</t>
+          <t>5.13 kg</t>
         </is>
       </c>
       <c r="BL24" s="20" t="inlineStr">
         <is>
-          <t>39奥行き x 30幅 x 20高さ cm</t>
+          <t>27.5長さ x 27.8幅 x 110.5高さ cm</t>
         </is>
       </c>
       <c r="BM24" s="20"/>
-      <c r="BN24" s="20"/>
-      <c r="BO24" s="20"/>
-      <c r="BP24" s="20"/>
-      <c r="BQ24" s="20"/>
-      <c r="BR24" s="11"/>
+      <c r="BN24" s="20" t="inlineStr">
+        <is>
+          <t>13 kg</t>
+        </is>
+      </c>
+      <c r="BO24" s="20" t="inlineStr">
+        <is>
+          <t>13.00 kg</t>
+        </is>
+      </c>
+      <c r="BP24" s="20" t="inlineStr">
+        <is>
+          <t>75 x 38 x 35 cm</t>
+        </is>
+      </c>
+      <c r="BQ24" s="20" t="inlineStr">
+        <is>
+          <t>75.00 x 38.00 x 35.00 cm</t>
+        </is>
+      </c>
+      <c r="BR24" s="11" t="inlineStr">
+        <is>
+          <t>大件</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
@@ -11948,40 +11870,40 @@
       <c r="B25" s="11"/>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>B0HHN61KPZ</t>
+          <t>B08XLW562G</t>
         </is>
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="12"/>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>Dyson(ダイソン)</t>
+          <t>不明</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jpnull</t>
+          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=%E4%B8%8D%E6%98%8E</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>Dyson(ダイソン) Dyson V12s Detect Slim Submarine 无线棒式吸尘器 戴森官方限定 延长保修1年款</t>
+          <t>黑色+Decker 干湿两用锂电池吸尘器 4536178960298</t>
         </is>
       </c>
       <c r="I25" s="12"/>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0HHN61KPZ?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B08XLW562G?psc=1</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31eRC+N6IRL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/31NELDCajpL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>B0HHN61KPZ</t>
+          <t>B08XLW562G</t>
         </is>
       </c>
       <c r="M25" s="12" t="inlineStr">
@@ -11995,11 +11917,13 @@
         </is>
       </c>
       <c r="O25" s="13">
-        <v>13685</v>
-      </c>
-      <c r="P25" s="13"/>
+        <v>73669</v>
+      </c>
+      <c r="P25" s="13">
+        <v>-54113</v>
+      </c>
       <c r="Q25" s="14">
-        <v>0</v>
+        <v>-2.77</v>
       </c>
       <c r="R25" s="15" t="inlineStr">
         <is>
@@ -12008,15 +11932,15 @@
       </c>
       <c r="S25" s="16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="T25" s="13">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="U25" s="14"/>
       <c r="V25" s="13">
-        <v>179997</v>
+        <v>135000</v>
       </c>
       <c r="W25" s="13"/>
       <c r="X25" s="13"/>
@@ -12024,50 +11948,60 @@
         <v>1</v>
       </c>
       <c r="Z25" s="13">
-        <v>59999</v>
+        <v>4500</v>
       </c>
       <c r="AA25"/>
       <c r="AB25"/>
       <c r="AC25" s="2"/>
-      <c r="AD25" s="17"/>
-      <c r="AE25" s="13"/>
-      <c r="AF25" s="18"/>
+      <c r="AD25" s="17">
+        <v>3</v>
+      </c>
+      <c r="AE25" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="18">
+        <v>2.7</v>
+      </c>
       <c r="AG25" s="19">
         <v>0</v>
       </c>
-      <c r="AH25" s="13"/>
+      <c r="AH25" s="13">
+        <v>472</v>
+      </c>
       <c r="AI25" s="14">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="AJ25"/>
       <c r="AK25" s="11" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2021-06-13</t>
         </is>
       </c>
       <c r="AL25" s="17">
-        <v>34</v>
+        <v>1943</v>
       </c>
       <c r="AM25" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN25" s="11"/>
       <c r="AO25" s="11"/>
       <c r="AP25"/>
-      <c r="AQ25" s="17"/>
+      <c r="AQ25" s="17">
+        <v>3</v>
+      </c>
       <c r="AR25" s="17">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AS25" s="12" t="inlineStr">
         <is>
-          <t>ダイソン公式ストア</t>
+          <t>Abeショップ関西</t>
         </is>
       </c>
       <c r="AT25" s="11" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU25" s="11" t="inlineStr">
@@ -12077,12 +12011,12 @@
       </c>
       <c r="AV25" s="12" t="inlineStr">
         <is>
-          <t>千代田区麹町 東京都 1020083 JP</t>
+          <t>初瀬６９３</t>
         </is>
       </c>
       <c r="AW25" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KRDRXNL1G5FA</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2RYDH17QLIL3V</t>
         </is>
       </c>
       <c r="AX25" s="11"/>
@@ -12099,21 +12033,49 @@
       <c r="BI25" s="20"/>
       <c r="BJ25" s="20" t="inlineStr">
         <is>
-          <t>3.2 キログラム</t>
-        </is>
-      </c>
-      <c r="BK25" s="20"/>
+          <t>1 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK25" s="20" t="inlineStr">
+        <is>
+          <t>1,000.00 g</t>
+        </is>
+      </c>
       <c r="BL25" s="20" t="inlineStr">
         <is>
-          <t>25.7長さ x 25.3幅 x 112.9高さ cm</t>
-        </is>
-      </c>
-      <c r="BM25" s="20"/>
-      <c r="BN25" s="20"/>
-      <c r="BO25" s="20"/>
-      <c r="BP25" s="20"/>
-      <c r="BQ25" s="20"/>
-      <c r="BR25" s="11"/>
+          <t>30 x 10 x 10 cm</t>
+        </is>
+      </c>
+      <c r="BM25" s="20" t="inlineStr">
+        <is>
+          <t>30.00 x 10.00 x 10.00 cm</t>
+        </is>
+      </c>
+      <c r="BN25" s="20" t="inlineStr">
+        <is>
+          <t>1 kg</t>
+        </is>
+      </c>
+      <c r="BO25" s="20" t="inlineStr">
+        <is>
+          <t>1,000.00 g</t>
+        </is>
+      </c>
+      <c r="BP25" s="20" t="inlineStr">
+        <is>
+          <t>43.8 x 13.9 x 11.7 cm</t>
+        </is>
+      </c>
+      <c r="BQ25" s="20" t="inlineStr">
+        <is>
+          <t>43.80 x 13.90 x 11.70 cm</t>
+        </is>
+      </c>
+      <c r="BR25" s="11" t="inlineStr">
+        <is>
+          <t>标准</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
@@ -12122,40 +12084,40 @@
       <c r="B26" s="11"/>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>B0CNJT8933</t>
+          <t>B0GS4QDH7R</t>
         </is>
       </c>
       <c r="D26" s="12"/>
       <c r="E26" s="12"/>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>dreame</t>
+          <t>uwant</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0CNJT8933&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/%E3%83%A6%E3%83%AF%E3%83%B3%E3%83%88%EF%BC%88UWANT/page/CFD932E4-87F0-4563-8A00-7E6F0611A613?lp_asin=B0GS4QDH7R&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>dreame (ドリーミー) H12 Dual 水拭き掃除機【4wayコードレス水拭き掃除機】 自动清洗和温风干燥 双向旋转式清洗 可达墙角的刷子设计 16000Pa强力吸力 电解水除菌 35分钟连续运行 智能污垢检测和自动吸力调节 语音引导 大容量</t>
+          <t>uwant 擦水吸尘器 自动清洗 干湿两用吸尘器 热风干燥 电解水除菌 连续工作35分钟 大容量清污分离水箱 水花吸尘器 D100</t>
         </is>
       </c>
       <c r="I26" s="12"/>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0CNJT8933?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0GS4QDH7R?psc=1</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61b-HbgIkBL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61j3dNdQj4L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L26" s="12" t="inlineStr">
         <is>
-          <t>B0CNJT8933</t>
+          <t>B0GS4QDH7R</t>
         </is>
       </c>
       <c r="M26" s="12" t="inlineStr">
@@ -12169,13 +12131,13 @@
         </is>
       </c>
       <c r="O26" s="13">
-        <v>133273</v>
+        <v>152194</v>
       </c>
       <c r="P26" s="13">
-        <v>2289</v>
+        <v>-13127</v>
       </c>
       <c r="Q26" s="14">
-        <v>0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="R26" s="15" t="inlineStr">
         <is>
@@ -12184,17 +12146,17 @@
       </c>
       <c r="S26" s="16" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>42</t>
         </is>
       </c>
       <c r="T26" s="13">
         <v>4</v>
       </c>
       <c r="U26" s="14">
-        <v>0.06</v>
+        <v>-0.94</v>
       </c>
       <c r="V26" s="13">
-        <v>171600</v>
+        <v>46644</v>
       </c>
       <c r="W26" s="13"/>
       <c r="X26" s="13"/>
@@ -12202,37 +12164,37 @@
         <v>1</v>
       </c>
       <c r="Z26" s="13">
-        <v>42900</v>
+        <v>11661</v>
       </c>
       <c r="AA26"/>
       <c r="AB26"/>
       <c r="AC26" s="2"/>
       <c r="AD26" s="17">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="AE26" s="13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF26" s="18">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AG26" s="19">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AH26" s="13">
-        <v>1100</v>
+        <v>1020</v>
       </c>
       <c r="AI26" s="14">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="AJ26"/>
       <c r="AK26" s="11" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AL26" s="17">
-        <v>1053</v>
+        <v>175</v>
       </c>
       <c r="AM26" s="11" t="inlineStr">
         <is>
@@ -12243,14 +12205,14 @@
       <c r="AO26" s="11"/>
       <c r="AP26"/>
       <c r="AQ26" s="17">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AR26" s="17">
         <v>1</v>
       </c>
       <c r="AS26" s="12" t="inlineStr">
         <is>
-          <t>Dreame公式ストア</t>
+          <t>Uwant公式ストア</t>
         </is>
       </c>
       <c r="AT26" s="11" t="inlineStr">
@@ -12260,29 +12222,29 @@
       </c>
       <c r="AU26" s="11" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV26" s="12" t="inlineStr">
         <is>
-          <t>ROOM H28G BLK EH 10TH FLOOR GOLDEN BEAR IND CTR 66-82</t>
+          <t>深圳市 广东省 518000 CN</t>
         </is>
       </c>
       <c r="AW26" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WV0MTJICL1UJ</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1O5QS9O13RS09</t>
         </is>
       </c>
       <c r="AX26" s="11"/>
-      <c r="AY26" s="11"/>
+      <c r="AY26" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ26" s="11"/>
       <c r="BA26" s="11"/>
       <c r="BB26" s="11"/>
-      <c r="BC26" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC26" s="11"/>
       <c r="BD26" s="11" t="inlineStr">
         <is>
           <t>Y</t>
@@ -12292,41 +12254,45 @@
       <c r="BF26" s="11"/>
       <c r="BG26" s="11"/>
       <c r="BH26" s="12"/>
-      <c r="BI26" s="20"/>
+      <c r="BI26" s="20" t="inlineStr">
+        <is>
+          <t>Amazon おすすめ</t>
+        </is>
+      </c>
       <c r="BJ26" s="20" t="inlineStr">
         <is>
-          <t>5.13 kg</t>
+          <t>4.29 Kilograms</t>
         </is>
       </c>
       <c r="BK26" s="20" t="inlineStr">
         <is>
-          <t>5.13 kg</t>
+          <t>4.29 kg</t>
         </is>
       </c>
       <c r="BL26" s="20" t="inlineStr">
         <is>
-          <t>27.5長さ x 27.8幅 x 110.5高さ cm</t>
+          <t>26.5長さ x 23.5幅 x 111.5高さ cm</t>
         </is>
       </c>
       <c r="BM26" s="20"/>
       <c r="BN26" s="20" t="inlineStr">
         <is>
-          <t>13 kg</t>
+          <t>4.29 kg</t>
         </is>
       </c>
       <c r="BO26" s="20" t="inlineStr">
         <is>
-          <t>13.00 kg</t>
+          <t>4.29 kg</t>
         </is>
       </c>
       <c r="BP26" s="20" t="inlineStr">
         <is>
-          <t>75 x 38 x 35 cm</t>
+          <t>72.5 x 31.2 x 29.1 cm</t>
         </is>
       </c>
       <c r="BQ26" s="20" t="inlineStr">
         <is>
-          <t>75.00 x 38.00 x 35.00 cm</t>
+          <t>72.50 x 31.20 x 29.10 cm</t>
         </is>
       </c>
       <c r="BR26" s="11" t="inlineStr">
@@ -12342,40 +12308,40 @@
       <c r="B27" s="11"/>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>B08XLW562G</t>
+          <t>B0H6DZMNPV</t>
         </is>
       </c>
       <c r="D27" s="12"/>
       <c r="E27" s="12"/>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>不明</t>
+          <t>dreame</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=%E4%B8%8D%E6%98%8E</t>
+          <t>https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0H6DZMNPV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>黑色+Decker 干湿两用锂电池吸尘器 4536178960298</t>
+          <t>dreame T16 擦水吸尘器&amp;旋转刷套装</t>
         </is>
       </c>
       <c r="I27" s="12"/>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B08XLW562G?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0H6DZMNPV?psc=1</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/31NELDCajpL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31ddgJIAJbL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>B08XLW562G</t>
+          <t>B0H6DZMNPV</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
@@ -12389,13 +12355,13 @@
         </is>
       </c>
       <c r="O27" s="13">
-        <v>73669</v>
+        <v>32651</v>
       </c>
       <c r="P27" s="13">
-        <v>-54113</v>
+        <v>540152</v>
       </c>
       <c r="Q27" s="14">
-        <v>-2.77</v>
+        <v>0.89</v>
       </c>
       <c r="R27" s="15" t="inlineStr">
         <is>
@@ -12404,15 +12370,15 @@
       </c>
       <c r="S27" s="16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>13</t>
         </is>
       </c>
       <c r="T27" s="13">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="U27" s="14"/>
       <c r="V27" s="13">
-        <v>135000</v>
+        <v>41862</v>
       </c>
       <c r="W27" s="13"/>
       <c r="X27" s="13"/>
@@ -12420,75 +12386,67 @@
         <v>1</v>
       </c>
       <c r="Z27" s="13">
-        <v>4500</v>
+        <v>41862</v>
       </c>
       <c r="AA27"/>
       <c r="AB27"/>
       <c r="AC27" s="2"/>
-      <c r="AD27" s="17">
-        <v>3</v>
-      </c>
-      <c r="AE27" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF27" s="18">
-        <v>2.7</v>
-      </c>
+      <c r="AD27" s="17"/>
+      <c r="AE27" s="13"/>
+      <c r="AF27" s="18"/>
       <c r="AG27" s="19">
         <v>0</v>
       </c>
-      <c r="AH27" s="13">
-        <v>472</v>
-      </c>
+      <c r="AH27" s="13"/>
       <c r="AI27" s="14">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="AJ27"/>
       <c r="AK27" s="11" t="inlineStr">
         <is>
-          <t>2021-06-13</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AL27" s="17">
-        <v>1943</v>
+        <v>106</v>
       </c>
       <c r="AM27" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN27" s="11"/>
       <c r="AO27" s="11"/>
       <c r="AP27"/>
       <c r="AQ27" s="17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AR27" s="17">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AS27" s="12" t="inlineStr">
         <is>
-          <t>Abeショップ関西</t>
+          <t>Dreame公式ストア</t>
         </is>
       </c>
       <c r="AT27" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU27" s="11" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV27" s="12" t="inlineStr">
         <is>
-          <t>初瀬６９３</t>
+          <t>ROOM H28G BLK EH 10TH FLOOR GOLDEN BEAR IND CTR 66-82</t>
         </is>
       </c>
       <c r="AW27" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2RYDH17QLIL3V</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WV0MTJICL1UJ</t>
         </is>
       </c>
       <c r="AX27" s="11"/>
@@ -12503,51 +12461,15 @@
       <c r="BG27" s="11"/>
       <c r="BH27" s="12"/>
       <c r="BI27" s="20"/>
-      <c r="BJ27" s="20" t="inlineStr">
-        <is>
-          <t>1 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK27" s="20" t="inlineStr">
-        <is>
-          <t>1,000.00 g</t>
-        </is>
-      </c>
-      <c r="BL27" s="20" t="inlineStr">
-        <is>
-          <t>30 x 10 x 10 cm</t>
-        </is>
-      </c>
-      <c r="BM27" s="20" t="inlineStr">
-        <is>
-          <t>30.00 x 10.00 x 10.00 cm</t>
-        </is>
-      </c>
-      <c r="BN27" s="20" t="inlineStr">
-        <is>
-          <t>1 kg</t>
-        </is>
-      </c>
-      <c r="BO27" s="20" t="inlineStr">
-        <is>
-          <t>1,000.00 g</t>
-        </is>
-      </c>
-      <c r="BP27" s="20" t="inlineStr">
-        <is>
-          <t>43.8 x 13.9 x 11.7 cm</t>
-        </is>
-      </c>
-      <c r="BQ27" s="20" t="inlineStr">
-        <is>
-          <t>43.80 x 13.90 x 11.70 cm</t>
-        </is>
-      </c>
-      <c r="BR27" s="11" t="inlineStr">
-        <is>
-          <t>标准</t>
-        </is>
-      </c>
+      <c r="BJ27" s="20"/>
+      <c r="BK27" s="20"/>
+      <c r="BL27" s="20"/>
+      <c r="BM27" s="20"/>
+      <c r="BN27" s="20"/>
+      <c r="BO27" s="20"/>
+      <c r="BP27" s="20"/>
+      <c r="BQ27" s="20"/>
+      <c r="BR27" s="11"/>
     </row>
     <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
@@ -12556,222 +12478,104 @@
       <c r="B28" s="11"/>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>B0GS4QDH7R</t>
+          <t>B09P2RKRWX</t>
         </is>
       </c>
       <c r="D28" s="12"/>
       <c r="E28" s="12"/>
-      <c r="F28" s="12" t="inlineStr">
-        <is>
-          <t>uwant</t>
-        </is>
-      </c>
+      <c r="F28" s="12"/>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%83%A6%E3%83%AF%E3%83%B3%E3%83%88%EF%BC%88UWANT/page/CFD932E4-87F0-4563-8A00-7E6F0611A613?lp_asin=B0GS4QDH7R&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jpundefined</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>uwant 擦水吸尘器 自动清洗 干湿两用吸尘器 热风干燥 电解水除菌 连续工作35分钟 大容量清污分离水箱 水花吸尘器 D100</t>
+          <t>Tineco Floor One S5 Plus 无线擦水吸尘器 干湿两用siLoop 智能传感器检测污垢,吸力强,自动清洁干燥,长时间运行,大容量水箱,2 年保修</t>
         </is>
       </c>
       <c r="I28" s="12"/>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0GS4QDH7R?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B09P2RKRWX?psc=1</t>
         </is>
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61j3dNdQj4L._AC_US600_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/615lYQCrd2L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L28" s="12" t="inlineStr">
         <is>
-          <t>B0GS4QDH7R</t>
-        </is>
-      </c>
-      <c r="M28" s="12" t="inlineStr">
-        <is>
-          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
-        </is>
-      </c>
-      <c r="N28" s="12" t="inlineStr">
-        <is>
-          <t>DIY・工具・ガーデン</t>
-        </is>
-      </c>
-      <c r="O28" s="13">
-        <v>152194</v>
-      </c>
-      <c r="P28" s="13">
-        <v>-13127</v>
-      </c>
-      <c r="Q28" s="14">
-        <v>-0.09</v>
-      </c>
-      <c r="R28" s="15" t="inlineStr">
-        <is>
-          <t>ウェットドライショップ掃除機</t>
-        </is>
-      </c>
-      <c r="S28" s="16" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="T28" s="13">
-        <v>4</v>
-      </c>
-      <c r="U28" s="14">
-        <v>-0.94</v>
-      </c>
-      <c r="V28" s="13">
-        <v>46644</v>
-      </c>
+          <t>B09P2RKRWX</t>
+        </is>
+      </c>
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
+      <c r="O28" s="13"/>
+      <c r="P28" s="13"/>
+      <c r="Q28" s="14"/>
+      <c r="R28" s="15"/>
+      <c r="S28" s="16"/>
+      <c r="T28" s="13"/>
+      <c r="U28" s="14"/>
+      <c r="V28" s="13"/>
       <c r="W28" s="13"/>
       <c r="X28" s="13"/>
-      <c r="Y28" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z28" s="13">
-        <v>11661</v>
-      </c>
+      <c r="Y28" s="17"/>
+      <c r="Z28" s="13"/>
       <c r="AA28"/>
       <c r="AB28"/>
       <c r="AC28" s="2"/>
       <c r="AD28" s="17">
-        <v>15</v>
-      </c>
-      <c r="AE28" s="13">
-        <v>3</v>
-      </c>
+        <v>3903</v>
+      </c>
+      <c r="AE28" s="13"/>
       <c r="AF28" s="18">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AG28" s="19">
-        <v>0.75</v>
-      </c>
-      <c r="AH28" s="13">
-        <v>1020</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH28" s="13"/>
       <c r="AI28" s="14">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="AJ28"/>
-      <c r="AK28" s="11" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="AL28" s="17">
-        <v>175</v>
-      </c>
-      <c r="AM28" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="AK28" s="11"/>
+      <c r="AL28" s="17"/>
+      <c r="AM28" s="11"/>
       <c r="AN28" s="11"/>
       <c r="AO28" s="11"/>
       <c r="AP28"/>
-      <c r="AQ28" s="17">
-        <v>5</v>
-      </c>
-      <c r="AR28" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS28" s="12" t="inlineStr">
-        <is>
-          <t>Uwant公式ストア</t>
-        </is>
-      </c>
-      <c r="AT28" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU28" s="11" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV28" s="12" t="inlineStr">
-        <is>
-          <t>深圳市 广东省 518000 CN</t>
-        </is>
-      </c>
-      <c r="AW28" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1O5QS9O13RS09</t>
-        </is>
-      </c>
+      <c r="AQ28" s="17"/>
+      <c r="AR28" s="17"/>
+      <c r="AS28" s="12"/>
+      <c r="AT28" s="11"/>
+      <c r="AU28" s="11"/>
+      <c r="AV28" s="12"/>
+      <c r="AW28" s="11"/>
       <c r="AX28" s="11"/>
-      <c r="AY28" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY28" s="11"/>
       <c r="AZ28" s="11"/>
       <c r="BA28" s="11"/>
       <c r="BB28" s="11"/>
       <c r="BC28" s="11"/>
-      <c r="BD28" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD28" s="11"/>
       <c r="BE28" s="11"/>
       <c r="BF28" s="11"/>
       <c r="BG28" s="11"/>
       <c r="BH28" s="12"/>
-      <c r="BI28" s="20" t="inlineStr">
-        <is>
-          <t>Amazon おすすめ</t>
-        </is>
-      </c>
-      <c r="BJ28" s="20" t="inlineStr">
-        <is>
-          <t>4.29 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK28" s="20" t="inlineStr">
-        <is>
-          <t>4.29 kg</t>
-        </is>
-      </c>
-      <c r="BL28" s="20" t="inlineStr">
-        <is>
-          <t>26.5長さ x 23.5幅 x 111.5高さ cm</t>
-        </is>
-      </c>
+      <c r="BI28" s="20"/>
+      <c r="BJ28" s="20"/>
+      <c r="BK28" s="20"/>
+      <c r="BL28" s="20"/>
       <c r="BM28" s="20"/>
-      <c r="BN28" s="20" t="inlineStr">
-        <is>
-          <t>4.29 kg</t>
-        </is>
-      </c>
-      <c r="BO28" s="20" t="inlineStr">
-        <is>
-          <t>4.29 kg</t>
-        </is>
-      </c>
-      <c r="BP28" s="20" t="inlineStr">
-        <is>
-          <t>72.5 x 31.2 x 29.1 cm</t>
-        </is>
-      </c>
-      <c r="BQ28" s="20" t="inlineStr">
-        <is>
-          <t>72.50 x 31.20 x 29.10 cm</t>
-        </is>
-      </c>
-      <c r="BR28" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
+      <c r="BN28" s="20"/>
+      <c r="BO28" s="20"/>
+      <c r="BP28" s="20"/>
+      <c r="BQ28" s="20"/>
+      <c r="BR28" s="11"/>
     </row>
     <row r="29" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
@@ -12780,40 +12584,40 @@
       <c r="B29" s="11"/>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>B0H6DZMNPV</t>
+          <t>B0C4HGZ1L6</t>
         </is>
       </c>
       <c r="D29" s="12"/>
       <c r="E29" s="12"/>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>dreame</t>
+          <t>NEODIT</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0H6DZMNPV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/NEODIT%E3%83%8D%E3%82%AA%E3%83%87%E3%82%A3%E3%83%83%E3%83%88/page/CD7250ED-8E04-4E58-A881-68B2A928AE8C?lp_asin=B0C4HGZ1L6&amp;ref_=ast_bln</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>dreame T16 擦水吸尘器&amp;旋转刷套装</t>
+          <t>NEODIT 地毯清洁剂 14000Pa强力吸力 淋水机清洗机 可温水40度清洗 地毯清洗机 去污 干湿两用吸尘器 沙发清洁剂 地毯清洁剂 水洗 车用吸尘器 浴室清洁器 地毯/布制品/宠物坐垫/车内/地毯/沙发/地毯/毛绒玩具/清扫用品</t>
         </is>
       </c>
       <c r="I29" s="12"/>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0H6DZMNPV?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0C4HGZ1L6?psc=1</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31ddgJIAJbL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81DHFglSw9L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>B0H6DZMNPV</t>
+          <t>B0C4HGZ1L6</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr">
@@ -12827,13 +12631,13 @@
         </is>
       </c>
       <c r="O29" s="13">
-        <v>32651</v>
+        <v>169234</v>
       </c>
       <c r="P29" s="13">
-        <v>540152</v>
+        <v>-1650</v>
       </c>
       <c r="Q29" s="14">
-        <v>0.89</v>
+        <v>-0.01</v>
       </c>
       <c r="R29" s="15" t="inlineStr">
         <is>
@@ -12842,83 +12646,87 @@
       </c>
       <c r="S29" s="16" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="T29" s="13">
-        <v>1</v>
-      </c>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="T29" s="13"/>
       <c r="U29" s="14"/>
-      <c r="V29" s="13">
-        <v>41862</v>
-      </c>
+      <c r="V29" s="13"/>
       <c r="W29" s="13"/>
       <c r="X29" s="13"/>
       <c r="Y29" s="17">
         <v>1</v>
       </c>
       <c r="Z29" s="13">
-        <v>41862</v>
+        <v>13998</v>
       </c>
       <c r="AA29"/>
       <c r="AB29"/>
       <c r="AC29" s="2"/>
-      <c r="AD29" s="17"/>
-      <c r="AE29" s="13"/>
-      <c r="AF29" s="18"/>
+      <c r="AD29" s="17">
+        <v>322</v>
+      </c>
+      <c r="AE29" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="18">
+        <v>4</v>
+      </c>
       <c r="AG29" s="19">
         <v>0</v>
       </c>
-      <c r="AH29" s="13"/>
+      <c r="AH29" s="13">
+        <v>781</v>
+      </c>
       <c r="AI29" s="14">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AJ29"/>
       <c r="AK29" s="11" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="AL29" s="17">
-        <v>106</v>
+        <v>1197</v>
       </c>
       <c r="AM29" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN29" s="11"/>
       <c r="AO29" s="11"/>
       <c r="AP29"/>
       <c r="AQ29" s="17">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AR29" s="17">
         <v>1</v>
       </c>
       <c r="AS29" s="12" t="inlineStr">
         <is>
-          <t>Dreame公式ストア</t>
+          <t>Neodit-tools</t>
         </is>
       </c>
       <c r="AT29" s="11" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU29" s="11" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV29" s="12" t="inlineStr">
         <is>
-          <t>ROOM H28G BLK EH 10TH FLOOR GOLDEN BEAR IND CTR 66-82</t>
+          <t>nanjingshi jiangsusheng 210043 CN</t>
         </is>
       </c>
       <c r="AW29" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WV0MTJICL1UJ</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2YB9P0HYGN84U</t>
         </is>
       </c>
       <c r="AX29" s="11"/>
@@ -12926,22 +12734,66 @@
       <c r="AZ29" s="11"/>
       <c r="BA29" s="11"/>
       <c r="BB29" s="11"/>
-      <c r="BC29" s="11"/>
-      <c r="BD29" s="11"/>
+      <c r="BC29" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD29" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE29" s="11"/>
       <c r="BF29" s="11"/>
       <c r="BG29" s="11"/>
       <c r="BH29" s="12"/>
       <c r="BI29" s="20"/>
-      <c r="BJ29" s="20"/>
-      <c r="BK29" s="20"/>
-      <c r="BL29" s="20"/>
-      <c r="BM29" s="20"/>
-      <c r="BN29" s="20"/>
-      <c r="BO29" s="20"/>
-      <c r="BP29" s="20"/>
-      <c r="BQ29" s="20"/>
-      <c r="BR29" s="11"/>
+      <c r="BJ29" s="20" t="inlineStr">
+        <is>
+          <t>5.24 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK29" s="20" t="inlineStr">
+        <is>
+          <t>5.24 kg</t>
+        </is>
+      </c>
+      <c r="BL29" s="20" t="inlineStr">
+        <is>
+          <t>18 x 35 x 29 cm</t>
+        </is>
+      </c>
+      <c r="BM29" s="20" t="inlineStr">
+        <is>
+          <t>18.00 x 35.00 x 29.00 cm</t>
+        </is>
+      </c>
+      <c r="BN29" s="20" t="inlineStr">
+        <is>
+          <t>5.24 kg</t>
+        </is>
+      </c>
+      <c r="BO29" s="20" t="inlineStr">
+        <is>
+          <t>5.24 kg</t>
+        </is>
+      </c>
+      <c r="BP29" s="20" t="inlineStr">
+        <is>
+          <t>37.9 x 36.9 x 26.2 cm</t>
+        </is>
+      </c>
+      <c r="BQ29" s="20" t="inlineStr">
+        <is>
+          <t>37.90 x 36.90 x 26.20 cm</t>
+        </is>
+      </c>
+      <c r="BR29" s="11" t="inlineStr">
+        <is>
+          <t>大件</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
@@ -12950,7 +12802,7 @@
       <c r="B30" s="11"/>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>B09P2RKRWX</t>
+          <t>B0CF9P7W51</t>
         </is>
       </c>
       <c r="D30" s="12"/>
@@ -12963,23 +12815,23 @@
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>Tineco Floor One S5 Plus 无线擦水吸尘器 干湿两用siLoop 智能传感器检测污垢,吸力强,自动清洁干燥,长时间运行,大容量水箱,2 年保修</t>
+          <t>Tineco Floor One S7 Lite 擦水吸尘器 无线/干湿两用/强力吸力/轻量化/长时间驾驶/静音 自洁式 自走式 iLoop 智能传感器 应用操作 语音指南 制造商2年保修</t>
         </is>
       </c>
       <c r="I30" s="12"/>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B09P2RKRWX?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0CF9P7W51?psc=1</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/615lYQCrd2L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61bJ0J+PfIL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L30" s="12" t="inlineStr">
         <is>
-          <t>B09P2RKRWX</t>
+          <t>B0CF9P7W51</t>
         </is>
       </c>
       <c r="M30" s="12"/>
@@ -13000,7 +12852,7 @@
       <c r="AB30"/>
       <c r="AC30" s="2"/>
       <c r="AD30" s="17">
-        <v>3903</v>
+        <v>23</v>
       </c>
       <c r="AE30" s="13"/>
       <c r="AF30" s="18">
@@ -13056,216 +12908,104 @@
       <c r="B31" s="11"/>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>B0C4HGZ1L6</t>
+          <t>B0D5HBSJFX</t>
         </is>
       </c>
       <c r="D31" s="12"/>
       <c r="E31" s="12"/>
-      <c r="F31" s="12" t="inlineStr">
-        <is>
-          <t>NEODIT</t>
-        </is>
-      </c>
+      <c r="F31" s="12"/>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/NEODIT%E3%83%8D%E3%82%AA%E3%83%87%E3%82%A3%E3%83%83%E3%83%88/page/CD7250ED-8E04-4E58-A881-68B2A928AE8C?lp_asin=B0C4HGZ1L6&amp;ref_=ast_bln</t>
+          <t>https://www.amazon.co.jpundefined</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>NEODIT 地毯清洁剂 14000Pa强力吸力 淋水机清洗机 可温水40度清洗 地毯清洗机 去污 干湿两用吸尘器 沙发清洁剂 地毯清洁剂 水洗 车用吸尘器 浴室清洁器 地毯/布制品/宠物坐垫/车内/地毯/沙发/地毯/毛绒玩具/清扫用品</t>
+          <t>dreame (ドリーミー) H12S 湿拖吸尘器 吸尘&amp;湿拖2in1 刷头自动清洗和温风干燥 除菌 贴墙边刷头设计 16000Pa强力吸力 35分钟连续运行 智能污垢检测和自动吸力调整 大容量水箱 语音导航 高速电机 静音设计 3种运行模式 专用清</t>
         </is>
       </c>
       <c r="I31" s="12"/>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0C4HGZ1L6?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0D5HBSJFX?psc=1</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81DHFglSw9L._AC_US600_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/51ioK4Vk3NL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>B0C4HGZ1L6</t>
-        </is>
-      </c>
-      <c r="M31" s="12" t="inlineStr">
-        <is>
-          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
-        </is>
-      </c>
-      <c r="N31" s="12" t="inlineStr">
-        <is>
-          <t>DIY・工具・ガーデン</t>
-        </is>
-      </c>
-      <c r="O31" s="13">
-        <v>169234</v>
-      </c>
-      <c r="P31" s="13">
-        <v>-1650</v>
-      </c>
-      <c r="Q31" s="14">
-        <v>-0.01</v>
-      </c>
-      <c r="R31" s="15" t="inlineStr">
-        <is>
-          <t>ウェットドライショップ掃除機</t>
-        </is>
-      </c>
-      <c r="S31" s="16" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
+          <t>B0D5HBSJFX</t>
+        </is>
+      </c>
+      <c r="M31" s="12"/>
+      <c r="N31" s="12"/>
+      <c r="O31" s="13"/>
+      <c r="P31" s="13"/>
+      <c r="Q31" s="14"/>
+      <c r="R31" s="15"/>
+      <c r="S31" s="16"/>
       <c r="T31" s="13"/>
       <c r="U31" s="14"/>
       <c r="V31" s="13"/>
       <c r="W31" s="13"/>
       <c r="X31" s="13"/>
-      <c r="Y31" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z31" s="13">
-        <v>13998</v>
-      </c>
+      <c r="Y31" s="17"/>
+      <c r="Z31" s="13"/>
       <c r="AA31"/>
       <c r="AB31"/>
       <c r="AC31" s="2"/>
       <c r="AD31" s="17">
-        <v>322</v>
-      </c>
-      <c r="AE31" s="13">
-        <v>0</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="AE31" s="13"/>
       <c r="AF31" s="18">
         <v>4</v>
       </c>
       <c r="AG31" s="19">
         <v>0</v>
       </c>
-      <c r="AH31" s="13">
-        <v>781</v>
-      </c>
+      <c r="AH31" s="13"/>
       <c r="AI31" s="14">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="AJ31"/>
-      <c r="AK31" s="11" t="inlineStr">
-        <is>
-          <t>2023-06-29</t>
-        </is>
-      </c>
-      <c r="AL31" s="17">
-        <v>1197</v>
-      </c>
-      <c r="AM31" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="AK31" s="11"/>
+      <c r="AL31" s="17"/>
+      <c r="AM31" s="11"/>
       <c r="AN31" s="11"/>
       <c r="AO31" s="11"/>
       <c r="AP31"/>
-      <c r="AQ31" s="17">
-        <v>10</v>
-      </c>
-      <c r="AR31" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS31" s="12" t="inlineStr">
-        <is>
-          <t>Neodit-tools</t>
-        </is>
-      </c>
-      <c r="AT31" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU31" s="11" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV31" s="12" t="inlineStr">
-        <is>
-          <t>nanjingshi jiangsusheng 210043 CN</t>
-        </is>
-      </c>
-      <c r="AW31" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2YB9P0HYGN84U</t>
-        </is>
-      </c>
+      <c r="AQ31" s="17"/>
+      <c r="AR31" s="17"/>
+      <c r="AS31" s="12"/>
+      <c r="AT31" s="11"/>
+      <c r="AU31" s="11"/>
+      <c r="AV31" s="12"/>
+      <c r="AW31" s="11"/>
       <c r="AX31" s="11"/>
       <c r="AY31" s="11"/>
       <c r="AZ31" s="11"/>
       <c r="BA31" s="11"/>
       <c r="BB31" s="11"/>
-      <c r="BC31" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD31" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC31" s="11"/>
+      <c r="BD31" s="11"/>
       <c r="BE31" s="11"/>
       <c r="BF31" s="11"/>
       <c r="BG31" s="11"/>
       <c r="BH31" s="12"/>
       <c r="BI31" s="20"/>
-      <c r="BJ31" s="20" t="inlineStr">
-        <is>
-          <t>5.24 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK31" s="20" t="inlineStr">
-        <is>
-          <t>5.24 kg</t>
-        </is>
-      </c>
-      <c r="BL31" s="20" t="inlineStr">
-        <is>
-          <t>18 x 35 x 29 cm</t>
-        </is>
-      </c>
-      <c r="BM31" s="20" t="inlineStr">
-        <is>
-          <t>18.00 x 35.00 x 29.00 cm</t>
-        </is>
-      </c>
-      <c r="BN31" s="20" t="inlineStr">
-        <is>
-          <t>5.24 kg</t>
-        </is>
-      </c>
-      <c r="BO31" s="20" t="inlineStr">
-        <is>
-          <t>5.24 kg</t>
-        </is>
-      </c>
-      <c r="BP31" s="20" t="inlineStr">
-        <is>
-          <t>37.9 x 36.9 x 26.2 cm</t>
-        </is>
-      </c>
-      <c r="BQ31" s="20" t="inlineStr">
-        <is>
-          <t>37.90 x 36.90 x 26.20 cm</t>
-        </is>
-      </c>
-      <c r="BR31" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
+      <c r="BJ31" s="20"/>
+      <c r="BK31" s="20"/>
+      <c r="BL31" s="20"/>
+      <c r="BM31" s="20"/>
+      <c r="BN31" s="20"/>
+      <c r="BO31" s="20"/>
+      <c r="BP31" s="20"/>
+      <c r="BQ31" s="20"/>
+      <c r="BR31" s="11"/>
     </row>
     <row r="32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
@@ -13274,7 +13014,7 @@
       <c r="B32" s="11"/>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>B0CF9P7W51</t>
+          <t>B0DHV7QRSK</t>
         </is>
       </c>
       <c r="D32" s="12"/>
@@ -13287,23 +13027,23 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>Tineco Floor One S7 Lite 擦水吸尘器 无线/干湿两用/强力吸力/轻量化/长时间驾驶/静音 自洁式 自走式 iLoop 智能传感器 应用操作 语音指南 制造商2年保修</t>
+          <t>Vittorio(ヴィットリオ) 乾湿両用掃除機 WET&amp;DRYクリーナー ZV-04-WDs【吸込仕事率65W 集塵約3.0L/吸水約1.5L】 小型コンパクトモデル(33×31×23cm) 本体重量2.5Kg 玄関 ベランダ掃除 作業現場の簡</t>
         </is>
       </c>
       <c r="I32" s="12"/>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0CF9P7W51?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0DHV7QRSK?psc=1</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61bJ0J+PfIL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61Coq6GGchL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L32" s="12" t="inlineStr">
         <is>
-          <t>B0CF9P7W51</t>
+          <t>B0DHV7QRSK</t>
         </is>
       </c>
       <c r="M32" s="12"/>
@@ -13319,16 +13059,18 @@
       <c r="W32" s="13"/>
       <c r="X32" s="13"/>
       <c r="Y32" s="17"/>
-      <c r="Z32" s="13"/>
+      <c r="Z32" s="13">
+        <v>46</v>
+      </c>
       <c r="AA32"/>
       <c r="AB32"/>
       <c r="AC32" s="2"/>
       <c r="AD32" s="17">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AE32" s="13"/>
       <c r="AF32" s="18">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AG32" s="19">
         <v>0</v>
@@ -13380,7 +13122,7 @@
       <c r="B33" s="11"/>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>B0D5HBSJFX</t>
+          <t>B0DXY4BJ5K</t>
         </is>
       </c>
       <c r="D33" s="12"/>
@@ -13393,23 +13135,23 @@
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>dreame (ドリーミー) H12S 湿拖吸尘器 吸尘&amp;湿拖2in1 刷头自动清洗和温风干燥 除菌 贴墙边刷头设计 16000Pa强力吸力 35分钟连续运行 智能污垢检测和自动吸力调整 大容量水箱 语音导航 高速电机 静音设计 3种运行模式 专用清</t>
+          <t>Narwal (ナーワル) S20 Pro コードレス水拭き掃除機 20,000Pa強力吸引 自動洗浄s家電批評ベストバイ, 自走式,モップ自動洗浄機能付き,乾湿両用 家具の下も清掃可能 フローリング、タイル、石床専用 絡まりゼロブラシ搭載 子ど</t>
         </is>
       </c>
       <c r="I33" s="12"/>
       <c r="J33" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0D5HBSJFX?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0DXY4BJ5K?psc=1</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/51ioK4Vk3NL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/516bWwYYlQL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>B0D5HBSJFX</t>
+          <t>B0DXY4BJ5K</t>
         </is>
       </c>
       <c r="M33" s="12"/>
@@ -13430,11 +13172,11 @@
       <c r="AB33"/>
       <c r="AC33" s="2"/>
       <c r="AD33" s="17">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="AE33" s="13"/>
       <c r="AF33" s="18">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AG33" s="19">
         <v>0</v>
@@ -13486,7 +13228,7 @@
       <c r="B34" s="11"/>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>B0DHV7QRSK</t>
+          <t>B0FBR52FBV</t>
         </is>
       </c>
       <c r="D34" s="12"/>
@@ -13499,23 +13241,23 @@
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>Vittorio(ヴィットリオ) 乾湿両用掃除機 WET&amp;DRYクリーナー ZV-04-WDs【吸込仕事率65W 集塵約3.0L/吸水約1.5L】 小型コンパクトモデル(33×31×23cm) 本体重量2.5Kg 玄関 ベランダ掃除 作業現場の簡</t>
+          <t>dreame (Dream) G10 干湿两用 擦水吸尘器 7000Pa吸力 暖风干燥 自动清洗 30分钟长时间运行 LED显示屏s地板擦拭 带拖把功能 擦拭 两用 无线棒 吸尘器 轻量级吸尘器</t>
         </is>
       </c>
       <c r="I34" s="12"/>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0DHV7QRSK?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FBR52FBV?psc=1</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61Coq6GGchL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/51Gx-JJE9mL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L34" s="12" t="inlineStr">
         <is>
-          <t>B0DHV7QRSK</t>
+          <t>B0FBR52FBV</t>
         </is>
       </c>
       <c r="M34" s="12"/>
@@ -13531,18 +13273,16 @@
       <c r="W34" s="13"/>
       <c r="X34" s="13"/>
       <c r="Y34" s="17"/>
-      <c r="Z34" s="13">
-        <v>46</v>
-      </c>
+      <c r="Z34" s="13"/>
       <c r="AA34"/>
       <c r="AB34"/>
       <c r="AC34" s="2"/>
       <c r="AD34" s="17">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="AE34" s="13"/>
       <c r="AF34" s="18">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="AG34" s="19">
         <v>0</v>
@@ -13594,104 +13334,208 @@
       <c r="B35" s="11"/>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>B0DXY4BJ5K</t>
+          <t>B0FGC7422M</t>
         </is>
       </c>
       <c r="D35" s="12"/>
       <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>JONR</t>
+        </is>
+      </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jpundefined</t>
+          <t>https://www.amazon.co.jp/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FGC7422M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>Narwal (ナーワル) S20 Pro コードレス水拭き掃除機 20,000Pa強力吸引 自動洗浄s家電批評ベストバイ, 自走式,モップ自動洗浄機能付き,乾湿両用 家具の下も清掃可能 フローリング、タイル、石床専用 絡まりゼロブラシ搭載 子ど</t>
+          <t>擦水吸尘器 吸水&amp;擦拭2合1无绳棒吸尘器 干湿两用 滚轮刷自动清洗&amp;干燥 150°睡眠结构 墙时1mm清扫 20000Pa强力吸力 长时间运行大容量清水&amp;污水桶 独自生活 家庭用 日语使用说明书 PSE认证</t>
         </is>
       </c>
       <c r="I35" s="12"/>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0DXY4BJ5K?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FGC7422M?psc=1</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/516bWwYYlQL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51PDVCpecuL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
-          <t>B0DXY4BJ5K</t>
-        </is>
-      </c>
-      <c r="M35" s="12"/>
-      <c r="N35" s="12"/>
-      <c r="O35" s="13"/>
-      <c r="P35" s="13"/>
-      <c r="Q35" s="14"/>
-      <c r="R35" s="15"/>
-      <c r="S35" s="16"/>
+          <t>B0FGC7422M</t>
+        </is>
+      </c>
+      <c r="M35" s="12" t="inlineStr">
+        <is>
+          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
+        </is>
+      </c>
+      <c r="N35" s="12" t="inlineStr">
+        <is>
+          <t>DIY・工具・ガーデン</t>
+        </is>
+      </c>
+      <c r="O35" s="13">
+        <v>156632</v>
+      </c>
+      <c r="P35" s="13">
+        <v>4124</v>
+      </c>
+      <c r="Q35" s="14">
+        <v>0.03</v>
+      </c>
+      <c r="R35" s="15" t="inlineStr">
+        <is>
+          <t>ウェットドライショップ掃除機</t>
+        </is>
+      </c>
+      <c r="S35" s="16" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="T35" s="13"/>
       <c r="U35" s="14"/>
       <c r="V35" s="13"/>
       <c r="W35" s="13"/>
       <c r="X35" s="13"/>
-      <c r="Y35" s="17"/>
-      <c r="Z35" s="13"/>
+      <c r="Y35" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z35" s="13">
+        <v>118000</v>
+      </c>
       <c r="AA35"/>
       <c r="AB35"/>
       <c r="AC35" s="2"/>
       <c r="AD35" s="17">
-        <v>62</v>
-      </c>
-      <c r="AE35" s="13"/>
+        <v>29</v>
+      </c>
+      <c r="AE35" s="13">
+        <v>2</v>
+      </c>
       <c r="AF35" s="18">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AG35" s="19">
         <v>0</v>
       </c>
-      <c r="AH35" s="13"/>
+      <c r="AH35" s="13">
+        <v>1020</v>
+      </c>
       <c r="AI35" s="14">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AJ35"/>
-      <c r="AK35" s="11"/>
-      <c r="AL35" s="17"/>
-      <c r="AM35" s="11"/>
+      <c r="AK35" s="11" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="AL35" s="17">
+        <v>443</v>
+      </c>
+      <c r="AM35" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="AN35" s="11"/>
       <c r="AO35" s="11"/>
       <c r="AP35"/>
-      <c r="AQ35" s="17"/>
-      <c r="AR35" s="17"/>
-      <c r="AS35" s="12"/>
-      <c r="AT35" s="11"/>
-      <c r="AU35" s="11"/>
-      <c r="AV35" s="12"/>
-      <c r="AW35" s="11"/>
+      <c r="AQ35" s="17">
+        <v>8</v>
+      </c>
+      <c r="AR35" s="17">
+        <v>1</v>
+      </c>
+      <c r="AS35" s="12" t="inlineStr">
+        <is>
+          <t>-公式ストア</t>
+        </is>
+      </c>
+      <c r="AT35" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU35" s="11" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV35" s="12" t="inlineStr">
+        <is>
+          <t>莆田市 福建 351119 CN</t>
+        </is>
+      </c>
+      <c r="AW35" s="11" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1UV3PJGHZIHW6</t>
+        </is>
+      </c>
       <c r="AX35" s="11"/>
       <c r="AY35" s="11"/>
       <c r="AZ35" s="11"/>
       <c r="BA35" s="11"/>
       <c r="BB35" s="11"/>
       <c r="BC35" s="11"/>
-      <c r="BD35" s="11"/>
+      <c r="BD35" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE35" s="11"/>
       <c r="BF35" s="11"/>
       <c r="BG35" s="11"/>
       <c r="BH35" s="12"/>
       <c r="BI35" s="20"/>
-      <c r="BJ35" s="20"/>
-      <c r="BK35" s="20"/>
-      <c r="BL35" s="20"/>
+      <c r="BJ35" s="20" t="inlineStr">
+        <is>
+          <t>3 kg</t>
+        </is>
+      </c>
+      <c r="BK35" s="20" t="inlineStr">
+        <is>
+          <t>3.00 kg</t>
+        </is>
+      </c>
+      <c r="BL35" s="20" t="inlineStr">
+        <is>
+          <t>29.6長さ x 26.9幅 x 113.4高さ cm</t>
+        </is>
+      </c>
       <c r="BM35" s="20"/>
-      <c r="BN35" s="20"/>
-      <c r="BO35" s="20"/>
-      <c r="BP35" s="20"/>
-      <c r="BQ35" s="20"/>
-      <c r="BR35" s="11"/>
+      <c r="BN35" s="20" t="inlineStr">
+        <is>
+          <t>5.96 kg</t>
+        </is>
+      </c>
+      <c r="BO35" s="20" t="inlineStr">
+        <is>
+          <t>5.96 kg</t>
+        </is>
+      </c>
+      <c r="BP35" s="20" t="inlineStr">
+        <is>
+          <t>55.4 x 33.7 x 31.2 cm</t>
+        </is>
+      </c>
+      <c r="BQ35" s="20" t="inlineStr">
+        <is>
+          <t>55.40 x 33.70 x 31.20 cm</t>
+        </is>
+      </c>
+      <c r="BR35" s="11" t="inlineStr">
+        <is>
+          <t>大件</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11">
@@ -13700,7 +13544,7 @@
       <c r="B36" s="11"/>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>B0FBR52FBV</t>
+          <t>B0FL2KXDMX</t>
         </is>
       </c>
       <c r="D36" s="12"/>
@@ -13713,23 +13557,23 @@
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>dreame (Dream) G10 干湿两用 擦水吸尘器 7000Pa吸力 暖风干燥 自动清洗 30分钟长时间运行 LED显示屏s地板擦拭 带拖把功能 擦拭 两用 无线棒 吸尘器 轻量级吸尘器</t>
+          <t>水擦拭吸尘器 JONR ED12 Lite 干湿两用吸尘器 吸水&amp;擦拭2合1无绳棒吸尘器 自动清洗&amp;干燥 150°睡眠结构 墙时1mm清扫 17000Pa强力吸力 长时间运行LED面板 大容量清水&amp;污水罐 经PSE认证</t>
         </is>
       </c>
       <c r="I36" s="12"/>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FBR52FBV?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FL2KXDMX?psc=1</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/51Gx-JJE9mL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61j+d1U1UHL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L36" s="12" t="inlineStr">
         <is>
-          <t>B0FBR52FBV</t>
+          <t>B0FL2KXDMX</t>
         </is>
       </c>
       <c r="M36" s="12"/>
@@ -13750,11 +13594,11 @@
       <c r="AB36"/>
       <c r="AC36" s="2"/>
       <c r="AD36" s="17">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AE36" s="13"/>
       <c r="AF36" s="18">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AG36" s="19">
         <v>0</v>
@@ -13806,40 +13650,40 @@
       <c r="B37" s="11"/>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>B0FGC7422M</t>
+          <t>B0FPXLZSWP</t>
         </is>
       </c>
       <c r="D37" s="12"/>
       <c r="E37" s="12"/>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>JONR</t>
+          <t>NARWAL(ナーワル)</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FGC7422M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/stores/NARWAL/page/48E89FF8-D8FF-42EA-91FA-300E4D5D5CBA?lp_asin=B0FPXLZSWP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>擦水吸尘器 吸水&amp;擦拭2合1无绳棒吸尘器 干湿两用 滚轮刷自动清洗&amp;干燥 150°睡眠结构 墙时1mm清扫 20000Pa强力吸力 长时间运行大容量清水&amp;污水桶 独自生活 家庭用 日语使用说明书 PSE认证</t>
+          <t>Narwal (ナーワル) S30 コードレス水拭き掃除機 20,000Pa吸引 使い捨てゴミネットs自走式 80℃温水モップ自動洗浄 ヒートアイロン乾燥 乾湿両用掃除機 家具の下も清掃可能 絡まり防止機能 子どもやペットのいるご家庭に最適 メン</t>
         </is>
       </c>
       <c r="I37" s="12"/>
       <c r="J37" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FGC7422M?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FPXLZSWP?psc=1</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51PDVCpecuL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51o9M+0xsCL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
-          <t>B0FGC7422M</t>
+          <t>B0FPXLZSWP</t>
         </is>
       </c>
       <c r="M37" s="12" t="inlineStr">
@@ -13853,13 +13697,13 @@
         </is>
       </c>
       <c r="O37" s="13">
-        <v>156632</v>
+        <v>155663</v>
       </c>
       <c r="P37" s="13">
-        <v>4124</v>
+        <v>2593</v>
       </c>
       <c r="Q37" s="14">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="R37" s="15" t="inlineStr">
         <is>
@@ -13868,11 +13712,13 @@
       </c>
       <c r="S37" s="16" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>43</t>
         </is>
       </c>
       <c r="T37" s="13"/>
-      <c r="U37" s="14"/>
+      <c r="U37" s="14">
+        <v>-0.78</v>
+      </c>
       <c r="V37" s="13"/>
       <c r="W37" s="13"/>
       <c r="X37" s="13"/>
@@ -13880,19 +13726,19 @@
         <v>1</v>
       </c>
       <c r="Z37" s="13">
-        <v>118000</v>
+        <v>54951</v>
       </c>
       <c r="AA37"/>
       <c r="AB37"/>
       <c r="AC37" s="2"/>
       <c r="AD37" s="17">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="AE37" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF37" s="18">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AG37" s="19">
         <v>0</v>
@@ -13901,62 +13747,54 @@
         <v>1020</v>
       </c>
       <c r="AI37" s="14">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="AJ37"/>
       <c r="AK37" s="11" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AL37" s="17">
-        <v>443</v>
+        <v>377</v>
       </c>
       <c r="AM37" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN37" s="11"/>
       <c r="AO37" s="11"/>
       <c r="AP37"/>
       <c r="AQ37" s="17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR37" s="17">
         <v>1</v>
       </c>
       <c r="AS37" s="12" t="inlineStr">
         <is>
-          <t>-公式ストア</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT37" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU37" s="11" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV37" s="12" t="inlineStr">
-        <is>
-          <t>莆田市 福建 351119 CN</t>
-        </is>
-      </c>
-      <c r="AW37" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1UV3PJGHZIHW6</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU37" s="11"/>
+      <c r="AV37" s="12"/>
+      <c r="AW37" s="11"/>
       <c r="AX37" s="11"/>
       <c r="AY37" s="11"/>
       <c r="AZ37" s="11"/>
       <c r="BA37" s="11"/>
       <c r="BB37" s="11"/>
-      <c r="BC37" s="11"/>
+      <c r="BC37" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD37" s="11" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13969,38 +13807,38 @@
       <c r="BI37" s="20"/>
       <c r="BJ37" s="20" t="inlineStr">
         <is>
-          <t>3 kg</t>
+          <t>8 Kilograms</t>
         </is>
       </c>
       <c r="BK37" s="20" t="inlineStr">
         <is>
-          <t>3.00 kg</t>
+          <t>8.00 kg</t>
         </is>
       </c>
       <c r="BL37" s="20" t="inlineStr">
         <is>
-          <t>29.6長さ x 26.9幅 x 113.4高さ cm</t>
+          <t>30長さ x 27.1幅 x 22.5高さ cm</t>
         </is>
       </c>
       <c r="BM37" s="20"/>
       <c r="BN37" s="20" t="inlineStr">
         <is>
-          <t>5.96 kg</t>
+          <t>8 kg</t>
         </is>
       </c>
       <c r="BO37" s="20" t="inlineStr">
         <is>
-          <t>5.96 kg</t>
+          <t>8.00 kg</t>
         </is>
       </c>
       <c r="BP37" s="20" t="inlineStr">
         <is>
-          <t>55.4 x 33.7 x 31.2 cm</t>
+          <t>74 x 35 x 29 cm</t>
         </is>
       </c>
       <c r="BQ37" s="20" t="inlineStr">
         <is>
-          <t>55.40 x 33.70 x 31.20 cm</t>
+          <t>74.00 x 35.00 x 29.00 cm</t>
         </is>
       </c>
       <c r="BR37" s="11" t="inlineStr">
@@ -14016,7 +13854,7 @@
       <c r="B38" s="11"/>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>B0FL2KXDMX</t>
+          <t>B0G4RMHHWV</t>
         </is>
       </c>
       <c r="D38" s="12"/>
@@ -14029,23 +13867,23 @@
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>水擦拭吸尘器 JONR ED12 Lite 干湿两用吸尘器 吸水&amp;擦拭2合1无绳棒吸尘器 自动清洗&amp;干燥 150°睡眠结构 墙时1mm清扫 17000Pa强力吸力 长时间运行LED面板 大容量清水&amp;污水罐 经PSE认证</t>
+          <t>【4个清洗头×17000Pa超强吸力地毯清洁器】 家用地毯清洁剂 漂浮污垢 布清洗机 浮起污垢强力吸力 去污 布清洗机 附带轻松进水口 沙发/地毯清洁剂 带去污功能 沙发/地毯/床垫/车内/玩偶/宠物垫 干湿两用 小巧(白)</t>
         </is>
       </c>
       <c r="I38" s="12"/>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FL2KXDMX?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0G4RMHHWV?psc=1</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61j+d1U1UHL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/61OeNyo9j3L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L38" s="12" t="inlineStr">
         <is>
-          <t>B0FL2KXDMX</t>
+          <t>B0G4RMHHWV</t>
         </is>
       </c>
       <c r="M38" s="12"/>
@@ -14066,11 +13904,11 @@
       <c r="AB38"/>
       <c r="AC38" s="2"/>
       <c r="AD38" s="17">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="AE38" s="13"/>
       <c r="AF38" s="18">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AG38" s="19">
         <v>0</v>
@@ -14122,138 +13960,76 @@
       <c r="B39" s="11"/>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>B0FPXLZSWP</t>
+          <t>B0GJZNZZBG</t>
         </is>
       </c>
       <c r="D39" s="12"/>
       <c r="E39" s="12"/>
-      <c r="F39" s="12" t="inlineStr">
-        <is>
-          <t>NARWAL(ナーワル)</t>
-        </is>
-      </c>
+      <c r="F39" s="12"/>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/NARWAL/page/48E89FF8-D8FF-42EA-91FA-300E4D5D5CBA?lp_asin=B0FPXLZSWP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jpundefined</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>Narwal (ナーワル) S30 コードレス水拭き掃除機 20,000Pa吸引 使い捨てゴミネットs自走式 80℃温水モップ自動洗浄 ヒートアイロン乾燥 乾湿両用掃除機 家具の下も清掃可能 絡まり防止機能 子どもやペットのいるご家庭に最適 メン</t>
+          <t>BOSCH 多功能吸尘器 VAC115 轻巧 小巧 干湿两用多功能吸尘器 鼓风机功能 大型脚轮 小巧收纳 博世</t>
         </is>
       </c>
       <c r="I39" s="12"/>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FPXLZSWP?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0GJZNZZBG?psc=1</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51o9M+0xsCL._AC_US600_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/41bBBiQaOQL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L39" s="12" t="inlineStr">
         <is>
-          <t>B0FPXLZSWP</t>
-        </is>
-      </c>
-      <c r="M39" s="12" t="inlineStr">
-        <is>
-          <t>DIY・工具・ガーデン:電動工具・エア工具:ウェットドライショップ掃除機</t>
-        </is>
-      </c>
-      <c r="N39" s="12" t="inlineStr">
-        <is>
-          <t>DIY・工具・ガーデン</t>
-        </is>
-      </c>
-      <c r="O39" s="13">
-        <v>155663</v>
-      </c>
-      <c r="P39" s="13">
-        <v>2593</v>
-      </c>
-      <c r="Q39" s="14">
-        <v>0.02</v>
-      </c>
-      <c r="R39" s="15" t="inlineStr">
-        <is>
-          <t>ウェットドライショップ掃除機</t>
-        </is>
-      </c>
-      <c r="S39" s="16" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
+          <t>B0GJZNZZBG</t>
+        </is>
+      </c>
+      <c r="M39" s="12"/>
+      <c r="N39" s="12"/>
+      <c r="O39" s="13"/>
+      <c r="P39" s="13"/>
+      <c r="Q39" s="14"/>
+      <c r="R39" s="15"/>
+      <c r="S39" s="16"/>
       <c r="T39" s="13"/>
-      <c r="U39" s="14">
-        <v>-0.78</v>
-      </c>
+      <c r="U39" s="14"/>
       <c r="V39" s="13"/>
       <c r="W39" s="13"/>
       <c r="X39" s="13"/>
-      <c r="Y39" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z39" s="13">
-        <v>54951</v>
-      </c>
+      <c r="Y39" s="17"/>
+      <c r="Z39" s="13"/>
       <c r="AA39"/>
       <c r="AB39"/>
       <c r="AC39" s="2"/>
-      <c r="AD39" s="17">
-        <v>41</v>
-      </c>
-      <c r="AE39" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF39" s="18">
-        <v>3.6</v>
-      </c>
+      <c r="AD39" s="17"/>
+      <c r="AE39" s="13"/>
+      <c r="AF39" s="18"/>
       <c r="AG39" s="19">
         <v>0</v>
       </c>
-      <c r="AH39" s="13">
-        <v>1020</v>
-      </c>
+      <c r="AH39" s="13"/>
       <c r="AI39" s="14">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="AJ39"/>
-      <c r="AK39" s="11" t="inlineStr">
-        <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="AL39" s="17">
-        <v>377</v>
-      </c>
-      <c r="AM39" s="11" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
+      <c r="AK39" s="11"/>
+      <c r="AL39" s="17"/>
+      <c r="AM39" s="11"/>
       <c r="AN39" s="11"/>
       <c r="AO39" s="11"/>
       <c r="AP39"/>
-      <c r="AQ39" s="17">
-        <v>9</v>
-      </c>
-      <c r="AR39" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS39" s="12" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT39" s="11" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
+      <c r="AQ39" s="17"/>
+      <c r="AR39" s="17"/>
+      <c r="AS39" s="12"/>
+      <c r="AT39" s="11"/>
       <c r="AU39" s="11"/>
       <c r="AV39" s="12"/>
       <c r="AW39" s="11"/>
@@ -14262,62 +14038,22 @@
       <c r="AZ39" s="11"/>
       <c r="BA39" s="11"/>
       <c r="BB39" s="11"/>
-      <c r="BC39" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD39" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC39" s="11"/>
+      <c r="BD39" s="11"/>
       <c r="BE39" s="11"/>
       <c r="BF39" s="11"/>
       <c r="BG39" s="11"/>
       <c r="BH39" s="12"/>
       <c r="BI39" s="20"/>
-      <c r="BJ39" s="20" t="inlineStr">
-        <is>
-          <t>8 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK39" s="20" t="inlineStr">
-        <is>
-          <t>8.00 kg</t>
-        </is>
-      </c>
-      <c r="BL39" s="20" t="inlineStr">
-        <is>
-          <t>30長さ x 27.1幅 x 22.5高さ cm</t>
-        </is>
-      </c>
+      <c r="BJ39" s="20"/>
+      <c r="BK39" s="20"/>
+      <c r="BL39" s="20"/>
       <c r="BM39" s="20"/>
-      <c r="BN39" s="20" t="inlineStr">
-        <is>
-          <t>8 kg</t>
-        </is>
-      </c>
-      <c r="BO39" s="20" t="inlineStr">
-        <is>
-          <t>8.00 kg</t>
-        </is>
-      </c>
-      <c r="BP39" s="20" t="inlineStr">
-        <is>
-          <t>74 x 35 x 29 cm</t>
-        </is>
-      </c>
-      <c r="BQ39" s="20" t="inlineStr">
-        <is>
-          <t>74.00 x 35.00 x 29.00 cm</t>
-        </is>
-      </c>
-      <c r="BR39" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
+      <c r="BN39" s="20"/>
+      <c r="BO39" s="20"/>
+      <c r="BP39" s="20"/>
+      <c r="BQ39" s="20"/>
+      <c r="BR39" s="11"/>
     </row>
     <row r="40" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="11">
@@ -14326,7 +14062,7 @@
       <c r="B40" s="11"/>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>B0G4RMHHWV</t>
+          <t>B0GP76R477</t>
         </is>
       </c>
       <c r="D40" s="12"/>
@@ -14339,23 +14075,23 @@
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>【4个清洗头×17000Pa超强吸力地毯清洁器】 家用地毯清洁剂 漂浮污垢 布清洗机 浮起污垢强力吸力 去污 布清洗机 附带轻松进水口 沙发/地毯清洁剂 带去污功能 沙发/地毯/床垫/车内/玩偶/宠物垫 干湿两用 小巧(白)</t>
+          <t>【官方/替换用卷刷&amp;过滤网×1】Mindoo AquaX Plus Mindoo AquaX Plus 可擦拭水的吸尘器 [吸水、擦拭、除菌、自我清洁、自动干燥] 自走式 垃圾收集1台3用 强力吸力 超轻 自动清洗 高性能 (黑色)</t>
         </is>
       </c>
       <c r="I40" s="12"/>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0G4RMHHWV?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0GP76R477?psc=1</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/61OeNyo9j3L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/21UZYI0dymL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L40" s="12" t="inlineStr">
         <is>
-          <t>B0G4RMHHWV</t>
+          <t>B0GP76R477</t>
         </is>
       </c>
       <c r="M40" s="12"/>
@@ -14375,13 +14111,9 @@
       <c r="AA40"/>
       <c r="AB40"/>
       <c r="AC40" s="2"/>
-      <c r="AD40" s="17">
-        <v>43</v>
-      </c>
+      <c r="AD40" s="17"/>
       <c r="AE40" s="13"/>
-      <c r="AF40" s="18">
-        <v>4.1</v>
-      </c>
+      <c r="AF40" s="18"/>
       <c r="AG40" s="19">
         <v>0</v>
       </c>
@@ -14432,7 +14164,7 @@
       <c r="B41" s="11"/>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>B0GJZNZZBG</t>
+          <t>B0H5WDMCLX</t>
         </is>
       </c>
       <c r="D41" s="12"/>
@@ -14445,23 +14177,23 @@
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>BOSCH 多功能吸尘器 VAC115 轻巧 小巧 干湿两用多功能吸尘器 鼓风机功能 大型脚轮 小巧收纳 博世</t>
+          <t>dreame H12 Pro FlexReach 擦水吸尘器与替换用过滤器 套装</t>
         </is>
       </c>
       <c r="I41" s="12"/>
       <c r="J41" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0GJZNZZBG?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0H5WDMCLX?psc=1</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/41bBBiQaOQL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-fe.ssl-images-amazon.com/images/I/31ZGQqLBLNL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
-          <t>B0GJZNZZBG</t>
+          <t>B0H5WDMCLX</t>
         </is>
       </c>
       <c r="M41" s="12"/>
@@ -14526,210 +14258,6 @@
       <c r="BP41" s="20"/>
       <c r="BQ41" s="20"/>
       <c r="BR41" s="11"/>
-    </row>
-    <row r="42" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="11">
-        <v>41</v>
-      </c>
-      <c r="B42" s="11"/>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>B0GP76R477</t>
-        </is>
-      </c>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H42" s="12" t="inlineStr">
-        <is>
-          <t>【官方/替换用卷刷&amp;过滤网×1】Mindoo AquaX Plus Mindoo AquaX Plus 可擦拭水的吸尘器 [吸水、擦拭、除菌、自我清洁、自动干燥] 自走式 垃圾收集1台3用 强力吸力 超轻 自动清洗 高性能 (黑色)</t>
-        </is>
-      </c>
-      <c r="I42" s="12"/>
-      <c r="J42" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0GP76R477?psc=1</t>
-        </is>
-      </c>
-      <c r="K42" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/21UZYI0dymL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L42" s="12" t="inlineStr">
-        <is>
-          <t>B0GP76R477</t>
-        </is>
-      </c>
-      <c r="M42" s="12"/>
-      <c r="N42" s="12"/>
-      <c r="O42" s="13"/>
-      <c r="P42" s="13"/>
-      <c r="Q42" s="14"/>
-      <c r="R42" s="15"/>
-      <c r="S42" s="16"/>
-      <c r="T42" s="13"/>
-      <c r="U42" s="14"/>
-      <c r="V42" s="13"/>
-      <c r="W42" s="13"/>
-      <c r="X42" s="13"/>
-      <c r="Y42" s="17"/>
-      <c r="Z42" s="13"/>
-      <c r="AA42"/>
-      <c r="AB42"/>
-      <c r="AC42" s="2"/>
-      <c r="AD42" s="17"/>
-      <c r="AE42" s="13"/>
-      <c r="AF42" s="18"/>
-      <c r="AG42" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH42" s="13"/>
-      <c r="AI42" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ42"/>
-      <c r="AK42" s="11"/>
-      <c r="AL42" s="17"/>
-      <c r="AM42" s="11"/>
-      <c r="AN42" s="11"/>
-      <c r="AO42" s="11"/>
-      <c r="AP42"/>
-      <c r="AQ42" s="17"/>
-      <c r="AR42" s="17"/>
-      <c r="AS42" s="12"/>
-      <c r="AT42" s="11"/>
-      <c r="AU42" s="11"/>
-      <c r="AV42" s="12"/>
-      <c r="AW42" s="11"/>
-      <c r="AX42" s="11"/>
-      <c r="AY42" s="11"/>
-      <c r="AZ42" s="11"/>
-      <c r="BA42" s="11"/>
-      <c r="BB42" s="11"/>
-      <c r="BC42" s="11"/>
-      <c r="BD42" s="11"/>
-      <c r="BE42" s="11"/>
-      <c r="BF42" s="11"/>
-      <c r="BG42" s="11"/>
-      <c r="BH42" s="12"/>
-      <c r="BI42" s="20"/>
-      <c r="BJ42" s="20"/>
-      <c r="BK42" s="20"/>
-      <c r="BL42" s="20"/>
-      <c r="BM42" s="20"/>
-      <c r="BN42" s="20"/>
-      <c r="BO42" s="20"/>
-      <c r="BP42" s="20"/>
-      <c r="BQ42" s="20"/>
-      <c r="BR42" s="11"/>
-    </row>
-    <row r="43" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="11">
-        <v>42</v>
-      </c>
-      <c r="B43" s="11"/>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>B0H5WDMCLX</t>
-        </is>
-      </c>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpundefined</t>
-        </is>
-      </c>
-      <c r="H43" s="12" t="inlineStr">
-        <is>
-          <t>dreame H12 Pro FlexReach 擦水吸尘器与替换用过滤器 套装</t>
-        </is>
-      </c>
-      <c r="I43" s="12"/>
-      <c r="J43" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0H5WDMCLX?psc=1</t>
-        </is>
-      </c>
-      <c r="K43" s="12" t="inlineStr">
-        <is>
-          <t>https://images-fe.ssl-images-amazon.com/images/I/31ZGQqLBLNL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L43" s="12" t="inlineStr">
-        <is>
-          <t>B0H5WDMCLX</t>
-        </is>
-      </c>
-      <c r="M43" s="12"/>
-      <c r="N43" s="12"/>
-      <c r="O43" s="13"/>
-      <c r="P43" s="13"/>
-      <c r="Q43" s="14"/>
-      <c r="R43" s="15"/>
-      <c r="S43" s="16"/>
-      <c r="T43" s="13"/>
-      <c r="U43" s="14"/>
-      <c r="V43" s="13"/>
-      <c r="W43" s="13"/>
-      <c r="X43" s="13"/>
-      <c r="Y43" s="17"/>
-      <c r="Z43" s="13"/>
-      <c r="AA43"/>
-      <c r="AB43"/>
-      <c r="AC43" s="2"/>
-      <c r="AD43" s="17"/>
-      <c r="AE43" s="13"/>
-      <c r="AF43" s="18"/>
-      <c r="AG43" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH43" s="13"/>
-      <c r="AI43" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ43"/>
-      <c r="AK43" s="11"/>
-      <c r="AL43" s="17"/>
-      <c r="AM43" s="11"/>
-      <c r="AN43" s="11"/>
-      <c r="AO43" s="11"/>
-      <c r="AP43"/>
-      <c r="AQ43" s="17"/>
-      <c r="AR43" s="17"/>
-      <c r="AS43" s="12"/>
-      <c r="AT43" s="11"/>
-      <c r="AU43" s="11"/>
-      <c r="AV43" s="12"/>
-      <c r="AW43" s="11"/>
-      <c r="AX43" s="11"/>
-      <c r="AY43" s="11"/>
-      <c r="AZ43" s="11"/>
-      <c r="BA43" s="11"/>
-      <c r="BB43" s="11"/>
-      <c r="BC43" s="11"/>
-      <c r="BD43" s="11"/>
-      <c r="BE43" s="11"/>
-      <c r="BF43" s="11"/>
-      <c r="BG43" s="11"/>
-      <c r="BH43" s="12"/>
-      <c r="BI43" s="20"/>
-      <c r="BJ43" s="20"/>
-      <c r="BK43" s="20"/>
-      <c r="BL43" s="20"/>
-      <c r="BM43" s="20"/>
-      <c r="BN43" s="20"/>
-      <c r="BO43" s="20"/>
-      <c r="BP43" s="20"/>
-      <c r="BQ43" s="20"/>
-      <c r="BR43" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14845,198 +14373,182 @@
     <hyperlink ref="M15" r:id="rId108" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N15" r:id="rId109"/>
     <hyperlink ref="AW15" r:id="rId110" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AKYM3EEDP1T3V"/>
-    <hyperlink ref="C16" r:id="rId111" tooltip="https://www.amazon.co.jp/dp/B0HGLFDYL5"/>
-    <hyperlink ref="G16" r:id="rId112" tooltip="https://www.amazon.co.jpnull"/>
-    <hyperlink ref="J16" r:id="rId113" tooltip="https://www.amazon.co.jp/dp/B0HGLFDYL5?psc=1"/>
-    <hyperlink ref="K16" r:id="rId114" tooltip="https://images-na.ssl-images-amazon.com/images/I/51O6JFJ9JfL._AC_US600_.jpg"/>
-    <hyperlink ref="L16" r:id="rId115" tooltip="https://www.amazon.co.jp/dp/B0HGLFDYL5"/>
-    <hyperlink ref="M16" r:id="rId116" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="C16" r:id="rId111" tooltip="https://www.amazon.co.jp/dp/B0FC18HMRN"/>
+    <hyperlink ref="G16" r:id="rId112" tooltip="https://www.amazon.co.jp/stores/mindoo/page/195B1567-B86E-4B16-A2C3-065A70917DA9?lp_asin=B0FC18HMRN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J16" r:id="rId113" tooltip="https://www.amazon.co.jp/dp/B0FC18HMRN?psc=1"/>
+    <hyperlink ref="K16" r:id="rId114" tooltip="https://m.media-amazon.com/images/I/21vmJWLJAbL._AC_US600_.jpg"/>
+    <hyperlink ref="L16" r:id="rId115" tooltip="https://www.amazon.co.jp/dp/B0FC18HMRN"/>
+    <hyperlink ref="M16" r:id="rId116" tooltip="https://www.amazon.co.jp/b?node=218875650051"/>
     <hyperlink ref="N16" r:id="rId117"/>
-    <hyperlink ref="AW16" r:id="rId118" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A24DDJVBL7M2LD"/>
-    <hyperlink ref="C17" r:id="rId119" tooltip="https://www.amazon.co.jp/dp/B0FC18HMRN"/>
-    <hyperlink ref="G17" r:id="rId120" tooltip="https://www.amazon.co.jp/stores/mindoo/page/195B1567-B86E-4B16-A2C3-065A70917DA9?lp_asin=B0FC18HMRN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J17" r:id="rId121" tooltip="https://www.amazon.co.jp/dp/B0FC18HMRN?psc=1"/>
-    <hyperlink ref="K17" r:id="rId122" tooltip="https://m.media-amazon.com/images/I/21vmJWLJAbL._AC_US600_.jpg"/>
-    <hyperlink ref="L17" r:id="rId123" tooltip="https://www.amazon.co.jp/dp/B0FC18HMRN"/>
-    <hyperlink ref="M17" r:id="rId124" tooltip="https://www.amazon.co.jp/b?node=218875650051"/>
+    <hyperlink ref="AW16" r:id="rId118" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3KERCWTE76M89"/>
+    <hyperlink ref="C17" r:id="rId119" tooltip="https://www.amazon.co.jp/dp/B0HGLNPJPC"/>
+    <hyperlink ref="G17" r:id="rId120" tooltip="https://www.amazon.co.jp/stores/%E3%83%80%E3%82%A4%E3%82%BD%E3%83%B3/page/0456F1ED-24D4-4719-8E99-5936EC69346F?lp_asin=B0HGLNPJPC&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J17" r:id="rId121" tooltip="https://www.amazon.co.jp/dp/B0HGLNPJPC?psc=1"/>
+    <hyperlink ref="K17" r:id="rId122" tooltip="https://images-na.ssl-images-amazon.com/images/I/616rJ-dkmUL._AC_US600_.jpg"/>
+    <hyperlink ref="L17" r:id="rId123" tooltip="https://www.amazon.co.jp/dp/B0HGLNPJPC"/>
+    <hyperlink ref="M17" r:id="rId124" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N17" r:id="rId125"/>
-    <hyperlink ref="AW17" r:id="rId126" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3KERCWTE76M89"/>
-    <hyperlink ref="C18" r:id="rId127" tooltip="https://www.amazon.co.jp/dp/B0HGLNPJPC"/>
-    <hyperlink ref="G18" r:id="rId128" tooltip="https://www.amazon.co.jp/stores/%E3%83%80%E3%82%A4%E3%82%BD%E3%83%B3/page/0456F1ED-24D4-4719-8E99-5936EC69346F?lp_asin=B0HGLNPJPC&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J18" r:id="rId129" tooltip="https://www.amazon.co.jp/dp/B0HGLNPJPC?psc=1"/>
-    <hyperlink ref="K18" r:id="rId130" tooltip="https://images-na.ssl-images-amazon.com/images/I/616rJ-dkmUL._AC_US600_.jpg"/>
-    <hyperlink ref="L18" r:id="rId131" tooltip="https://www.amazon.co.jp/dp/B0HGLNPJPC"/>
+    <hyperlink ref="AW17" r:id="rId126" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KRDRXNL1G5FA"/>
+    <hyperlink ref="C18" r:id="rId127" tooltip="https://www.amazon.co.jp/dp/B0HHN8HTLL"/>
+    <hyperlink ref="G18" r:id="rId128" tooltip="https://www.amazon.co.jpnull"/>
+    <hyperlink ref="J18" r:id="rId129" tooltip="https://www.amazon.co.jp/dp/B0HHN8HTLL?psc=1"/>
+    <hyperlink ref="K18" r:id="rId130" tooltip="https://images-na.ssl-images-amazon.com/images/I/51z7B-TmeXL._AC_US600_.jpg"/>
+    <hyperlink ref="L18" r:id="rId131" tooltip="https://www.amazon.co.jp/dp/B0HHN8HTLL"/>
     <hyperlink ref="M18" r:id="rId132" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N18" r:id="rId133"/>
-    <hyperlink ref="AW18" r:id="rId134" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KRDRXNL1G5FA"/>
-    <hyperlink ref="C19" r:id="rId135" tooltip="https://www.amazon.co.jp/dp/B0HHN8HTLL"/>
-    <hyperlink ref="G19" r:id="rId136" tooltip="https://www.amazon.co.jpnull"/>
-    <hyperlink ref="J19" r:id="rId137" tooltip="https://www.amazon.co.jp/dp/B0HHN8HTLL?psc=1"/>
-    <hyperlink ref="K19" r:id="rId138" tooltip="https://images-na.ssl-images-amazon.com/images/I/51z7B-TmeXL._AC_US600_.jpg"/>
-    <hyperlink ref="L19" r:id="rId139" tooltip="https://www.amazon.co.jp/dp/B0HHN8HTLL"/>
+    <hyperlink ref="AW18" r:id="rId134" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3JH293JNBT5IZ"/>
+    <hyperlink ref="C19" r:id="rId135" tooltip="https://www.amazon.co.jp/dp/B0FK9HN17M"/>
+    <hyperlink ref="G19" r:id="rId136" tooltip="https://www.amazon.co.jp/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FK9HN17M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J19" r:id="rId137" tooltip="https://www.amazon.co.jp/dp/B0FK9HN17M?psc=1"/>
+    <hyperlink ref="K19" r:id="rId138" tooltip="https://images-na.ssl-images-amazon.com/images/I/61gNWZ3JF6L._AC_US600_.jpg"/>
+    <hyperlink ref="L19" r:id="rId139" tooltip="https://www.amazon.co.jp/dp/B0FK9HN17M"/>
     <hyperlink ref="M19" r:id="rId140" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N19" r:id="rId141"/>
-    <hyperlink ref="AW19" r:id="rId142" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3JH293JNBT5IZ"/>
-    <hyperlink ref="C20" r:id="rId143" tooltip="https://www.amazon.co.jp/dp/B0FK9HN17M"/>
-    <hyperlink ref="G20" r:id="rId144" tooltip="https://www.amazon.co.jp/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FK9HN17M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J20" r:id="rId145" tooltip="https://www.amazon.co.jp/dp/B0FK9HN17M?psc=1"/>
-    <hyperlink ref="K20" r:id="rId146" tooltip="https://images-na.ssl-images-amazon.com/images/I/61gNWZ3JF6L._AC_US600_.jpg"/>
-    <hyperlink ref="L20" r:id="rId147" tooltip="https://www.amazon.co.jp/dp/B0FK9HN17M"/>
-    <hyperlink ref="M20" r:id="rId148" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="AW19" r:id="rId142" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2SR0DVTECF9BI"/>
+    <hyperlink ref="C20" r:id="rId143" tooltip="https://www.amazon.co.jp/dp/B0CPPHYW3B"/>
+    <hyperlink ref="G20" r:id="rId144" tooltip="https://www.amazon.co.jp/stores/%E3%83%9F%E3%83%8A%E3%83%88%E3%83%AF%E3%83%BC%E3%82%AF%E3%82%B9/page/7E77FCE9-0862-4057-994E-E5C8A30E6C6D?lp_asin=B0CPPHYW3B&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J20" r:id="rId145" tooltip="https://www.amazon.co.jp/dp/B0CPPHYW3B?psc=1"/>
+    <hyperlink ref="K20" r:id="rId146" tooltip="https://m.media-amazon.com/images/I/41ZrF14970L._AC_US600_.jpg"/>
+    <hyperlink ref="L20" r:id="rId147" tooltip="https://www.amazon.co.jp/dp/B0CPPHYW3B"/>
+    <hyperlink ref="M20" r:id="rId148" tooltip="https://www.amazon.co.jp/b?node=3450851051"/>
     <hyperlink ref="N20" r:id="rId149"/>
-    <hyperlink ref="AW20" r:id="rId150" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2SR0DVTECF9BI"/>
-    <hyperlink ref="C21" r:id="rId151" tooltip="https://www.amazon.co.jp/dp/B0CPPHYW3B"/>
-    <hyperlink ref="G21" r:id="rId152" tooltip="https://www.amazon.co.jp/stores/%E3%83%9F%E3%83%8A%E3%83%88%E3%83%AF%E3%83%BC%E3%82%AF%E3%82%B9/page/7E77FCE9-0862-4057-994E-E5C8A30E6C6D?lp_asin=B0CPPHYW3B&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J21" r:id="rId153" tooltip="https://www.amazon.co.jp/dp/B0CPPHYW3B?psc=1"/>
-    <hyperlink ref="K21" r:id="rId154" tooltip="https://m.media-amazon.com/images/I/41ZrF14970L._AC_US600_.jpg"/>
-    <hyperlink ref="L21" r:id="rId155" tooltip="https://www.amazon.co.jp/dp/B0CPPHYW3B"/>
-    <hyperlink ref="M21" r:id="rId156" tooltip="https://www.amazon.co.jp/b?node=3450851051"/>
+    <hyperlink ref="AW20" r:id="rId150" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A35R5657DWBR35"/>
+    <hyperlink ref="C21" r:id="rId151" tooltip="https://www.amazon.co.jp/dp/B07KR2J116"/>
+    <hyperlink ref="G21" r:id="rId152" tooltip="https://www.amazon.co.jp/stores/%E3%83%9F%E3%83%8A%E3%83%88%E3%83%AF%E3%83%BC%E3%82%AF%E3%82%B9/page/7E77FCE9-0862-4057-994E-E5C8A30E6C6D?lp_asin=B07KR2J116&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J21" r:id="rId153" tooltip="https://www.amazon.co.jp/dp/B07KR2J116?psc=1"/>
+    <hyperlink ref="K21" r:id="rId154" tooltip="https://m.media-amazon.com/images/I/41ovXwP+o+L._AC_US600_.jpg"/>
+    <hyperlink ref="L21" r:id="rId155" tooltip="https://www.amazon.co.jp/dp/B07KR2J116"/>
+    <hyperlink ref="M21" r:id="rId156" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N21" r:id="rId157"/>
     <hyperlink ref="AW21" r:id="rId158" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A35R5657DWBR35"/>
-    <hyperlink ref="C22" r:id="rId159" tooltip="https://www.amazon.co.jp/dp/B07KR2J116"/>
-    <hyperlink ref="G22" r:id="rId160" tooltip="https://www.amazon.co.jp/stores/%E3%83%9F%E3%83%8A%E3%83%88%E3%83%AF%E3%83%BC%E3%82%AF%E3%82%B9/page/7E77FCE9-0862-4057-994E-E5C8A30E6C6D?lp_asin=B07KR2J116&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J22" r:id="rId161" tooltip="https://www.amazon.co.jp/dp/B07KR2J116?psc=1"/>
-    <hyperlink ref="K22" r:id="rId162" tooltip="https://m.media-amazon.com/images/I/41ovXwP+o+L._AC_US600_.jpg"/>
-    <hyperlink ref="L22" r:id="rId163" tooltip="https://www.amazon.co.jp/dp/B07KR2J116"/>
+    <hyperlink ref="C22" r:id="rId159" tooltip="https://www.amazon.co.jp/dp/B0D2VPQT2V"/>
+    <hyperlink ref="G22" r:id="rId160" tooltip="https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0D2VPQT2V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J22" r:id="rId161" tooltip="https://www.amazon.co.jp/dp/B0D2VPQT2V?psc=1"/>
+    <hyperlink ref="K22" r:id="rId162" tooltip="https://images-na.ssl-images-amazon.com/images/I/61KqhLRxwYL._AC_US600_.jpg"/>
+    <hyperlink ref="L22" r:id="rId163" tooltip="https://www.amazon.co.jp/dp/B0D2VPQT2V"/>
     <hyperlink ref="M22" r:id="rId164" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N22" r:id="rId165"/>
-    <hyperlink ref="AW22" r:id="rId166" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A35R5657DWBR35"/>
-    <hyperlink ref="C23" r:id="rId167" tooltip="https://www.amazon.co.jp/dp/B0D2VPQT2V"/>
-    <hyperlink ref="G23" r:id="rId168" tooltip="https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0D2VPQT2V&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J23" r:id="rId169" tooltip="https://www.amazon.co.jp/dp/B0D2VPQT2V?psc=1"/>
-    <hyperlink ref="K23" r:id="rId170" tooltip="https://images-na.ssl-images-amazon.com/images/I/61KqhLRxwYL._AC_US600_.jpg"/>
-    <hyperlink ref="L23" r:id="rId171" tooltip="https://www.amazon.co.jp/dp/B0D2VPQT2V"/>
+    <hyperlink ref="AW22" r:id="rId166" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WSQAA92JSPUW"/>
+    <hyperlink ref="C23" r:id="rId167" tooltip="https://www.amazon.co.jp/dp/B0CZKHJXNG"/>
+    <hyperlink ref="G23" r:id="rId168" tooltip="https://www.amazon.co.jp/stores/Eureka/page/0DAE79FF-361F-4FFE-9129-4ACEDAF99AD5?lp_asin=B0CZKHJXNG&amp;ref_=ast_bln"/>
+    <hyperlink ref="J23" r:id="rId169" tooltip="https://www.amazon.co.jp/dp/B0CZKHJXNG?psc=1"/>
+    <hyperlink ref="K23" r:id="rId170" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41nAma6e0eL._AC_US600_.jpg"/>
+    <hyperlink ref="L23" r:id="rId171" tooltip="https://www.amazon.co.jp/dp/B0CZKHJXNG"/>
     <hyperlink ref="M23" r:id="rId172" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N23" r:id="rId173"/>
-    <hyperlink ref="AW23" r:id="rId174" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WSQAA92JSPUW"/>
-    <hyperlink ref="C24" r:id="rId175" tooltip="https://www.amazon.co.jp/dp/B0CZKHJXNG"/>
-    <hyperlink ref="G24" r:id="rId176" tooltip="https://www.amazon.co.jp/stores/Eureka/page/0DAE79FF-361F-4FFE-9129-4ACEDAF99AD5?lp_asin=B0CZKHJXNG&amp;ref_=ast_bln"/>
-    <hyperlink ref="J24" r:id="rId177" tooltip="https://www.amazon.co.jp/dp/B0CZKHJXNG?psc=1"/>
-    <hyperlink ref="K24" r:id="rId178" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/41nAma6e0eL._AC_US600_.jpg"/>
-    <hyperlink ref="L24" r:id="rId179" tooltip="https://www.amazon.co.jp/dp/B0CZKHJXNG"/>
+    <hyperlink ref="AW23" r:id="rId174" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3JXXBYW06ZFVU"/>
+    <hyperlink ref="C24" r:id="rId175" tooltip="https://www.amazon.co.jp/dp/B0CNJT8933"/>
+    <hyperlink ref="G24" r:id="rId176" tooltip="https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0CNJT8933&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J24" r:id="rId177" tooltip="https://www.amazon.co.jp/dp/B0CNJT8933?psc=1"/>
+    <hyperlink ref="K24" r:id="rId178" tooltip="https://images-na.ssl-images-amazon.com/images/I/61b-HbgIkBL._AC_US600_.jpg"/>
+    <hyperlink ref="L24" r:id="rId179" tooltip="https://www.amazon.co.jp/dp/B0CNJT8933"/>
     <hyperlink ref="M24" r:id="rId180" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N24" r:id="rId181"/>
-    <hyperlink ref="AW24" r:id="rId182" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3JXXBYW06ZFVU"/>
-    <hyperlink ref="C25" r:id="rId183" tooltip="https://www.amazon.co.jp/dp/B0HHN61KPZ"/>
-    <hyperlink ref="G25" r:id="rId184" tooltip="https://www.amazon.co.jpnull"/>
-    <hyperlink ref="J25" r:id="rId185" tooltip="https://www.amazon.co.jp/dp/B0HHN61KPZ?psc=1"/>
-    <hyperlink ref="K25" r:id="rId186" tooltip="https://m.media-amazon.com/images/I/31eRC+N6IRL._AC_US600_.jpg"/>
-    <hyperlink ref="L25" r:id="rId187" tooltip="https://www.amazon.co.jp/dp/B0HHN61KPZ"/>
+    <hyperlink ref="AW24" r:id="rId182" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WV0MTJICL1UJ"/>
+    <hyperlink ref="C25" r:id="rId183" tooltip="https://www.amazon.co.jp/dp/B08XLW562G"/>
+    <hyperlink ref="G25" r:id="rId184" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=%E4%B8%8D%E6%98%8E"/>
+    <hyperlink ref="J25" r:id="rId185" tooltip="https://www.amazon.co.jp/dp/B08XLW562G?psc=1"/>
+    <hyperlink ref="K25" r:id="rId186" tooltip="https://images-na.ssl-images-amazon.com/images/I/31NELDCajpL._AC_US600_.jpg"/>
+    <hyperlink ref="L25" r:id="rId187" tooltip="https://www.amazon.co.jp/dp/B08XLW562G"/>
     <hyperlink ref="M25" r:id="rId188" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N25" r:id="rId189"/>
-    <hyperlink ref="AW25" r:id="rId190" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KRDRXNL1G5FA"/>
-    <hyperlink ref="C26" r:id="rId191" tooltip="https://www.amazon.co.jp/dp/B0CNJT8933"/>
-    <hyperlink ref="G26" r:id="rId192" tooltip="https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0CNJT8933&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J26" r:id="rId193" tooltip="https://www.amazon.co.jp/dp/B0CNJT8933?psc=1"/>
-    <hyperlink ref="K26" r:id="rId194" tooltip="https://images-na.ssl-images-amazon.com/images/I/61b-HbgIkBL._AC_US600_.jpg"/>
-    <hyperlink ref="L26" r:id="rId195" tooltip="https://www.amazon.co.jp/dp/B0CNJT8933"/>
+    <hyperlink ref="AW25" r:id="rId190" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2RYDH17QLIL3V"/>
+    <hyperlink ref="C26" r:id="rId191" tooltip="https://www.amazon.co.jp/dp/B0GS4QDH7R"/>
+    <hyperlink ref="G26" r:id="rId192" tooltip="https://www.amazon.co.jp/stores/%E3%83%A6%E3%83%AF%E3%83%B3%E3%83%88%EF%BC%88UWANT/page/CFD932E4-87F0-4563-8A00-7E6F0611A613?lp_asin=B0GS4QDH7R&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J26" r:id="rId193" tooltip="https://www.amazon.co.jp/dp/B0GS4QDH7R?psc=1"/>
+    <hyperlink ref="K26" r:id="rId194" tooltip="https://images-na.ssl-images-amazon.com/images/I/61j3dNdQj4L._AC_US600_.jpg"/>
+    <hyperlink ref="L26" r:id="rId195" tooltip="https://www.amazon.co.jp/dp/B0GS4QDH7R"/>
     <hyperlink ref="M26" r:id="rId196" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N26" r:id="rId197"/>
-    <hyperlink ref="AW26" r:id="rId198" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WV0MTJICL1UJ"/>
-    <hyperlink ref="C27" r:id="rId199" tooltip="https://www.amazon.co.jp/dp/B08XLW562G"/>
-    <hyperlink ref="G27" r:id="rId200" tooltip="https://www.amazon.co.jp/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=%E4%B8%8D%E6%98%8E"/>
-    <hyperlink ref="J27" r:id="rId201" tooltip="https://www.amazon.co.jp/dp/B08XLW562G?psc=1"/>
-    <hyperlink ref="K27" r:id="rId202" tooltip="https://images-na.ssl-images-amazon.com/images/I/31NELDCajpL._AC_US600_.jpg"/>
-    <hyperlink ref="L27" r:id="rId203" tooltip="https://www.amazon.co.jp/dp/B08XLW562G"/>
+    <hyperlink ref="AW26" r:id="rId198" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1O5QS9O13RS09"/>
+    <hyperlink ref="C27" r:id="rId199" tooltip="https://www.amazon.co.jp/dp/B0H6DZMNPV"/>
+    <hyperlink ref="G27" r:id="rId200" tooltip="https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0H6DZMNPV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J27" r:id="rId201" tooltip="https://www.amazon.co.jp/dp/B0H6DZMNPV?psc=1"/>
+    <hyperlink ref="K27" r:id="rId202" tooltip="https://m.media-amazon.com/images/I/31ddgJIAJbL._AC_US600_.jpg"/>
+    <hyperlink ref="L27" r:id="rId203" tooltip="https://www.amazon.co.jp/dp/B0H6DZMNPV"/>
     <hyperlink ref="M27" r:id="rId204" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
     <hyperlink ref="N27" r:id="rId205"/>
-    <hyperlink ref="AW27" r:id="rId206" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2RYDH17QLIL3V"/>
-    <hyperlink ref="C28" r:id="rId207" tooltip="https://www.amazon.co.jp/dp/B0GS4QDH7R"/>
-    <hyperlink ref="G28" r:id="rId208" tooltip="https://www.amazon.co.jp/stores/%E3%83%A6%E3%83%AF%E3%83%B3%E3%83%88%EF%BC%88UWANT/page/CFD932E4-87F0-4563-8A00-7E6F0611A613?lp_asin=B0GS4QDH7R&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J28" r:id="rId209" tooltip="https://www.amazon.co.jp/dp/B0GS4QDH7R?psc=1"/>
-    <hyperlink ref="K28" r:id="rId210" tooltip="https://images-na.ssl-images-amazon.com/images/I/61j3dNdQj4L._AC_US600_.jpg"/>
-    <hyperlink ref="L28" r:id="rId211" tooltip="https://www.amazon.co.jp/dp/B0GS4QDH7R"/>
-    <hyperlink ref="M28" r:id="rId212" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N28" r:id="rId213"/>
-    <hyperlink ref="AW28" r:id="rId214" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1O5QS9O13RS09"/>
-    <hyperlink ref="C29" r:id="rId215" tooltip="https://www.amazon.co.jp/dp/B0H6DZMNPV"/>
-    <hyperlink ref="G29" r:id="rId216" tooltip="https://www.amazon.co.jp/stores/DREAME/page/124CB9C6-E892-4D09-BEA0-8BF1AE9958DA?lp_asin=B0H6DZMNPV&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J29" r:id="rId217" tooltip="https://www.amazon.co.jp/dp/B0H6DZMNPV?psc=1"/>
-    <hyperlink ref="K29" r:id="rId218" tooltip="https://m.media-amazon.com/images/I/31ddgJIAJbL._AC_US600_.jpg"/>
-    <hyperlink ref="L29" r:id="rId219" tooltip="https://www.amazon.co.jp/dp/B0H6DZMNPV"/>
-    <hyperlink ref="M29" r:id="rId220" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N29" r:id="rId221"/>
-    <hyperlink ref="AW29" r:id="rId222" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WV0MTJICL1UJ"/>
-    <hyperlink ref="C30" r:id="rId223" tooltip="https://www.amazon.co.jp/dp/B09P2RKRWX"/>
-    <hyperlink ref="G30" r:id="rId224" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J30" r:id="rId225" tooltip="https://www.amazon.co.jp/dp/B09P2RKRWX?psc=1"/>
-    <hyperlink ref="K30" r:id="rId226" tooltip="https://images-fe.ssl-images-amazon.com/images/I/615lYQCrd2L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L30" r:id="rId227" tooltip="https://www.amazon.co.jp/dp/B09P2RKRWX"/>
-    <hyperlink ref="C31" r:id="rId228" tooltip="https://www.amazon.co.jp/dp/B0C4HGZ1L6"/>
-    <hyperlink ref="G31" r:id="rId229" tooltip="https://www.amazon.co.jp/stores/NEODIT%E3%83%8D%E3%82%AA%E3%83%87%E3%82%A3%E3%83%83%E3%83%88/page/CD7250ED-8E04-4E58-A881-68B2A928AE8C?lp_asin=B0C4HGZ1L6&amp;ref_=ast_bln"/>
-    <hyperlink ref="J31" r:id="rId230" tooltip="https://www.amazon.co.jp/dp/B0C4HGZ1L6?psc=1"/>
-    <hyperlink ref="K31" r:id="rId231" tooltip="https://images-na.ssl-images-amazon.com/images/I/81DHFglSw9L._AC_US600_.jpg"/>
-    <hyperlink ref="L31" r:id="rId232" tooltip="https://www.amazon.co.jp/dp/B0C4HGZ1L6"/>
-    <hyperlink ref="M31" r:id="rId233" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N31" r:id="rId234"/>
-    <hyperlink ref="AW31" r:id="rId235" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2YB9P0HYGN84U"/>
-    <hyperlink ref="C32" r:id="rId236" tooltip="https://www.amazon.co.jp/dp/B0CF9P7W51"/>
-    <hyperlink ref="G32" r:id="rId237" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J32" r:id="rId238" tooltip="https://www.amazon.co.jp/dp/B0CF9P7W51?psc=1"/>
-    <hyperlink ref="K32" r:id="rId239" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61bJ0J+PfIL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L32" r:id="rId240" tooltip="https://www.amazon.co.jp/dp/B0CF9P7W51"/>
-    <hyperlink ref="C33" r:id="rId241" tooltip="https://www.amazon.co.jp/dp/B0D5HBSJFX"/>
-    <hyperlink ref="G33" r:id="rId242" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J33" r:id="rId243" tooltip="https://www.amazon.co.jp/dp/B0D5HBSJFX?psc=1"/>
-    <hyperlink ref="K33" r:id="rId244" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51ioK4Vk3NL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L33" r:id="rId245" tooltip="https://www.amazon.co.jp/dp/B0D5HBSJFX"/>
-    <hyperlink ref="C34" r:id="rId246" tooltip="https://www.amazon.co.jp/dp/B0DHV7QRSK"/>
-    <hyperlink ref="G34" r:id="rId247" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J34" r:id="rId248" tooltip="https://www.amazon.co.jp/dp/B0DHV7QRSK?psc=1"/>
-    <hyperlink ref="K34" r:id="rId249" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61Coq6GGchL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L34" r:id="rId250" tooltip="https://www.amazon.co.jp/dp/B0DHV7QRSK"/>
-    <hyperlink ref="C35" r:id="rId251" tooltip="https://www.amazon.co.jp/dp/B0DXY4BJ5K"/>
-    <hyperlink ref="G35" r:id="rId252" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J35" r:id="rId253" tooltip="https://www.amazon.co.jp/dp/B0DXY4BJ5K?psc=1"/>
-    <hyperlink ref="K35" r:id="rId254" tooltip="https://images-fe.ssl-images-amazon.com/images/I/516bWwYYlQL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L35" r:id="rId255" tooltip="https://www.amazon.co.jp/dp/B0DXY4BJ5K"/>
-    <hyperlink ref="C36" r:id="rId256" tooltip="https://www.amazon.co.jp/dp/B0FBR52FBV"/>
-    <hyperlink ref="G36" r:id="rId257" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J36" r:id="rId258" tooltip="https://www.amazon.co.jp/dp/B0FBR52FBV?psc=1"/>
-    <hyperlink ref="K36" r:id="rId259" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51Gx-JJE9mL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L36" r:id="rId260" tooltip="https://www.amazon.co.jp/dp/B0FBR52FBV"/>
-    <hyperlink ref="C37" r:id="rId261" tooltip="https://www.amazon.co.jp/dp/B0FGC7422M"/>
-    <hyperlink ref="G37" r:id="rId262" tooltip="https://www.amazon.co.jp/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FGC7422M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J37" r:id="rId263" tooltip="https://www.amazon.co.jp/dp/B0FGC7422M?psc=1"/>
-    <hyperlink ref="K37" r:id="rId264" tooltip="https://images-na.ssl-images-amazon.com/images/I/51PDVCpecuL._AC_US600_.jpg"/>
-    <hyperlink ref="L37" r:id="rId265" tooltip="https://www.amazon.co.jp/dp/B0FGC7422M"/>
-    <hyperlink ref="M37" r:id="rId266" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N37" r:id="rId267"/>
-    <hyperlink ref="AW37" r:id="rId268" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1UV3PJGHZIHW6"/>
-    <hyperlink ref="C38" r:id="rId269" tooltip="https://www.amazon.co.jp/dp/B0FL2KXDMX"/>
-    <hyperlink ref="G38" r:id="rId270" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J38" r:id="rId271" tooltip="https://www.amazon.co.jp/dp/B0FL2KXDMX?psc=1"/>
-    <hyperlink ref="K38" r:id="rId272" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61j+d1U1UHL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L38" r:id="rId273" tooltip="https://www.amazon.co.jp/dp/B0FL2KXDMX"/>
-    <hyperlink ref="C39" r:id="rId274" tooltip="https://www.amazon.co.jp/dp/B0FPXLZSWP"/>
-    <hyperlink ref="G39" r:id="rId275" tooltip="https://www.amazon.co.jp/stores/NARWAL/page/48E89FF8-D8FF-42EA-91FA-300E4D5D5CBA?lp_asin=B0FPXLZSWP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J39" r:id="rId276" tooltip="https://www.amazon.co.jp/dp/B0FPXLZSWP?psc=1"/>
-    <hyperlink ref="K39" r:id="rId277" tooltip="https://images-na.ssl-images-amazon.com/images/I/51o9M+0xsCL._AC_US600_.jpg"/>
-    <hyperlink ref="L39" r:id="rId278" tooltip="https://www.amazon.co.jp/dp/B0FPXLZSWP"/>
-    <hyperlink ref="M39" r:id="rId279" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
-    <hyperlink ref="N39" r:id="rId280"/>
-    <hyperlink ref="C40" r:id="rId281" tooltip="https://www.amazon.co.jp/dp/B0G4RMHHWV"/>
-    <hyperlink ref="G40" r:id="rId282" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J40" r:id="rId283" tooltip="https://www.amazon.co.jp/dp/B0G4RMHHWV?psc=1"/>
-    <hyperlink ref="K40" r:id="rId284" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61OeNyo9j3L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L40" r:id="rId285" tooltip="https://www.amazon.co.jp/dp/B0G4RMHHWV"/>
-    <hyperlink ref="C41" r:id="rId286" tooltip="https://www.amazon.co.jp/dp/B0GJZNZZBG"/>
-    <hyperlink ref="G41" r:id="rId287" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J41" r:id="rId288" tooltip="https://www.amazon.co.jp/dp/B0GJZNZZBG?psc=1"/>
-    <hyperlink ref="K41" r:id="rId289" tooltip="https://images-fe.ssl-images-amazon.com/images/I/41bBBiQaOQL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L41" r:id="rId290" tooltip="https://www.amazon.co.jp/dp/B0GJZNZZBG"/>
-    <hyperlink ref="C42" r:id="rId291" tooltip="https://www.amazon.co.jp/dp/B0GP76R477"/>
-    <hyperlink ref="G42" r:id="rId292" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J42" r:id="rId293" tooltip="https://www.amazon.co.jp/dp/B0GP76R477?psc=1"/>
-    <hyperlink ref="K42" r:id="rId294" tooltip="https://images-fe.ssl-images-amazon.com/images/I/21UZYI0dymL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L42" r:id="rId295" tooltip="https://www.amazon.co.jp/dp/B0GP76R477"/>
-    <hyperlink ref="C43" r:id="rId296" tooltip="https://www.amazon.co.jp/dp/B0H5WDMCLX"/>
-    <hyperlink ref="G43" r:id="rId297" tooltip="https://www.amazon.co.jpundefined"/>
-    <hyperlink ref="J43" r:id="rId298" tooltip="https://www.amazon.co.jp/dp/B0H5WDMCLX?psc=1"/>
-    <hyperlink ref="K43" r:id="rId299" tooltip="https://images-fe.ssl-images-amazon.com/images/I/31ZGQqLBLNL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L43" r:id="rId300" tooltip="https://www.amazon.co.jp/dp/B0H5WDMCLX"/>
+    <hyperlink ref="AW27" r:id="rId206" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1WV0MTJICL1UJ"/>
+    <hyperlink ref="C28" r:id="rId207" tooltip="https://www.amazon.co.jp/dp/B09P2RKRWX"/>
+    <hyperlink ref="G28" r:id="rId208" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J28" r:id="rId209" tooltip="https://www.amazon.co.jp/dp/B09P2RKRWX?psc=1"/>
+    <hyperlink ref="K28" r:id="rId210" tooltip="https://images-fe.ssl-images-amazon.com/images/I/615lYQCrd2L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L28" r:id="rId211" tooltip="https://www.amazon.co.jp/dp/B09P2RKRWX"/>
+    <hyperlink ref="C29" r:id="rId212" tooltip="https://www.amazon.co.jp/dp/B0C4HGZ1L6"/>
+    <hyperlink ref="G29" r:id="rId213" tooltip="https://www.amazon.co.jp/stores/NEODIT%E3%83%8D%E3%82%AA%E3%83%87%E3%82%A3%E3%83%83%E3%83%88/page/CD7250ED-8E04-4E58-A881-68B2A928AE8C?lp_asin=B0C4HGZ1L6&amp;ref_=ast_bln"/>
+    <hyperlink ref="J29" r:id="rId214" tooltip="https://www.amazon.co.jp/dp/B0C4HGZ1L6?psc=1"/>
+    <hyperlink ref="K29" r:id="rId215" tooltip="https://images-na.ssl-images-amazon.com/images/I/81DHFglSw9L._AC_US600_.jpg"/>
+    <hyperlink ref="L29" r:id="rId216" tooltip="https://www.amazon.co.jp/dp/B0C4HGZ1L6"/>
+    <hyperlink ref="M29" r:id="rId217" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="N29" r:id="rId218"/>
+    <hyperlink ref="AW29" r:id="rId219" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2YB9P0HYGN84U"/>
+    <hyperlink ref="C30" r:id="rId220" tooltip="https://www.amazon.co.jp/dp/B0CF9P7W51"/>
+    <hyperlink ref="G30" r:id="rId221" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J30" r:id="rId222" tooltip="https://www.amazon.co.jp/dp/B0CF9P7W51?psc=1"/>
+    <hyperlink ref="K30" r:id="rId223" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61bJ0J+PfIL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L30" r:id="rId224" tooltip="https://www.amazon.co.jp/dp/B0CF9P7W51"/>
+    <hyperlink ref="C31" r:id="rId225" tooltip="https://www.amazon.co.jp/dp/B0D5HBSJFX"/>
+    <hyperlink ref="G31" r:id="rId226" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J31" r:id="rId227" tooltip="https://www.amazon.co.jp/dp/B0D5HBSJFX?psc=1"/>
+    <hyperlink ref="K31" r:id="rId228" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51ioK4Vk3NL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L31" r:id="rId229" tooltip="https://www.amazon.co.jp/dp/B0D5HBSJFX"/>
+    <hyperlink ref="C32" r:id="rId230" tooltip="https://www.amazon.co.jp/dp/B0DHV7QRSK"/>
+    <hyperlink ref="G32" r:id="rId231" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J32" r:id="rId232" tooltip="https://www.amazon.co.jp/dp/B0DHV7QRSK?psc=1"/>
+    <hyperlink ref="K32" r:id="rId233" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61Coq6GGchL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L32" r:id="rId234" tooltip="https://www.amazon.co.jp/dp/B0DHV7QRSK"/>
+    <hyperlink ref="C33" r:id="rId235" tooltip="https://www.amazon.co.jp/dp/B0DXY4BJ5K"/>
+    <hyperlink ref="G33" r:id="rId236" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J33" r:id="rId237" tooltip="https://www.amazon.co.jp/dp/B0DXY4BJ5K?psc=1"/>
+    <hyperlink ref="K33" r:id="rId238" tooltip="https://images-fe.ssl-images-amazon.com/images/I/516bWwYYlQL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L33" r:id="rId239" tooltip="https://www.amazon.co.jp/dp/B0DXY4BJ5K"/>
+    <hyperlink ref="C34" r:id="rId240" tooltip="https://www.amazon.co.jp/dp/B0FBR52FBV"/>
+    <hyperlink ref="G34" r:id="rId241" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J34" r:id="rId242" tooltip="https://www.amazon.co.jp/dp/B0FBR52FBV?psc=1"/>
+    <hyperlink ref="K34" r:id="rId243" tooltip="https://images-fe.ssl-images-amazon.com/images/I/51Gx-JJE9mL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L34" r:id="rId244" tooltip="https://www.amazon.co.jp/dp/B0FBR52FBV"/>
+    <hyperlink ref="C35" r:id="rId245" tooltip="https://www.amazon.co.jp/dp/B0FGC7422M"/>
+    <hyperlink ref="G35" r:id="rId246" tooltip="https://www.amazon.co.jp/stores/JONR/page/791ACF44-A8D9-4AB0-BFBA-EAA0E0B7B60D?lp_asin=B0FGC7422M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J35" r:id="rId247" tooltip="https://www.amazon.co.jp/dp/B0FGC7422M?psc=1"/>
+    <hyperlink ref="K35" r:id="rId248" tooltip="https://images-na.ssl-images-amazon.com/images/I/51PDVCpecuL._AC_US600_.jpg"/>
+    <hyperlink ref="L35" r:id="rId249" tooltip="https://www.amazon.co.jp/dp/B0FGC7422M"/>
+    <hyperlink ref="M35" r:id="rId250" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="N35" r:id="rId251"/>
+    <hyperlink ref="AW35" r:id="rId252" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1UV3PJGHZIHW6"/>
+    <hyperlink ref="C36" r:id="rId253" tooltip="https://www.amazon.co.jp/dp/B0FL2KXDMX"/>
+    <hyperlink ref="G36" r:id="rId254" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J36" r:id="rId255" tooltip="https://www.amazon.co.jp/dp/B0FL2KXDMX?psc=1"/>
+    <hyperlink ref="K36" r:id="rId256" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61j+d1U1UHL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L36" r:id="rId257" tooltip="https://www.amazon.co.jp/dp/B0FL2KXDMX"/>
+    <hyperlink ref="C37" r:id="rId258" tooltip="https://www.amazon.co.jp/dp/B0FPXLZSWP"/>
+    <hyperlink ref="G37" r:id="rId259" tooltip="https://www.amazon.co.jp/stores/NARWAL/page/48E89FF8-D8FF-42EA-91FA-300E4D5D5CBA?lp_asin=B0FPXLZSWP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J37" r:id="rId260" tooltip="https://www.amazon.co.jp/dp/B0FPXLZSWP?psc=1"/>
+    <hyperlink ref="K37" r:id="rId261" tooltip="https://images-na.ssl-images-amazon.com/images/I/51o9M+0xsCL._AC_US600_.jpg"/>
+    <hyperlink ref="L37" r:id="rId262" tooltip="https://www.amazon.co.jp/dp/B0FPXLZSWP"/>
+    <hyperlink ref="M37" r:id="rId263" tooltip="https://www.amazon.co.jp/b?node=13698381"/>
+    <hyperlink ref="N37" r:id="rId264"/>
+    <hyperlink ref="C38" r:id="rId265" tooltip="https://www.amazon.co.jp/dp/B0G4RMHHWV"/>
+    <hyperlink ref="G38" r:id="rId266" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J38" r:id="rId267" tooltip="https://www.amazon.co.jp/dp/B0G4RMHHWV?psc=1"/>
+    <hyperlink ref="K38" r:id="rId268" tooltip="https://images-fe.ssl-images-amazon.com/images/I/61OeNyo9j3L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L38" r:id="rId269" tooltip="https://www.amazon.co.jp/dp/B0G4RMHHWV"/>
+    <hyperlink ref="C39" r:id="rId270" tooltip="https://www.amazon.co.jp/dp/B0GJZNZZBG"/>
+    <hyperlink ref="G39" r:id="rId271" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J39" r:id="rId272" tooltip="https://www.amazon.co.jp/dp/B0GJZNZZBG?psc=1"/>
+    <hyperlink ref="K39" r:id="rId273" tooltip="https://images-fe.ssl-images-amazon.com/images/I/41bBBiQaOQL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L39" r:id="rId274" tooltip="https://www.amazon.co.jp/dp/B0GJZNZZBG"/>
+    <hyperlink ref="C40" r:id="rId275" tooltip="https://www.amazon.co.jp/dp/B0GP76R477"/>
+    <hyperlink ref="G40" r:id="rId276" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J40" r:id="rId277" tooltip="https://www.amazon.co.jp/dp/B0GP76R477?psc=1"/>
+    <hyperlink ref="K40" r:id="rId278" tooltip="https://images-fe.ssl-images-amazon.com/images/I/21UZYI0dymL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L40" r:id="rId279" tooltip="https://www.amazon.co.jp/dp/B0GP76R477"/>
+    <hyperlink ref="C41" r:id="rId280" tooltip="https://www.amazon.co.jp/dp/B0H5WDMCLX"/>
+    <hyperlink ref="G41" r:id="rId281" tooltip="https://www.amazon.co.jpundefined"/>
+    <hyperlink ref="J41" r:id="rId282" tooltip="https://www.amazon.co.jp/dp/B0H5WDMCLX?psc=1"/>
+    <hyperlink ref="K41" r:id="rId283" tooltip="https://images-fe.ssl-images-amazon.com/images/I/31ZGQqLBLNL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L41" r:id="rId284" tooltip="https://www.amazon.co.jp/dp/B0H5WDMCLX"/>
   </hyperlinks>
-  <drawing r:id="rId301"/>
+  <drawing r:id="rId285"/>
 </worksheet>
 </file>
 
@@ -15095,18 +14607,18 @@
         </is>
       </c>
       <c r="B2" s="13">
-        <v>547</v>
+        <v>507</v>
       </c>
       <c r="C2" s="13">
-        <v>39987497</v>
+        <v>38763360</v>
       </c>
       <c r="D2" s="13"/>
       <c r="E2" s="13"/>
       <c r="F2" s="13">
-        <v>73103.28519195612</v>
+        <v>76456.33136094674</v>
       </c>
       <c r="G2" s="19">
-        <v>0.12992874109263658</v>
+        <v>0.12158273381294964</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15127,7 +14639,7 @@
         <v>26550.59405940594</v>
       </c>
       <c r="G3" s="19">
-        <v>0.11995249406175772</v>
+        <v>0.1211031175059952</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15148,7 +14660,7 @@
         <v>48783.15238095238</v>
       </c>
       <c r="G4" s="19">
-        <v>0.0498812351543943</v>
+        <v>0.050359712230215826</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15169,7 +14681,7 @@
         <v>4980.0</v>
       </c>
       <c r="G5" s="19">
-        <v>0.3862232779097387</v>
+        <v>0.3899280575539568</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15190,7 +14702,7 @@
         <v>39377.755102040814</v>
       </c>
       <c r="G6" s="19">
-        <v>0.04655581947743468</v>
+        <v>0.04700239808153477</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15211,7 +14723,7 @@
         <v>15955.0</v>
       </c>
       <c r="G7" s="19">
-        <v>0.10498812351543943</v>
+        <v>0.10599520383693045</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15232,7 +14744,7 @@
         <v>64446.76119402985</v>
       </c>
       <c r="G8" s="19">
-        <v>0.015914489311163897</v>
+        <v>0.01606714628297362</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15253,7 +14765,7 @@
         <v>8999.0</v>
       </c>
       <c r="G9" s="19">
-        <v>0.10403800475059383</v>
+        <v>0.10503597122302158</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15274,7 +14786,7 @@
         <v>32880.0</v>
       </c>
       <c r="G10" s="19">
-        <v>0.009738717339667458</v>
+        <v>0.009832134292565946</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15295,7 +14807,7 @@
         <v>74800.0</v>
       </c>
       <c r="G11" s="19">
-        <v>0.0026128266033254156</v>
+        <v>0.0026378896882494006</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15316,7 +14828,7 @@
         <v>12687.619047619048</v>
       </c>
       <c r="G12" s="19">
-        <v>0.01496437054631829</v>
+        <v>0.015107913669064749</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15337,7 +14849,7 @@
         <v>7160.0</v>
       </c>
       <c r="G13" s="19">
-        <v>0.007125890736342043</v>
+        <v>0.007194244604316547</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15358,7 +14870,7 @@
         <v>4500.0</v>
       </c>
       <c r="G14" s="19">
-        <v>0.007125890736342043</v>
+        <v>0.007194244604316547</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15379,7 +14891,7 @@
         <v>11661.0</v>
       </c>
       <c r="G15" s="19">
-        <v>0.0009501187648456057</v>
+        <v>0.0009592326139088729</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15511,7 +15023,7 @@
         <v>49598.41251448436</v>
       </c>
       <c r="G2" s="19">
-        <v>0.20498812351543944</v>
+        <v>0.20695443645083933</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15532,7 +15044,7 @@
         <v>26550.59405940594</v>
       </c>
       <c r="G3" s="19">
-        <v>0.11995249406175772</v>
+        <v>0.1211031175059952</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15553,7 +15065,7 @@
         <v>52362.628272251306</v>
       </c>
       <c r="G4" s="19">
-        <v>0.04536817102137767</v>
+        <v>0.04580335731414868</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15574,7 +15086,7 @@
         <v>4980.0</v>
       </c>
       <c r="G5" s="19">
-        <v>0.3862232779097387</v>
+        <v>0.3899280575539568</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15595,7 +15107,7 @@
         <v>39377.755102040814</v>
       </c>
       <c r="G6" s="19">
-        <v>0.04655581947743468</v>
+        <v>0.04700239808153477</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15616,7 +15128,7 @@
         <v>64446.76119402985</v>
       </c>
       <c r="G7" s="19">
-        <v>0.015914489311163897</v>
+        <v>0.01606714628297362</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15637,7 +15149,7 @@
         <v>8999.0</v>
       </c>
       <c r="G8" s="19">
-        <v>0.10403800475059383</v>
+        <v>0.10503597122302158</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15647,18 +15159,18 @@
         </is>
       </c>
       <c r="B9" s="13">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="C9" s="13">
-        <v>2811188</v>
+        <v>1767048</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
       <c r="F9" s="13">
-        <v>26773.219047619048</v>
+        <v>25986.0</v>
       </c>
       <c r="G9" s="19">
-        <v>0.02494061757719715</v>
+        <v>0.01630695443645084</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15679,7 +15191,7 @@
         <v>32880.0</v>
       </c>
       <c r="G10" s="19">
-        <v>0.009738717339667458</v>
+        <v>0.009832134292565946</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15700,49 +15212,49 @@
         <v>74800.0</v>
       </c>
       <c r="G11" s="19">
-        <v>0.0026128266033254156</v>
+        <v>0.0026378896882494006</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>ダイソン公式ストア</t>
+          <t>【ミナトワークス】</t>
         </is>
       </c>
       <c r="B12" s="13">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="C12" s="13">
-        <v>819989</v>
+        <v>799320</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
       <c r="F12" s="13">
-        <v>74544.45454545454</v>
+        <v>12687.619047619048</v>
       </c>
       <c r="G12" s="19">
-        <v>0.0026128266033254156</v>
+        <v>0.015107913669064749</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>【ミナトワークス】</t>
+          <t>ダイソン公式ストア</t>
         </is>
       </c>
       <c r="B13" s="13">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="C13" s="13">
-        <v>799320</v>
+        <v>639992</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
       <c r="F13" s="13">
-        <v>12687.619047619048</v>
+        <v>79999.0</v>
       </c>
       <c r="G13" s="19">
-        <v>0.01496437054631829</v>
+        <v>0.0019184652278177458</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15763,7 +15275,7 @@
         <v>60500.0</v>
       </c>
       <c r="G14" s="19">
-        <v>0.0023752969121140144</v>
+        <v>0.002398081534772182</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15784,7 +15296,7 @@
         <v>12800.0</v>
       </c>
       <c r="G15" s="19">
-        <v>0.004513064133016627</v>
+        <v>0.004556354916067146</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15805,7 +15317,7 @@
         <v>7160.0</v>
       </c>
       <c r="G16" s="19">
-        <v>0.007125890736342043</v>
+        <v>0.007194244604316547</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15826,7 +15338,7 @@
         <v>4500.0</v>
       </c>
       <c r="G17" s="19">
-        <v>0.007125890736342043</v>
+        <v>0.007194244604316547</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -15847,7 +15359,7 @@
         <v>11661.0</v>
       </c>
       <c r="G18" s="19">
-        <v>0.0009501187648456057</v>
+        <v>0.0009592326139088729</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
